--- a/기획안/혼합안_이탈리아_스페인_독일.xlsx
+++ b/기획안/혼합안_이탈리아_스페인_독일.xlsx
@@ -692,47 +692,47 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>현재의 이탈리아: 1부=2014년에서 9부=2024~25년, 에필로그≈2029년(가까운 미래)까지 약 15년. 1992~93년 폭탄 학살의 시대와 1990년대 초 반부패 수사는 배경사(벨란디의 과거, 어린 알레시오의 기억)로만 쓴다. 가상의 시칠리아 항구도시 토레네라(Torrenera)와 석유화학 단지, 가상의 남부 산유 지역 '레조네 요니카(Regione Ionica)', 로마·밀라노. 의원내각제: 총선 → 대통령의 조각 위임(incarico) → 퀴리날레 선서 → 양원 신임투표. 총리 연임 제한이 없는 제도에서 주인공이 스스로 '연속 두 번의 입법기' 한계를 만든다. 하이브리드판 액자: 2029년 로마 벙커 법정에서 열리는 '리날디 총리 암살 사건' 중죄법원(Corte d'Assise) 재판 — 협력자 파올로 세라가 보호 거처에서 화상으로 증언하고, 피고인석엔 실행범·조직자에 이어 신병 인도된 자금원들이 앉는다.</t>
+          <t>현재의 이탈리아: 1부=2014년에서 10부=2024~26년, 에필로그≈2029년(가까운 미래)까지 약 15년. 1992~93년 폭탄 학살의 시대와 1990년대 초 반부패 수사는 배경사(벨란디의 과거, 어린 알레시오의 기억)로만 쓴다. 가상의 시칠리아 항구도시 토레네라(Torrenera)와 석유화학 단지, 가상의 남부 산유 지역 '레조네 요니카(Regione Ionica)', 로마·밀라노·팔레르모. 의원내각제: 총선 → 대통령의 조각 위임(incarico) → 퀴리날레 선서 → 양원 신임투표. 비상 통치의 실제 장치: 1948년 헌법은 파시즘의 경험 때문에 일반 비상조항을 두지 않았다. 있는 것은 ①제78조 전쟁상태(양원이 의결하고 정부에 필요한 권한을 부여, 대통령이 선포 — 제87조), ②제77조 긴급 법령(decreto-legge: 필요·긴급 시 정부가 제정, 대통령이 서명·공포, 60일 안에 법률로 전환되지 않으면 소급 실효, 헌법재판소 1996년 제360호 판결로 같은 내용의 재발령 금지), ③전환 법안에 거는 신임 문제(questione di fiducia), ④민방위법(D.Lgs. 1/2018)의 국가적 비상사태(최장 12개월+12개월 연장)와 코로나19 시기의 총리령(DPCM) 통치 선례, ⑤도시 군 병력 배치('Strade sicure'형 작전), ⑥정보기관 예방 감청(로마 항소법원 검찰총장의 승인 필요), ⑦41-bis 특별 수감 체제와 반마피아법의 예방 조치·지방의회 해산, ⑧제138조 개헌(두 차례 의결, 두 번째 의결에서 양원 각 3분의 2면 국민투표 없이 확정, 아니면 확정 국민투표 가능), 헌법재판소 1988년 제1146호 판결의 '최고 원리는 헌법 개정으로도 바꿀 수 없다'는 법리와 제139조(공화정체는 개정 대상이 아님), ⑨제60조(의회 임기 연장은 전쟁 시 법률로만), ⑩대통령의 긴급 법령 서명 거부와 법률 재의 요구(제74조), 불신임 동의(제94조), 장관 범죄의 의회 소추 허가(제96조). 7~10부의 비상 통치는 모두 이 실제 장치들을 늘이고 비틀어서 만든다 — 가상의 '제78조의2(국가 비상사태)' 개헌이 유일한 창작 조항이다. 직권남용죄(형법 제323조)는 2024년 8월 폐지되어(법률 제114호) 소급 적용되므로, 알레시오가 스스로 털어놓는 범죄는 불법 감청, 불법 구금, 구금 중 사망에 대한 책임, 살레미 잔당과의 거래다. 하이브리드판 액자: 2029년 토레네라 벙커 법정의 중죄법원(Corte d'Assise) 재판 — 언론이 '리날디 사건(processo Rinaldi)'이라 부르는 이 재판은 6부까지는 전 총리의 재판처럼 보이지만, 실은 2026년 그를 살해한 실행범·조직자·자금원의 재판이다(피고인의 사망은 형사 소추를 소멸시키므로 알레시오 자신은 재판받지 않는다). 협력자 파올로가 보호 거처에서 화상으로 증언하고, 알레시오가 죽기 전 검찰에 맡긴 자백서(memoriale)가 형사소송법 제512조(예측할 수 없는 사유로 반복 불가능해진 진술의 낭독)에 따라 법정에서 읽힌다.</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>토레네라 지방검찰청 신참 검사(sostituto procuratore) → 반마피아검찰국 풀, 피고인 300여 명의 대재판 → 밀라노 파견, 전국 공공공사 반부패 수사의 얼굴 → 최고사법위원회(CSM) 징계·강제 전보 후 사직 → 시민정당 '온다 치빌레' 창당, 토레네라 소선거구 하원의원 → 의회 반마피아위원회 위원장·연합 총리 후보 → 총리(2개 입법기) → 퇴임 직후 피격 사망</t>
+          <t>토레네라 지방검찰청 신참 검사 → 반마피아검찰국 풀, 피고인 300여 명의 대재판 → 밀라노 파견, 전국 반부패 수사의 얼굴 → CSM 징계·강제 전보 후 사직 → 시민정당 '온다 치빌레' 창당, 하원의원 → 반마피아위원회 위원장 → 총리(첫 정부, 스스로 '연속 두 입법기' 한계 도입) → 당대회장 폭탄 뒤 공포 속 재신임 → 긴급 법령·비상사태·개헌으로 비상대권 장악 → 비상 체제의 총리('괴물') → 헌재 위헌 결정·대통령 거부·지휘관 거부 앞에서 불복하지 않고 사임 → 자백서 제출, 증인으로 나서기 전날 피살</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>이탈리아 공화국 각료회의 의장(Presidente del Consiglio dei ministri, 총리)</t>
+          <t>이탈리아 공화국 각료회의 의장(총리) — 비상대권을 내려놓고 사임, 2026년 증언 전날 피살(2029년 재판의 '피해자')</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>7부: 마피아와 비밀 로지가 손잡은 새 '폭탄의 계절'과 국채 스프레드 공격이 겹치자, 내무장관 라디체가 반마피아 특별법(예방적 자산 몰수, 행정 금지명령, 트로이목마 감청, 지방의회 해산, 특별 격리수용)을 '국가 전복 세력'이라는 이름으로 야당 운동·언론사로 넓히는 긴급 법령(decreto-legge)을 올린다. 지방선거 연기, 신문사에 대한 금지명령, 기자 휴대전화 감청 승인이 차례로 유혹이 된다.</t>
+          <t>유혹은 거절되지 않고 받아들여진다. 6부 카타니아 당대회장 폭탄으로 욜란다가 죽고 이레네가 다친 뒤, 알레시오는 키케로의 «Salus populi suprema lex esto»를 내걸고 공포 속에 두 번째 신임을 얻는다. 7부(권력의 획득): 새 '폭탄의 계절'에 긴급 법령을 잇따라 내고 전환 법안마다 신임 문제를 걸며, 가뭄 대응 민방위 비상사태를 치안으로 늘여 총리령(DPCM)으로 다스린다. 60일이 지나 실효된 법령을 거의 그대로 다시 내려다 대통령이 서명을 거부하자 국민에게 직접 호소하고, 가상의 '제78조의2(국가 비상사태)' 개헌을 밀어붙인다 — 하원은 공포에 질린 야당까지 3분의 2로, 상원은 몇 표가 모자라 확정 국민투표로 가고, 그는 투표에서 이긴다. 작은 월권(승인 없는 스파이웨어 감청)은 멈춤이 아니라 첫걸음이다. 8부(체제의 일상): 비상대권 아래 41-bis, 예방 조치, 지방의회 해산, 스파이웨어, 거리의 군이 기자·검사·NGO·시위대에게 돌아가고, '질서'를 위해 살레미 잔당과 에르메테 로지의 방법에 손을 내민다. 9부(정점): 하이브리드전을 '전쟁'으로 규정해 제78조 전쟁상태를 의결받고 제60조로 입법기를 늘이려 하며, 끝내 헌재 결정에 불복할 것인가의 문턱에 선다.</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>암살·증언</t>
+          <t>몰락·귀환·암살</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>퇴임 전날 로마 테베레 강변에서 저격당해 숨지지만, 후계자 이레네 마르텔리는 이튿날 예정대로 퀴리날레에서 선서한다. 사흘 전 모호한 경고밖에 하지 못했던 파올로가 선서 이튿날 자수해 협력자가 되고, 그가 6부부터 몰래 복사해 둔 송금 기록이 실행범·조직자 기소를 연다. 2029년 벙커 법정에서 그의 증언이 외부 증거로 보강되어 신병 인도된 자금원 브란카티와 두 자금책의 유죄를 결정하고, 같은 해 이레네의 입법기가 끝나 마리나 페를리토가 총리로 선서한다. 한 사람이 아니라 제도 — 선서, 독립 수사, 협력자 제도와 공개 법정 — 가 이어졌음을 증명한다. 파올로는 살아남지만 새 이름과 보호 프로그램 속에서 가족 없이 형을 산다.</t>
+          <t>헌재가 비상 개헌의 핵심을 무효화하고 대통령이 불복 법령에 서명하지 않으며 사령관들이 위법 명령을 거부한 밤(9부 끝), 알레시오는 불복하지 않기로 한다(10부). 그는 헌재 결정을 이행하고 비상사태를 거두며, 하원에서 자신의 책임을 공개적으로 인정한 뒤 퀴리날레에 사표를 낸다. 재건된 총선에서 이레네가 이기고, 그는 의원 면책을 내려놓고 자기 범죄와 비상 시절 살레미 잔당·에르메테 로지와의 거래를 담은 자백서를 검사 엘레나 사르토리에게 맡긴다. 토레네라에서 사과하고 다시 먼저 커피를 내는 짧은 인간의 계절 끝에, 증언대에 서기 전날 항구의 바에서 살레미 잔당의 총에 쓰러진다 — 반마피아 과거에 대한 복수이자 입막음. 피고인의 죽음으로 그 자신에 대한 소추는 소멸하지만, 2029년 토레네라 벙커 법정에서 협력자 파올로의 증언과 형사소송법 제512조로 낭독된 그의 자백서가 실행범·조직자·니노 살레미와 신병 인도된 로지 자금원 브란카티의 유죄를 결정한다. 법정은 살해자를 심판하고, 그의 자백서는 그가 무엇이었는지를 심판한다. 키케로와의 대비로 닫힌다: 재판 없이 처형했던 키케로는 뉘우치지 않은 채 권력 투쟁 속에 안토니우스의 살생부에 올라 죽었고, 알레시오는 뉘우치고 진실을 말하려다 죽었다. 비상대권을 멈춘 것은 한 사람의 양심보다 먼저 제도였고, 그의 귀환은 제도가 열어 둔 문으로 걸어 나온 것이었다.</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>9부</t>
+          <t>10부</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>기존 틀(연대기 9부×12화+에필로그, 알레시오의 검사→총리 경로, 암살 결말)은 그대로 두고 두 장치를 더한 하이브리드판이다. ① 2029 증언 액자: 매 부 1화는 로마 벙커 법정의 리날디 암살 재판에서 협력자 파올로 세라가 화상 스크린 뒤에서 하는 증언으로 콜드 오픈하고, 그 부의 핵심 질문과 답이 이야기를 연다. 9부와 에필로그에서 이 증언과 그가 모아 둔 장부 사본이 자금원 브란카티 일당의 유죄를 결정한다. ② 친구 시점: 매 부 2~3화를 파올로의 시점으로 서술해(시놉시스에 '(친구 시점)' 표시) 소꿉친구 → 가문 변호사 → 로지의 정치인 → 느린 전향 → 협력자의 궤적을 알레시오의 궤적과 거울처럼 겹친다. 무게중심은 여전히 수사와 재판이다(원작 2부를 대재판·밀라노 로지 수사 두 부로 늘리고, 원작 선거 두 부를 4부 「신임」으로 압축). 원작의 친구 죽음(5부 5화)은 파올로가 증인으로 살아남아야 하므로 새 인물인 동료 검사 다비데 로카시오가 넘겨받아 마모의 리듬을 지킨다.</t>
+          <t>연대기 10부×12화+에필로그. 두 하이브리드 장치(① 매 부 1화의 2029 법정 콜드 오픈, ② 매 부 2~3화의 파올로 시점)를 유지하되 후반부를 뒤집은 '몰락·귀환' 판이다. 1~5부는 이상주의 검사의 상승을 거의 그대로 두고 결함의 씨앗(확신, '나는 안다'는 절차 경멸, 벨란디의 회색 방법)만 심는다. 6부 공포의 재신임 → 7부 비상대권의 획득 → 8부 비상 체제의 일상 → 9부 괴물의 정점과 제도의 반격 → 10부 귀환·사임·자백·암살. 부를 10개로 늘린 이유: 원작 9부 구조에서는 권력의 획득과 남용, 몰락이 두 부에 몰려 비상 체제가 '줄거리'로만 지나간다. 8부 한 부 전체를 체제 아래의 삶에 바쳐 — 검문소의 병사, 자기검열하는 편집국, 전보된 검사, 예방 조치를 받은 구조선 선장, 해산된 고향 의회와 밀고자, 굽는 법원, 조용히 이득을 보는 마피아 — 알레시오를 점점 남의 눈으로만 보여 주고, 그 대가(루치아의 죽음)를 관객이 먼저 겪게 한다. 그래야 9부의 정점과 10부의 귀환이 무게를 가진다. 원작 7부의 '유혹 거절'은 '유혹 수용'으로, 원작 8부의 '권력의 한계'는 '권력의 남용'으로 뒤집히고, 원작 9부(마지막 해·저격)는 10부로 옮겨 '귀환 뒤 피살'로 바뀐다. 액자의 반전: 1~6부 콜드 오픈은 피고인석을 비추지 않은 채 '리날디'에 관한 질문만 쌓아 관객이 그를 피고인으로 믿게 하고(5부 1화 '그를 단죄하는 건 그 자신의 말', 6부 1화 '그는 폭탄 자금 증거를 검찰에 넘기지 않았다'), 7부 1화 재판장의 공소 사실 낭독으로 이 재판이 2026년 리날디 살해 사건 재판이며 그는 이미 죽었음이 드러난다 — 이후 피고인 측은 '피해자는 괴물이었다'는 전략으로 파올로를 공격한다. 10부 1화 파올로가 봉인된 자백서를 건네받고, 에필로그에서 그 마지막 줄을 읽는다. 원작 제목의 궤적(법정에서 권력까지)은 법정으로 되돌아오며 닫힌다 — 그가 대재판을 위해 세운 벙커 법정이 그의 살해자들을 심판한다. 원작 5부 5화의 친구 죽음은 동료 검사 다비데가 넘겨받는다.</t>
         </is>
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>현안(사법개혁 국민투표, 총리 직선제, 스파이웨어, 치안 법령, 해협 대교, 역외 수용)은 실제 2024~2026년 보도에 근거하되 실존 정치인·기업·피해자는 인물로 쓰지 않는다. 시간축은 현재(2014~2029)이며 1990년대 사건은 배경사로만 언급한다. 2부 대재판은 1980년대 실제 대재판을 떠올리게 하되 2015년의 가상 재판(가상 가문·가상 피고인)으로 그리고, 회개자(pentiti) 제도와 증인 보호의 실제 문제를 다루며 회개자를 영웅화하지도 악마화하지도 않는다. 실존 반마피아 판사·검사(특히 1992년 희생자들)와 실제 학살 사건명을 인물·사건으로 쓰지 않는다. 폭탄 암살·로지·일탈 정보기관은 역사적 모티프만 빌려 전부 가상화하고, 실존 조직명(Cosa Nostra 등)도 대사에서 일반명사('조직', '가문들')로 처리한다. 시칠리아·남부를 마피아와 동일시하는 고정관념을 피하려 반마피아 시민·협동조합·기자의 저항을 주인공만큼 비중 있게 그린다. 프리메이슨 일반을 악마화하지 않도록 '정규 결사와 무관한 불법 비밀 로지'로 명시한다. 실존 정치인·정당명 금지, 가상 정당만 사용. 하이브리드판의 협력자(collaboratore di giustizia) 묘사: 파올로의 전향을 구원 서사나 영웅담으로 미화하지 않는다 — 그의 증언은 감형과 보호를 대가로 한 거래이며, 그가 흘린 은신처, 키아라와 다비데의 죽음에 대한 책임은 판결로도 지워지지 않는다. 법정 장면은 실제 절차(원격 화상 증언과 가림막, 교차신문에서의 신빙성 공격, 협력자 진술에 대한 외부 증거 보강 요구)에 맞추되 실존 회개자·협력자의 생애, 증언, 사건을 복제하지 않는다. 피해자와 유족을 증언의 배경 소품으로 쓰지 않고 방청석의 목소리와 존엄을 주며, 증인 보호 프로그램의 실제 결함(버려진 증인, 가족의 해체)은 비판적으로 다루되 조롱하지 않는다. 마피아 문화와 '배신자' 낙인을 매혹적으로 그리지 않는다.</t>
+          <t>현안(사법개혁 국민투표, 총리 직선제, 스파이웨어, 치안 법령, 해협 대교, 역외 수용)은 실제 2024~2026년 보도에 근거하되 실존 정치인·기업·피해자는 인물로 쓰지 않는다. 시간축은 현재(2014~2029)이며 1990년대 사건은 배경사로만 언급한다. 2부 대재판은 1980년대 실제 대재판을 떠올리게 하되 2015년의 가상 재판(가상 가문·가상 피고인)으로 그리고, 회개자(pentiti) 제도와 증인 보호의 실제 문제를 다루며 회개자를 영웅화하지도 악마화하지도 않는다. 실존 반마피아 판사·검사(특히 1992년 희생자들)와 실제 학살 사건명을 인물·사건으로 쓰지 않는다. 폭탄 암살·로지·일탈 정보기관은 역사적 모티프만 빌려 전부 가상화하고, 실존 조직명(Cosa Nostra 등)도 대사에서 일반명사('조직', '가문들')로 처리한다. 시칠리아·남부를 마피아와 동일시하는 고정관념을 피하려 반마피아 시민·협동조합·기자의 저항을 주인공만큼 비중 있게 그린다. 프리메이슨 일반을 악마화하지 않도록 '정규 결사와 무관한 불법 비밀 로지'로 명시한다. 실존 정치인·정당명 금지, 가상 정당만 사용. 하이브리드판의 협력자(collaboratore di giustizia) 묘사: 파올로의 전향을 구원 서사나 영웅담으로 미화하지 않는다 — 그의 증언은 감형과 보호를 대가로 한 거래이며, 그가 흘린 은신처, 키아라와 다비데의 죽음에 대한 책임은 판결로도 지워지지 않는다. 법정 장면은 실제 절차(원격 화상 증언과 가림막, 교차신문에서의 신빙성 공격, 협력자 진술에 대한 외부 증거 보강 요구)에 맞추되 실존 회개자·협력자의 생애, 증언, 사건을 복제하지 않는다. 피해자와 유족을 증언의 배경 소품으로 쓰지 않고 방청석의 목소리와 존엄을 주며, 증인 보호 프로그램의 실제 결함(버려진 증인, 가족의 해체)은 비판적으로 다루되 조롱하지 않는다. 마피아 문화와 '배신자' 낙인을 매혹적으로 그리지 않는다. 뒤집힌 후반부 관련: 알레시오와 그의 정부·정당은 실존 이탈리아 총리·정당과 닮지 않게 설계한다(정책·말투·지지 기반·외모를 특정인과 겹치지 않게, 좌우 어느 쪽의 알레고리로도 읽히지 않게 — 그는 반마피아 영웅 출신의 초당파적 인물이다). 권위주의를 매혹적으로 그리지 않는다: 비상 통치의 '효율'을 쾌감으로 연출하지 않고, 8부 전체를 그 대가를 치르는 사람(병사, 기자, 검사, 구조선 선장, 구금자의 가족)의 눈으로 보여 준다. 제도가 작동하는 모습을 정확히 그린다 — 대통령의 서명 거부와 재의 요구, 헌법재판소 결정, 검찰의 독립 수사, 판사의 위헌 제청, 지방정부의 제소, 해안경비대의 구조, 군·카라비니에리의 위법 명령 거부(군 기본법의 '명백한 범죄 명령 불복' 원칙), 의회의 불신임 — 그리고 이들이 영웅이 아니라 규칙을 지키는 평범한 공직자로 보이게 한다. 파시즘의 기억은 조심스럽게 다룬다: 무솔리니를 인용하거나 영웅적으로 비추지 않고, 검은 셔츠·로마식 경례 같은 도상을 쓰지 않으며, 마테오티는 추모와 경고의 방식으로만 호명한다. 알레시오를 곧바로 파시스트와 동일시하지 않되, 1948년 헌법이 비상조항을 두지 않은 이유를 극중 인물들(대통령, 이레네, 지타)이 말하게 한다. 10부의 귀환은 면죄가 아니다: 그의 사임과 자백은 죽은 루치아를 돌려놓지 않으며, 암살이 그를 순교자로 만들지 않도록 장례와 재판에서 피해자 유족의 목소리를 그의 목소리보다 앞에 둔다. 암살 장면은 절제한다(총성과 남은 커피잔, 피와 시신을 보여 주지 않음). 실존 반마피아 판사(팔코네·보르셀리노)는 인용과 기억으로만 등장시키고, 역사 인물의 말 중 출전이 불확실한 것은 극중에서도 '~라고 전해진다'로 처리한다. Paragon 스파이웨어 사건, 2025년 치안 법령, premierato 논쟁은 실제 보도에 근거하되 극중 사건은 모두 가상화하며 실존 피해 기자·활동가·구조 NGO를 암시하지 않는다.</t>
         </is>
       </c>
       <c r="N6" s="5" t="inlineStr">
@@ -4253,7 +4253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F164"/>
+  <dimension ref="A1:F182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4290,7 +4290,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="75" customHeight="1">
+    <row r="5" ht="90" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>로그라인</t>
@@ -4298,11 +4298,11 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>2029년 로마 벙커 법정, 암살된 전 총리 알레시오 리날디의 소꿉친구이자 마피아 가문의 변호사였던 전 하원의원 파올로 세라가 협력자(collaboratore di giustizia)로 화상 스크린 뒤에 앉는다. 그의 증언 한 조각마다 열리는 과거 속에서, 시칠리아 신참 검사 알레시오는 스승의 폭사 뒤 대재판과 로지 수사를 거쳐 법복을 벗고 총리에 오르며, 연쇄 폭탄 속 특별법 확대의 유혹 앞에서 스스로 권력에 일몰 조항을 건다. 같은 15년 동안 파올로는 가문의 변호사에서 비밀 로지 '에르메테'의 얼굴 노릇을 하는 정치인으로 미끄러지다가 느리게 돌아선다. 알레시오는 퇴임 전날 저격당하지만 제도는 그 없이 선서를 치르고, 친구의 증언은 암살의 돈줄을 법정에 세운다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="90" customHeight="1">
+          <t>2029년 시칠리아 토레네라의 벙커 법정 — 한때 알레시오 리날디가 대재판을 위해 세운 그 법정 — 에서 언론이 '리날디 사건'이라 부르는 재판이 열리고, 그의 소꿉친구이자 마피아 가문의 변호사였던 파올로 세라가 협력자(collaboratore di giustizia)로 화상 스크린 뒤에 앉는다. 증언이 여는 과거 속에서 스승의 폭사를 딛고 일어선 이상주의 검사 알레시오는 총리가 되지만, 당대회장 폭탄 뒤 공포로 두 번째 신임을 얻고 긴급 법령·민방위 비상사태·헌법 개정으로 비상대권을 손에 넣어 반마피아의 무기를 기자와 검사, 시민에게 겨누는 괴물이 된다. 헌법재판소와 대통령, 명령을 거부한 지휘관들 앞의 벼랑에서 그는 끝내 인간으로 돌아와 권력을 내려놓고, 비상 시절 살레미 잔당·로지와 맺은 거래까지 모두 증언하겠다고 나서지만, 증언대에 서기 전날 마피아의 총에 쓰러진다. 법정은 그의 살해자들을 심판하고, 그가 남긴 자백서가 그 자신이 무엇이었는지를 심판한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="255" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
           <t>시대·배경</t>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>현재의 이탈리아: 1부=2014년에서 9부=2024~25년, 에필로그≈2029년(가까운 미래)까지 약 15년. 1992~93년 폭탄 학살의 시대와 1990년대 초 반부패 수사는 배경사(벨란디의 과거, 어린 알레시오의 기억)로만 쓴다. 가상의 시칠리아 항구도시 토레네라(Torrenera)와 석유화학 단지, 가상의 남부 산유 지역 '레조네 요니카(Regione Ionica)', 로마·밀라노. 의원내각제: 총선 → 대통령의 조각 위임(incarico) → 퀴리날레 선서 → 양원 신임투표. 총리 연임 제한이 없는 제도에서 주인공이 스스로 '연속 두 번의 입법기' 한계를 만든다. 하이브리드판 액자: 2029년 로마 벙커 법정에서 열리는 '리날디 총리 암살 사건' 중죄법원(Corte d'Assise) 재판 — 협력자 파올로 세라가 보호 거처에서 화상으로 증언하고, 피고인석엔 실행범·조직자에 이어 신병 인도된 자금원들이 앉는다.</t>
+          <t>현재의 이탈리아: 1부=2014년에서 10부=2024~26년, 에필로그≈2029년(가까운 미래)까지 약 15년. 1992~93년 폭탄 학살의 시대와 1990년대 초 반부패 수사는 배경사(벨란디의 과거, 어린 알레시오의 기억)로만 쓴다. 가상의 시칠리아 항구도시 토레네라(Torrenera)와 석유화학 단지, 가상의 남부 산유 지역 '레조네 요니카(Regione Ionica)', 로마·밀라노·팔레르모. 의원내각제: 총선 → 대통령의 조각 위임(incarico) → 퀴리날레 선서 → 양원 신임투표. 비상 통치의 실제 장치: 1948년 헌법은 파시즘의 경험 때문에 일반 비상조항을 두지 않았다. 있는 것은 ①제78조 전쟁상태(양원이 의결하고 정부에 필요한 권한을 부여, 대통령이 선포 — 제87조), ②제77조 긴급 법령(decreto-legge: 필요·긴급 시 정부가 제정, 대통령이 서명·공포, 60일 안에 법률로 전환되지 않으면 소급 실효, 헌법재판소 1996년 제360호 판결로 같은 내용의 재발령 금지), ③전환 법안에 거는 신임 문제(questione di fiducia), ④민방위법(D.Lgs. 1/2018)의 국가적 비상사태(최장 12개월+12개월 연장)와 코로나19 시기의 총리령(DPCM) 통치 선례, ⑤도시 군 병력 배치('Strade sicure'형 작전), ⑥정보기관 예방 감청(로마 항소법원 검찰총장의 승인 필요), ⑦41-bis 특별 수감 체제와 반마피아법의 예방 조치·지방의회 해산, ⑧제138조 개헌(두 차례 의결, 두 번째 의결에서 양원 각 3분의 2면 국민투표 없이 확정, 아니면 확정 국민투표 가능), 헌법재판소 1988년 제1146호 판결의 '최고 원리는 헌법 개정으로도 바꿀 수 없다'는 법리와 제139조(공화정체는 개정 대상이 아님), ⑨제60조(의회 임기 연장은 전쟁 시 법률로만), ⑩대통령의 긴급 법령 서명 거부와 법률 재의 요구(제74조), 불신임 동의(제94조), 장관 범죄의 의회 소추 허가(제96조). 7~10부의 비상 통치는 모두 이 실제 장치들을 늘이고 비틀어서 만든다 — 가상의 '제78조의2(국가 비상사태)' 개헌이 유일한 창작 조항이다. 직권남용죄(형법 제323조)는 2024년 8월 폐지되어(법률 제114호) 소급 적용되므로, 알레시오가 스스로 털어놓는 범죄는 불법 감청, 불법 구금, 구금 중 사망에 대한 책임, 살레미 잔당과의 거래다. 하이브리드판 액자: 2029년 토레네라 벙커 법정의 중죄법원(Corte d'Assise) 재판 — 언론이 '리날디 사건(processo Rinaldi)'이라 부르는 이 재판은 6부까지는 전 총리의 재판처럼 보이지만, 실은 2026년 그를 살해한 실행범·조직자·자금원의 재판이다(피고인의 사망은 형사 소추를 소멸시키므로 알레시오 자신은 재판받지 않는다). 협력자 파올로가 보호 거처에서 화상으로 증언하고, 알레시오가 죽기 전 검찰에 맡긴 자백서(memoriale)가 형사소송법 제512조(예측할 수 없는 사유로 반복 불가능해진 진술의 낭독)에 따라 법정에서 읽힌다.</t>
         </is>
       </c>
     </row>
@@ -4326,7 +4326,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="45" customHeight="1">
+    <row r="8" ht="60" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
           <t>경로</t>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>토레네라 지방검찰청 신참 검사(sostituto procuratore) → 반마피아검찰국 풀, 피고인 300여 명의 대재판 → 밀라노 파견, 전국 공공공사 반부패 수사의 얼굴 → 최고사법위원회(CSM) 징계·강제 전보 후 사직 → 시민정당 '온다 치빌레' 창당, 토레네라 소선거구 하원의원 → 의회 반마피아위원회 위원장·연합 총리 후보 → 총리(2개 입법기) → 퇴임 직후 피격 사망</t>
+          <t>토레네라 지방검찰청 신참 검사 → 반마피아검찰국 풀, 피고인 300여 명의 대재판 → 밀라노 파견, 전국 반부패 수사의 얼굴 → CSM 징계·강제 전보 후 사직 → 시민정당 '온다 치빌레' 창당, 하원의원 → 반마피아위원회 위원장 → 총리(첫 정부, 스스로 '연속 두 입법기' 한계 도입) → 당대회장 폭탄 뒤 공포 속 재신임 → 긴급 법령·비상사태·개헌으로 비상대권 장악 → 비상 체제의 총리('괴물') → 헌재 위헌 결정·대통령 거부·지휘관 거부 앞에서 불복하지 않고 사임 → 자백서 제출, 증인으로 나서기 전날 피살</t>
         </is>
       </c>
     </row>
@@ -4346,11 +4346,11 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>이탈리아 공화국 각료회의 의장(Presidente del Consiglio dei ministri, 총리)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="90" customHeight="1">
+          <t>이탈리아 공화국 각료회의 의장(총리) — 비상대권을 내려놓고 사임, 2026년 증언 전날 피살(2029년 재판의 '피해자')</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="105" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
           <t>마모</t>
@@ -4358,11 +4358,11 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>부마다 곁의 한 사람이 사라진다: 스승 벨란디(1부, 차량 폭탄), 대재판의 대가로 회개자의 형과 아녜세의 자유, 파올로의 우정(2부, 은신처 유출), 로지를 건드린 기자 키아라(3부, '흰 루파라'식 실종), 아버지와 아녜세(4부, 뺑소니와 옥중 사망), 동료 검사 다비데(5부, 청부 총격), 감사역 욜란다(6부, 당대회장 폭탄), 7부는 사람 대신 주인공의 원칙이 깎여 나가는 부, 카를로(8부), 그리고 9부 주인공 자신. 하이브리드판에서 친구 파올로는 죽지 않는 대신 부마다 한 겹씩 깎여 나간다 — 양심(2부), 키아라에 대한 침묵(3부), 우정(4부), 다비데에 대한 침묵(5부) — 그리고 전향의 대가로 이름과 가족을 잃는다. 마모는 죽은 이들만이 아니라 살아남아 증언하는 자의 몫이기도 하다. 이탈리아 반마피아 투쟁의 '살아 있는 죽은 이들(cadaveri eccellenti)' 기억과 겹친다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="45" customHeight="1">
+          <t>마모와 회복. 바깥의 마모: 부마다 곁의 한 사람이 사라진다 — 스승 벨란디(1부), 회개자의 형과 아녜세의 자유·파올로의 우정(2부), 기자 키아라(3부), 아버지와 아녜세(4부), 동료 검사 다비데(5부), 감사역 욜란다(6부), 기자 루치아(8부), 카를로(9부). 안쪽의 마모: 6부부터는 주인공 자신의 원칙이 깎여 나간다 — 절차(6부), 영장과 대통령의 서명, 스스로 만든 두 입법기 한계(7부), 반마피아의 무기를 시민에게 쓰지 않는다는 선(8부), 선거와 헌법재판소(9부). 1~5부에 이미 씨앗이 있다: '나는 누가 범인인지 안다'는 확신, 절차에 대한 경멸, 영장 없이 '귀동냥'하던 스승 벨란디의 방법. 8부에서 그의 서명으로 루치아가 구금 중 숨질 때, 그는 4부에 아녜세를 죽인 바로 그 체제가 된다. 10부는 회복의 부다: 피해자 어머니의 부엌, 어머니 안나, 이레네, 정직하게 다시 읽은 벨란디의 수첩 앞에서 그는 권력을 내려놓고 자기 죄를 스스로 말하며 원칙을 되찾는다 — 그리고 그 대가로 목숨을 잃는다. 친구 파올로는 반대 방향의 거울이다: 1~6부 동안 깎여 나가고, 8부에 알레시오의 해결사로 바닥을 친 뒤, 9부에 협력자로 돌아선다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="105" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
           <t>권력의 유혹</t>
@@ -4370,11 +4370,11 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>7부: 마피아와 비밀 로지가 손잡은 새 '폭탄의 계절'과 국채 스프레드 공격이 겹치자, 내무장관 라디체가 반마피아 특별법(예방적 자산 몰수, 행정 금지명령, 트로이목마 감청, 지방의회 해산, 특별 격리수용)을 '국가 전복 세력'이라는 이름으로 야당 운동·언론사로 넓히는 긴급 법령(decreto-legge)을 올린다. 지방선거 연기, 신문사에 대한 금지명령, 기자 휴대전화 감청 승인이 차례로 유혹이 된다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="45" customHeight="1">
+          <t>유혹은 거절되지 않고 받아들여진다. 6부 카타니아 당대회장 폭탄으로 욜란다가 죽고 이레네가 다친 뒤, 알레시오는 키케로의 «Salus populi suprema lex esto»를 내걸고 공포 속에 두 번째 신임을 얻는다. 7부(권력의 획득): 새 '폭탄의 계절'에 긴급 법령을 잇따라 내고 전환 법안마다 신임 문제를 걸며, 가뭄 대응 민방위 비상사태를 치안으로 늘여 총리령(DPCM)으로 다스린다. 60일이 지나 실효된 법령을 거의 그대로 다시 내려다 대통령이 서명을 거부하자 국민에게 직접 호소하고, 가상의 '제78조의2(국가 비상사태)' 개헌을 밀어붙인다 — 하원은 공포에 질린 야당까지 3분의 2로, 상원은 몇 표가 모자라 확정 국민투표로 가고, 그는 투표에서 이긴다. 작은 월권(승인 없는 스파이웨어 감청)은 멈춤이 아니라 첫걸음이다. 8부(체제의 일상): 비상대권 아래 41-bis, 예방 조치, 지방의회 해산, 스파이웨어, 거리의 군이 기자·검사·NGO·시위대에게 돌아가고, '질서'를 위해 살레미 잔당과 에르메테 로지의 방법에 손을 내민다. 9부(정점): 하이브리드전을 '전쟁'으로 규정해 제78조 전쟁상태를 의결받고 제60조로 입법기를 늘이려 하며, 끝내 헌재 결정에 불복할 것인가의 문턱에 선다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="90" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
           <t>자기 제한</t>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>알레시오는 긴급 법령을 철회하고, 모든 특별 조치에 일몰 조항과 의회 사전 승인을 걸며, 당헌과 헌법 개정안에 '총리 연속 두 번 입법기' 한계를 넣는다. 강한 총리직선제(premierato) 요구를 거부하고, 개헌 패키지 통과 뒤 스스로 사임해 조기 총선으로 새 위임을 구한다. 8부 「권력의 한계」 법으로 긴급 법령 남용·신임투표 연계를 제한한다.</t>
+          <t>자기 제한의 실패와, 그 대신 그를 묶는 제도, 그리고 너무 늦은 자기 제한. 5부에 그가 스스로 만든 '연속 두 입법기' 한계는 7부 개헌으로 스스로 걷어낸다. 그를 멈추는 것은 먼저 제도다: 긴급 법령 서명을 미루고 재발령을 거부하며 전쟁상태 선포와 임기 연장법을 거부하는 대통령(퀴리날레), 개헌 조항의 핵심을 '최고 원리' 위반으로 무효화하는 헌법재판소(1988년 제1146호 판결 법리, 제139조), 승인 없는 감청을 파고드는 젊은 검사, 헌재에 제소하는 레조네 요니카 주지사, 위헌 심판을 제청하는 판사, 명백히 위법한 명령을 거부하는 카라비니에리 사령관과 군 지휘부, 불신임 동의를 준비하는 연정. 10부 벼랑 끝에서 그는 헌재 결정에 불복하는 긴급 법령 초안을 찢고 스스로 권력을 내려놓는다 — 킨키나투스의 늦고 쓰라린 메아리이지만 그가 한 일을 씻어 주지는 않는다. 퇴임 뒤에는 면책과 '폐지된 죄목'에 숨지 않고 자백서를 검찰에 맡기며 증인이 되기로 한다. 그것이 그의 유일하고 마지막 자기 제한이다.</t>
         </is>
       </c>
     </row>
@@ -4394,11 +4394,11 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>암살·증언</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="60" customHeight="1">
+          <t>몰락·귀환·암살</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="120" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
           <t>결말</t>
@@ -4406,11 +4406,11 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>퇴임 전날 로마 테베레 강변에서 저격당해 숨지지만, 후계자 이레네 마르텔리는 이튿날 예정대로 퀴리날레에서 선서한다. 사흘 전 모호한 경고밖에 하지 못했던 파올로가 선서 이튿날 자수해 협력자가 되고, 그가 6부부터 몰래 복사해 둔 송금 기록이 실행범·조직자 기소를 연다. 2029년 벙커 법정에서 그의 증언이 외부 증거로 보강되어 신병 인도된 자금원 브란카티와 두 자금책의 유죄를 결정하고, 같은 해 이레네의 입법기가 끝나 마리나 페를리토가 총리로 선서한다. 한 사람이 아니라 제도 — 선서, 독립 수사, 협력자 제도와 공개 법정 — 가 이어졌음을 증명한다. 파올로는 살아남지만 새 이름과 보호 프로그램 속에서 가족 없이 형을 산다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="90" customHeight="1">
+          <t>헌재가 비상 개헌의 핵심을 무효화하고 대통령이 불복 법령에 서명하지 않으며 사령관들이 위법 명령을 거부한 밤(9부 끝), 알레시오는 불복하지 않기로 한다(10부). 그는 헌재 결정을 이행하고 비상사태를 거두며, 하원에서 자신의 책임을 공개적으로 인정한 뒤 퀴리날레에 사표를 낸다. 재건된 총선에서 이레네가 이기고, 그는 의원 면책을 내려놓고 자기 범죄와 비상 시절 살레미 잔당·에르메테 로지와의 거래를 담은 자백서를 검사 엘레나 사르토리에게 맡긴다. 토레네라에서 사과하고 다시 먼저 커피를 내는 짧은 인간의 계절 끝에, 증언대에 서기 전날 항구의 바에서 살레미 잔당의 총에 쓰러진다 — 반마피아 과거에 대한 복수이자 입막음. 피고인의 죽음으로 그 자신에 대한 소추는 소멸하지만, 2029년 토레네라 벙커 법정에서 협력자 파올로의 증언과 형사소송법 제512조로 낭독된 그의 자백서가 실행범·조직자·니노 살레미와 신병 인도된 로지 자금원 브란카티의 유죄를 결정한다. 법정은 살해자를 심판하고, 그의 자백서는 그가 무엇이었는지를 심판한다. 키케로와의 대비로 닫힌다: 재판 없이 처형했던 키케로는 뉘우치지 않은 채 권력 투쟁 속에 안토니우스의 살생부에 올라 죽었고, 알레시오는 뉘우치고 진실을 말하려다 죽었다. 비상대권을 멈춘 것은 한 사람의 양심보다 먼저 제도였고, 그의 귀환은 제도가 열어 둔 문으로 걸어 나온 것이었다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="180" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
           <t>구성·무게중심</t>
@@ -4418,11 +4418,11 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>9부 × 12화 + 에필로그. 기존 틀(연대기 9부×12화+에필로그, 알레시오의 검사→총리 경로, 암살 결말)은 그대로 두고 두 장치를 더한 하이브리드판이다. ① 2029 증언 액자: 매 부 1화는 로마 벙커 법정의 리날디 암살 재판에서 협력자 파올로 세라가 화상 스크린 뒤에서 하는 증언으로 콜드 오픈하고, 그 부의 핵심 질문과 답이 이야기를 연다. 9부와 에필로그에서 이 증언과 그가 모아 둔 장부 사본이 자금원 브란카티 일당의 유죄를 결정한다. ② 친구 시점: 매 부 2~3화를 파올로의 시점으로 서술해(시놉시스에 '(친구 시점)' 표시) 소꿉친구 → 가문 변호사 → 로지의 정치인 → 느린 전향 → 협력자의 궤적을 알레시오의 궤적과 거울처럼 겹친다. 무게중심은 여전히 수사와 재판이다(원작 2부를 대재판·밀라노 로지 수사 두 부로 늘리고, 원작 선거 두 부를 4부 「신임」으로 압축). 원작의 친구 죽음(5부 5화)은 파올로가 증인으로 살아남아야 하므로 새 인물인 동료 검사 다비데 로카시오가 넘겨받아 마모의 리듬을 지킨다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="60" customHeight="1">
+          <t>10부 × 12화 + 에필로그. 연대기 10부×12화+에필로그. 두 하이브리드 장치(① 매 부 1화의 2029 법정 콜드 오픈, ② 매 부 2~3화의 파올로 시점)를 유지하되 후반부를 뒤집은 '몰락·귀환' 판이다. 1~5부는 이상주의 검사의 상승을 거의 그대로 두고 결함의 씨앗(확신, '나는 안다'는 절차 경멸, 벨란디의 회색 방법)만 심는다. 6부 공포의 재신임 → 7부 비상대권의 획득 → 8부 비상 체제의 일상 → 9부 괴물의 정점과 제도의 반격 → 10부 귀환·사임·자백·암살. 부를 10개로 늘린 이유: 원작 9부 구조에서는 권력의 획득과 남용, 몰락이 두 부에 몰려 비상 체제가 '줄거리'로만 지나간다. 8부 한 부 전체를 체제 아래의 삶에 바쳐 — 검문소의 병사, 자기검열하는 편집국, 전보된 검사, 예방 조치를 받은 구조선 선장, 해산된 고향 의회와 밀고자, 굽는 법원, 조용히 이득을 보는 마피아 — 알레시오를 점점 남의 눈으로만 보여 주고, 그 대가(루치아의 죽음)를 관객이 먼저 겪게 한다. 그래야 9부의 정점과 10부의 귀환이 무게를 가진다. 원작 7부의 '유혹 거절'은 '유혹 수용'으로, 원작 8부의 '권력의 한계'는 '권력의 남용'으로 뒤집히고, 원작 9부(마지막 해·저격)는 10부로 옮겨 '귀환 뒤 피살'로 바뀐다. 액자의 반전: 1~6부 콜드 오픈은 피고인석을 비추지 않은 채 '리날디'에 관한 질문만 쌓아 관객이 그를 피고인으로 믿게 하고(5부 1화 '그를 단죄하는 건 그 자신의 말', 6부 1화 '그는 폭탄 자금 증거를 검찰에 넘기지 않았다'), 7부 1화 재판장의 공소 사실 낭독으로 이 재판이 2026년 리날디 살해 사건 재판이며 그는 이미 죽었음이 드러난다 — 이후 피고인 측은 '피해자는 괴물이었다'는 전략으로 파올로를 공격한다. 10부 1화 파올로가 봉인된 자백서를 건네받고, 에필로그에서 그 마지막 줄을 읽는다. 원작 제목의 궤적(법정에서 권력까지)은 법정으로 되돌아오며 닫힌다 — 그가 대재판을 위해 세운 벙커 법정이 그의 살해자들을 심판한다. 원작 5부 5화의 친구 죽음은 동료 검사 다비데가 넘겨받는다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="105" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
           <t>작은 모티프</t>
@@ -4430,11 +4430,11 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>모카포트 커피: 벨란디는 누가 찾아오든 먼저 모카로 커피를 끓여 낸다 — «Prima un caffè, poi parliamo.» 젊은 알레시오는 시간 낭비라 여긴다. 이 습관은 감사역 욜란다에게서 다시 나타나고(보온병 미네스트로네도), 8부에서 그녀의 카드 «Non dimenticare il caffè»가 '고통을 안고 온 사람에게 먼저 커피를'로 해독된다. 하이브리드판에서는 파올로의 궤적에도 걸린다: 3부 9화 그는 키아라에게 커피를 내준 뒤 브란카티에게 전화를 걸고(뒤집힌 모티프), 9부 8화 경고하러 온 그에게 알레시오가 먼저 커피를 내며, 에필로그에서 새 이름의 파올로가 호위 경관에게 먼저 커피를 낸다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="240" customHeight="1">
+          <t>모카포트 커피: 벨란디는 누가 찾아오든 먼저 모카로 커피를 끓여 낸다 — «Prima un caffè, poi parliamo.» 1부 장례식에서 알레시오가 무심코 조문객에게 커피부터 내며 모티프를 물려받고, 2부 회개자에게, 4부 욜란다에게서 되돌아온다. 4부 11화 면책을 흥정하러 온 파올로에게 처음으로 커피를 내지 않는다. 뒤집힘: 6부 11화 욜란다의 빈 책상에 모카포트가 올라가는 밤 그는 오지 않고, 7부부터 총리실의 커피는 비서가 나르는 물건이 되며, 8부 2화 욜란다의 카드 «Non dimenticare il caffè»를 그는 읽지 않고 서랍에 넣는다. 8부 3화 검문소의 병사는 루치아의 어머니에게 커피 대신 신분증을 요구한다. 9부 12화 새벽 리나가 마지막으로 커피를 놓고 나간다. 되찾음: 10부 1화 그는 루치아의 어머니 집 부엌에서 처음으로 먼저 커피를 끓이겠다고 청하고, 10부 9화 토레네라에서 어부와 쫓겨난 시장, 회개자의 아내에게 다시 먼저 커피를 낸다. 10부 11화 총성 뒤 바 탁자에는 김이 오르는 잔 두 개와 모카포트가 남는다(1부 11화 식은 모카포트의 메아리). 에필로그 마지막 장면: 새 이름의 파올로가 보호 거처에서 호위 경관에게 먼저 커피를 낸다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="360" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
           <t>실제 현안</t>
@@ -4451,11 +4451,15 @@
 · 이주민 역외 수용(제3국 수용소)과 '안전한 출신국' 지정에 대한 유럽사법재판소 판결, 해상 구조 NGO 압박
 · 시칠리아 가뭄 비상사태와 급수 제한, 기후 위기 속 폭염·산불
 · 재정 규율: EU 과잉적자 절차와 3% 기준, 국채 스프레드 축소와 남부 지방 부채·의료 재정
-· 농업 불법 인력 중개(caporalato)와 석유화학 단지 오염·산업재해</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="525" customHeight="1">
+· 농업 불법 인력 중개(caporalato)와 석유화학 단지 오염·산업재해
+· 비상 통치 논쟁: 일반 비상조항이 없는 1948년 헌법, 긴급 법령 남용과 재발령 금지 판례, 코로나19 시기 민방위 비상사태·총리령(DPCM) 통치의 선례
+· 2025년 치안 긴급 법령(decreto-legge 제48호)의 법률 전환: 도로 봉쇄·연좌·수동적 저항 형사처벌과 경찰권 확대에 대한 '비자유주의적 전환' 비판
+· 총리 권한 강화 논쟁: premierato 개헌안과 2026년 선거법 개정(총리 후보 사전 지명)이 '개헌 없는 사실상의 premierato'라는 야당 비판
+· 직권남용죄 폐지(2024)와 EU 반부패 지침을 둘러싼 재도입 논쟁</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="750" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
         <is>
           <t>현안 출처(웹 확인)</t>
@@ -4473,11 +4477,16 @@
 · 유럽사법재판소가 '안전한 출신국' 지정 요건을 엄격히 판단, 알바니아 역외 수용 구상에 타격 — Euronews, 2025-08-01, https://www.euronews.com/my-europe/2025/08/01/eu-court-rebukes-italy-over-migrant-transfers-to-albania
 · 시칠리아 가뭄 비상사태, 기후 변화가 극한 가뭄의 핵심 요인 — World Weather Attribution, 2024, https://www.worldweatherattribution.org/climate-change-key-driver-of-extreme-drought-in-water-scarce-sicily-and-sardinia/
 · 2026년 예산 최종 승인, 적자 3% 미만 목표와 과잉적자 절차 탈출 과제 — Reuters via KFGO, 2025-12-30, https://kfgo.com/2025/12/30/italian-parliament-gives-final-approval-to-governments-2026-budget/
-· 은드랑게타 132명 대상 초국적 작전과 레조칼라브리아 대재판(유죄 76명) — Eurojust, https://www.eurojust.europa.eu/news/over-1-000-years-imprisonment-mafia-members-following-largest-ever-action-against-italian</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="255" customHeight="1">
+· 은드랑게타 132명 대상 초국적 작전과 레조칼라브리아 대재판(유죄 76명) — Eurojust, https://www.eurojust.europa.eu/news/over-1-000-years-imprisonment-mafia-members-following-largest-ever-action-against-italian
+· 2025년 4월 11일 치안 긴급 법령(DL 48/2025)이 6월 9일 법률 제80호로 전환, 시위 처벌 확대에 대한 헌법학계·유럽평의회 인권위원 등의 우려 — Verfassungsblog, 2025, https://verfassungsblog.de/the-securitarian-turn-in-italian-criminal-law/
+· 치안 법령의 조치가 의회 승인 전 긴급 법령으로 먼저 시행됨 — Civic Space Watch, 2025, https://civicspacewatch.eu/alert/italy-security-law-enacted-in-june-2025-but-its-measures-were-already-applied-before-approval/
+· 선거법 개정안 하원 최종 심의 착수(총리 후보 사전 지명 등, '사실상의 premierato' 논란) — ANSA, 2026-09-20, https://www.ansa.it/sito/notizie/politica/2026/09/20/legge-elettorale-al-via-alla-camera-lultimo-step-della-riforma_9eeeaa9d-59a7-4070-8fc5-3780eb563458.html
+· 직권남용죄 폐지 법률(2024년 8월 9일 법률 제114호) 공포 — Il Sole 24 Ore, 2024-08, https://en.ilsole24ore.com/art/abolition-abuse-of-office-mattarella-signs-nordio-reform-and-law-AFPalqID
+· EU 반부패 지침 채택과 직권남용죄 재도입 논쟁 — Eunews, 2026-03-26, https://www.eunews.it/en/2026/03/26/eu-approves-anti-corruption-directive-italy-faces-controversy-over-reintroducing-abuse-of-office-law/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="675" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
           <t>인용 자원</t>
@@ -4492,11 +4501,22 @@
 · 주세페 토마시 디 람페두사 『표범(Il Gattopardo)』 — «Se vogliamo che tutto rimanga come è, bisogna che tutto cambi»(악역의 논리로)
 · 이탈리아 공화국 헌법 제1조·제54조(공직자의 '규율과 명예')
 · 속담: «Tra il dire e il fare c'è di mezzo il mare», «Chi tace acconsente», «Il pesce puzza dalla testa», «Chi va piano va sano e va lontano»
-· 시칠리아 속담: «Càlati juncu, ca passa la china»(골풀아 몸을 숙여라, 홍수가 지나간다 — 순응의 논리)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="165" customHeight="1">
+· 시칠리아 속담: «Càlati juncu, ca passa la china»(골풀아 몸을 숙여라, 홍수가 지나간다 — 순응의 논리)
+· 이탈리아 공화국 헌법 제78조(전쟁상태), 제77조(긴급 법령), 제60조(임기 연장은 전쟁 시 법률로만), 제139조(«La forma repubblicana non può essere oggetto di revisione costituzionale»)
+· 체사레 베카리아 『범죄와 형벌(Dei delitti e delle pene)』(1764) — 고문 반대의 장, «Uno dei più gran freni dei delitti non è la crudeltà delle pene, ma l'infallibilità di esse»(형벌의 잔혹함이 아니라 확실함): 1부 2화 벨란디의 선물 → 9부 3화 파올로가 총리 책상에서 챙김 → 9부 8화 엘레나에게 → 10부 5화 알레시오가 되찾음 → 에필로그
+· 조반니 팔코네 — «Gli uomini passano, le idee restano…»(전해지는 말), '돈을 따라가라'는 수사 방법(그의 방법으로 전해짐): 1부 12화, 3부 1화, 8부 8화(루치아가 파올로에게). 실존 인물은 인용으로만, 극중 인물로 등장시키지 않음
+· 파올로 보르셀리노 — «Chi ha paura muore ogni giorno, chi non ha paura muore una volta sola»(전해지는 말): 5부 6화, 10부 10화
+· 킨키나투스 — 기원전 458년 독재관에 올라 16일 만에 권력을 내려놓고 쟁기로 돌아감(리비우스 『로마사』 3권): 5부 12화 → 7부 8화('킨키나투스에겐 쟁기가 있었지, 나한텐 폭탄이 있어') → 8부 10화 이레네 → 10부 5화 알레시오가 되찾되 '그는 용서받을 일이 없었다'
+· 주세페 가리발디 — 1860년 테아노에서 정복한 남부를 국왕에게 넘기고 카프레라 섬으로 돌아감(씨앗 자루 일화는 전해지는 이야기): 5부 10화, 8부 10화
+· 키케로 — «Salus populi suprema lex esto»(『법률론』 3권), 기원전 63년 원로원 최종 결의 아래 카틸리나 공모자들을 재판 없이 처형 → 기원전 58년 추방 → 기원전 43년 안토니우스의 살생부(proscriptio)로 피살: 6부 9화, 7부 8화, 에필로그(대비로 닫힘)
+· 카이사르의 루비콘 도하 «alea iacta est»(수에토니우스 『황제 열전』 카이사르 32장): 7부 11화
+· 마키아벨리 『군주론』 17장 — «è molto più sicuro essere temuto che amato»: 8부 9화 알레시오가 인용 → 10부 5화 스스로 반박
+· 자코모 마테오티 — 1924년 5월 30일 하원 연설로 선거 폭력을 고발하고 6월 10일 납치·살해됨, «Io, il mio discorso l'ho fatto. Ora voi preparate il discorso funebre per me»(전해지는 말): 8부 12화(파시즘의 그림자, 추모의 방식으로만)
+· 조르다노 브루노 — «Forse tremate più voi nel pronunciare questa sentenza che io nell'ascoltarla»(전해지는 말): 8부 5화 엘레나 사르토리</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="330" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
         <is>
           <t>민감도·주의</t>
@@ -4504,7 +4524,7 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>현안(사법개혁 국민투표, 총리 직선제, 스파이웨어, 치안 법령, 해협 대교, 역외 수용)은 실제 2024~2026년 보도에 근거하되 실존 정치인·기업·피해자는 인물로 쓰지 않는다. 시간축은 현재(2014~2029)이며 1990년대 사건은 배경사로만 언급한다. 2부 대재판은 1980년대 실제 대재판을 떠올리게 하되 2015년의 가상 재판(가상 가문·가상 피고인)으로 그리고, 회개자(pentiti) 제도와 증인 보호의 실제 문제를 다루며 회개자를 영웅화하지도 악마화하지도 않는다. 실존 반마피아 판사·검사(특히 1992년 희생자들)와 실제 학살 사건명을 인물·사건으로 쓰지 않는다. 폭탄 암살·로지·일탈 정보기관은 역사적 모티프만 빌려 전부 가상화하고, 실존 조직명(Cosa Nostra 등)도 대사에서 일반명사('조직', '가문들')로 처리한다. 시칠리아·남부를 마피아와 동일시하는 고정관념을 피하려 반마피아 시민·협동조합·기자의 저항을 주인공만큼 비중 있게 그린다. 프리메이슨 일반을 악마화하지 않도록 '정규 결사와 무관한 불법 비밀 로지'로 명시한다. 실존 정치인·정당명 금지, 가상 정당만 사용. 하이브리드판의 협력자(collaboratore di giustizia) 묘사: 파올로의 전향을 구원 서사나 영웅담으로 미화하지 않는다 — 그의 증언은 감형과 보호를 대가로 한 거래이며, 그가 흘린 은신처, 키아라와 다비데의 죽음에 대한 책임은 판결로도 지워지지 않는다. 법정 장면은 실제 절차(원격 화상 증언과 가림막, 교차신문에서의 신빙성 공격, 협력자 진술에 대한 외부 증거 보강 요구)에 맞추되 실존 회개자·협력자의 생애, 증언, 사건을 복제하지 않는다. 피해자와 유족을 증언의 배경 소품으로 쓰지 않고 방청석의 목소리와 존엄을 주며, 증인 보호 프로그램의 실제 결함(버려진 증인, 가족의 해체)은 비판적으로 다루되 조롱하지 않는다. 마피아 문화와 '배신자' 낙인을 매혹적으로 그리지 않는다.</t>
+          <t>현안(사법개혁 국민투표, 총리 직선제, 스파이웨어, 치안 법령, 해협 대교, 역외 수용)은 실제 2024~2026년 보도에 근거하되 실존 정치인·기업·피해자는 인물로 쓰지 않는다. 시간축은 현재(2014~2029)이며 1990년대 사건은 배경사로만 언급한다. 2부 대재판은 1980년대 실제 대재판을 떠올리게 하되 2015년의 가상 재판(가상 가문·가상 피고인)으로 그리고, 회개자(pentiti) 제도와 증인 보호의 실제 문제를 다루며 회개자를 영웅화하지도 악마화하지도 않는다. 실존 반마피아 판사·검사(특히 1992년 희생자들)와 실제 학살 사건명을 인물·사건으로 쓰지 않는다. 폭탄 암살·로지·일탈 정보기관은 역사적 모티프만 빌려 전부 가상화하고, 실존 조직명(Cosa Nostra 등)도 대사에서 일반명사('조직', '가문들')로 처리한다. 시칠리아·남부를 마피아와 동일시하는 고정관념을 피하려 반마피아 시민·협동조합·기자의 저항을 주인공만큼 비중 있게 그린다. 프리메이슨 일반을 악마화하지 않도록 '정규 결사와 무관한 불법 비밀 로지'로 명시한다. 실존 정치인·정당명 금지, 가상 정당만 사용. 하이브리드판의 협력자(collaboratore di giustizia) 묘사: 파올로의 전향을 구원 서사나 영웅담으로 미화하지 않는다 — 그의 증언은 감형과 보호를 대가로 한 거래이며, 그가 흘린 은신처, 키아라와 다비데의 죽음에 대한 책임은 판결로도 지워지지 않는다. 법정 장면은 실제 절차(원격 화상 증언과 가림막, 교차신문에서의 신빙성 공격, 협력자 진술에 대한 외부 증거 보강 요구)에 맞추되 실존 회개자·협력자의 생애, 증언, 사건을 복제하지 않는다. 피해자와 유족을 증언의 배경 소품으로 쓰지 않고 방청석의 목소리와 존엄을 주며, 증인 보호 프로그램의 실제 결함(버려진 증인, 가족의 해체)은 비판적으로 다루되 조롱하지 않는다. 마피아 문화와 '배신자' 낙인을 매혹적으로 그리지 않는다. 뒤집힌 후반부 관련: 알레시오와 그의 정부·정당은 실존 이탈리아 총리·정당과 닮지 않게 설계한다(정책·말투·지지 기반·외모를 특정인과 겹치지 않게, 좌우 어느 쪽의 알레고리로도 읽히지 않게 — 그는 반마피아 영웅 출신의 초당파적 인물이다). 권위주의를 매혹적으로 그리지 않는다: 비상 통치의 '효율'을 쾌감으로 연출하지 않고, 8부 전체를 그 대가를 치르는 사람(병사, 기자, 검사, 구조선 선장, 구금자의 가족)의 눈으로 보여 준다. 제도가 작동하는 모습을 정확히 그린다 — 대통령의 서명 거부와 재의 요구, 헌법재판소 결정, 검찰의 독립 수사, 판사의 위헌 제청, 지방정부의 제소, 해안경비대의 구조, 군·카라비니에리의 위법 명령 거부(군 기본법의 '명백한 범죄 명령 불복' 원칙), 의회의 불신임 — 그리고 이들이 영웅이 아니라 규칙을 지키는 평범한 공직자로 보이게 한다. 파시즘의 기억은 조심스럽게 다룬다: 무솔리니를 인용하거나 영웅적으로 비추지 않고, 검은 셔츠·로마식 경례 같은 도상을 쓰지 않으며, 마테오티는 추모와 경고의 방식으로만 호명한다. 알레시오를 곧바로 파시스트와 동일시하지 않되, 1948년 헌법이 비상조항을 두지 않은 이유를 극중 인물들(대통령, 이레네, 지타)이 말하게 한다. 10부의 귀환은 면죄가 아니다: 그의 사임과 자백은 죽은 루치아를 돌려놓지 않으며, 암살이 그를 순교자로 만들지 않도록 장례와 재판에서 피해자 유족의 목소리를 그의 목소리보다 앞에 둔다. 암살 장면은 절제한다(총성과 남은 커피잔, 피와 시신을 보여 주지 않음). 실존 반마피아 판사(팔코네·보르셀리노)는 인용과 기억으로만 등장시키고, 역사 인물의 말 중 출전이 불확실한 것은 극중에서도 '~라고 전해진다'로 처리한다. Paragon 스파이웨어 사건, 2025년 치안 법령, premierato 논쟁은 실제 보도에 근거하되 극중 사건은 모두 가상화하며 실존 피해 기자·활동가·구조 NGO를 암시하지 않는다.</t>
         </is>
       </c>
     </row>
@@ -4561,12 +4581,12 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>토레네라 지방검찰청 차장검사(procuratore aggiunto), 알레시오의 스승. 1990년대 초 폭탄 학살의 시대를 겪은 세대로, 1993년 부실 콘크리트 고발 사건을 맡았다가 '환경 부적합'으로 전보당한 과거(배경사)</t>
+          <t>토레네라 지방검찰청 차장검사(procuratore aggiunto), 알레시오의 스승. 1990년대 초 폭탄 학살의 시대를 겪은 세대로, 1993년 부실 콘크리트 고발 사건을 맡았다가 '환경 부적합'으로 전보당한 과거(배경사). 위대하지만 회색의 검사: 증거가 모자랄 때 친한 카라비니에리에게 영장 없는 '귀동냥'을 부탁하곤 했고(«La legge arriva tardi; noi no»), 말년의 수첩에 그 방법을 후회하는 문장을 남긴다</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>1부 9화 익명 투서('코르보')와 조작된 정보 문서로 경호가 해제되고, 11화 차량 폭탄으로 사망. 그가 시작한 수사 파일이 2부 대재판의 뼈대가 된다</t>
+          <t>1부 9화 익명 투서로 경호 해제, 11화 차량 폭탄으로 사망. 7부 9화 알레시오는 그의 수첩에서 회색 방법만 읽고 마지막 장('예외는 늘 가장 좋은 이유로 온다')을 찢는다. 10부 2화 지타가 간직한 사본으로 그 장이 돌아온다. 에필로그에서 그 문장이 자백서의 첫 줄로 드러난다</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr"/>
@@ -4589,12 +4609,12 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>알레시오의 소꿉친구(토레네라 항만 동네에서 함께 자람), 하이브리드판 공동 주인공이자 2029년 암살 재판의 핵심 증인. 빚에 몰린 형사 변호사 → 살레미 가문 간부의 변호인 → 살레미 그룹·에르메테 로지의 법률 대리인 → 로지가 후원하는 가상 정당 «Alleanza del Mezzogiorno» 비례대표 하원의원 → 협력자(collaboratore di giustizia). 아내 줄리아, 두 아이</t>
+          <t>알레시오의 소꿉친구, 공동 주인공이자 2029년 '리날디 사건' 재판의 핵심 증인. 빚에 몰린 형사 변호사 → 살레미 가문 간부의 변호인 → 살레미 그룹·에르메테 로지의 법률 대리인 → 가상 정당 «Alleanza del Mezzogiorno» 하원의원 → 비상 정부의 비공식 해결사 → 협력자(collaboratore di giustizia). 아내 줄리아, 두 아이</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>1부 10화 조작 문서를 함께 밝힘 → 2부 6화 가문 변호 수임, 10화 딸을 겨냥한 협박에 회개자 은신처를 흘림 → 3부 8화 로지 입회, 9화 키아라의 장부 확인 사실을 브란카티에게 보고(평생의 죄책) → 4부 3화 표 매수 기계를 돌려 알레시오와 맞붙고 비례로 원내 진입 → 5부 5화 다비데에게 경고 전화를 걸다 끊음, 8화 살레미의 도피에 동행하지 않음 → 6부 7화 자신이 나른 대금이 당대회장 폭탄 자금이었음을 알고 송금 기록을 복사하기 시작 → 7부 10화 익명 제보로 가장 큰 폭탄을 막음 → 8부 12화 브란카티의 동반 도피 제안 거절 → 9부 8화 저격 계획을 모호하게 경고하지만 알레시오는 경호 강화를 거절 → 9부 12화 자수·협력자 선언, 의원직 상실 → 에필로그(2029) 증언으로 브란카티 일당 유죄. 살아남되 대가를 치른다: 새 이름과 증인 보호 프로그램, 아내의 이혼과 아이들의 이주, 어머니 장례식에도 가지 못함, 감형된 형을 보호 거처에서 복역. 알레시오와는 끝내 화해하지 못함</t>
+          <t>1부 10화 조작 문서를 넘김 → 2부 10화 협박에 회개자 은신처 유출 → 3부 8화 로지 입회, 9화 키아라를 브란카티에게 보고 → 4부 표 매수, 비례로 원내 → 5부 5화 다비데에게 경고 전화를 걸다 끊음 → 6부 7화 자신이 나른 대금이 당대회장 폭탄 자금임을 알고 송금 기록을 복사 → 7부 4화 10년 만에 알레시오의 부름을 받고 그 사본을 넘기며 그의 사람이 됨 → 8부 해결사로 살레미 잔당과 41-bis·비상 조달 거래를 중개하고, 8부 8화 취재하러 온 루치아를 총리실에 보고(키아라 때의 반복) → 8부 11화 루치아의 죽음 → 9부 3화 전쟁 초안을 받아 치다 베카리아를 챙김 → 9부 8화 '두 번째 장부'를 들고 검사 엘레나 사르토리에게 가 협력자가 됨(가족과 이별, 새 이름) → 10부 10화 살해 계획 첩보를 검찰에 전해 경호 강화를 이끌지만 막지 못함 → 에필로그(2029) 증언과 자백서 낭독으로 살해자들의 유죄를 결정. 살아남되 감형된 형과 새 이름, 가족 없는 보호 거처. 죽은 친구와 제대로 화해하지 못함(마지막 대화는 10부 10화의 한 문장짜리 통화)</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr"/>
@@ -4622,7 +4642,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>2부 1화 풀에서 첫 등장 → 2부 10화 은신처 유출 경로 끝에서 파올로의 이름을 찾음 → 5부 5화 CSM 계파 비리 조사에 자원했다가 청부 총격으로 사망 → 5부 9화 청부금이 키아라 사건과 같은 사슬로 확인 → 2029년 파올로의 증언으로 살해 지시 경로가 법정에서 확정</t>
+          <t>2부 1화 첫 등장, 2부 2화 알레시오의 '나는 안다'를 처음 말림 → 2부 10화 유출 경로 끝에서 파올로의 이름을 찾음 → 5부 5화 청부 총격으로 사망. 8부 5화 엘레나 사르토리가 그의 옛 사건 기록으로 수사를 배웠음이 드러남</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr"/>
@@ -4678,7 +4698,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>2부 7화 항만 매립 공사 봉쇄로 구속 → 3부 7화 유죄 → 4부 7화 옥중 단식 끝에 병원 이송 지연으로 사망</t>
+          <t>2부 7화 구속 → 3부 7화 유죄 → 4부 7화 옥중 단식 끝에 병원 이송 지연으로 사망. 8부 11화 루치아의 죽음이 같은 방식으로 반복되며 알레시오가 '아녜세를 죽인 체제'가 되었음을 보여 줌. 8부 7화 그녀의 협동조합을 이은 시장이 쫓겨남</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr"/>
@@ -4706,7 +4726,7 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>아버지는 2부 11화 항만 협동조합에서 해고, 4부 2화 총선 중 뺑소니로 사망. 어머니는 끝까지 곁에 있다가 에필로그 이전 화면 밖에서 조용히 세상을 떠남</t>
+          <t>아버지는 2부 11화 해고, 4부 2화 뺑소니로 사망. 어머니 안나는 8부 11화 아들의 전화를 받지 않고, 10부 2화 아들을 부엌에 앉혀 지타가 보낸 벨란디의 마지막 장을 식탁에 놓는다. 10부 11화 아들을 잃고, 에필로그 방청석 유족 자리에 루치아의 어머니와 나란히 앉는다</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr"/>
@@ -4734,7 +4754,7 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>2부 12화 대재판에서 가문 간부들은 종신형, 본인은 증거 불충분 무죄 → 4부 11화 연정 신임표를 미끼로 한 기만적 지지 → 5부 8화 해외 도피 직전 공항에서 체포(파올로 몫의 좌석은 비어 있었음) → 8부 11화 1심 판결과 몰수 자산의 사회적 재사용</t>
+          <t>2부 12화 본인 무죄 → 5부 8화 공항에서 체포, 41-bis 수감 → 8부 2화 파올로를 통한 거래로 12화 '건강상 이유'로 병원 가택연금에 옮겨지고 알레시오에게 '이제야 서로 이해하는군' → 10부 4화 알레시오가 사임 전 41-bis로 되돌림 → 에필로그 화상으로 출석해 끝까지 침묵('Io non parlo')</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr"/>
@@ -4742,27 +4762,27 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>크릴로프(보안기관장)</t>
+          <t>신규(리트비노프 계열의 후계)</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>gen. Corrado Crivelli</t>
+          <t>Nino Salemi</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>코라도 크리벨리 장군</t>
+          <t>니노 살레미</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>가상 정보기관 '국가안보중앙국(UCSN)' 부국장, 에르메테 로지와 닿아 있는 일탈 정보라인의 설계자</t>
+          <t>아르투로의 아들, 대재판 뒤 흩어진 가문을 새 세대 사업(폐기물·항만 물류·비상 조달)으로 재건한 '잔당'의 우두머리. 8부 비상 정부와의 거래 상대</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>2부 8화 거래 제안 → 4부 4화 첫 담판 → 4부 9화 진압 대신 협상을 택함 → 5부 9화 키아라 사건 방조가 드러나 사임 → 8부 5화 마지막 대화 → 9부 7화 노환으로 조용히 사망, 알레시오 혼자 장례식에</t>
+          <t>8부 2화 파올로와 교도소 면회실 거래 → 8부 8화 수의계약 비상 조달로 이득 → 10부 8화 알레시오의 자백서 소식에 브란카티의 로지 자금으로 살해 지시 → 10부 12화 체포 → 에필로그 종신형</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr"/>
@@ -4770,27 +4790,27 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>이리나(후계자)</t>
+          <t>크릴로프(보안기관장)</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Irene Martelli</t>
+          <t>gen. Corrado Crivelli</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>이레네 마르텔리</t>
+          <t>코라도 크리벨리 장군</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>팔레르모 법대생, 반마피아위원회 연수생 → 총리실 차관(sottosegretaria alla Presidenza) → 후계자</t>
+          <t>가상 정보기관 '국가안보중앙국(UCSN)' 부국장, 에르메테 로지와 닿아 있는 일탈 정보라인의 설계자</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>4부 6화 합류 → 6부 6화 테러로 중상 → 7부 8화 알레시오와 정면 대결 → 8부 6화 실권 위임 → 9부 11화 총리 선서</t>
+          <t>2부 8화 거래 제안 → 4부 9화 로지를 거스름 → 5부 9화 사임 → 8부 9화 신상 파일망을 다시 짜 달라는 알레시오를 거절('나는 40년 걸렸는데 당신은 3년이군') → 9부 9화 조용히 사망, 불법 감청 지시 목록이 든 봉투를 엘레나 사르토리에게 남김</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr"/>
@@ -4798,27 +4818,27 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>카탸(참모)</t>
+          <t>이리나(후계자)</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Caterina "Rina" Lisi</t>
+          <t>Irene Martelli</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>카테리나 '리나' 리시</t>
+          <t>이레네 마르텔리</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>토레네라 검찰청 사법경찰 수사관 출신 실무 동지(은행 기록 분석) → 선거본부장 → 총리실 비서실장</t>
+          <t>팔레르모 법대생, 반마피아위원회 연수생 → 총리실 차관 → 사임 후 변호사이자 합법적 반대의 얼굴 → 총리</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>끝까지 남아 7부 8화에서 처음으로 공개 반대, 에필로그에서도 제도 안에 남음</t>
+          <t>4부 6화 합류 → 6부 6화 당대회장 폭탄으로 중상 → 7부 8화 정면 대결, 7부 12화 사임 → 8부 10화 구금된 기자 루치아의 변호인으로 굽는 법원에 지지만 킨키나투스와 가리발디로 응수 → 9부 2화 다른 판사를 통해 위헌 심판 제청 → 9부 10화 헌재 결정 → 10부 7화 재건된 총선에서 승리해 총리 선서 → 10부 12화 알레시오의 장례를 국장이 아닌 가족장으로 치르되 조문 행렬을 막지 않음 → 에필로그 재판에 일절 논평하지 않음</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr"/>
@@ -4826,27 +4846,27 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>그레벤시코프(원로)</t>
+          <t>카탸(참모)</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Ettore Grimaldi</t>
+          <t>Caterina "Rina" Lisi</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>에토레 그리말디</t>
+          <t>카테리나 '리나' 리시</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>노(老)상원의원, 알레시오를 정치로 이끄는 현실주의 전략가</t>
+          <t>토레네라 검찰청 사법경찰 수사관 출신 실무 동지(은행 기록 분석) → 선거본부장 → 총리실 비서실장</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>3부 12화 첫 등장 → 7부 스스로의 변질을 자각 → 8부 폭로 자료(도시에) 사용을 포기하며 '작은 망치'로 남음</t>
+          <t>7부 7화 첫 반대, 7부 8화 이레네와 함께 대결하지만 '안에서 막겠다'며 남음 → 8부 비서실장으로 모든 구두 지시를 기록 → 9부 12화 그 기록을 의회 정보위원회(COPASIR)에 내겠다고 알레시오에게 먼저 알리고 커피를 놓고 나감 → 10부 5화 사임 연설문 초안을 함께 씀 → 에필로그 검찰 측 증인</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr"/>
@@ -4854,27 +4874,27 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>이졸다·키릴(감사팀)</t>
+          <t>그레벤시코프(원로)</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Iolanda Sacchi / Carlo Ardenghi (Nora Ardenghi, Beniamino Stresa)</t>
+          <t>Ettore Grimaldi</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>욜란다 사키 / 카를로 아르뎅기 (노라 아르뎅기, 베니아미노 스트레사)</t>
+          <t>에토레 그리말디</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>6인 민간 감사사 «Bussola Revisioni»: 경력 30년 수석 감사역 욜란다(«Trent'anni di mestiere…», 부부를 'ragazzi', 'piccioncini'라 부름), 원칙주의자 카를로와 현실주의자 아내 노라, 포렌식 회계사 베니아미노. 5부부터 '국가재정투명성청'</t>
+          <t>노(老)상원의원, 알레시오를 정치로 이끄는 현실주의 전략가</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>4부 5화 반마피아위원회 자금 추적 자문으로 첫 등장 → 욜란다는 6부 6화 당대회장 폭탄으로 사망 → 카를로는 8부 8화 헌법재판소 증언 직후 심장질환으로 사망</t>
+          <t>3부 12화 첫 등장 → 7부 11화 개헌안에 반대표, 당에서 축출 → 9부 11화 불신임 동의안을 들고 총리실에 와서 '내가 당신을 여기로 데려왔으니 내가 내보내겠다' → 알레시오의 사임으로 동의안은 표결되지 않음 → 10부 12화 운구를 멤</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr"/>
@@ -4882,27 +4902,27 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>조야(스승의 벗)</t>
+          <t>이졸다·키릴(감사팀)</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Zita Pellegrino</t>
+          <t>Iolanda Sacchi / Carlo Ardenghi (Nora Ardenghi, Beniamino Stresa)</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>지타 펠레그리노</t>
+          <t>욜란다 사키 / 카를로 아르뎅기 (노라 아르뎅기, 베니아미노 스트레사)</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>벨란디의 40년 동반자, 은퇴한 법원 서기. 그의 수첩(agende)을 간직</t>
+          <t>6인 민간 감사사 «Bussola Revisioni»: 경력 30년 수석 감사역 욜란다(«Trent'anni di mestiere…», 부부를 'ragazzi', 'piccioncini'라 부름), 원칙주의자 카를로와 현실주의자 아내 노라, 포렌식 회계사 베니아미노. 5부부터 '국가재정투명성청'</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>7부 9화 벨란디의 수첩을 건넴, 에필로그 선서식 셋째 줄</t>
+          <t>욜란다는 6부 6화 당대회장 폭탄으로 사망 → 7부 6화 노라가 민방위 조달 감사 발표 연기 부탁을 거절하고 «Bussola»·투명성청 계약이 끊김 → 카를로는 9부 5화 헌법재판소 전문가 청문에서 비상 지출·스파이웨어 계약 자료와 12년 전 자기 과오를 증언한 직후 심장질환으로 사망 → 노라와 베니아미노의 자료가 9부 10화 헌재 결정문의 근거로 남음</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr"/>
@@ -4910,27 +4930,27 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>마리나 젤레즈냐크(차차기)</t>
+          <t>조야(스승의 벗)</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Marina Ferlito</t>
+          <t>Zita Pellegrino</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>마리나 페를리토</t>
+          <t>지타 펠레그리노</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>가상 '레조네 요니카' 예산 담당 부지사(assessora al bilancio) 출신 내부고발자 → 투명성청 → 지역정책 담당</t>
+          <t>벨란디의 40년 동반자, 은퇴한 법원 서기. 그의 수첩(agende)을 간직</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>5부 4화 내부고발 → 8부 7화 레조네 요니카 주지사 당선 → 9부 9화 이레네 정부 총리실 차관 → 에필로그 총리 선서</t>
+          <t>7부 9화 벨란디의 수첩을 건네고, 알레시오가 마지막 장을 찢는 것을 보고 커피 없이 떠남 → 10부 2화 복사해 둔 그 장을 어머니 안나를 통해 돌려보냄 → 에필로그 이전 세상을 떠남, 사본은 증거로 채택</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr"/>
@@ -4938,27 +4958,27 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>보구슬랍스키(최종 자금원)</t>
+          <t>마리나 젤레즈냐크(차차기)</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Ottavio Brancati</t>
+          <t>Marina Ferlito</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>오타비오 브란카티</t>
+          <t>마리나 페를리토</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>전 경제부 차관, 에르메테 로지의 '재무관'. 3부 5화 압수된 로지 명단에 이름이 있었으나 기소를 피함. 파올로를 로지에 추천하고 '보안 컨설팅' 대금 전달을 맡긴 사람</t>
+          <t>가상 '레조네 요니카' 예산 담당 부지사 출신 내부고발자 → 주지사 → 이레네 정부 법무장관</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>5부 1화 «Fra un anno lei qui non ci sarà» → 8부 12화 파올로에게 동행을 권하며 해외 도피 → 9부 12화 파올로의 첫 진술과 장부로 테러·암살의 공통 자금원으로 특정, 신병 인도 요청 → 에필로그(2029) 인도되어 벙커 법정에서 파올로의 증언으로 두 자금책과 함께 종신형</t>
+          <t>5부 4화 내부고발 → 9부 2화 주지사로서 비상 총리령 적용을 거부하고 '제78조의2' 개헌의 핵심을 헌법재판소에 제소 → 9부 10화 위헌 결정 → 10부 7화 법무장관, 41-bis 남용 사례 재심사와 예방 감청 승인 절차 복원 → 에필로그 방청석이 아닌 장관실에서 판결 소식을 듣는다('정부는 법정에 앉지 않는다')</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr"/>
@@ -4966,27 +4986,27 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>코발추크(포퓰리스트 경쟁자)</t>
+          <t>보구슬랍스키(최종 자금원)</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Artemio Colasanti</t>
+          <t>Ottavio Brancati</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>아르테미오 콜라산티</t>
+          <t>오타비오 브란카티</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>포퓰리스트 운동 «Nuova Riscossa» 지도자. 첫 정부의 불편한 연정 파트너였다가 6부에 연정을 깨고 주적이 됨</t>
+          <t>전 경제부 차관, 에르메테 로지의 '재무관'. 3부 5화 압수된 로지 명단에 이름이 있었으나 기소를 피함. 파올로를 로지에 추천하고 '보안 컨설팅' 대금 전달을 맡긴 사람</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>6부 1화 연정 이탈 → 6부 패배 후 승복 → 9부 1화 제1야당 지도자로 재등장해 존중받는 경쟁자로</t>
+          <t>3부 로지 명단 → 5부 1화 '1년 뒤 당신은 없다' → 6부 당대회장 폭탄 자금원(파올로의 사본) → 7부 4화 알레시오가 그 증거를 금고에 넣고 기소 대신 약점으로 쥐어 로지의 신상 파일망과 조달망을 비상 정부에 쓰게 함 → 10부 8화 자백서에 모든 것이 적히자 니노 살레미에게 살해 자금을 댐 → 10부 12화 해외 도피, 인도 요청 → 에필로그 인도되어 당대회장 폭탄과 리날디 살해 자금으로 종신형</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr"/>
@@ -4994,585 +5014,589 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
+          <t>코발추크(포퓰리스트 경쟁자)</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>Artemio Colasanti</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>아르테미오 콜라산티</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>포퓰리스트 운동 «Nuova Riscossa» 지도자. 첫 정부의 불편한 연정 파트너였다가 6부에 연정을 깨고 주적이 됨</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>6부 1화 연정 이탈, 6부 12화 패배 승복 → 7부 11화 공포에 질린 야당의 얼굴로 개헌안에 찬성 → 9부 4화 입법기 연장 앞에서 등을 돌림 → 9부 11화 불신임 동의 연서</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
           <t>라디셰프(유혹의 목소리)</t>
         </is>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>Rodolfo Radice</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>로돌포 라디체</t>
         </is>
       </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>내무장관, 강경파 '유혹의 목소리'</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>7부 3·8·10화 특별법 확대를 밀어붙이다 12화 의회 감독 아래 위기위원회 위원으로 묶임</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr"/>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>내무장관, 원래의 '유혹의 목소리'. 뒤집힌 판에서는 알레시오가 그를 앞질러 가며 오히려 그의 집행자가 됨</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>7부 3화 알레시오의 법령이 자기 안보다 넓어 놀람 → 8부 집행자 → 9부 11화 헌재 불복 법령과 구금 유지 명령서를 들고 옴 → 10부 4화 알레시오가 그것을 찢음 → 10부 6화 먼저 수사를 받자 모든 책임을 알레시오에게 돌림 → 에필로그 이전 불법 감청으로 별도 유죄</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>3. 부 구성</t>
-        </is>
-      </c>
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>신규(원작 8부 4화 청년 인재의 변형)</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>Elena Sartori</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>엘레나 사르토리</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>로마 검찰청의 젊은 검사(sostituto procuratore), 다비데의 옛 기록으로 수사를 배운 세대. 젊은 알레시오의 거울</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>8부 5화 승인 없는 스파이웨어 감청 수사 착수 → 비상 인사로 전보·감청당하고 CSM 청문에서 브루노의 말로 전해지는 문장을 인용 → 9부 8화 협력자 파올로를 받음 → 9부 9화 크리벨리의 봉투 → 10부 8화 알레시오의 자백서를 받음 → 에필로그(2029) 살해 사건 공소 검사로 키케로의 최후와 대비하는 논고</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>부</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>제목(한국어)</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>제목(현지어)</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>시기·주인공 신분</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>줄거리</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t>핵심 상실</t>
-        </is>
-      </c>
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>신규(8부 희생자)</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Lucia Ferrante / Rosa Ferrante</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>루치아 페란테 / 로사 페란테</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>키아라의 옛 인턴이던 «L'Osservatore Siculo» 기자(스물아홉), 살레미 41-bis 거래와 비상 조달을 추적. 로사는 그녀의 어머니, 토레네라의 초등교사</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>8부 4화 편집국의 자기검열과 감청 목록 → 8부 8화 파올로에게 논평을 청하러 감 → 8부 10화 '국가 비상 위해 인물'로 예방 구금, 판사가 구금을 승인 → 8부 11화 병원 이송이 '보안 절차'로 지연되어 구금 중 사망(알레시오가 서명한 위해 등급) → 로사는 9부 11화 키지궁 앞에 서고, 10부 1화 알레시오를 부엌에 들인다 → 에필로그 방청석 첫 줄</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>1부</t>
+          <t>신규(대통령)</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>법정의 각성</t>
+          <t>Presidente Angelo Berti</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Il risveglio in aula</t>
+          <t>안젤로 베르티 대통령(가상)</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>0년(2014) / 토레네라 지방검찰청 신참 검사</t>
+          <t>공화국 대통령(퀴리날레). 전직 헌법학자, 헌법이 비상조항을 두지 않은 이유를 가장 조용히 말하는 사람</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>[액자] 2029년, 파올로의 첫 증언 — '우리는 아홉 살부터 친구였습니다.' 석유화학 공장 폭발을 '인적 과실'로 덮으려는 시도에 맞서며 알레시오는 스승 벨란디에게서 검사의 의무를 배운다. 살레미 그룹과 일탈 정보라인이 드러나자 벨란디는 익명 투서로 고립되고 경호를 잃는다. 친구 시점에선 빚에 몰린 변호사 파올로가 살레미 그룹의 '작은 일'을 받으면서도 조작 문서를 알레시오에게 넘긴다.</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>스승 비토리오 벨란디 — 차량 폭탄</t>
-        </is>
-      </c>
+          <t>6부 12화 조각 위임 때 '헌법에는 공포를 위한 조항이 없다' → 7부 3화 서명 지연, 7부 6화 재발령 법령 거부, 7부 12화 개헌 공포와 함께 양원에 메시지 → 9부 7화 전쟁상태 선포 거부·임기 연장법 재의 요구 → 9부 11화 불복 법령 서명 거부, 최고국방회의 소집 → 10부 5화 사표 수리, 양원 해산</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2부</t>
+          <t>신규(제도의 얼굴)</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>대재판</t>
+          <t>gen. Lorenza Montalto</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Il maxiprocesso</t>
+          <t>로렌차 몬탈토 장군</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.5~2년(2014~16) / 지방반마피아검찰국(DDA) 풀의 검사</t>
+          <t>카라비니에리 사령관(Comandante generale dell'Arma)</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>[액자] '회개자의 은신처 주소를 누구에게 넘겼나.' 벨란디의 파일을 이어받은 알레시오는 선배 검사 다비데와 함께 살레미 가문의 회계사를 첫 회개자로 끌어내고, 피고인 300여 명의 대재판을 벙커 법정에 세운다. 회개자의 형제가 살해되고, 아녜세가 새 치안 법령으로 구속된다. 친구 시점에선 가문의 변호인이 된 파올로가 딸을 겨냥한 협박 앞에서 은신처를 흘린다. 판결은 가문을 무너뜨리지만 살레미 본인은 빠져나간다.</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>아녜세의 구속과 파올로의 배신(그리고 회개자의 형제)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>3부</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>돈을 따라가라</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>Segui il denaro</t>
-        </is>
-      </c>
-      <c r="D46" s="4" t="inlineStr">
-        <is>
-          <t>2~3년(2016~17) / 밀라노 파견 검사, 전국 반부패 수사의 얼굴</t>
-        </is>
-      </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>[액자] '에르메테 로지에 언제, 누구의 추천으로 가입했나.' 대재판의 돈줄을 따라 밀라노로 간 알레시오는 공공공사 담합과 정당 자금을 거쳐 비밀 로지 '에르메테'의 명단에 닿는다. 친구 시점에선 살레미 그룹 법률 대리인 파올로가 알레시오의 징계 청구서를 대필해 로지에 입회하고, 장부 확인을 청하러 온 키아라를 브란카티에게 보고한다. 키아라는 기사가 나간 날 사라지고, 알레시오는 법복을 벗는다.</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>연인 키아라 비탈레 — 실종</t>
-        </is>
-      </c>
+          <t>9부 6화 카를로의 장례 행렬 진압을 거부한 대위를 징계하라는 요구를 묵살 → 9부 11화 헌재 결정 뒤 구금 유지 명령을 '명백한 위법'이라며 서면으로 거부하고 대통령에게 보고</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>4부</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>신임</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>La fiducia</t>
-        </is>
-      </c>
-      <c r="D47" s="4" t="inlineStr">
-        <is>
-          <t>3~5년(2017~19) / 신생 정당 창당자 → 토레네라 소선거구 하원의원 → 반마피아위원회 위원장 → 조각 위임(총리)</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>[액자] '2017년 총선에서 표를 샀나.' '한 표에 50유로였습니다.' 원작의 선거 두 부를 하나로 압축한다. 총선에서 아버지를 잃고, 표 매수 기계를 돌리는 친구 파올로와 같은 선거구에서 맞붙은 끝에 하원에 들어간 알레시오는 반마피아위원회로 로지 명단을 의회에 올린다. 아녜세가 옥중에서 숨지고 정부가 무너지자 연정 협상과 신임투표로 총리가 되며, 면책을 조건으로 신임표를 흥정하러 온 파올로를 돌려보낸다.</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>아버지 니콜라와 아녜세 만쿠소</t>
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>3. 부 구성</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>5부</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>첫 정부</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>Il primo governo</t>
-        </is>
-      </c>
-      <c r="D48" s="4" t="inlineStr">
-        <is>
-          <t>5~6.5년(2019~20) / 총리(첫 정부)</t>
-        </is>
-      </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>[액자] '다비데 로카시오 검사의 살해를 미리 알았나.' 투명성·사법 개혁이 살레미 제국과 로지, 일탈 장교들의 반격을 부른다. 친구 시점에선 야당 의원 파올로가 개혁 저지에 앞장서다 다비데의 이름이 오가는 만찬에서 침묵하고, 살레미의 전용기에 오르지 않는다. 쿠데타 기도를 막고 개헌 패키지를 통과시킨 알레시오는 스스로 사임해 새 위임을 구하기로 한다.</t>
-        </is>
-      </c>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>동료 검사 다비데 로카시오 — 청부 총격</t>
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>부</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>제목(한국어)</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>제목(현지어)</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>시기·주인공 신분</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>줄거리</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>핵심 상실</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>6부</t>
+          <t>1부</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>두 번째 신임</t>
+          <t>법정의 각성</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>La seconda fiducia</t>
+          <t>Il risveglio in aula</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>6.5년(2020~21) / 사임 후 조기 총선을 치르는 총리</t>
+          <t>0년(2014) / 토레네라 지방검찰청 신참 검사</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>[액자] '카타니아 당대회 전 보안 컨설팅 대금을 누가 전달했나.' '제가 들고 갔습니다.' 연정 파트너 콜라산티가 이탈하며 딥페이크와 감사팀 흠집내기로 공세를 편다. 카타니아 당대회장이 폭탄에 무너져 욜란다를 잃고 이레네가 다친다. 친구 시점에선 자신이 나른 봉투가 폭탄 자금이었음을 안 파올로가 브란카티의 송금 기록을 몰래 복사하기 시작한다. 유세보다 의회 논쟁과 연정 재구성으로 두 번째 신임을 얻는다.</t>
+          <t>[액자] 2029년 토레네라 벙커 법정, 파올로의 첫 증언 — '리날디를 아홉 살부터 알았습니다.' 카메라는 피고인석을 비추지 않는다. 석유화학 공장 폭발을 덮으려는 시도에 맞서며 알레시오는 스승 벨란디에게서 검사의 의무와 베카리아를, 그리고 영장 없는 '귀동냥'이라는 회색 방법도 배운다. 친구 시점에선 빚에 몰린 변호사 파올로가 살레미 그룹의 '작은 일'을 받으면서도 조작 문서를 알레시오에게 넘긴다.</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>감사역 욜란다 사키 — 당대회장 폭탄</t>
+          <t>스승 비토리오 벨란디 — 차량 폭탄</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>7부</t>
+          <t>2부</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>비상의 유혹</t>
+          <t>대재판</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>La tentazione dell'emergenza</t>
+          <t>Il maxiprocesso</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>6.6~7.1년(2021) / 총리(두 번째 정부 초기)</t>
+          <t>0.5~2년(2014~16) / 지방반마피아검찰국(DDA) 풀의 검사</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>[액자] '2021년 선거 연기안은 누구의 생각이었나.' 새로운 '폭탄의 계절'과 스프레드 공격 속에서 특별법을 야당과 언론으로 넓히라는 유혹이 한 단계씩 다가온다. 스파이웨어 감청이라는 작은 월권을 저지른 알레시오는 이레네와 벨란디의 수첩 앞에서 멈추고 스스로 권력을 묶는다. 친구 시점에선 로지의 선거 연기안을 장관에게 건넨 파올로가, 가장 큰 폭탄의 밤 공중전화로 익명 제보를 해 처음으로 돌아선다.</t>
+          <t>[액자] '회개자의 은신처 주소를 누구에게 넘겼나 — 리날디는 알았나.' '알았습니다. 그때는 용서하지 않았죠.' 벨란디의 파일을 이어받은 알레시오는 선배 검사 다비데와 함께 살레미 가문의 회계사를 첫 회개자로 끌어내고, 피고인 300여 명의 대재판을 벙커 법정에 세운다. 회개자의 형제가 살해되고, 아녜세가 새 치안 법령으로 구속된다. 친구 시점에선 가문의 변호인이 된 파올로가 딸을 겨냥한 협박 앞에서 은신처를 흘린다. 판결은 가문을 무너뜨리지만 살레미 본인은 빠져나간다. 알레시오의 '나는 안다'는 확신이 처음 드러난다.</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>사람이 아니라 주인공의 원칙이 깎여 나감(그리고 되찾음)</t>
+          <t>아녜세의 구속과 파올로의 배신(그리고 회개자의 형제)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>8부</t>
+          <t>3부</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>권력의 무게</t>
+          <t>돈을 따라가라</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Il peso del potere</t>
+          <t>Segui il denaro</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>7.2~8.5년(2021~22) / 총리(두 번째 정부 1~2년차)</t>
+          <t>2~3년(2016~17) / 밀라노 파견 검사, 전국 반부패 수사의 얼굴</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>[액자] '브란카티가 출국하던 날 당신은 어디 있었나.' 「권력의 한계」 법으로 총리 권한 자체를 줄이고 이레네에게 실권을 넘기는 사이, 카를로가 헌재 증언 직후 쓰러진다. 친구 시점에선 파올로가 버려진 회개자의 가족을 찾아가 증인의 삶을 보고, 해외로 달아나는 브란카티의 동행 제안을 거절한 채 장부 사본을 숨긴다.</t>
+          <t>[액자] '로지의 방법 — 신상 파일과 감청 — 을 리날디에게 가르친 게 당신인가?' '그때 그는 그걸 증오했습니다.' 대재판의 돈줄을 따라 밀라노로 간 알레시오는 공공공사 담합과 정당 자금을 거쳐 비밀 로지 '에르메테'의 명단에 닿는다. 친구 시점에선 살레미 그룹 법률 대리인 파올로가 알레시오의 징계 청구서를 대필해 로지에 입회하고, 장부 확인을 청하러 온 키아라를 브란카티에게 보고한다. 키아라는 기사가 나간 날 사라지고, 알레시오는 법복을 벗는다.</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>카를로 아르뎅기 — 심장질환</t>
+          <t>연인 키아라 비탈레 — 실종</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>9부</t>
+          <t>4부</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>홀로 선 자리</t>
+          <t>신임</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Il posto dove si sta da soli</t>
+          <t>La fiducia</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>9.5~10.5년(2024~25), 에필로그 ≈2029년 / 마지막 해의 총리 → 퇴임</t>
+          <t>3~5년(2017~19) / 신생 정당 창당자 → 토레네라 소선거구 하원의원 → 반마피아위원회 위원장 → 조각 위임(총리)</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>[액자] '리날디 총리 저격 사흘 전 무엇을 알았나.' 스스로 정한 두 번의 입법기가 끝나 가고 이레네가 후계자로 선다. 친구 시점에선 저격 계획을 들은 파올로가 10년 만에 찾아와 경고하지만 알레시오는 경호 강화를 거절하고, 퇴임 전날 강변에서 저격당한다. 이레네가 예정대로 선서한 이튿날 파올로는 자수해 협력자가 되고, 에필로그(2029)에서 그의 증언이 자금원들의 유죄를 결정한다.</t>
+          <t>[액자] '2017년 총선에서 표를 샀나.' '한 표에 50유로였습니다.' '리날디는 왜 당신을 고발하지 않았나.' 원작의 선거 두 부를 하나로 압축한다. 총선에서 아버지를 잃고, 표 매수 기계를 돌리는 친구 파올로와 같은 선거구에서 맞붙은 끝에 하원에 들어간 알레시오는 반마피아위원회로 로지 명단을 의회에 올린다. 아녜세가 옥중에서 숨지고 정부가 무너지자 연정 협상과 신임투표로 총리가 되며, 면책을 조건으로 신임표를 흥정하러 온 파올로를 돌려보낸다.</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>주인공 알레시오 리날디 — 저격 (살아남은 파올로는 이름과 가족을 잃는다)</t>
+          <t>아버지 니콜라와 아녜세 만쿠소</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>5부</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>첫 정부</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>Il primo governo</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>5~6.5년(2019~20) / 총리(첫 정부)</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>[액자] '다비데 로카시오의 살해를 미리 알았나.' 변호인: '살인을 알고도 침묵한 증인의 말로 누구를 단죄하겠다는 건가.' 파올로: '그를 단죄하는 건 제 말이 아닐 겁니다. 그 자신의 말이죠.' 투명성·사법 개혁이 살레미 제국과 로지, 일탈 장교들의 반격을 부른다. 친구 시점에선 파올로가 다비데의 이름이 오가는 만찬에서 침묵하고, 살레미의 전용기에 오르지 않는다. 쿠데타의 밤 영장 없이 장군들을 구금하자던 알레시오는 법무장관에게 막히지만, 개헌 패키지에 스스로 '연속 두 입법기' 한계를 넣고 킨키나투스를 인용하며 사임해 새 위임을 구한다.</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>동료 검사 다비데 로카시오 — 청부 총격</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>4. 화별 구성</t>
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>6부</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>공포의 신임</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>La fiducia della paura</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>6.5년(2020~21) / 사임 후 조기 총선을 치르는 총리 → 두 번째 조각</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>[액자] '카타니아 당대회 전 대금을 누가 전달했나.' '제가 들고 갔습니다.' '그 사실을 리날디에게 언제 말했나.' '2021년 7월. 그는 그걸 검찰에 넘기지 않았습니다.' 방청석이 술렁인다. 콜라산티가 연정을 깨고, 카타니아 당대회장 폭탄에 욜란다가 죽고 이레네가 다친다. 병실에서 알레시오는 처음으로 '절차는 사치'라고 말하고, 하원에서 키케로의 «Salus populi suprema lex esto»를 내건다. 친구 시점에선 자신이 나른 봉투가 폭탄 자금이었음을 안 파올로가 브란카티의 송금 기록을 복사한다. 그는 공포 위에서 압승하고, 대통령은 조각을 맡기며 '헌법에는 공포를 위한 조항이 없다'고 말한다.</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>감사역 욜란다 사키 — 당대회장 폭탄 (그리고 주인공의 절차에 대한 믿음)</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>부·화</t>
-        </is>
-      </c>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>제목(한국어)</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>제목(현지어)</t>
-        </is>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>대응 원작 화</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="inlineStr">
-        <is>
-          <t>한 줄 줄거리</t>
-        </is>
-      </c>
-      <c r="F55" s="3" t="inlineStr"/>
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>7부</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>비상</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>L'emergenza</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>6.6~8년(2021~22) / 총리(두 번째 정부) — 비상대권을 쌓아 가는 총리</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>[액자] 재판장이 공소 사실을 읽는다 — '2026년 3월 토레네라에서 전 총리 알레시오 리날디를 살해한 혐의.' 카메라가 처음 피고인석을 비춘다: 실행범과 조직자, 니노 살레미. 그는 피고인이 아니라 피해자였다. 피고인 측 변호인: '비상 법령 초안은 누가 썼나.' '그가 불렀고 제가 쳤습니다.' '그러니까 괴물은 리날디였다는 거군요.' 새 폭탄의 계절에 알레시오는 긴급 법령과 신임 문제를 잇달아 걸고, 가뭄 민방위 비상사태를 치안으로 늘여 총리령으로 다스리며 거리에 군을 늘린다. 실효된 법령을 다시 내려다 대통령에게 막히자 국민에게 호소하고, 승인 없는 스파이웨어 감청이라는 첫걸음을 내디딘다. 벨란디의 수첩에서 회색 방법만 읽고 경고의 장을 찢은 그는 루비콘을 인용하며 '제78조의2(국가 비상사태)' 개헌을 밀어붙이고, 상원에서 몇 표가 모자라자 국민투표에서 이긴다. 친구 시점에선 10년 만에 부름을 받은 파올로가 폭탄 자금 사본을 건네며 그의 사람이 되고, 알레시오는 그 증거를 금고에 넣는다. 이레네는 사임한다.</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>주인공의 원칙 — 되찾지 못함 (그리고 이레네와 지타)</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>1부 1화</t>
+          <t>8부</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>첫 사건</t>
+          <t>정지된 공화국</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Il primo fascicolo</t>
+          <t>La Repubblica sospesa</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>1부 1화 변형</t>
+          <t>8~9년(2022~23) / 비상대권의 총리 — 남의 눈으로만 보이는 사람</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>[2029 법정] 스크린 뒤의 협력자 파올로가 '리날디를 언제부터 알았나'에 답한다. 2014년 공장 폭발로 셋이 죽고, 벨란디가 모카 커피를 내며 알레시오에게 첫 수사를 맡긴다.</t>
-        </is>
-      </c>
-      <c r="F56" s="4" t="inlineStr"/>
+          <t>[액자] '비상 체제에서 당신의 직함은 무엇이었나.' '없었습니다. 그게 제 직함이었죠.' 한 부 전체가 체제 아래의 삶이다: 검문소에 선 토레네라 출신 병사, 자기검열하는 편집국, 전보되고 감청당한 젊은 검사 엘레나, 예방 조치로 바다에서 쫓겨난 구조선 선장, '마피아 침투'로 해산된 고향 의회와 밀고자, 구금을 승인하는 판사, 수의계약으로 조용히 이득을 보는 살레미 잔당. 알레시오는 대부분 포스터와 화면, 남의 입으로만 등장하고, 크리벨리 앞에서 마키아벨리를 인용한다. 친구 시점에선 해결사 파올로가 41-bis 거래를 중개하고, 키아라 때처럼 취재하러 온 기자 루치아를 총리실에 보고한다. 루치아는 그의 서명 아래 구금되어 병원 이송이 지연된 채 숨지고 — 아녜세를 죽인 체제가 그 자신이 된다. 6월 10일 이레네가 광장에서 마테오티를 낭독하는 날, 살레미는 병원 가택연금으로 옮겨진다.</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>기자 루치아 페란테 — 그의 서명 아래 구금 중 사망</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>1부 2화</t>
+          <t>9부</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>스승과 제자</t>
+          <t>괴물</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Il maestro e l'allievo</t>
+          <t>Il mostro</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>1부 2화</t>
+          <t>9~10년(2023~24) / 비상대권의 정점에 선 총리</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>목격자 설득에 나선 알레시오는 벨란디가 1993년 부실 콘크리트 사건으로 전보당한 과거를 지타에게서 듣는다.</t>
-        </is>
-      </c>
-      <c r="F57" s="4" t="inlineStr"/>
+          <t>[액자] '2024년 11월 그 밤, 리날디는 헌재 결정에 불복하려 했나.' '했습니다. 그리고 하지 않았습니다.' 입법기 끝이 다가오자 알레시오는 '외국 자금의 하이브리드 전쟁'을 명분으로 제78조 전쟁상태 의결과 제60조 입법기 연장을 노린다. 제도가 차례로 선다: 판사의 위헌 제청과 마리나의 헌재 제소, 헌재 청문에서 증언한 뒤 숨진 카를로, 장례 행렬 진압을 거부한 카라비니에리, 전쟁상태 선포를 거부한 대통령, 그리고 비상 개헌의 핵심을 '최고 원리' 위반으로 무효화한 헌법재판소. 친구 시점에선 파올로가 전쟁 초안을 받아 치다 벨란디의 베카리아를 챙기고, 두 번째 장부를 들고 협력자가 된다. 결정의 밤, 라디체가 불복 법령과 구금 유지 명령서를 가져오고, 사령관은 서면으로 거부하며, 대통령은 서명하지 않고, 그리말디는 불신임 동의안을 들고 온다. 새벽, 펜은 아직 그의 손에 있다.</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>카를로 아르뎅기 — 헌재 청문 후 심장질환 (그리고 친구 파올로, 연정, 고향)</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>1부 3화</t>
+          <t>10부</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>회색지대</t>
+          <t>돌아오는 길</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>La zona grigia</t>
+          <t>La via del ritorno</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>1부 3화 변형</t>
+          <t>10~11.5년(2024~26), 에필로그 ≈2029년 / 비상대권의 총리 → 사임 → 자백한 전 총리 → 피살</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>(친구 시점) 빚에 몰린 변호사 파올로가 살레미 그룹 농장 피해자 합의금 배분이라는 '작은 일'을 받는다. 같은 날 알레시오는 로마 요직 제안을 거절한다.</t>
-        </is>
-      </c>
-      <c r="F58" s="4" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="4" t="inlineStr">
-        <is>
-          <t>1부 4화</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t>첫 협박</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t>La prima intimidazione</t>
-        </is>
-      </c>
-      <c r="D59" s="4" t="inlineStr">
-        <is>
-          <t>1부 4화</t>
-        </is>
-      </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>부모 집 문 앞에 불탄 자동차와 양 머리가 놓인다. 아버지 니콜라는 '이 도시는 못 이긴다'며 아들을 말린다.</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="inlineStr"/>
+          <t>[액자] 파올로에게 봉인된 봉투가 건네진다 — 리날디가 죽기 전 검찰에 맡긴 자백서. 결정의 새벽, 알레시오는 경호를 물리고 루치아의 어머니 부엌으로 가 처음으로 먼저 커피를 끓이겠다고 청하고, 어머니 안나는 벨란디의 찢긴 장을 식탁에 놓는다. 그는 불복 법령을 찢고 헌재 결정을 이행한 뒤 하원에서 책임을 인정하고 사임한다. 재건된 총선에서 이레네가 이기고, 그는 면책을 내려놓고 비상 시절 살레미 잔당·로지와의 거래까지 적은 자백서를 엘레나에게 맡긴다. 토레네라에서 사과하고 다시 먼저 커피를 내는 짧은 계절 — 파올로의 경고에 이번엔 경호를 받아들이지만, 증언대에 서기 전날 항구의 바에서 살레미 잔당의 총에 쓰러진다. 자백서는 남는다.</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>주인공 알레시오 리날디 — 권력을 내려놓고 진실을 말하려다 피살 (살아남은 파올로는 이름과 가족을 잃는다)</t>
+        </is>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="inlineStr">
-        <is>
-          <t>1부 5화</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="inlineStr">
-        <is>
-          <t>작은 승리</t>
-        </is>
-      </c>
-      <c r="C60" s="4" t="inlineStr">
-        <is>
-          <t>Una piccola vittoria</t>
-        </is>
-      </c>
-      <c r="D60" s="4" t="inlineStr">
-        <is>
-          <t>1부 5화</t>
-        </is>
-      </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>밭에 독성 폐기물을 묻은 업자가 유죄 판결을 받는다. 법정에서 알레시오는 기자 키아라와 처음 마주친다.</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="inlineStr"/>
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>4. 화별 구성</t>
+        </is>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="inlineStr">
-        <is>
-          <t>1부 6화</t>
-        </is>
-      </c>
-      <c r="B61" s="4" t="inlineStr">
-        <is>
-          <t>키아라와의 인연</t>
-        </is>
-      </c>
-      <c r="C61" s="4" t="inlineStr">
-        <is>
-          <t>Il patto con Chiara</t>
-        </is>
-      </c>
-      <c r="D61" s="4" t="inlineStr">
-        <is>
-          <t>1부 6화</t>
-        </is>
-      </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>키아라가 공장 점검 기록의 공백을 들고 정보 교환을 제안한다. 번호판 없는 차가 두 사람을 따라붙는다.</t>
-        </is>
-      </c>
-      <c r="F61" s="4" t="inlineStr"/>
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>부·화</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>제목(한국어)</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>제목(현지어)</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>대응 원작 화</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>한 줄 줄거리</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>1부 7화</t>
+          <t>1부 1화</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>아녜세의 등장</t>
+          <t>첫 사건</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Arriva Agnese</t>
+          <t>Il primo fascicolo</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>1부 7화</t>
+          <t>1부 1화 변형</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>해협 대교 진입로 공사로 삶터를 잃게 된 어촌을 찾은 알레시오는 몰수 토지 협동조합의 아녜세와 만난다.</t>
+          <t>[2029 법정] 토레네라 벙커 법정, 스크린 뒤의 협력자 파올로에게 검사가 묻는다. '리날디를 언제부터 알았나.' '아홉 살부터요.' 카메라는 피고인석을 비추지 않는다. 2014년 공장 폭발로 셋이 죽고, 벨란디가 모카 커피를 내며 알레시오에게 첫 수사를 맡긴다.</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr"/>
@@ -5580,27 +5604,27 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>1부 8화</t>
+          <t>1부 2화</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>크리벨리의 그림자</t>
+          <t>스승과 제자</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>L'ombra di Crivelli</t>
+          <t>Il maestro e l'allievo</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>1부 8화</t>
+          <t>1부 2화</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>세 사건이 한 줄로 이어질 무렵, 정보기관 부국장 크리벨리가 벨란디를 조용히 불러 '국익'을 말한다.</t>
+          <t>벨란디가 밑줄 친 베카리아 『범죄와 형벌』을 건넨다 — '형벌의 잔혹함이 아니라 확실함.' 목격자 설득에 나선 알레시오는 벨란디가 1993년 전보당한 과거를 지타에게서 듣는다.</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr"/>
@@ -5608,27 +5632,27 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>1부 9화</t>
+          <t>1부 3화</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>까마귀</t>
+          <t>회색지대</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Il corvo</t>
+          <t>La zona grigia</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>1부 9화 변형</t>
+          <t>1부 3화 변형</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>벨란디를 겨냥한 익명 투서가 최고사법위원회로 날아들고, 그의 경호가 '위험 등급 하향'으로 해제된다.</t>
+          <t>(친구 시점) 빚에 몰린 변호사 파올로가 살레미 그룹 농장 피해자 합의금 배분이라는 '작은 일'을 받는다. 같은 날 알레시오는 로마 요직 제안을 거절한다.</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr"/>
@@ -5636,27 +5660,27 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>1부 10화</t>
+          <t>1부 4화</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>조작된 문서</t>
+          <t>첫 협박</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Il dossier fabbricato</t>
+          <t>La prima intimidazione</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>1부 10화 변형</t>
+          <t>1부 4화</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>(친구 시점) 파올로는 의뢰인 서류 더미에서 가짜 진술 문서의 원본을 발견하고, 고객을 잃을 각오로 알레시오에게 넘긴다. 두 친구의 마지막 떳떳한 밤.</t>
+          <t>부모 집 문 앞에 불탄 자동차와 양 머리가 놓인다. 아버지 니콜라는 '이 도시는 못 이긴다'며 아들을 말린다.</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr"/>
@@ -5664,27 +5688,27 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>1부 11화</t>
+          <t>1부 5화</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>벨란디의 죽음</t>
+          <t>작은 승리</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>La morte di Bellandi</t>
+          <t>Una piccola vittoria</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>1부 11화 변형</t>
+          <t>1부 5화</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>경호 없이 퇴근하던 벨란디의 차가 해안도로에서 폭발한다. 모카포트만 사무실에 식은 채 남는다.</t>
+          <t>밭에 독성 폐기물을 묻은 업자가 유죄 판결을 받는다. 법정에서 알레시오는 기자 키아라와 처음 마주친다.</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr"/>
@@ -5692,223 +5716,223 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
+          <t>1부 6화</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>키아라와의 인연</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>Il patto con Chiara</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>1부 6화</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>키아라가 공장 점검 기록의 공백을 들고 정보 교환을 제안한다. 번호판 없는 차가 두 사람을 따라붙는다.</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>1부 7화</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>아녜세의 등장</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>Arriva Agnese</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>1부 7화</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>해협 대교 진입로 공사로 삶터를 잃게 된 어촌을 찾은 알레시오는 몰수 토지 협동조합의 아녜세와 만난다.</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>1부 8화</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>크리벨리의 그림자</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>L'ombra di Crivelli</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>1부 8화</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>크리벨리가 벨란디를 불러 '국익'을 말한다. 그날 밤 벨란디는 친한 카라비니에리에게 영장 없는 '귀동냥'을 부탁하고, 알레시오는 보고도 묻지 않는다. «La legge arriva tardi; noi no.»</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>1부 9화</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>까마귀</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>Il corvo</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>1부 9화 변형</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>벨란디를 겨냥한 익명 투서가 최고사법위원회로 날아들고, 그의 경호가 '위험 등급 하향'으로 해제된다.</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>1부 10화</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>조작된 문서</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>Il dossier fabbricato</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>1부 10화 변형</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>(친구 시점) 파올로는 의뢰인 서류 더미에서 가짜 진술 문서의 원본을 발견하고, 고객을 잃을 각오로 알레시오에게 넘긴다. 두 친구의 마지막 떳떳한 밤.</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>1부 11화</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>벨란디의 죽음</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>La morte di Bellandi</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>1부 11화 변형</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>경호 없이 퇴근하던 벨란디의 차가 해안도로에서 폭발한다. 모카포트만 사무실에 식은 채 남는다.</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
           <t>1부 12화</t>
         </is>
       </c>
-      <c r="B67" s="4" t="inlineStr">
+      <c r="B73" s="4" t="inlineStr">
         <is>
           <t>결심</t>
         </is>
       </c>
-      <c r="C67" s="4" t="inlineStr">
+      <c r="C73" s="4" t="inlineStr">
         <is>
           <t>La decisione</t>
         </is>
       </c>
-      <c r="D67" s="4" t="inlineStr">
+      <c r="D73" s="4" t="inlineStr">
         <is>
           <t>1부 12화</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>장례식에 그가 도운 사람들이 모여든다. 알레시오는 무심코 조문객에게 커피부터 내고, 끝까지 가겠다고 맹세한다.</t>
-        </is>
-      </c>
-      <c r="F67" s="4" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="9" t="inlineStr">
-        <is>
-          <t>2부 1화</t>
-        </is>
-      </c>
-      <c r="B68" s="9" t="inlineStr">
-        <is>
-          <t>풀</t>
-        </is>
-      </c>
-      <c r="C68" s="9" t="inlineStr">
-        <is>
-          <t>Il pool</t>
-        </is>
-      </c>
-      <c r="D68" s="9" t="inlineStr">
-        <is>
-          <t>2부 1화 변형</t>
-        </is>
-      </c>
-      <c r="E68" s="9" t="inlineStr">
-        <is>
-          <t>[2029 법정] '회개자의 은신처 주소를 누구에게 넘겼나.' 파올로가 눈을 감는다. 2014년 가을, 알레시오는 반마피아검찰국 풀에서 선배 검사 다비데와 벨란디의 파일 상자를 연다.</t>
-        </is>
-      </c>
-      <c r="F68" s="9" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="9" t="inlineStr">
-        <is>
-          <t>2부 2화</t>
-        </is>
-      </c>
-      <c r="B69" s="9" t="inlineStr">
-        <is>
-          <t>첫 회개자</t>
-        </is>
-      </c>
-      <c r="C69" s="9" t="inlineStr">
-        <is>
-          <t>Il primo pentito</t>
-        </is>
-      </c>
-      <c r="D69" s="9" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="E69" s="9" t="inlineStr">
-        <is>
-          <t>살레미 가문의 장부를 맡던 회계사가 협력을 제안한다. 알레시오는 밤새 그의 진술과 거짓을 가려낸다.</t>
-        </is>
-      </c>
-      <c r="F69" s="9" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="9" t="inlineStr">
-        <is>
-          <t>2부 3화</t>
-        </is>
-      </c>
-      <c r="B70" s="9" t="inlineStr">
-        <is>
-          <t>돈의 유혹</t>
-        </is>
-      </c>
-      <c r="C70" s="9" t="inlineStr">
-        <is>
-          <t>La tentazione del denaro</t>
-        </is>
-      </c>
-      <c r="D70" s="9" t="inlineStr">
-        <is>
-          <t>2부 2화 변형</t>
-        </is>
-      </c>
-      <c r="E70" s="9" t="inlineStr">
-        <is>
-          <t>정체불명 재단이 «Luce»에 거액을 제안한다. 회개자의 장부에서 리나가 그 재단의 이름을 찾아낸다.</t>
-        </is>
-      </c>
-      <c r="F70" s="9" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="9" t="inlineStr">
-        <is>
-          <t>2부 4화</t>
-        </is>
-      </c>
-      <c r="B71" s="9" t="inlineStr">
-        <is>
-          <t>벙커 법정</t>
-        </is>
-      </c>
-      <c r="C71" s="9" t="inlineStr">
-        <is>
-          <t>L'aula bunker</t>
-        </is>
-      </c>
-      <c r="D71" s="9" t="inlineStr">
-        <is>
-          <t>2부 3화 확장</t>
-        </is>
-      </c>
-      <c r="E71" s="9" t="inlineStr">
-        <is>
-          <t>피고인 300여 명을 세울 벙커 법정이 교도소 옆에 지어진다. 대재판을 취재하던 키아라와 알레시오가 가까워진다.</t>
-        </is>
-      </c>
-      <c r="F71" s="9" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="9" t="inlineStr">
-        <is>
-          <t>2부 5화</t>
-        </is>
-      </c>
-      <c r="B72" s="9" t="inlineStr">
-        <is>
-          <t>회개자의 가족</t>
-        </is>
-      </c>
-      <c r="C72" s="9" t="inlineStr">
-        <is>
-          <t>La famiglia del pentito</t>
-        </is>
-      </c>
-      <c r="D72" s="9" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="E72" s="9" t="inlineStr">
-        <is>
-          <t>회개자의 형이 살해되는 '가로지르는 보복'이 일어난다. 흔들리는 그에게 알레시오는 먼저 커피를 낸다.</t>
-        </is>
-      </c>
-      <c r="F72" s="9" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="9" t="inlineStr">
-        <is>
-          <t>2부 6화</t>
-        </is>
-      </c>
-      <c r="B73" s="9" t="inlineStr">
-        <is>
-          <t>파올로의 균열</t>
-        </is>
-      </c>
-      <c r="C73" s="9" t="inlineStr">
-        <is>
-          <t>La crepa di Paolo</t>
-        </is>
-      </c>
-      <c r="D73" s="9" t="inlineStr">
-        <is>
-          <t>2부 5화 변형</t>
-        </is>
-      </c>
-      <c r="E73" s="9" t="inlineStr">
-        <is>
-          <t>(친구 시점) 파올로가 살레미 가문 간부의 변호를 맡는다. 사무실 빚을 갚아 주겠다는 조건, 그리고 딸의 학교 이름을 알고 있는 의뢰인.</t>
-        </is>
-      </c>
-      <c r="F73" s="9" t="inlineStr"/>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>장례식에 그가 도운 사람들이 모여든다. 알레시오는 무심코 조문객에게 커피부터 내고, 팔코네의 말로 전해지는 '사람은 가도 생각은 남는다'를 되뇌며 끝까지 가겠다고 맹세한다.</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="9" t="inlineStr">
         <is>
-          <t>2부 7화</t>
+          <t>2부 1화</t>
         </is>
       </c>
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t>아녜세의 구속</t>
+          <t>풀</t>
         </is>
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>L'arresto di Agnese</t>
+          <t>Il pool</t>
         </is>
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>2부 6화</t>
+          <t>2부 1화 변형</t>
         </is>
       </c>
       <c r="E74" s="9" t="inlineStr">
         <is>
-          <t>대교 진입로 공사장을 몸으로 막아선 아녜세가 새 치안 법령의 '도로 봉쇄죄'로 구속된다. 재판 원고석이 빈다.</t>
+          <t>[2029 법정] '회개자의 은신처 주소를 누구에게 넘겼나 — 리날디는 그걸 알았나.' '알았습니다. 그때는 용서하지 않았죠.' 2014년 가을, 알레시오는 반마피아검찰국 풀에서 선배 검사 다비데와 벨란디의 파일 상자를 연다.</t>
         </is>
       </c>
       <c r="F74" s="9" t="inlineStr"/>
@@ -5916,27 +5940,27 @@
     <row r="75">
       <c r="A75" s="9" t="inlineStr">
         <is>
-          <t>2부 8화</t>
+          <t>2부 2화</t>
         </is>
       </c>
       <c r="B75" s="9" t="inlineStr">
         <is>
-          <t>크리벨리의 제안</t>
+          <t>첫 회개자</t>
         </is>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>La proposta di Crivelli</t>
+          <t>Il primo pentito</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
-          <t>2부 7화 변형</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="E75" s="9" t="inlineStr">
         <is>
-          <t>크리벨리가 알레시오에게 영전을 약속하며, 대재판에서 로지로 향하는 진술만 빼라고 한다.</t>
+          <t>살레미 가문의 회계사가 협력을 제안한다. 알레시오는 밤새 진술과 거짓을 가려내지만, 증거가 모자란 한 이름만은 '나는 안다'며 밀어붙이고 다비데가 처음으로 그를 말린다.</t>
         </is>
       </c>
       <c r="F75" s="9" t="inlineStr"/>
@@ -5944,27 +5968,27 @@
     <row r="76">
       <c r="A76" s="9" t="inlineStr">
         <is>
-          <t>2부 9화</t>
+          <t>2부 3화</t>
         </is>
       </c>
       <c r="B76" s="9" t="inlineStr">
         <is>
-          <t>개정</t>
+          <t>돈의 유혹</t>
         </is>
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>Si apre il maxiprocesso</t>
+          <t>La tentazione del denaro</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>2부 2화 변형</t>
         </is>
       </c>
       <c r="E76" s="9" t="inlineStr">
         <is>
-          <t>철창 속 피고인들이 소리치는 가운데 대재판이 열린다. 배심 시민판사 둘이 협박을 받고 사퇴한다.</t>
+          <t>정체불명 재단이 «Luce»에 거액을 제안한다. 회개자의 장부에서 리나가 그 재단의 이름을 찾아낸다.</t>
         </is>
       </c>
       <c r="F76" s="9" t="inlineStr"/>
@@ -5972,27 +5996,27 @@
     <row r="77">
       <c r="A77" s="9" t="inlineStr">
         <is>
-          <t>2부 10화</t>
+          <t>2부 4화</t>
         </is>
       </c>
       <c r="B77" s="9" t="inlineStr">
         <is>
-          <t>파올로의 배신</t>
+          <t>벙커 법정</t>
         </is>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>Il tradimento di Paolo</t>
+          <t>L'aula bunker</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>2부 10화 변형</t>
+          <t>2부 3화 확장</t>
         </is>
       </c>
       <c r="E77" s="9" t="inlineStr">
         <is>
-          <t>(친구 시점) 딸의 사진이 든 봉투를 받은 밤, 파올로가 회개자 은신처 주소를 넘긴다. 회개자의 아내가 총격을 겨우 피하고, 다비데가 유출 경로 끝에서 그의 이름을 찾는다.</t>
+          <t>피고인 300여 명을 세울 벙커 법정이 교도소 옆에 지어진다. 대재판을 취재하던 키아라와 알레시오가 가까워진다.</t>
         </is>
       </c>
       <c r="F77" s="9" t="inlineStr"/>
@@ -6000,27 +6024,27 @@
     <row r="78">
       <c r="A78" s="9" t="inlineStr">
         <is>
-          <t>2부 11화</t>
+          <t>2부 5화</t>
         </is>
       </c>
       <c r="B78" s="9" t="inlineStr">
         <is>
-          <t>증언대</t>
+          <t>회개자의 가족</t>
         </is>
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>Il testimone</t>
+          <t>La famiglia del pentito</t>
         </is>
       </c>
       <c r="D78" s="9" t="inlineStr">
         <is>
-          <t>2부 8화 변형</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="E78" s="9" t="inlineStr">
         <is>
-          <t>회개자가 끝내 증언대에 선다. 같은 주, 아버지 니콜라가 항만 협동조합에서 해고되고 부자는 처음 서로를 이해한다.</t>
+          <t>회개자의 형이 살해되는 '가로지르는 보복'이 일어난다. 흔들리는 그에게 알레시오는 먼저 커피를 낸다.</t>
         </is>
       </c>
       <c r="F78" s="9" t="inlineStr"/>
@@ -6028,223 +6052,223 @@
     <row r="79">
       <c r="A79" s="9" t="inlineStr">
         <is>
+          <t>2부 6화</t>
+        </is>
+      </c>
+      <c r="B79" s="9" t="inlineStr">
+        <is>
+          <t>파올로의 균열</t>
+        </is>
+      </c>
+      <c r="C79" s="9" t="inlineStr">
+        <is>
+          <t>La crepa di Paolo</t>
+        </is>
+      </c>
+      <c r="D79" s="9" t="inlineStr">
+        <is>
+          <t>2부 5화 변형</t>
+        </is>
+      </c>
+      <c r="E79" s="9" t="inlineStr">
+        <is>
+          <t>(친구 시점) 파올로가 살레미 가문 간부의 변호를 맡는다. 사무실 빚을 갚아 주겠다는 조건, 그리고 딸의 학교 이름을 알고 있는 의뢰인.</t>
+        </is>
+      </c>
+      <c r="F79" s="9" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="9" t="inlineStr">
+        <is>
+          <t>2부 7화</t>
+        </is>
+      </c>
+      <c r="B80" s="9" t="inlineStr">
+        <is>
+          <t>아녜세의 구속</t>
+        </is>
+      </c>
+      <c r="C80" s="9" t="inlineStr">
+        <is>
+          <t>L'arresto di Agnese</t>
+        </is>
+      </c>
+      <c r="D80" s="9" t="inlineStr">
+        <is>
+          <t>2부 6화</t>
+        </is>
+      </c>
+      <c r="E80" s="9" t="inlineStr">
+        <is>
+          <t>대교 진입로 공사장을 몸으로 막아선 아녜세가 새 치안 법령의 '도로 봉쇄죄'로 구속된다. 재판 원고석이 빈다.</t>
+        </is>
+      </c>
+      <c r="F80" s="9" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="9" t="inlineStr">
+        <is>
+          <t>2부 8화</t>
+        </is>
+      </c>
+      <c r="B81" s="9" t="inlineStr">
+        <is>
+          <t>크리벨리의 제안</t>
+        </is>
+      </c>
+      <c r="C81" s="9" t="inlineStr">
+        <is>
+          <t>La proposta di Crivelli</t>
+        </is>
+      </c>
+      <c r="D81" s="9" t="inlineStr">
+        <is>
+          <t>2부 7화 변형</t>
+        </is>
+      </c>
+      <c r="E81" s="9" t="inlineStr">
+        <is>
+          <t>크리벨리가 알레시오에게 영전을 약속하며, 대재판에서 로지로 향하는 진술만 빼라고 한다.</t>
+        </is>
+      </c>
+      <c r="F81" s="9" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="9" t="inlineStr">
+        <is>
+          <t>2부 9화</t>
+        </is>
+      </c>
+      <c r="B82" s="9" t="inlineStr">
+        <is>
+          <t>개정</t>
+        </is>
+      </c>
+      <c r="C82" s="9" t="inlineStr">
+        <is>
+          <t>Si apre il maxiprocesso</t>
+        </is>
+      </c>
+      <c r="D82" s="9" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="E82" s="9" t="inlineStr">
+        <is>
+          <t>철창 속 피고인들이 소리치는 가운데 대재판이 열린다. 배심 시민판사 둘이 협박을 받고 사퇴한다.</t>
+        </is>
+      </c>
+      <c r="F82" s="9" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="9" t="inlineStr">
+        <is>
+          <t>2부 10화</t>
+        </is>
+      </c>
+      <c r="B83" s="9" t="inlineStr">
+        <is>
+          <t>파올로의 배신</t>
+        </is>
+      </c>
+      <c r="C83" s="9" t="inlineStr">
+        <is>
+          <t>Il tradimento di Paolo</t>
+        </is>
+      </c>
+      <c r="D83" s="9" t="inlineStr">
+        <is>
+          <t>2부 10화 변형</t>
+        </is>
+      </c>
+      <c r="E83" s="9" t="inlineStr">
+        <is>
+          <t>(친구 시점) 딸의 사진이 든 봉투를 받은 밤, 파올로가 회개자 은신처 주소를 넘긴다. 회개자의 아내가 총격을 겨우 피하고, 다비데가 유출 경로 끝에서 그의 이름을 찾는다.</t>
+        </is>
+      </c>
+      <c r="F83" s="9" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="9" t="inlineStr">
+        <is>
+          <t>2부 11화</t>
+        </is>
+      </c>
+      <c r="B84" s="9" t="inlineStr">
+        <is>
+          <t>증언대</t>
+        </is>
+      </c>
+      <c r="C84" s="9" t="inlineStr">
+        <is>
+          <t>Il testimone</t>
+        </is>
+      </c>
+      <c r="D84" s="9" t="inlineStr">
+        <is>
+          <t>2부 8화 변형</t>
+        </is>
+      </c>
+      <c r="E84" s="9" t="inlineStr">
+        <is>
+          <t>회개자가 끝내 증언대에 선다. 같은 주, 아버지 니콜라가 항만 협동조합에서 해고되고 부자는 처음 서로를 이해한다.</t>
+        </is>
+      </c>
+      <c r="F84" s="9" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="9" t="inlineStr">
+        <is>
           <t>2부 12화</t>
         </is>
       </c>
-      <c r="B79" s="9" t="inlineStr">
+      <c r="B85" s="9" t="inlineStr">
         <is>
           <t>판결</t>
         </is>
       </c>
-      <c r="C79" s="9" t="inlineStr">
+      <c r="C85" s="9" t="inlineStr">
         <is>
           <t>La sentenza</t>
         </is>
       </c>
-      <c r="D79" s="9" t="inlineStr">
+      <c r="D85" s="9" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="E79" s="9" t="inlineStr">
+      <c r="E85" s="9" t="inlineStr">
         <is>
           <t>종신형 열아홉 명, 가문은 무너진다. 그러나 살레미 본인은 증거 불충분으로 무죄. 알레시오는 돈을 따라가기로 한다.</t>
         </is>
       </c>
-      <c r="F79" s="9" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="4" t="inlineStr">
-        <is>
-          <t>3부 1화</t>
-        </is>
-      </c>
-      <c r="B80" s="4" t="inlineStr">
-        <is>
-          <t>밀라노로</t>
-        </is>
-      </c>
-      <c r="C80" s="4" t="inlineStr">
-        <is>
-          <t>Verso Milano</t>
-        </is>
-      </c>
-      <c r="D80" s="4" t="inlineStr">
-        <is>
-          <t>2부 1화 변형</t>
-        </is>
-      </c>
-      <c r="E80" s="4" t="inlineStr">
-        <is>
-          <t>[2029 법정] '에르메테 로지에 언제, 누구의 추천으로 가입했나.' 2016년, 알레시오는 대재판의 돈을 따라 밀라노 공공공사 수사팀에 파견된다. 북부의 사무실엔 모카포트가 없다.</t>
-        </is>
-      </c>
-      <c r="F80" s="4" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="4" t="inlineStr">
-        <is>
-          <t>3부 2화</t>
-        </is>
-      </c>
-      <c r="B81" s="4" t="inlineStr">
-        <is>
-          <t>담합의 지도</t>
-        </is>
-      </c>
-      <c r="C81" s="4" t="inlineStr">
-        <is>
-          <t>La mappa del cartello</t>
-        </is>
-      </c>
-      <c r="D81" s="4" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="E81" s="4" t="inlineStr">
-        <is>
-          <t>리나가 은행 기록으로 해협 대교 입찰 담합의 지도를 그린다. 남부의 가문과 북부 건설사, 로마의 정당이 한 장에 담긴다.</t>
-        </is>
-      </c>
-      <c r="F81" s="4" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="4" t="inlineStr">
-        <is>
-          <t>3부 3화</t>
-        </is>
-      </c>
-      <c r="B82" s="4" t="inlineStr">
-        <is>
-          <t>키아라의 특종</t>
-        </is>
-      </c>
-      <c r="C82" s="4" t="inlineStr">
-        <is>
-          <t>Lo scoop di Chiara</t>
-        </is>
-      </c>
-      <c r="D82" s="4" t="inlineStr">
-        <is>
-          <t>2부 3화 확장</t>
-        </is>
-      </c>
-      <c r="E82" s="4" t="inlineStr">
-        <is>
-          <t>키아라가 공공공사와 정당 자금의 연결을 폭로하고, 알레시오는 하룻밤 사이 전국 반부패 수사의 얼굴이 된다.</t>
-        </is>
-      </c>
-      <c r="F82" s="4" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="4" t="inlineStr">
-        <is>
-          <t>3부 4화</t>
-        </is>
-      </c>
-      <c r="B83" s="4" t="inlineStr">
-        <is>
-          <t>광장의 목소리</t>
-        </is>
-      </c>
-      <c r="C83" s="4" t="inlineStr">
-        <is>
-          <t>La voce della piazza</t>
-        </is>
-      </c>
-      <c r="D83" s="4" t="inlineStr">
-        <is>
-          <t>2부 4화</t>
-        </is>
-      </c>
-      <c r="E83" s="4" t="inlineStr">
-        <is>
-          <t>«Luce»와 시민들이 로마에서 '정의를 위한 행진'을 연다. 알레시오는 검사로서 연단을 사양한다.</t>
-        </is>
-      </c>
-      <c r="F83" s="4" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="4" t="inlineStr">
-        <is>
-          <t>3부 5화</t>
-        </is>
-      </c>
-      <c r="B84" s="4" t="inlineStr">
-        <is>
-          <t>로지의 명단</t>
-        </is>
-      </c>
-      <c r="C84" s="4" t="inlineStr">
-        <is>
-          <t>La lista</t>
-        </is>
-      </c>
-      <c r="D84" s="4" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="E84" s="4" t="inlineStr">
-        <is>
-          <t>한 별장 금고에서 비밀 로지 '에르메테'의 명단이 압수된다. 장관, 장군, 판사, 그리고 브란카티의 이름이 있다.</t>
-        </is>
-      </c>
-      <c r="F84" s="4" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="4" t="inlineStr">
-        <is>
-          <t>3부 6화</t>
-        </is>
-      </c>
-      <c r="B85" s="4" t="inlineStr">
-        <is>
-          <t>첫 이탈자들</t>
-        </is>
-      </c>
-      <c r="C85" s="4" t="inlineStr">
-        <is>
-          <t>I primi che se ne vanno</t>
-        </is>
-      </c>
-      <c r="D85" s="4" t="inlineStr">
-        <is>
-          <t>2부 9화</t>
-        </is>
-      </c>
-      <c r="E85" s="4" t="inlineStr">
-        <is>
-          <t>명단 공개 뒤 수사팀 경찰관들이 줄줄이 전보되고 동료 검사들이 파견을 거둔다. 남은 사람은 리나와 둘뿐이다.</t>
-        </is>
-      </c>
-      <c r="F85" s="4" t="inlineStr"/>
+      <c r="F85" s="9" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>3부 7화</t>
+          <t>3부 1화</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>아녜세의 재판</t>
+          <t>밀라노로</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>Il processo ad Agnese</t>
+          <t>Verso Milano</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>2부 11화</t>
+          <t>2부 1화 변형</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>아녜세가 유죄를 선고받고, 법정에서 '법이 공사장 편에 섰다'고 말한다. 키아라가 그 말을 전국에 싣는다.</t>
+          <t>[2029 법정] 반대신문. '로지의 방법 — 신상 파일과 감청 — 을 리날디에게 가르친 게 당신 아닌가?' '그때 그는 그걸 증오했습니다.' 2016년, 알레시오는 팔코네의 방법대로 돈을 따라 밀라노로 파견된다. 북부의 사무실엔 모카포트가 없다.</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr"/>
@@ -6252,27 +6276,27 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>3부 8화</t>
+          <t>3부 2화</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>CSM의 칼</t>
+          <t>담합의 지도</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>La spada del CSM</t>
+          <t>La mappa del cartello</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>2부 12화 변형</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>(친구 시점) 살레미 그룹 법률 대리인이 된 파올로가 계파 판사들을 위해 알레시오 징계 청구서를 대필하고, 그 대가로 브란카티의 추천을 받아 로지에 입회한다.</t>
+          <t>리나가 은행 기록으로 해협 대교 입찰 담합의 지도를 그린다. 남부의 가문과 북부 건설사, 로마의 정당이 한 장에 담긴다.</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr"/>
@@ -6280,27 +6304,27 @@
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>3부 9화</t>
+          <t>3부 3화</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>키아라의 폭로</t>
+          <t>키아라의 특종</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>L'inchiesta di Chiara</t>
+          <t>Lo scoop di Chiara</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>3부 5화 변형</t>
+          <t>2부 3화 확장</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>(친구 시점) 로지와 살레미, 표 매수 조직을 잇는 장부를 손에 넣은 키아라가 확인을 청하러 온다. 파올로는 커피를 내주고, 그녀가 떠난 뒤 브란카티에게 전화를 건다.</t>
+          <t>키아라가 공공공사와 정당 자금의 연결을 폭로하고, 알레시오는 하룻밤 사이 전국 반부패 수사의 얼굴이 된다.</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr"/>
@@ -6308,27 +6332,27 @@
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>3부 10화</t>
+          <t>3부 4화</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>키아라의 실종</t>
+          <t>광장의 목소리</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>La scomparsa di Chiara</t>
+          <t>La voce della piazza</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>3부 7화 변형</t>
+          <t>2부 4화</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>기사가 아침에 공개되고 그날 밤 키아라가 사라진다. 그녀의 차만 부두에 남아 있다.</t>
+          <t>«Luce»와 시민들이 로마에서 '정의를 위한 행진'을 연다. 알레시오는 검사로서 연단을 사양한다.</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr"/>
@@ -6336,27 +6360,27 @@
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>3부 11화</t>
+          <t>3부 5화</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>거리로 나선 시민들</t>
+          <t>로지의 명단</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>I cittadini in piazza</t>
+          <t>La lista</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>3부 8화 변형</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>열두 도시에서 '키아라는 어디 있나' 시위가 동시에 일어난다. 알레시오는 처음으로 광장에 선다.</t>
+          <t>한 별장 금고에서 비밀 로지 '에르메테'의 명단이 압수된다. 장관, 장군, 판사, 그리고 브란카티의 이름이 있다.</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr"/>
@@ -6364,223 +6388,223 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
+          <t>3부 6화</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>첫 이탈자들</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>I primi che se ne vanno</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>2부 9화</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>명단 공개 뒤 수사팀 경찰관들이 줄줄이 전보되고 동료 검사들이 파견을 거둔다. 남은 리나에게 알레시오는 '절차가 우리를 죽이고 있다'고 처음 말한다.</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>3부 7화</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>아녜세의 재판</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>Il processo ad Agnese</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>2부 11화</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>아녜세가 유죄를 선고받고, 법정에서 '법이 공사장 편에 섰다'고 말한다. 키아라가 그 말을 전국에 싣는다.</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>3부 8화</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>CSM의 칼</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>La spada del CSM</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>2부 12화 변형</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>(친구 시점) 살레미 그룹 법률 대리인이 된 파올로가 계파 판사들을 위해 알레시오 징계 청구서를 대필하고, 그 대가로 브란카티의 추천을 받아 로지에 입회한다.</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>3부 9화</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>키아라의 폭로</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>L'inchiesta di Chiara</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>3부 5화 변형</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>(친구 시점) 로지와 살레미, 표 매수 조직을 잇는 장부를 손에 넣은 키아라가 확인을 청하러 온다. 파올로는 커피를 내주고, 그녀가 떠난 뒤 브란카티에게 전화를 건다.</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>3부 10화</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>키아라의 실종</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>La scomparsa di Chiara</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>3부 7화 변형</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>기사가 아침에 공개되고 그날 밤 키아라가 사라진다. 그녀의 차만 부두에 남아 있다.</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>3부 11화</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>거리로 나선 시민들</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>I cittadini in piazza</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>3부 8화 변형</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>열두 도시에서 '키아라는 어디 있나' 시위가 동시에 일어난다. 알레시오는 처음으로 광장에 선다.</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
           <t>3부 12화</t>
         </is>
       </c>
-      <c r="B91" s="4" t="inlineStr">
+      <c r="B97" s="4" t="inlineStr">
         <is>
           <t>법복을 벗다</t>
         </is>
       </c>
-      <c r="C91" s="4" t="inlineStr">
+      <c r="C97" s="4" t="inlineStr">
         <is>
           <t>Via la toga</t>
         </is>
       </c>
-      <c r="D91" s="4" t="inlineStr">
+      <c r="D97" s="4" t="inlineStr">
         <is>
           <t>2부 12화 확장</t>
         </is>
       </c>
-      <c r="E91" s="4" t="inlineStr">
+      <c r="E97" s="4" t="inlineStr">
         <is>
           <t>강제 전보가 확정되자 알레시오는 법복을 벗는다. 그리말디가 찾아와 의회로 가자고 한다. 키아라의 자리는 비워 둔다.</t>
         </is>
       </c>
-      <c r="F91" s="4" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="9" t="inlineStr">
-        <is>
-          <t>4부 1화</t>
-        </is>
-      </c>
-      <c r="B92" s="9" t="inlineStr">
-        <is>
-          <t>창당</t>
-        </is>
-      </c>
-      <c r="C92" s="9" t="inlineStr">
-        <is>
-          <t>Nasce un partito</t>
-        </is>
-      </c>
-      <c r="D92" s="9" t="inlineStr">
-        <is>
-          <t>3부 1화 변형</t>
-        </is>
-      </c>
-      <c r="E92" s="9" t="inlineStr">
-        <is>
-          <t>[2029 법정] '2017년 총선에서 표를 샀나.' '한 표에 50유로였습니다.' 법복을 벗은 알레시오는 그리말디, 지역 활동가들과 몰수된 빵집에서 시민정당 '온다 치빌레'를 창당한다.</t>
-        </is>
-      </c>
-      <c r="F92" s="9" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="9" t="inlineStr">
-        <is>
-          <t>4부 2화</t>
-        </is>
-      </c>
-      <c r="B93" s="9" t="inlineStr">
-        <is>
-          <t>아버지의 죽음</t>
-        </is>
-      </c>
-      <c r="C93" s="9" t="inlineStr">
-        <is>
-          <t>La morte del padre</t>
-        </is>
-      </c>
-      <c r="D93" s="9" t="inlineStr">
-        <is>
-          <t>3부 4화 변형</t>
-        </is>
-      </c>
-      <c r="E93" s="9" t="inlineStr">
-        <is>
-          <t>조기 총선에서 토레네라 소선거구에 나선 지 일주일, '아들이 자랑스럽다'던 니콜라가 뺑소니로 숨진다.</t>
-        </is>
-      </c>
-      <c r="F93" s="9" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="9" t="inlineStr">
-        <is>
-          <t>4부 3화</t>
-        </is>
-      </c>
-      <c r="B94" s="9" t="inlineStr">
-        <is>
-          <t>맞은편 후보</t>
-        </is>
-      </c>
-      <c r="C94" s="9" t="inlineStr">
-        <is>
-          <t>Il candidato di fronte</t>
-        </is>
-      </c>
-      <c r="D94" s="9" t="inlineStr">
-        <is>
-          <t>3부 9화 변형</t>
-        </is>
-      </c>
-      <c r="E94" s="9" t="inlineStr">
-        <is>
-          <t>(친구 시점) 살레미가 후원하는 «Alleanza del Mezzogiorno»의 토레네라 후보가 된 파올로가 대리 투표와 표 매수 기계를 돌린다. 니콜라의 장례식 뒷줄에 섰다가 쫓겨난다.</t>
-        </is>
-      </c>
-      <c r="F94" s="9" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="9" t="inlineStr">
-        <is>
-          <t>4부 4화</t>
-        </is>
-      </c>
-      <c r="B95" s="9" t="inlineStr">
-        <is>
-          <t>당선, 그러나</t>
-        </is>
-      </c>
-      <c r="C95" s="9" t="inlineStr">
-        <is>
-          <t>Eletto, ma…</t>
-        </is>
-      </c>
-      <c r="D95" s="9" t="inlineStr">
-        <is>
-          <t>3부 11화 변형</t>
-        </is>
-      </c>
-      <c r="E95" s="9" t="inlineStr">
-        <is>
-          <t>근소한 차로 알레시오가 소선거구에서 이기고, 파올로는 비례대표로 원내에 들어온다. 그 밤 크리벨리가 키아라를 묻는 알레시오에게 거래를 말한다.</t>
-        </is>
-      </c>
-      <c r="F95" s="9" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="9" t="inlineStr">
-        <is>
-          <t>4부 5화</t>
-        </is>
-      </c>
-      <c r="B96" s="9" t="inlineStr">
-        <is>
-          <t>반마피아위원회</t>
-        </is>
-      </c>
-      <c r="C96" s="9" t="inlineStr">
-        <is>
-          <t>La commissione</t>
-        </is>
-      </c>
-      <c r="D96" s="9" t="inlineStr">
-        <is>
-          <t>3부 12화 변형</t>
-        </is>
-      </c>
-      <c r="E96" s="9" t="inlineStr">
-        <is>
-          <t>알레시오가 의회 반마피아위원회 위원장이 된다. 리나가 자금 추적 자문으로 «Bussola»를 데려오고, 욜란다가 먼저 커피를 낸다.</t>
-        </is>
-      </c>
-      <c r="F96" s="9" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="9" t="inlineStr">
-        <is>
-          <t>4부 6화</t>
-        </is>
-      </c>
-      <c r="B97" s="9" t="inlineStr">
-        <is>
-          <t>이레네의 등장</t>
-        </is>
-      </c>
-      <c r="C97" s="9" t="inlineStr">
-        <is>
-          <t>Arriva Irene</t>
-        </is>
-      </c>
-      <c r="D97" s="9" t="inlineStr">
-        <is>
-          <t>4부 3화 변형</t>
-        </is>
-      </c>
-      <c r="E97" s="9" t="inlineStr">
-        <is>
-          <t>위원회 연수생으로 온 스물두 살 법대생 이레네가 로지 명단의 빈칸을 가리키며 날카로운 질문을 던진다.</t>
-        </is>
-      </c>
-      <c r="F97" s="9" t="inlineStr"/>
+      <c r="F97" s="4" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="9" t="inlineStr">
         <is>
-          <t>4부 7화</t>
+          <t>4부 1화</t>
         </is>
       </c>
       <c r="B98" s="9" t="inlineStr">
         <is>
-          <t>아녜세의 죽음</t>
+          <t>창당</t>
         </is>
       </c>
       <c r="C98" s="9" t="inlineStr">
         <is>
-          <t>La morte di Agnese</t>
+          <t>Nasce un partito</t>
         </is>
       </c>
       <c r="D98" s="9" t="inlineStr">
         <is>
-          <t>4부 5화 변형</t>
+          <t>3부 1화 변형</t>
         </is>
       </c>
       <c r="E98" s="9" t="inlineStr">
         <is>
-          <t>옥중 단식 14일째, 병원 이송이 '호송 절차'로 하루 지체되고 아녜세가 숨진다.</t>
+          <t>[2029 법정] '2017년 총선에서 표를 샀나.' '한 표에 50유로였습니다.' '리날디는 왜 당신을 고발하지 않았나.' 침묵. 법복을 벗은 알레시오는 그리말디, 지역 활동가들과 몰수된 빵집에서 시민정당 '온다 치빌레'를 창당한다.</t>
         </is>
       </c>
       <c r="F98" s="9" t="inlineStr"/>
@@ -6588,27 +6612,27 @@
     <row r="99">
       <c r="A99" s="9" t="inlineStr">
         <is>
-          <t>4부 8화</t>
+          <t>4부 2화</t>
         </is>
       </c>
       <c r="B99" s="9" t="inlineStr">
         <is>
-          <t>거리의 혁명</t>
+          <t>아버지의 죽음</t>
         </is>
       </c>
       <c r="C99" s="9" t="inlineStr">
         <is>
-          <t>La rivoluzione delle piazze</t>
+          <t>La morte del padre</t>
         </is>
       </c>
       <c r="D99" s="9" t="inlineStr">
         <is>
-          <t>4부 6화</t>
+          <t>3부 4화 변형</t>
         </is>
       </c>
       <c r="E99" s="9" t="inlineStr">
         <is>
-          <t>추모 집회가 전국으로 번지고 항만과 공장이 멈춘다. 진압 명령을 거부한 경찰관이 상징이 된다.</t>
+          <t>조기 총선에서 토레네라 소선거구에 나선 지 일주일, '아들이 자랑스럽다'던 니콜라가 뺑소니로 숨진다.</t>
         </is>
       </c>
       <c r="F99" s="9" t="inlineStr"/>
@@ -6616,27 +6640,27 @@
     <row r="100">
       <c r="A100" s="9" t="inlineStr">
         <is>
-          <t>4부 9화</t>
+          <t>4부 3화</t>
         </is>
       </c>
       <c r="B100" s="9" t="inlineStr">
         <is>
-          <t>크리벨리의 선택</t>
+          <t>맞은편 후보</t>
         </is>
       </c>
       <c r="C100" s="9" t="inlineStr">
         <is>
-          <t>La scelta di Crivelli</t>
+          <t>Il candidato di fronte</t>
         </is>
       </c>
       <c r="D100" s="9" t="inlineStr">
         <is>
-          <t>4부 7화</t>
+          <t>3부 9화 변형</t>
         </is>
       </c>
       <c r="E100" s="9" t="inlineStr">
         <is>
-          <t>안보위원회에서 강경 진압과 협상 사이에 선 크리벨리는 처음으로 로지의 지시를 거스른다.</t>
+          <t>(친구 시점) 살레미가 후원하는 «Alleanza del Mezzogiorno»의 토레네라 후보가 된 파올로가 대리 투표와 표 매수 기계를 돌린다. 니콜라의 장례식 뒷줄에 섰다가 쫓겨난다.</t>
         </is>
       </c>
       <c r="F100" s="9" t="inlineStr"/>
@@ -6644,27 +6668,27 @@
     <row r="101">
       <c r="A101" s="9" t="inlineStr">
         <is>
-          <t>4부 10화</t>
+          <t>4부 4화</t>
         </is>
       </c>
       <c r="B101" s="9" t="inlineStr">
         <is>
-          <t>불신임</t>
+          <t>당선, 그러나</t>
         </is>
       </c>
       <c r="C101" s="9" t="inlineStr">
         <is>
-          <t>La sfiducia</t>
+          <t>Eletto, ma…</t>
         </is>
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
-          <t>4부 9화 변형</t>
+          <t>3부 11화 변형</t>
         </is>
       </c>
       <c r="E101" s="9" t="inlineStr">
         <is>
-          <t>위원회가 로지 명단 전체를 의회에 공개하고, 정부가 불신임 투표로 무너진다.</t>
+          <t>근소한 차로 알레시오가 소선거구에서 이기고, 파올로는 비례대표로 원내에 들어온다. 그 밤 크리벨리가 키아라를 묻는 알레시오에게 거래를 말한다.</t>
         </is>
       </c>
       <c r="F101" s="9" t="inlineStr"/>
@@ -6672,27 +6696,27 @@
     <row r="102">
       <c r="A102" s="9" t="inlineStr">
         <is>
-          <t>4부 11화</t>
+          <t>4부 5화</t>
         </is>
       </c>
       <c r="B102" s="9" t="inlineStr">
         <is>
-          <t>조각 위임</t>
+          <t>반마피아위원회</t>
         </is>
       </c>
       <c r="C102" s="9" t="inlineStr">
         <is>
-          <t>L'incarico</t>
+          <t>La commissione</t>
         </is>
       </c>
       <c r="D102" s="9" t="inlineStr">
         <is>
-          <t>4부 4화 변형</t>
+          <t>3부 12화 변형</t>
         </is>
       </c>
       <c r="E102" s="9" t="inlineStr">
         <is>
-          <t>(친구 시점) 퀴리날레가 알레시오에게 조각을 맡기자, 파올로가 살레미 쪽 의원들의 사자로 면책과 맞바꿀 신임표를 들고 온다. 알레시오는 처음으로 커피를 내지 않는다.</t>
+          <t>알레시오가 의회 반마피아위원회 위원장이 된다. 리나가 자금 추적 자문으로 «Bussola»를 데려오고, 욜란다가 먼저 커피를 낸다.</t>
         </is>
       </c>
       <c r="F102" s="9" t="inlineStr"/>
@@ -6700,223 +6724,223 @@
     <row r="103">
       <c r="A103" s="9" t="inlineStr">
         <is>
+          <t>4부 6화</t>
+        </is>
+      </c>
+      <c r="B103" s="9" t="inlineStr">
+        <is>
+          <t>이레네의 등장</t>
+        </is>
+      </c>
+      <c r="C103" s="9" t="inlineStr">
+        <is>
+          <t>Arriva Irene</t>
+        </is>
+      </c>
+      <c r="D103" s="9" t="inlineStr">
+        <is>
+          <t>4부 3화 변형</t>
+        </is>
+      </c>
+      <c r="E103" s="9" t="inlineStr">
+        <is>
+          <t>위원회 연수생으로 온 스물두 살 법대생 이레네가 로지 명단의 빈칸을 가리키며 날카로운 질문을 던진다.</t>
+        </is>
+      </c>
+      <c r="F103" s="9" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="9" t="inlineStr">
+        <is>
+          <t>4부 7화</t>
+        </is>
+      </c>
+      <c r="B104" s="9" t="inlineStr">
+        <is>
+          <t>아녜세의 죽음</t>
+        </is>
+      </c>
+      <c r="C104" s="9" t="inlineStr">
+        <is>
+          <t>La morte di Agnese</t>
+        </is>
+      </c>
+      <c r="D104" s="9" t="inlineStr">
+        <is>
+          <t>4부 5화 변형</t>
+        </is>
+      </c>
+      <c r="E104" s="9" t="inlineStr">
+        <is>
+          <t>옥중 단식 14일째, 병원 이송이 '호송 절차'로 하루 지체되고 아녜세가 숨진다.</t>
+        </is>
+      </c>
+      <c r="F104" s="9" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="9" t="inlineStr">
+        <is>
+          <t>4부 8화</t>
+        </is>
+      </c>
+      <c r="B105" s="9" t="inlineStr">
+        <is>
+          <t>거리의 혁명</t>
+        </is>
+      </c>
+      <c r="C105" s="9" t="inlineStr">
+        <is>
+          <t>La rivoluzione delle piazze</t>
+        </is>
+      </c>
+      <c r="D105" s="9" t="inlineStr">
+        <is>
+          <t>4부 6화</t>
+        </is>
+      </c>
+      <c r="E105" s="9" t="inlineStr">
+        <is>
+          <t>추모 집회가 전국으로 번지고 항만과 공장이 멈춘다. 진압 명령을 거부한 경찰관이 상징이 된다.</t>
+        </is>
+      </c>
+      <c r="F105" s="9" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="9" t="inlineStr">
+        <is>
+          <t>4부 9화</t>
+        </is>
+      </c>
+      <c r="B106" s="9" t="inlineStr">
+        <is>
+          <t>크리벨리의 선택</t>
+        </is>
+      </c>
+      <c r="C106" s="9" t="inlineStr">
+        <is>
+          <t>La scelta di Crivelli</t>
+        </is>
+      </c>
+      <c r="D106" s="9" t="inlineStr">
+        <is>
+          <t>4부 7화</t>
+        </is>
+      </c>
+      <c r="E106" s="9" t="inlineStr">
+        <is>
+          <t>안보위원회에서 강경 진압과 협상 사이에 선 크리벨리는 처음으로 로지의 지시를 거스른다.</t>
+        </is>
+      </c>
+      <c r="F106" s="9" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="9" t="inlineStr">
+        <is>
+          <t>4부 10화</t>
+        </is>
+      </c>
+      <c r="B107" s="9" t="inlineStr">
+        <is>
+          <t>불신임</t>
+        </is>
+      </c>
+      <c r="C107" s="9" t="inlineStr">
+        <is>
+          <t>La sfiducia</t>
+        </is>
+      </c>
+      <c r="D107" s="9" t="inlineStr">
+        <is>
+          <t>4부 9화 변형</t>
+        </is>
+      </c>
+      <c r="E107" s="9" t="inlineStr">
+        <is>
+          <t>위원회가 로지 명단 전체를 의회에 공개하고, 정부가 불신임 투표로 무너진다.</t>
+        </is>
+      </c>
+      <c r="F107" s="9" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="9" t="inlineStr">
+        <is>
+          <t>4부 11화</t>
+        </is>
+      </c>
+      <c r="B108" s="9" t="inlineStr">
+        <is>
+          <t>조각 위임</t>
+        </is>
+      </c>
+      <c r="C108" s="9" t="inlineStr">
+        <is>
+          <t>L'incarico</t>
+        </is>
+      </c>
+      <c r="D108" s="9" t="inlineStr">
+        <is>
+          <t>4부 4화 변형</t>
+        </is>
+      </c>
+      <c r="E108" s="9" t="inlineStr">
+        <is>
+          <t>(친구 시점) 퀴리날레가 알레시오에게 조각을 맡기자, 파올로가 살레미 쪽 의원들의 사자로 면책과 맞바꿀 신임표를 들고 온다. 알레시오는 처음으로 커피를 내지 않는다.</t>
+        </is>
+      </c>
+      <c r="F108" s="9" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="9" t="inlineStr">
+        <is>
           <t>4부 12화</t>
         </is>
       </c>
-      <c r="B103" s="9" t="inlineStr">
+      <c r="B109" s="9" t="inlineStr">
         <is>
           <t>신임 투표</t>
         </is>
       </c>
-      <c r="C103" s="9" t="inlineStr">
+      <c r="C109" s="9" t="inlineStr">
         <is>
           <t>Il voto di fiducia</t>
         </is>
       </c>
-      <c r="D103" s="9" t="inlineStr">
+      <c r="D109" s="9" t="inlineStr">
         <is>
           <t>4부 12화 변형</t>
         </is>
       </c>
-      <c r="E103" s="9" t="inlineStr">
+      <c r="E109" s="9" t="inlineStr">
         <is>
           <t>살레미의 표 없이 양원 신임을 얻은 밤, 알레시오는 선서 전 벨란디와 아버지, 아녜세의 무덤을 찾는다.</t>
         </is>
       </c>
-      <c r="F103" s="9" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="4" t="inlineStr">
-        <is>
-          <t>5부 1화</t>
-        </is>
-      </c>
-      <c r="B104" s="4" t="inlineStr">
-        <is>
-          <t>선서와 첫 벽</t>
-        </is>
-      </c>
-      <c r="C104" s="4" t="inlineStr">
-        <is>
-          <t>Il giuramento e il primo muro</t>
-        </is>
-      </c>
-      <c r="D104" s="4" t="inlineStr">
-        <is>
-          <t>5부 1화 변형</t>
-        </is>
-      </c>
-      <c r="E104" s="4" t="inlineStr">
-        <is>
-          <t>[2029 법정] '다비데 로카시오 검사의 살해를 미리 알았나.' 긴 침묵, 재판장의 답변 명령. 2019년, 예비비 자료를 막는 경제부에서 브란카티가 '1년 뒤 당신은 없다'고 한다.</t>
-        </is>
-      </c>
-      <c r="F104" s="4" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="4" t="inlineStr">
-        <is>
-          <t>5부 2화</t>
-        </is>
-      </c>
-      <c r="B105" s="4" t="inlineStr">
-        <is>
-          <t>크리벨리와의 재계약</t>
-        </is>
-      </c>
-      <c r="C105" s="4" t="inlineStr">
-        <is>
-          <t>Il nuovo patto con Crivelli</t>
-        </is>
-      </c>
-      <c r="D105" s="4" t="inlineStr">
-        <is>
-          <t>5부 2화</t>
-        </is>
-      </c>
-      <c r="E105" s="4" t="inlineStr">
-        <is>
-          <t>예비비 추적이 정보기관 기밀비로 이어진다. 알레시오는 크리벨리와 조건부 협력을 맺는다.</t>
-        </is>
-      </c>
-      <c r="F105" s="4" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="4" t="inlineStr">
-        <is>
-          <t>5부 3화</t>
-        </is>
-      </c>
-      <c r="B106" s="4" t="inlineStr">
-        <is>
-          <t>살레미의 마지막 카드</t>
-        </is>
-      </c>
-      <c r="C106" s="4" t="inlineStr">
-        <is>
-          <t>L'ultima carta di Salemi</t>
-        </is>
-      </c>
-      <c r="D106" s="4" t="inlineStr">
-        <is>
-          <t>5부 3화 변형</t>
-        </is>
-      </c>
-      <c r="E106" s="4" t="inlineStr">
-        <is>
-          <t>(친구 시점) 실소유자 공개 법안이 살레미 제국을 겨누자, 야당 의원 파올로가 해변 영업권 업자들의 거리 시위를 조직하고 하원에서 법안 저지 연설을 한다.</t>
-        </is>
-      </c>
-      <c r="F106" s="4" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="4" t="inlineStr">
-        <is>
-          <t>5부 4화</t>
-        </is>
-      </c>
-      <c r="B107" s="4" t="inlineStr">
-        <is>
-          <t>지방의 반란</t>
-        </is>
-      </c>
-      <c r="C107" s="4" t="inlineStr">
-        <is>
-          <t>La rivolta della regione</t>
-        </is>
-      </c>
-      <c r="D107" s="4" t="inlineStr">
-        <is>
-          <t>5부 4화</t>
-        </is>
-      </c>
-      <c r="E107" s="4" t="inlineStr">
-        <is>
-          <t>산유 지역 레조네 요니카의 주지사가 투명성법 적용을 거부한다. 부지사 마리나 페를리토가 장부를 들고 온다.</t>
-        </is>
-      </c>
-      <c r="F107" s="4" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="4" t="inlineStr">
-        <is>
-          <t>5부 5화</t>
-        </is>
-      </c>
-      <c r="B108" s="4" t="inlineStr">
-        <is>
-          <t>개혁의 대가</t>
-        </is>
-      </c>
-      <c r="C108" s="4" t="inlineStr">
-        <is>
-          <t>Il prezzo della riforma</t>
-        </is>
-      </c>
-      <c r="D108" s="4" t="inlineStr">
-        <is>
-          <t>5부 5화 변형</t>
-        </is>
-      </c>
-      <c r="E108" s="4" t="inlineStr">
-        <is>
-          <t>(친구 시점) 로지 만찬에서 CSM 계파 비리 조사에 자원한 다비데의 이름이 오간다. 파올로는 경고 전화를 걸다 끊고, 이튿날 다비데가 총에 맞는다.</t>
-        </is>
-      </c>
-      <c r="F108" s="4" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="4" t="inlineStr">
-        <is>
-          <t>5부 6화</t>
-        </is>
-      </c>
-      <c r="B109" s="4" t="inlineStr">
-        <is>
-          <t>국제적 고립과 압박</t>
-        </is>
-      </c>
-      <c r="C109" s="4" t="inlineStr">
-        <is>
-          <t>Isolamento e pressioni</t>
-        </is>
-      </c>
-      <c r="D109" s="4" t="inlineStr">
-        <is>
-          <t>5부 6화</t>
-        </is>
-      </c>
-      <c r="E109" s="4" t="inlineStr">
-        <is>
-          <t>EU 과잉적자 절차와 스프레드 공격, 감사원의 대교 사업 제동이 겹치고 우방마저 값을 깎으려 한다.</t>
-        </is>
-      </c>
-      <c r="F109" s="4" t="inlineStr"/>
+      <c r="F109" s="9" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>5부 7화</t>
+          <t>5부 1화</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>쿠데타 기도</t>
+          <t>선서와 첫 벽</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>Il tentato golpe</t>
+          <t>Il giuramento e il primo muro</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>5부 7화</t>
+          <t>5부 1화 변형</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>새벽 다섯 시, 일탈 장교들과 로지가 병력을 움직였다는 보고가 들어온다. 짧고 빠른 한 밤이 시작된다.</t>
+          <t>[2029 법정] '다비데 로카시오의 살해를 미리 알았나.' 긴 침묵. 변호인이 '살인을 알고도 침묵한 증인'이라 몰아붙이자 파올로는 '그를 단죄하는 건 제 말이 아니라 그 자신의 말일 것'이라 답한다. 2019년 경제부에서 브란카티가 '1년 뒤 당신은 없다'고 한다.</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr"/>
@@ -6924,27 +6948,27 @@
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>5부 8화</t>
+          <t>5부 2화</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>살레미의 최후</t>
+          <t>크리벨리와의 재계약</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>La caduta di Salemi</t>
+          <t>Il nuovo patto con Crivelli</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>5부 8화 변형</t>
+          <t>5부 2화</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>(친구 시점) 투명성청이 마지막 은닉 구조를 밝혀낸 날, 전용기의 한 좌석은 파올로 몫이었다. 그는 타지 않고, 살레미는 공항에서 체포된다. 빈자리는 브란카티가 채운다.</t>
+          <t>예비비 추적이 정보기관 기밀비로 이어진다. 알레시오는 크리벨리와 조건부 협력을 맺는다.</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr"/>
@@ -6952,27 +6976,27 @@
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>5부 9화</t>
+          <t>5부 3화</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>크리벨리의 끝</t>
+          <t>살레미의 마지막 카드</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>La fine di Crivelli</t>
+          <t>L'ultima carta di Salemi</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>5부 9화 변형</t>
+          <t>5부 3화 변형</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>다비데 청부금의 흐름이 키아라 실종 당일의 송금과 같은 사슬로 이어진다. 키아라의 유해가 발견되고 크리벨리가 사임한다.</t>
+          <t>(친구 시점) 실소유자 공개 법안이 살레미 제국을 겨누자, 야당 의원 파올로가 해변 영업권 업자들의 거리 시위를 조직하고 하원에서 법안 저지 연설을 한다.</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr"/>
@@ -6980,27 +7004,27 @@
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>5부 10화</t>
+          <t>5부 4화</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>대의의 완성</t>
+          <t>지방의 반란</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>Il compimento</t>
+          <t>La rivolta della regione</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>5부 10화</t>
+          <t>5부 4화</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>개헌 패키지가 확정 국민투표를 통과한다. 경력 분리 대신 CSM 개혁, 그리고 총리 연속 두 번의 한계가 함께 담긴다.</t>
+          <t>산유 지역 레조네 요니카의 주지사가 투명성법 적용을 거부한다. 부지사 마리나 페를리토가 장부를 들고 온다.</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr"/>
@@ -7008,27 +7032,27 @@
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>5부 11화</t>
+          <t>5부 5화</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>개혁의 피로</t>
+          <t>개혁의 대가</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>La stanchezza delle riforme</t>
+          <t>Il prezzo della riforma</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>5부 11화</t>
+          <t>5부 5화 변형</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>그림자 경제에 기대 살던 사람들이 일자리를 잃고, 폭로 피로가 쌓인다. 지방선거엔 다시 표 매수 징후가 보인다.</t>
+          <t>(친구 시점) 로지 만찬에서 CSM 계파 비리 조사에 자원한 다비데의 이름이 오간다. 파올로는 경고 전화를 걸다 끊고, 이튿날 다비데가 총에 맞는다.</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr"/>
@@ -7036,223 +7060,223 @@
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
+          <t>5부 6화</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>국제적 고립과 압박</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>Isolamento e pressioni</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr">
+        <is>
+          <t>5부 6화</t>
+        </is>
+      </c>
+      <c r="E115" s="4" t="inlineStr">
+        <is>
+          <t>EU 과잉적자 절차와 스프레드 공격, 감사원의 대교 사업 제동이 겹친다. 다비데를 잃은 알레시오는 경호 증원을 거절하며 보르셀리노의 말로 전해지는 '두려워하는 자는 매일 죽는다'를 인용한다.</t>
+        </is>
+      </c>
+      <c r="F115" s="4" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="4" t="inlineStr">
+        <is>
+          <t>5부 7화</t>
+        </is>
+      </c>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
+          <t>쿠데타 기도</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="inlineStr">
+        <is>
+          <t>Il tentato golpe</t>
+        </is>
+      </c>
+      <c r="D116" s="4" t="inlineStr">
+        <is>
+          <t>5부 7화</t>
+        </is>
+      </c>
+      <c r="E116" s="4" t="inlineStr">
+        <is>
+          <t>새벽 다섯 시, 일탈 장교들과 로지가 병력을 움직였다는 보고. 알레시오는 영장 없이 장군들을 구금하자고 했다가 법무장관에게 막힌다. 쿠데타는 절차대로 진압된다.</t>
+        </is>
+      </c>
+      <c r="F116" s="4" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>5부 8화</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>살레미의 최후</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>La caduta di Salemi</t>
+        </is>
+      </c>
+      <c r="D117" s="4" t="inlineStr">
+        <is>
+          <t>5부 8화 변형</t>
+        </is>
+      </c>
+      <c r="E117" s="4" t="inlineStr">
+        <is>
+          <t>(친구 시점) 투명성청이 마지막 은닉 구조를 밝혀낸 날, 전용기의 한 좌석은 파올로 몫이었다. 그는 타지 않고, 살레미는 공항에서 체포된다. 빈자리는 브란카티가 채운다.</t>
+        </is>
+      </c>
+      <c r="F117" s="4" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="4" t="inlineStr">
+        <is>
+          <t>5부 9화</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>크리벨리의 끝</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>La fine di Crivelli</t>
+        </is>
+      </c>
+      <c r="D118" s="4" t="inlineStr">
+        <is>
+          <t>5부 9화 변형</t>
+        </is>
+      </c>
+      <c r="E118" s="4" t="inlineStr">
+        <is>
+          <t>다비데 청부금의 흐름이 키아라 실종 당일의 송금과 같은 사슬로 이어진다. 키아라의 유해가 발견되고 크리벨리가 사임한다.</t>
+        </is>
+      </c>
+      <c r="F118" s="4" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t>5부 10화</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>대의의 완성</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>Il compimento</t>
+        </is>
+      </c>
+      <c r="D119" s="4" t="inlineStr">
+        <is>
+          <t>5부 10화</t>
+        </is>
+      </c>
+      <c r="E119" s="4" t="inlineStr">
+        <is>
+          <t>개헌 패키지가 확정 국민투표를 통과한다. CSM 개혁과 함께 그가 스스로 제안한 '총리 연속 두 입법기' 한계가 담기고, 그는 테아노의 가리발디를 인용한다.</t>
+        </is>
+      </c>
+      <c r="F119" s="4" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="4" t="inlineStr">
+        <is>
+          <t>5부 11화</t>
+        </is>
+      </c>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t>개혁의 피로</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="inlineStr">
+        <is>
+          <t>La stanchezza delle riforme</t>
+        </is>
+      </c>
+      <c r="D120" s="4" t="inlineStr">
+        <is>
+          <t>5부 11화</t>
+        </is>
+      </c>
+      <c r="E120" s="4" t="inlineStr">
+        <is>
+          <t>그림자 경제에 기대 살던 사람들이 일자리를 잃고, 폭로 피로가 쌓인다. 지방선거엔 다시 표 매수 징후가 보인다.</t>
+        </is>
+      </c>
+      <c r="F120" s="4" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="4" t="inlineStr">
+        <is>
           <t>5부 12화</t>
         </is>
       </c>
-      <c r="B115" s="4" t="inlineStr">
+      <c r="B121" s="4" t="inlineStr">
         <is>
           <t>재신임의 기로</t>
         </is>
       </c>
-      <c r="C115" s="4" t="inlineStr">
+      <c r="C121" s="4" t="inlineStr">
         <is>
           <t>Al bivio</t>
         </is>
       </c>
-      <c r="D115" s="4" t="inlineStr">
+      <c r="D121" s="4" t="inlineStr">
         <is>
           <t>5부 12화</t>
         </is>
       </c>
-      <c r="E115" s="4" t="inlineStr">
-        <is>
-          <t>지지율이 떨어지는 가운데 알레시오는 약속대로 퀴리날레에 사표를 낸다. 반년 뒤 조기 총선이 확정된다.</t>
-        </is>
-      </c>
-      <c r="F115" s="4" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="9" t="inlineStr">
-        <is>
-          <t>6부 1화</t>
-        </is>
-      </c>
-      <c r="B116" s="9" t="inlineStr">
-        <is>
-          <t>연정의 균열</t>
-        </is>
-      </c>
-      <c r="C116" s="9" t="inlineStr">
-        <is>
-          <t>La crepa nella maggioranza</t>
-        </is>
-      </c>
-      <c r="D116" s="9" t="inlineStr">
-        <is>
-          <t>6부 1화 변형</t>
-        </is>
-      </c>
-      <c r="E116" s="9" t="inlineStr">
-        <is>
-          <t>[2029 법정] '카타니아 당대회 전 보안 컨설팅 대금을 누가 전달했나.' '제가 들고 갔습니다.' 콜라산티가 역외 수용과 총리 직선제를 내걸고 연정을 깬다.</t>
-        </is>
-      </c>
-      <c r="F116" s="9" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="9" t="inlineStr">
-        <is>
-          <t>6부 2화</t>
-        </is>
-      </c>
-      <c r="B117" s="9" t="inlineStr">
-        <is>
-          <t>이레네의 신고식</t>
-        </is>
-      </c>
-      <c r="C117" s="9" t="inlineStr">
-        <is>
-          <t>Il battesimo di Irene</t>
-        </is>
-      </c>
-      <c r="D117" s="9" t="inlineStr">
-        <is>
-          <t>6부 2화 변형</t>
-        </is>
-      </c>
-      <c r="E117" s="9" t="inlineStr">
-        <is>
-          <t>알레시오 대신 하원 연단에 선 이레네가 처음으로 혼자 정부를 변론한다. 떨리는 목소리로 레오파르디를 인용한다.</t>
-        </is>
-      </c>
-      <c r="F117" s="9" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="9" t="inlineStr">
-        <is>
-          <t>6부 3화</t>
-        </is>
-      </c>
-      <c r="B118" s="9" t="inlineStr">
-        <is>
-          <t>딥페이크 공작</t>
-        </is>
-      </c>
-      <c r="C118" s="9" t="inlineStr">
-        <is>
-          <t>L'operazione deepfake</t>
-        </is>
-      </c>
-      <c r="D118" s="9" t="inlineStr">
-        <is>
-          <t>6부 3화 변형</t>
-        </is>
-      </c>
-      <c r="E118" s="9" t="inlineStr">
-        <is>
-          <t>(친구 시점) 로지 쪽 정치기술자가 파올로의 사무실에서 알레시오 딥페이크 영상을 시사한다. 파올로는 '선을 넘는다'고 말하지만, 영상은 그날 밤 퍼진다.</t>
-        </is>
-      </c>
-      <c r="F118" s="9" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="9" t="inlineStr">
-        <is>
-          <t>6부 4화</t>
-        </is>
-      </c>
-      <c r="B119" s="9" t="inlineStr">
-        <is>
-          <t>감사팀 흔들기</t>
-        </is>
-      </c>
-      <c r="C119" s="9" t="inlineStr">
-        <is>
-          <t>L'attacco alla Bussola</t>
-        </is>
-      </c>
-      <c r="D119" s="9" t="inlineStr">
-        <is>
-          <t>6부 4화</t>
-        </is>
-      </c>
-      <c r="E119" s="9" t="inlineStr">
-        <is>
-          <t>«Bussola» 시절 고객 건을 비튼 조작 스캔들이 터진다. 욜란다는 '30년 장부'를 통째로 공개하자고 한다.</t>
-        </is>
-      </c>
-      <c r="F119" s="9" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="9" t="inlineStr">
-        <is>
-          <t>6부 5화</t>
-        </is>
-      </c>
-      <c r="B120" s="9" t="inlineStr">
-        <is>
-          <t>원점 순회</t>
-        </is>
-      </c>
-      <c r="C120" s="9" t="inlineStr">
-        <is>
-          <t>Il giro delle origini</t>
-        </is>
-      </c>
-      <c r="D120" s="9" t="inlineStr">
-        <is>
-          <t>6부 5화 변형</t>
-        </is>
-      </c>
-      <c r="E120" s="9" t="inlineStr">
-        <is>
-          <t>알레시오는 토레네라와 어촌, 벙커 법정 옆 협동조합을 사흘 동안 다시 찾는다. 회개자의 아내가 인사를 건넨다.</t>
-        </is>
-      </c>
-      <c r="F120" s="9" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="9" t="inlineStr">
-        <is>
-          <t>6부 6화</t>
-        </is>
-      </c>
-      <c r="B121" s="9" t="inlineStr">
-        <is>
-          <t>당대회장 폭탄</t>
-        </is>
-      </c>
-      <c r="C121" s="9" t="inlineStr">
-        <is>
-          <t>La bomba al congresso</t>
-        </is>
-      </c>
-      <c r="D121" s="9" t="inlineStr">
-        <is>
-          <t>6부 6화 변형</t>
-        </is>
-      </c>
-      <c r="E121" s="9" t="inlineStr">
-        <is>
-          <t>카타니아 당대회에 처음으로 현장을 보러 온 욜란다가 폭발에 휘말려 숨지고, 이레네가 중상을 입는다.</t>
-        </is>
-      </c>
-      <c r="F121" s="9" t="inlineStr"/>
+      <c r="E121" s="4" t="inlineStr">
+        <is>
+          <t>지지율이 떨어지는 가운데 알레시오는 약속대로 퀴리날레에 사표를 낸다. '킨키나투스는 16일 만에 쟁기로 돌아갔다.' 반년 뒤 조기 총선이 확정된다.</t>
+        </is>
+      </c>
+      <c r="F121" s="4" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="9" t="inlineStr">
         <is>
-          <t>6부 7화</t>
+          <t>6부 1화</t>
         </is>
       </c>
       <c r="B122" s="9" t="inlineStr">
         <is>
-          <t>배후 수사</t>
+          <t>연정의 균열</t>
         </is>
       </c>
       <c r="C122" s="9" t="inlineStr">
         <is>
-          <t>Le indagini</t>
+          <t>La crepa nella maggioranza</t>
         </is>
       </c>
       <c r="D122" s="9" t="inlineStr">
         <is>
-          <t>6부 7화 변형</t>
+          <t>6부 1화 변형</t>
         </is>
       </c>
       <c r="E122" s="9" t="inlineStr">
         <is>
-          <t>(친구 시점) 실행범이 특정되자 파올로는 자신이 나른 봉투의 수취 회사명을 뉴스에서 본다. 그날부터 그는 브란카티의 송금 기록을 몰래 복사한다.</t>
+          <t>[2029 법정] '카타니아 당대회 전 대금을 누가 전달했나.' '제가.' '그 사실을 리날디에게 언제 말했나.' '2021년 7월. 그는 검찰에 넘기지 않았습니다.' 방청석이 술렁인다. 2020년, 콜라산티가 역외 수용과 총리 직선제를 내걸고 연정을 깬다.</t>
         </is>
       </c>
       <c r="F122" s="9" t="inlineStr"/>
@@ -7260,27 +7284,27 @@
     <row r="123">
       <c r="A123" s="9" t="inlineStr">
         <is>
-          <t>6부 8화</t>
+          <t>6부 2화</t>
         </is>
       </c>
       <c r="B123" s="9" t="inlineStr">
         <is>
-          <t>콜라산티의 배후</t>
+          <t>이레네의 신고식</t>
         </is>
       </c>
       <c r="C123" s="9" t="inlineStr">
         <is>
-          <t>Chi c'è dietro Colasanti</t>
+          <t>Il battesimo di Irene</t>
         </is>
       </c>
       <c r="D123" s="9" t="inlineStr">
         <is>
-          <t>6부 8화</t>
+          <t>6부 2화 변형</t>
         </is>
       </c>
       <c r="E123" s="9" t="inlineStr">
         <is>
-          <t>콜라산티 캠프의 정치기술자가 로지와 연결되어 있었음이 드러난다. 콜라산티는 그와 결별한다.</t>
+          <t>알레시오 대신 하원 연단에 선 이레네가 처음으로 혼자 정부를 변론한다. 떨리는 목소리로 레오파르디를 인용한다.</t>
         </is>
       </c>
       <c r="F123" s="9" t="inlineStr"/>
@@ -7288,27 +7312,27 @@
     <row r="124">
       <c r="A124" s="9" t="inlineStr">
         <is>
-          <t>6부 9화</t>
+          <t>6부 3화</t>
         </is>
       </c>
       <c r="B124" s="9" t="inlineStr">
         <is>
-          <t>하원 토론</t>
+          <t>딥페이크 공작</t>
         </is>
       </c>
       <c r="C124" s="9" t="inlineStr">
         <is>
-          <t>Il dibattito in aula</t>
+          <t>L'operazione deepfake</t>
         </is>
       </c>
       <c r="D124" s="9" t="inlineStr">
         <is>
-          <t>6부 9화 변형</t>
+          <t>6부 3화 변형</t>
         </is>
       </c>
       <c r="E124" s="9" t="inlineStr">
         <is>
-          <t>테러 아흐레째 하원 특별 토론. 알레시오는 폭탄을 정치에 쓰지 않겠다고 선언하고 콜라산티도 박수를 친다.</t>
+          <t>(친구 시점) 로지 쪽 정치기술자가 파올로의 사무실에서 알레시오 딥페이크 영상을 시사한다. 파올로는 '선을 넘는다'고 말하지만, 영상은 그날 밤 퍼진다.</t>
         </is>
       </c>
       <c r="F124" s="9" t="inlineStr"/>
@@ -7316,27 +7340,27 @@
     <row r="125">
       <c r="A125" s="9" t="inlineStr">
         <is>
-          <t>6부 10화</t>
+          <t>6부 4화</t>
         </is>
       </c>
       <c r="B125" s="9" t="inlineStr">
         <is>
-          <t>이레네의 회복과 결단</t>
+          <t>감사팀 흔들기</t>
         </is>
       </c>
       <c r="C125" s="9" t="inlineStr">
         <is>
-          <t>Irene si rialza</t>
+          <t>L'attacco alla Bussola</t>
         </is>
       </c>
       <c r="D125" s="9" t="inlineStr">
         <is>
-          <t>6부 10화</t>
+          <t>6부 4화</t>
         </is>
       </c>
       <c r="E125" s="9" t="inlineStr">
         <is>
-          <t>퇴원한 이레네가 팔에 붕대를 감은 채 마지막 연단에 설지 스스로 결정한다.</t>
+          <t>«Bussola» 시절 고객 건을 비튼 조작 스캔들이 터진다. 욜란다는 '30년 장부'를 통째로 공개하자고 한다.</t>
         </is>
       </c>
       <c r="F125" s="9" t="inlineStr"/>
@@ -7344,27 +7368,27 @@
     <row r="126">
       <c r="A126" s="9" t="inlineStr">
         <is>
-          <t>6부 11화</t>
+          <t>6부 5화</t>
         </is>
       </c>
       <c r="B126" s="9" t="inlineStr">
         <is>
-          <t>선거 침묵의 날</t>
+          <t>원점 순회</t>
         </is>
       </c>
       <c r="C126" s="9" t="inlineStr">
         <is>
-          <t>Il silenzio elettorale</t>
+          <t>Il giro delle origini</t>
         </is>
       </c>
       <c r="D126" s="9" t="inlineStr">
         <is>
-          <t>6부 11화</t>
+          <t>6부 5화 변형</t>
         </is>
       </c>
       <c r="E126" s="9" t="inlineStr">
         <is>
-          <t>모든 운동이 끝난 밤. 노라와 베니아미노는 욜란다의 빈 책상에 모카포트를 올려놓는다.</t>
+          <t>알레시오는 토레네라와 어촌, 벙커 법정 옆 협동조합을 다시 찾는다. 회개자의 아내에게 '이제 누구도 당신 가족을 건드리지 못하게 하겠다'고 약속한다 — 방법은 말하지 않는다.</t>
         </is>
       </c>
       <c r="F126" s="9" t="inlineStr"/>
@@ -7372,223 +7396,223 @@
     <row r="127">
       <c r="A127" s="9" t="inlineStr">
         <is>
+          <t>6부 6화</t>
+        </is>
+      </c>
+      <c r="B127" s="9" t="inlineStr">
+        <is>
+          <t>당대회장 폭탄</t>
+        </is>
+      </c>
+      <c r="C127" s="9" t="inlineStr">
+        <is>
+          <t>La bomba al congresso</t>
+        </is>
+      </c>
+      <c r="D127" s="9" t="inlineStr">
+        <is>
+          <t>6부 6화 변형</t>
+        </is>
+      </c>
+      <c r="E127" s="9" t="inlineStr">
+        <is>
+          <t>카타니아 당대회에 처음 현장을 보러 온 욜란다가 폭발에 휘말려 숨지고, 이레네가 중상을 입는다. 무대 뒤 알레시오의 셔츠에 욜란다의 보온병이 쏟아져 있다.</t>
+        </is>
+      </c>
+      <c r="F127" s="9" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="9" t="inlineStr">
+        <is>
+          <t>6부 7화</t>
+        </is>
+      </c>
+      <c r="B128" s="9" t="inlineStr">
+        <is>
+          <t>배후 수사</t>
+        </is>
+      </c>
+      <c r="C128" s="9" t="inlineStr">
+        <is>
+          <t>Le indagini</t>
+        </is>
+      </c>
+      <c r="D128" s="9" t="inlineStr">
+        <is>
+          <t>6부 7화 변형</t>
+        </is>
+      </c>
+      <c r="E128" s="9" t="inlineStr">
+        <is>
+          <t>(친구 시점) 실행범이 특정되자 파올로는 자신이 나른 봉투의 수취 회사명을 뉴스에서 본다. 그날부터 그는 브란카티의 송금 기록을 몰래 복사한다.</t>
+        </is>
+      </c>
+      <c r="F128" s="9" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="9" t="inlineStr">
+        <is>
+          <t>6부 8화</t>
+        </is>
+      </c>
+      <c r="B129" s="9" t="inlineStr">
+        <is>
+          <t>절차는 사치</t>
+        </is>
+      </c>
+      <c r="C129" s="9" t="inlineStr">
+        <is>
+          <t>La procedura è un lusso</t>
+        </is>
+      </c>
+      <c r="D129" s="9" t="inlineStr">
+        <is>
+          <t>6부 8화 변형</t>
+        </is>
+      </c>
+      <c r="E129" s="9" t="inlineStr">
+        <is>
+          <t>이레네의 병상 곁에서 알레시오가 리나에게 말한다. '이제 절차는 사치야. 누가 했는지 나는 안다.' 같은 날 콜라산티 캠프의 정치기술자가 로지와 연결된 사실이 드러난다.</t>
+        </is>
+      </c>
+      <c r="F129" s="9" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="9" t="inlineStr">
+        <is>
+          <t>6부 9화</t>
+        </is>
+      </c>
+      <c r="B130" s="9" t="inlineStr">
+        <is>
+          <t>하원 토론</t>
+        </is>
+      </c>
+      <c r="C130" s="9" t="inlineStr">
+        <is>
+          <t>Il dibattito in aula</t>
+        </is>
+      </c>
+      <c r="D130" s="9" t="inlineStr">
+        <is>
+          <t>6부 9화 반전</t>
+        </is>
+      </c>
+      <c r="E130" s="9" t="inlineStr">
+        <is>
+          <t>테러 아흐레째 하원 특별 토론. 원작과 반대로 알레시오는 폭탄을 정면으로 정치에 쓴다 — «Salus populi suprema lex esto.» 콜라산티는 다른 이유로 박수를 치고, 지지율이 치솟는다.</t>
+        </is>
+      </c>
+      <c r="F130" s="9" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="9" t="inlineStr">
+        <is>
+          <t>6부 10화</t>
+        </is>
+      </c>
+      <c r="B131" s="9" t="inlineStr">
+        <is>
+          <t>이레네의 회복과 결단</t>
+        </is>
+      </c>
+      <c r="C131" s="9" t="inlineStr">
+        <is>
+          <t>Irene si rialza</t>
+        </is>
+      </c>
+      <c r="D131" s="9" t="inlineStr">
+        <is>
+          <t>6부 10화 변형</t>
+        </is>
+      </c>
+      <c r="E131" s="9" t="inlineStr">
+        <is>
+          <t>퇴원한 이레네가 팔에 붕대를 감은 채 연단에 서기 전, 키케로 인용을 거둬 달라고 부탁한다. 알레시오는 '키케로는 공화국을 구했다'며 거절한다.</t>
+        </is>
+      </c>
+      <c r="F131" s="9" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="9" t="inlineStr">
+        <is>
+          <t>6부 11화</t>
+        </is>
+      </c>
+      <c r="B132" s="9" t="inlineStr">
+        <is>
+          <t>선거 침묵의 날</t>
+        </is>
+      </c>
+      <c r="C132" s="9" t="inlineStr">
+        <is>
+          <t>Il silenzio elettorale</t>
+        </is>
+      </c>
+      <c r="D132" s="9" t="inlineStr">
+        <is>
+          <t>6부 11화 변형</t>
+        </is>
+      </c>
+      <c r="E132" s="9" t="inlineStr">
+        <is>
+          <t>모든 운동이 끝난 밤. 노라와 베니아미노가 욜란다의 빈 책상에 모카포트를 올려놓는다. 알레시오는 오기로 했지만 오지 않는다.</t>
+        </is>
+      </c>
+      <c r="F132" s="9" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="9" t="inlineStr">
+        <is>
           <t>6부 12화</t>
         </is>
       </c>
-      <c r="B127" s="9" t="inlineStr">
+      <c r="B133" s="9" t="inlineStr">
         <is>
           <t>두 번째 조각</t>
         </is>
       </c>
-      <c r="C127" s="9" t="inlineStr">
+      <c r="C133" s="9" t="inlineStr">
         <is>
           <t>Il secondo incarico</t>
         </is>
       </c>
-      <c r="D127" s="9" t="inlineStr">
-        <is>
-          <t>6부 12화 변형</t>
-        </is>
-      </c>
-      <c r="E127" s="9" t="inlineStr">
-        <is>
-          <t>연합이 다시 과반을 얻고 퀴리날레가 두 번째 조각을 맡긴다. 콜라산티는 승복하고 야당에 남기로 한다.</t>
-        </is>
-      </c>
-      <c r="F127" s="9" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="4" t="inlineStr">
-        <is>
-          <t>7부 1화</t>
-        </is>
-      </c>
-      <c r="B128" s="4" t="inlineStr">
-        <is>
-          <t>두 번째 정부</t>
-        </is>
-      </c>
-      <c r="C128" s="4" t="inlineStr">
-        <is>
-          <t>Il secondo governo</t>
-        </is>
-      </c>
-      <c r="D128" s="4" t="inlineStr">
-        <is>
-          <t>7부 1화 변형</t>
-        </is>
-      </c>
-      <c r="E128" s="4" t="inlineStr">
-        <is>
-          <t>[2029 법정] '2021년 선거 연기안은 누구의 생각이었나.' '브란카티. 저는 전달자였습니다.' 두 번째 선서 한 달 뒤, 욜란다의 부재가 국정 곳곳에 드리운다.</t>
-        </is>
-      </c>
-      <c r="F128" s="4" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="4" t="inlineStr">
-        <is>
-          <t>7부 2화</t>
-        </is>
-      </c>
-      <c r="B129" s="4" t="inlineStr">
-        <is>
-          <t>복합 위기</t>
-        </is>
-      </c>
-      <c r="C129" s="4" t="inlineStr">
-        <is>
-          <t>La crisi perfetta</t>
-        </is>
-      </c>
-      <c r="D129" s="4" t="inlineStr">
-        <is>
-          <t>7부 2화</t>
-        </is>
-      </c>
-      <c r="E129" s="4" t="inlineStr">
-        <is>
-          <t>박물관과 성당을 노린 연쇄 폭탄과 국채 스프레드 공격이 한 주에 겹치자 안보위원회가 소집된다.</t>
-        </is>
-      </c>
-      <c r="F129" s="4" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="4" t="inlineStr">
-        <is>
-          <t>7부 3화</t>
-        </is>
-      </c>
-      <c r="B130" s="4" t="inlineStr">
-        <is>
-          <t>특별법의 유혹</t>
-        </is>
-      </c>
-      <c r="C130" s="4" t="inlineStr">
-        <is>
-          <t>La tentazione delle leggi speciali</t>
-        </is>
-      </c>
-      <c r="D130" s="4" t="inlineStr">
-        <is>
-          <t>7부 3화</t>
-        </is>
-      </c>
-      <c r="E130" s="4" t="inlineStr">
-        <is>
-          <t>라디체가 특별 조치를 '전복 세력'에 넓히는 긴급 법령안을 올린다. 명단엔 야당 운동과 해상 구조 NGO도 있다.</t>
-        </is>
-      </c>
-      <c r="F130" s="4" t="inlineStr"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="4" t="inlineStr">
-        <is>
-          <t>7부 4화</t>
-        </is>
-      </c>
-      <c r="B131" s="4" t="inlineStr">
-        <is>
-          <t>선거 연기 논의</t>
-        </is>
-      </c>
-      <c r="C131" s="4" t="inlineStr">
-        <is>
-          <t>Rinviare il voto</t>
-        </is>
-      </c>
-      <c r="D131" s="4" t="inlineStr">
-        <is>
-          <t>7부 4화 변형</t>
-        </is>
-      </c>
-      <c r="E131" s="4" t="inlineStr">
-        <is>
-          <t>(친구 시점) 파올로가 라디체 내무장관과의 비공개 오찬에서 치안을 이유로 지방선거를 미루자는 로지의 안을 건넨다. 안은 이튿날 공식 테이블에 오른다.</t>
-        </is>
-      </c>
-      <c r="F131" s="4" t="inlineStr"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="4" t="inlineStr">
-        <is>
-          <t>7부 5화</t>
-        </is>
-      </c>
-      <c r="B132" s="4" t="inlineStr">
-        <is>
-          <t>언론 통제의 유혹</t>
-        </is>
-      </c>
-      <c r="C132" s="4" t="inlineStr">
-        <is>
-          <t>La tentazione del bavaglio</t>
-        </is>
-      </c>
-      <c r="D132" s="4" t="inlineStr">
-        <is>
-          <t>7부 5화</t>
-        </is>
-      </c>
-      <c r="E132" s="4" t="inlineStr">
-        <is>
-          <t>폭탄 위협을 부풀린 허위정보가 퍼지자 신문사에 행정 금지명령을 내리고 사이트를 차단하자는 안이 나온다.</t>
-        </is>
-      </c>
-      <c r="F132" s="4" t="inlineStr"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="4" t="inlineStr">
-        <is>
-          <t>7부 6화</t>
-        </is>
-      </c>
-      <c r="B133" s="4" t="inlineStr">
-        <is>
-          <t>감사팀에게 부탁</t>
-        </is>
-      </c>
-      <c r="C133" s="4" t="inlineStr">
-        <is>
-          <t>Un favore alla Bussola</t>
-        </is>
-      </c>
-      <c r="D133" s="4" t="inlineStr">
-        <is>
-          <t>7부 6화</t>
-        </is>
-      </c>
-      <c r="E133" s="4" t="inlineStr">
-        <is>
-          <t>민방위 조달 감사가 불편한 사실을 찾아낸다. 알레시오는 노라에게 발표를 두 주만 미뤄 달라고 부탁한다.</t>
-        </is>
-      </c>
-      <c r="F133" s="4" t="inlineStr"/>
+      <c r="D133" s="9" t="inlineStr">
+        <is>
+          <t>6부 12화 반전</t>
+        </is>
+      </c>
+      <c r="E133" s="9" t="inlineStr">
+        <is>
+          <t>공포 위의 압승. 조각을 맡기며 베르티 대통령은 말한다. '1948년 우리는 헌법에 비상조항을 넣지 않았습니다. 공포를 위한 조항은 없어요.' 알레시오는 '그럼 만들면 됩니다'라고 답한다.</t>
+        </is>
+      </c>
+      <c r="F133" s="9" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>7부 7화</t>
+          <t>7부 1화</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>작은 월권</t>
+          <t>두 번째 정부</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>Un piccolo abuso</t>
+          <t>Il secondo governo</t>
         </is>
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>7부 7화</t>
+          <t>7부 1화 변형</t>
         </is>
       </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t>새 폭탄 경보가 울린 밤, 알레시오는 한 기자와 구조선 활동가의 휴대전화에 스파이웨어 감청을 구두로 승인한다.</t>
+          <t>[2029 법정] 재판장이 공소 사실을 읽고 카메라가 처음 피고인석을 비춘다 — 리날디 살해 혐의의 실행범과 조직자, 니노 살레미. 그는 피해자였다. 변호인: '비상 법령 초안은 누가 썼나.' '그가 불렀고 제가 쳤습니다.' '그러니까 괴물은 리날디였군요.' 2021년, 토레네라 거리에 군이 늘어난다.</t>
         </is>
       </c>
       <c r="F134" s="4" t="inlineStr"/>
@@ -7596,27 +7620,27 @@
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>7부 8화</t>
+          <t>7부 2화</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>이레네의 정면 대결</t>
+          <t>복합 위기</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>Irene contro Alessio</t>
+          <t>La crisi perfetta</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>7부 8화</t>
+          <t>7부 2화</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>감청 사실을 안 이레네와 리나가 총리실에서 알레시오에게 처음으로 공개적으로 반기를 든다.</t>
+          <t>박물관과 성당을 노린 연쇄 폭탄과 국채 스프레드 공격이 한 주에 겹치자 안보위원회가 소집된다.</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr"/>
@@ -7624,27 +7648,27 @@
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>7부 9화</t>
+          <t>7부 3화</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>벨란디의 수첩</t>
+          <t>첫 번째 법령</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>Le agende di Bellandi</t>
+          <t>Il primo decreto</t>
         </is>
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>7부 9화</t>
+          <t>7부 3화 반전</t>
         </is>
       </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t>알레시오는 지타를 찾아가 벨란디의 옛 수첩을 편다. '예외는 늘 가장 좋은 이유로 온다'는 문장이 있다.</t>
+          <t>첫 긴급 법령: 반마피아 예방 조치를 '헌정 전복 위해 세력'으로 넓힌다. 전환 법안에 신임 문제를 걸어 표결을 봉쇄하자 강경파 라디체마저 '내 안보다 넓다'며 놀란다. 대통령은 닷새 동안 서명을 미룬다.</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr"/>
@@ -7652,27 +7676,27 @@
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>7부 10화</t>
+          <t>7부 4화</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>공중전화</t>
+          <t>부름</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>Il telefono pubblico</t>
+          <t>La chiamata</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>7부 10화 변형</t>
+          <t>7부 4화 반전</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>(친구 시점) 가장 큰 폭탄 위협의 밤, 장소를 안 파올로가 공중전화로 익명 제보를 한다. 알레시오는 긴급 법령에 서명하지 않고 통상 절차로 폭탄을 막는다.</t>
+          <t>(친구 시점) 10년 만에 총리실에서 전화가 온다. '로지가 어떻게 했는지 알려 줘.' 파올로는 폭탄 자금 사본을 내밀고 그의 사람이 된다. 알레시오는 사본을 검찰이 아니라 금고에 넣는다 — 풀리지 않은 위협이 비상을 지켜 주니까.</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr"/>
@@ -7680,27 +7704,27 @@
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
         <is>
-          <t>7부 11화</t>
+          <t>7부 5화</t>
         </is>
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>정치적 대가</t>
+          <t>물과 질서</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>Il prezzo politico</t>
+          <t>Acqua e ordine</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>7부 11화</t>
+          <t>7부 5화 변형</t>
         </is>
       </c>
       <c r="E138" s="4" t="inlineStr">
         <is>
-          <t>위협은 막았지만 강경파는 '나약한 총리'라 공격하고 지지율이 흔들린다. 그리말디가 처음 자랑스럽다고 한다.</t>
+          <t>시칠리아 가뭄 비상사태(민방위법)가 '공공질서 위기'까지 늘어나고, 코로나 시절처럼 총리령(DPCM)이 의회를 건너뛴다. 12개월 뒤 다시 12개월 연장이 이미 계획표에 있다.</t>
         </is>
       </c>
       <c r="F138" s="4" t="inlineStr"/>
@@ -7708,223 +7732,223 @@
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
         <is>
+          <t>7부 6화</t>
+        </is>
+      </c>
+      <c r="B139" s="4" t="inlineStr">
+        <is>
+          <t>재발령</t>
+        </is>
+      </c>
+      <c r="C139" s="4" t="inlineStr">
+        <is>
+          <t>La reiterazione</t>
+        </is>
+      </c>
+      <c r="D139" s="4" t="inlineStr">
+        <is>
+          <t>7부 6화 반전</t>
+        </is>
+      </c>
+      <c r="E139" s="4" t="inlineStr">
+        <is>
+          <t>첫 법령이 60일 안에 전환되지 못하고 실효되자 알레시오는 거의 같은 법령을 다시 올리고, 대통령이 1996년 헌재 판례를 들어 서명을 거부한다. 같은 주 노라는 민방위 조달 감사 발표를 미뤄 달라는 부탁을 거절하고, 계약이 끊긴다.</t>
+        </is>
+      </c>
+      <c r="F139" s="4" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="4" t="inlineStr">
+        <is>
+          <t>7부 7화</t>
+        </is>
+      </c>
+      <c r="B140" s="4" t="inlineStr">
+        <is>
+          <t>작은 월권</t>
+        </is>
+      </c>
+      <c r="C140" s="4" t="inlineStr">
+        <is>
+          <t>Un piccolo abuso</t>
+        </is>
+      </c>
+      <c r="D140" s="4" t="inlineStr">
+        <is>
+          <t>7부 7화 반전</t>
+        </is>
+      </c>
+      <c r="E140" s="4" t="inlineStr">
+        <is>
+          <t>새 폭탄 경보의 밤, 알레시오는 한 기자와 구조선 활동가의 휴대전화에 로마 항소법원 검찰총장의 승인 없이 스파이웨어 감청을 구두로 명령한다. 리나가 막아서자 '나는 그들이 누군지 안다.' 작은 월권은 첫걸음이 된다.</t>
+        </is>
+      </c>
+      <c r="F140" s="4" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="4" t="inlineStr">
+        <is>
+          <t>7부 8화</t>
+        </is>
+      </c>
+      <c r="B141" s="4" t="inlineStr">
+        <is>
+          <t>이레네의 정면 대결</t>
+        </is>
+      </c>
+      <c r="C141" s="4" t="inlineStr">
+        <is>
+          <t>Irene contro Alessio</t>
+        </is>
+      </c>
+      <c r="D141" s="4" t="inlineStr">
+        <is>
+          <t>7부 8화 변형</t>
+        </is>
+      </c>
+      <c r="E141" s="4" t="inlineStr">
+        <is>
+          <t>감청 사실을 안 이레네와 리나가 반기를 든다. 이레네: '키케로는 재판 없이 카틸리나 일당을 처형했어요. 그다음에 무슨 일이 있었는지 아시죠.' 알레시오: '킨키나투스에겐 쟁기가 있었지. 나한텐 폭탄이 있어.'</t>
+        </is>
+      </c>
+      <c r="F141" s="4" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="4" t="inlineStr">
+        <is>
+          <t>7부 9화</t>
+        </is>
+      </c>
+      <c r="B142" s="4" t="inlineStr">
+        <is>
+          <t>벨란디의 수첩</t>
+        </is>
+      </c>
+      <c r="C142" s="4" t="inlineStr">
+        <is>
+          <t>Le agende di Bellandi</t>
+        </is>
+      </c>
+      <c r="D142" s="4" t="inlineStr">
+        <is>
+          <t>7부 9화 반전</t>
+        </is>
+      </c>
+      <c r="E142" s="4" t="inlineStr">
+        <is>
+          <t>지타가 벨란디의 수첩을 건넨다. 알레시오는 영장 없는 '귀동냥'의 기록을 정당화로 읽고, 마지막 장 — '예외는 늘 가장 좋은 이유로 온다' — 을 찢어 주머니에 넣는다. 지타는 커피를 기다리지 않고 떠난다.</t>
+        </is>
+      </c>
+      <c r="F142" s="4" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="4" t="inlineStr">
+        <is>
+          <t>7부 10화</t>
+        </is>
+      </c>
+      <c r="B143" s="4" t="inlineStr">
+        <is>
+          <t>공중전화</t>
+        </is>
+      </c>
+      <c r="C143" s="4" t="inlineStr">
+        <is>
+          <t>Il telefono pubblico</t>
+        </is>
+      </c>
+      <c r="D143" s="4" t="inlineStr">
+        <is>
+          <t>7부 10화 반전</t>
+        </is>
+      </c>
+      <c r="E143" s="4" t="inlineStr">
+        <is>
+          <t>(친구 시점) 가장 큰 폭탄 위협의 밤, 파올로가 로지 선에서 들은 장소를 총리에게 직접 전한다. 폭탄은 막히지만 알레시오는 카메라 앞에서 '스파이웨어 덕분'이라 말하고, 파올로는 자기 이름이 지워진 공을 본다.</t>
+        </is>
+      </c>
+      <c r="F143" s="4" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="4" t="inlineStr">
+        <is>
+          <t>7부 11화</t>
+        </is>
+      </c>
+      <c r="B144" s="4" t="inlineStr">
+        <is>
+          <t>루비콘</t>
+        </is>
+      </c>
+      <c r="C144" s="4" t="inlineStr">
+        <is>
+          <t>Il Rubicone</t>
+        </is>
+      </c>
+      <c r="D144" s="4" t="inlineStr">
+        <is>
+          <t>7부 11화 반전</t>
+        </is>
+      </c>
+      <c r="E144" s="4" t="inlineStr">
+        <is>
+          <t>'제78조의2(국가 비상사태)' 개헌안. 하원은 공포에 질린 야당까지 3분의 2로 통과시키지만 상원은 세 표가 모자라고, 그리말디가 반대표를 던진다. 야당 상원의원 5분의 1이 국민투표를 청구하자 알레시오는 '주사위는 던져졌다'.</t>
+        </is>
+      </c>
+      <c r="F144" s="4" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="4" t="inlineStr">
+        <is>
           <t>7부 12화</t>
         </is>
       </c>
-      <c r="B139" s="4" t="inlineStr">
-        <is>
-          <t>새로운 균형</t>
-        </is>
-      </c>
-      <c r="C139" s="4" t="inlineStr">
-        <is>
-          <t>Un nuovo equilibrio</t>
-        </is>
-      </c>
-      <c r="D139" s="4" t="inlineStr">
-        <is>
-          <t>7부 12화</t>
-        </is>
-      </c>
-      <c r="E139" s="4" t="inlineStr">
-        <is>
-          <t>알레시오는 모든 특별 조치에 일몰 조항과 의회 사전 승인을 거는 위기위원회 법을 발표한다.</t>
-        </is>
-      </c>
-      <c r="F139" s="4" t="inlineStr"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="9" t="inlineStr">
-        <is>
-          <t>8부 1화</t>
-        </is>
-      </c>
-      <c r="B140" s="9" t="inlineStr">
-        <is>
-          <t>권력의 한계</t>
-        </is>
-      </c>
-      <c r="C140" s="9" t="inlineStr">
-        <is>
-          <t>I limiti del potere</t>
-        </is>
-      </c>
-      <c r="D140" s="9" t="inlineStr">
-        <is>
-          <t>8부 1화 변형</t>
-        </is>
-      </c>
-      <c r="E140" s="9" t="inlineStr">
-        <is>
-          <t>[2029 법정] '브란카티가 출국하던 날 당신은 어디 있었나.' 위기위원회 법 통과 직후, 알레시오는 총리 직선제 요구를 물리치고 「권력의 한계」 법 착수를 발표한다.</t>
-        </is>
-      </c>
-      <c r="F140" s="9" t="inlineStr"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="9" t="inlineStr">
-        <is>
-          <t>8부 2화</t>
-        </is>
-      </c>
-      <c r="B141" s="9" t="inlineStr">
-        <is>
-          <t>팀의 재편</t>
-        </is>
-      </c>
-      <c r="C141" s="9" t="inlineStr">
-        <is>
-          <t>La squadra si ricompone</t>
-        </is>
-      </c>
-      <c r="D141" s="9" t="inlineStr">
-        <is>
-          <t>8부 2화</t>
-        </is>
-      </c>
-      <c r="E141" s="9" t="inlineStr">
-        <is>
-          <t>욜란다 없이 38명 청이 된 투명성청의 첫 개편. 그녀의 책상에서 «Non dimenticare il caffè» 카드가 나온다.</t>
-        </is>
-      </c>
-      <c r="F141" s="9" t="inlineStr"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="9" t="inlineStr">
-        <is>
-          <t>8부 3화</t>
-        </is>
-      </c>
-      <c r="B142" s="9" t="inlineStr">
-        <is>
-          <t>돌아온 증인들</t>
-        </is>
-      </c>
-      <c r="C142" s="9" t="inlineStr">
-        <is>
-          <t>I testimoni che tornano</t>
-        </is>
-      </c>
-      <c r="D142" s="9" t="inlineStr">
-        <is>
-          <t>8부 3화 변형</t>
-        </is>
-      </c>
-      <c r="E142" s="9" t="inlineStr">
-        <is>
-          <t>(친구 시점) 파올로가 보호 프로그램에서 버려져 고향에 돌아온 회개자의 아내를 찾아간다. 자신이 은신처를 흘렸던 그 가족의 부엌에서 그는 증인의 삶을 본다.</t>
-        </is>
-      </c>
-      <c r="F142" s="9" t="inlineStr"/>
-    </row>
-    <row r="143">
-      <c r="A143" s="9" t="inlineStr">
-        <is>
-          <t>8부 4화</t>
-        </is>
-      </c>
-      <c r="B143" s="9" t="inlineStr">
-        <is>
-          <t>세대교체</t>
-        </is>
-      </c>
-      <c r="C143" s="9" t="inlineStr">
-        <is>
-          <t>Il cambio di generazione</t>
-        </is>
-      </c>
-      <c r="D143" s="9" t="inlineStr">
-        <is>
-          <t>8부 4화</t>
-        </is>
-      </c>
-      <c r="E143" s="9" t="inlineStr">
-        <is>
-          <t>알레시오는 핵심 요직 열두 자리를 측근 명단이 아닌 익명 공개 경쟁으로 뽑는다. 청년 알레나가 1위를 한다.</t>
-        </is>
-      </c>
-      <c r="F143" s="9" t="inlineStr"/>
-    </row>
-    <row r="144">
-      <c r="A144" s="9" t="inlineStr">
-        <is>
-          <t>8부 5화</t>
-        </is>
-      </c>
-      <c r="B144" s="9" t="inlineStr">
-        <is>
-          <t>크리벨리와의 마지막 대화</t>
-        </is>
-      </c>
-      <c r="C144" s="9" t="inlineStr">
-        <is>
-          <t>L'ultimo colloquio con Crivelli</t>
-        </is>
-      </c>
-      <c r="D144" s="9" t="inlineStr">
-        <is>
-          <t>8부 5화</t>
-        </is>
-      </c>
-      <c r="E144" s="9" t="inlineStr">
-        <is>
-          <t>스파이웨어 계약과 불법 신상 조회망을 걷어내는 법안을 앞두고, 알레시오가 은퇴한 크리벨리를 찾아간다.</t>
-        </is>
-      </c>
-      <c r="F144" s="9" t="inlineStr"/>
-    </row>
-    <row r="145">
-      <c r="A145" s="9" t="inlineStr">
-        <is>
-          <t>8부 6화</t>
-        </is>
-      </c>
-      <c r="B145" s="9" t="inlineStr">
-        <is>
-          <t>이레네에게 실권을</t>
-        </is>
-      </c>
-      <c r="C145" s="9" t="inlineStr">
-        <is>
-          <t>Il potere a Irene</t>
-        </is>
-      </c>
-      <c r="D145" s="9" t="inlineStr">
-        <is>
-          <t>8부 6화</t>
-        </is>
-      </c>
-      <c r="E145" s="9" t="inlineStr">
-        <is>
-          <t>노후 교량·수도망 위기 속에 알레시오는 이레네에게 확대된 실권을 넘기고, 야당은 헌재에 제소한다.</t>
-        </is>
-      </c>
-      <c r="F145" s="9" t="inlineStr"/>
+      <c r="B145" s="4" t="inlineStr">
+        <is>
+          <t>국민의 이름으로</t>
+        </is>
+      </c>
+      <c r="C145" s="4" t="inlineStr">
+        <is>
+          <t>In nome del popolo</t>
+        </is>
+      </c>
+      <c r="D145" s="4" t="inlineStr">
+        <is>
+          <t>7부 12화 반전</t>
+        </is>
+      </c>
+      <c r="E145" s="4" t="inlineStr">
+        <is>
+          <t>공포의 캠페인 끝에 확정 국민투표 58% 찬성. 대통령은 공포하며 양원에 메시지를 보내 '최고 원리는 개정할 수 없다'고 경고한다. 이레네가 차관직을 내려놓고 총리실을 나선다.</t>
+        </is>
+      </c>
+      <c r="F145" s="4" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="9" t="inlineStr">
         <is>
-          <t>8부 7화</t>
+          <t>8부 1화</t>
         </is>
       </c>
       <c r="B146" s="9" t="inlineStr">
         <is>
-          <t>요니카의 빚</t>
+          <t>비상사태 선포</t>
         </is>
       </c>
       <c r="C146" s="9" t="inlineStr">
         <is>
-          <t>I debiti della Ionica</t>
+          <t>Lo stato d'emergenza</t>
         </is>
       </c>
       <c r="D146" s="9" t="inlineStr">
         <is>
-          <t>8부 7화</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="E146" s="9" t="inlineStr">
         <is>
-          <t>레조네 요니카의 숨겨진 의료 부채로 교사 월급이 위태롭다. 마리나 페를리토가 주지사 선거에 나선다.</t>
+          <t>[2029 법정] '비상 체제에서 당신의 직함은 무엇이었나.' '없었습니다. 그게 제 직함이었죠.' 2022년 가을, '제78조의2'에 따른 첫 국가 비상사태가 선포되고 방송은 총리 대신 초침만 비춘다.</t>
         </is>
       </c>
       <c r="F146" s="9" t="inlineStr"/>
@@ -7932,27 +7956,27 @@
     <row r="147">
       <c r="A147" s="9" t="inlineStr">
         <is>
-          <t>8부 8화</t>
+          <t>8부 2화</t>
         </is>
       </c>
       <c r="B147" s="9" t="inlineStr">
         <is>
-          <t>마지막 정치적 결전</t>
+          <t>면회실</t>
         </is>
       </c>
       <c r="C147" s="9" t="inlineStr">
         <is>
-          <t>L'ultima battaglia politica</t>
+          <t>Il parlatorio</t>
         </is>
       </c>
       <c r="D147" s="9" t="inlineStr">
         <is>
-          <t>8부 8화</t>
+          <t>8부 2화 반전</t>
         </is>
       </c>
       <c r="E147" s="9" t="inlineStr">
         <is>
-          <t>구체제 잔존 세력이 헌재·의회·언론·검찰 네 전선에서 총공세를 편다. 카를로가 12년 전 과오를 증언한다.</t>
+          <t>(친구 시점) 해결사 파올로가 교도소 면회실에서 니노 살레미를 만난다. 아버지의 41-bis를 풀어 주는 대가로 항만의 '질서'와 NGO·반대파 정보. 집에 돌아온 파올로는 오늘의 지시를 복사한다. 총리 서랍엔 욜란다의 카드가 읽히지 않은 채 있다.</t>
         </is>
       </c>
       <c r="F147" s="9" t="inlineStr"/>
@@ -7960,27 +7984,27 @@
     <row r="148">
       <c r="A148" s="9" t="inlineStr">
         <is>
-          <t>8부 9화</t>
+          <t>8부 3화</t>
         </is>
       </c>
       <c r="B148" s="9" t="inlineStr">
         <is>
-          <t>법안의 최종 완성</t>
+          <t>검문소</t>
         </is>
       </c>
       <c r="C148" s="9" t="inlineStr">
         <is>
-          <t>La legge compiuta</t>
+          <t>Il posto di blocco</t>
         </is>
       </c>
       <c r="D148" s="9" t="inlineStr">
         <is>
-          <t>8부 9화</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="E148" s="9" t="inlineStr">
         <is>
-          <t>카를로가 증언 직후 숨진 뒤 「권력의 한계」 법이 통과된다. '연속 두 번의 입법기' 한계가 재확인된다.</t>
+          <t>토레네라 출신 스무 살 병사의 하루. 검문소에서 옛 담임선생 로사 페란테의 신분증을 받고, 막사 벽의 총리 포스터를 본다. 저녁엔 어머니가 '저 사람이 우리 동네 검사였다'고 말한다.</t>
         </is>
       </c>
       <c r="F148" s="9" t="inlineStr"/>
@@ -7988,27 +8012,27 @@
     <row r="149">
       <c r="A149" s="9" t="inlineStr">
         <is>
-          <t>8부 10화</t>
+          <t>8부 4화</t>
         </is>
       </c>
       <c r="B149" s="9" t="inlineStr">
         <is>
-          <t>욜란다를 기리며</t>
+          <t>편집국</t>
         </is>
       </c>
       <c r="C149" s="9" t="inlineStr">
         <is>
-          <t>In memoria</t>
+          <t>La redazione</t>
         </is>
       </c>
       <c r="D149" s="9" t="inlineStr">
         <is>
-          <t>8부 10화</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="E149" s="9" t="inlineStr">
         <is>
-          <t>추모의 밤, 카드의 뜻이 풀린다. 알레시오는 벨란디도 늘 먼저 커피를 냈음을 떠올리며 같은 원칙이었음을 깨닫는다.</t>
+          <t>«L'Osservatore Siculo» 편집국. 편집장이 살레미 41-bis 거래 기사를 '지금은 아니다'며 내리고, 기자들은 휴대전화를 냉장고에 넣고 회의한다. 키아라의 옛 인턴 루치아만 원고를 지우지 않는다.</t>
         </is>
       </c>
       <c r="F149" s="9" t="inlineStr"/>
@@ -8016,27 +8040,27 @@
     <row r="150">
       <c r="A150" s="9" t="inlineStr">
         <is>
-          <t>8부 11화</t>
+          <t>8부 5화</t>
         </is>
       </c>
       <c r="B150" s="9" t="inlineStr">
         <is>
-          <t>살레미 판결</t>
+          <t>젊은 검사</t>
         </is>
       </c>
       <c r="C150" s="9" t="inlineStr">
         <is>
-          <t>La sentenza Salemi</t>
+          <t>La giovane pm</t>
         </is>
       </c>
       <c r="D150" s="9" t="inlineStr">
         <is>
-          <t>8부 11화</t>
+          <t>8부 4화 변형</t>
         </is>
       </c>
       <c r="E150" s="9" t="inlineStr">
         <is>
-          <t>살레미에게 1심 판결이 내려지고 몰수 자산이 학교와 협동조합으로 돌아간다. 두 사람의 마지막 대면.</t>
+          <t>로마의 젊은 검사 엘레나 사르토리가 승인 없는 스파이웨어 감청 수사를 연다. 비상 인사로 전보되고 감청당한 그녀는 CSM 청문에서 브루노의 말로 전해지는 문장을 읽는다. '선고하는 여러분이 더 떨고 있을지 모릅니다.'</t>
         </is>
       </c>
       <c r="F150" s="9" t="inlineStr"/>
@@ -8044,223 +8068,223 @@
     <row r="151">
       <c r="A151" s="9" t="inlineStr">
         <is>
+          <t>8부 6화</t>
+        </is>
+      </c>
+      <c r="B151" s="9" t="inlineStr">
+        <is>
+          <t>바다에서 쫓겨난 선장</t>
+        </is>
+      </c>
+      <c r="C151" s="9" t="inlineStr">
+        <is>
+          <t>La capitana a terra</t>
+        </is>
+      </c>
+      <c r="D151" s="9" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="E151" s="9" t="inlineStr">
+        <is>
+          <t>구조선 선장이 '위해 인물' 예방 조치로 항구에 묶이고 배는 행정 억류된다. 그날 밤 난파 신호를 받은 해안경비대가 규칙대로 출동해 모두를 건진다. 선장은 무전으로만 듣는다.</t>
+        </is>
+      </c>
+      <c r="F151" s="9" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="9" t="inlineStr">
+        <is>
+          <t>8부 7화</t>
+        </is>
+      </c>
+      <c r="B152" s="9" t="inlineStr">
+        <is>
+          <t>해산된 의회</t>
+        </is>
+      </c>
+      <c r="C152" s="9" t="inlineStr">
+        <is>
+          <t>Il consiglio sciolto</t>
+        </is>
+      </c>
+      <c r="D152" s="9" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="E152" s="9" t="inlineStr">
+        <is>
+          <t>'마피아 침투'를 이유로 토레네라 시의회에 해산 명령. 아녜세의 협동조합을 이은 시장이 쫓겨나고, 이웃의 익명 신고가 근거 서류가 된다. 밀고한 이웃은 급수차 배정 순번을 받는다.</t>
+        </is>
+      </c>
+      <c r="F152" s="9" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="9" t="inlineStr">
+        <is>
+          <t>8부 8화</t>
+        </is>
+      </c>
+      <c r="B153" s="9" t="inlineStr">
+        <is>
+          <t>질서의 값</t>
+        </is>
+      </c>
+      <c r="C153" s="9" t="inlineStr">
+        <is>
+          <t>Il prezzo dell'ordine</t>
+        </is>
+      </c>
+      <c r="D153" s="9" t="inlineStr">
+        <is>
+          <t>3부 9화 반복(신규)</t>
+        </is>
+      </c>
+      <c r="E153" s="9" t="inlineStr">
+        <is>
+          <t>(친구 시점) 수의계약 비상 조달로 니노 살레미의 회사들이 급수차와 방벽 공사를 따낸다. 루치아가 팔코네의 '돈을 따라가라'를 인용하며 파올로에게 논평을 청하고, 그는 커피를 내준 뒤 총리실에 전화를 건다 — 키아라 때처럼.</t>
+        </is>
+      </c>
+      <c r="F153" s="9" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="9" t="inlineStr">
+        <is>
+          <t>8부 9화</t>
+        </is>
+      </c>
+      <c r="B154" s="9" t="inlineStr">
+        <is>
+          <t>두려움의 대상</t>
+        </is>
+      </c>
+      <c r="C154" s="9" t="inlineStr">
+        <is>
+          <t>Temuto</t>
+        </is>
+      </c>
+      <c r="D154" s="9" t="inlineStr">
+        <is>
+          <t>8부 5화 반전</t>
+        </is>
+      </c>
+      <c r="E154" s="9" t="inlineStr">
+        <is>
+          <t>은퇴한 크리벨리의 시점. 총리가 찾아와 로지의 신상 파일망을 다시 짜 달라며 마키아벨리 17장을 인용한다 — '사랑받는 것보다 두려움의 대상이 되는 게 훨씬 안전하다.' '나는 40년 걸렸는데 당신은 3년이군.' 거절.</t>
+        </is>
+      </c>
+      <c r="F154" s="9" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="9" t="inlineStr">
+        <is>
+          <t>8부 10화</t>
+        </is>
+      </c>
+      <c r="B155" s="9" t="inlineStr">
+        <is>
+          <t>굽는 법원</t>
+        </is>
+      </c>
+      <c r="C155" s="9" t="inlineStr">
+        <is>
+          <t>Il giudice che si piega</t>
+        </is>
+      </c>
+      <c r="D155" s="9" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="E155" s="9" t="inlineStr">
+        <is>
+          <t>루치아가 '국가 비상 위해 인물'로 예방 구금된다. 변호사 이레네의 이의를 판사가 '비상 조항에 따라' 기각한다. 법원 계단에서 이레네는 총리의 마키아벨리에 킨키나투스와 가리발디로 답한다.</t>
+        </is>
+      </c>
+      <c r="F155" s="9" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="9" t="inlineStr">
+        <is>
+          <t>8부 11화</t>
+        </is>
+      </c>
+      <c r="B156" s="9" t="inlineStr">
+        <is>
+          <t>루치아</t>
+        </is>
+      </c>
+      <c r="C156" s="9" t="inlineStr">
+        <is>
+          <t>Lucia</t>
+        </is>
+      </c>
+      <c r="D156" s="9" t="inlineStr">
+        <is>
+          <t>4부 7화 반복(신규)</t>
+        </is>
+      </c>
+      <c r="E156" s="9" t="inlineStr">
+        <is>
+          <t>구금 23일째, 루치아의 병원 이송이 '보안 절차'로 하루 지연되고 그녀가 숨진다 — 총리가 서명한 위해 등급. 4부의 아녜세와 같은 방식이다. 어머니 안나는 아들의 전화를 받지 않는다.</t>
+        </is>
+      </c>
+      <c r="F156" s="9" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="9" t="inlineStr">
+        <is>
           <t>8부 12화</t>
         </is>
       </c>
-      <c r="B151" s="9" t="inlineStr">
-        <is>
-          <t>욜란다를 죽인 돈</t>
-        </is>
-      </c>
-      <c r="C151" s="9" t="inlineStr">
-        <is>
-          <t>I soldi che hanno ucciso Iolanda</t>
-        </is>
-      </c>
-      <c r="D151" s="9" t="inlineStr">
-        <is>
-          <t>8부 12화 변형</t>
-        </is>
-      </c>
-      <c r="E151" s="9" t="inlineStr">
-        <is>
-          <t>(친구 시점) 테러 자금의 증거가 끊기자 브란카티가 해외로 떠나며 파올로에게 동행을 권한다. 그는 거절하고, 복사해 둔 장부를 아이 방 벽 속에 숨긴다.</t>
-        </is>
-      </c>
-      <c r="F151" s="9" t="inlineStr"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="4" t="inlineStr">
-        <is>
-          <t>9부 1화</t>
-        </is>
-      </c>
-      <c r="B152" s="4" t="inlineStr">
-        <is>
-          <t>마지막 해</t>
-        </is>
-      </c>
-      <c r="C152" s="4" t="inlineStr">
-        <is>
-          <t>L'ultimo anno</t>
-        </is>
-      </c>
-      <c r="D152" s="4" t="inlineStr">
-        <is>
-          <t>9부 1화 변형</t>
-        </is>
-      </c>
-      <c r="E152" s="4" t="inlineStr">
-        <is>
-          <t>[2029 법정] '리날디 총리 저격 사흘 전 무엇을 알았나.' 방청석이 숨을 죽인다. 1년 전, 두 번째 입법기의 마지막 해가 시작되고 콜라산티가 제1야당 지도자로 돌아온다.</t>
-        </is>
-      </c>
-      <c r="F152" s="4" t="inlineStr"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="4" t="inlineStr">
-        <is>
-          <t>9부 2화</t>
-        </is>
-      </c>
-      <c r="B153" s="4" t="inlineStr">
-        <is>
-          <t>타는 땅</t>
-        </is>
-      </c>
-      <c r="C153" s="4" t="inlineStr">
-        <is>
-          <t>La terra che brucia</t>
-        </is>
-      </c>
-      <c r="D153" s="4" t="inlineStr">
-        <is>
-          <t>9부 2화 변형</t>
-        </is>
-      </c>
-      <c r="E153" s="4" t="inlineStr">
-        <is>
-          <t>급수 제한 비상사태 속 시칠리아에 산불이 번진다. 알레시오는 귀향해 어촌과 1부의 사람들을 다시 만난다.</t>
-        </is>
-      </c>
-      <c r="F153" s="4" t="inlineStr"/>
-    </row>
-    <row r="154">
-      <c r="A154" s="4" t="inlineStr">
-        <is>
-          <t>9부 3화</t>
-        </is>
-      </c>
-      <c r="B154" s="4" t="inlineStr">
-        <is>
-          <t>낙인</t>
-        </is>
-      </c>
-      <c r="C154" s="4" t="inlineStr">
-        <is>
-          <t>Il marchio</t>
-        </is>
-      </c>
-      <c r="D154" s="4" t="inlineStr">
-        <is>
-          <t>9부 3화</t>
-        </is>
-      </c>
-      <c r="E154" s="4" t="inlineStr">
-        <is>
-          <t>치안 법령의 시위 처벌 조항과 시민단체 행정 금지명령 남용, 기자 봉쇄 소송이 폐지 표결에 오른다.</t>
-        </is>
-      </c>
-      <c r="F154" s="4" t="inlineStr"/>
-    </row>
-    <row r="155">
-      <c r="A155" s="4" t="inlineStr">
-        <is>
-          <t>9부 4화</t>
-        </is>
-      </c>
-      <c r="B155" s="4" t="inlineStr">
-        <is>
-          <t>회개자의 재판</t>
-        </is>
-      </c>
-      <c r="C155" s="4" t="inlineStr">
-        <is>
-          <t>Il processo al pentito</t>
-        </is>
-      </c>
-      <c r="D155" s="4" t="inlineStr">
-        <is>
-          <t>9부 4화 변형</t>
-        </is>
-      </c>
-      <c r="E155" s="4" t="inlineStr">
-        <is>
-          <t>(친구 시점) 벨란디 폭탄 가담을 자백한 회개자의 재판을 파올로가 방청석에서 지켜본다. 스크린 뒤의 목소리, 새 이름, 끊긴 가족 — 자기 앞날을 본다.</t>
-        </is>
-      </c>
-      <c r="F155" s="4" t="inlineStr"/>
-    </row>
-    <row r="156">
-      <c r="A156" s="4" t="inlineStr">
-        <is>
-          <t>9부 5화</t>
-        </is>
-      </c>
-      <c r="B156" s="4" t="inlineStr">
-        <is>
-          <t>이레네, 공식 후계자로</t>
-        </is>
-      </c>
-      <c r="C156" s="4" t="inlineStr">
-        <is>
-          <t>Irene, l'erede</t>
-        </is>
-      </c>
-      <c r="D156" s="4" t="inlineStr">
-        <is>
-          <t>9부 5화</t>
-        </is>
-      </c>
-      <c r="E156" s="4" t="inlineStr">
-        <is>
-          <t>연합 경선에서 이레네가 공식 총리 후보로 선출된다. 경선에서 진 주지사는 탈당을 예고한다.</t>
-        </is>
-      </c>
-      <c r="F156" s="4" t="inlineStr"/>
-    </row>
-    <row r="157">
-      <c r="A157" s="4" t="inlineStr">
-        <is>
-          <t>9부 6화</t>
-        </is>
-      </c>
-      <c r="B157" s="4" t="inlineStr">
-        <is>
-          <t>개인적 화해와 정리</t>
-        </is>
-      </c>
-      <c r="C157" s="4" t="inlineStr">
-        <is>
-          <t>Il pellegrinaggio</t>
-        </is>
-      </c>
-      <c r="D157" s="4" t="inlineStr">
-        <is>
-          <t>9부 6화 변형</t>
-        </is>
-      </c>
-      <c r="E157" s="4" t="inlineStr">
-        <is>
-          <t>알레시오는 벨란디, 아버지, 키아라, 아녜세, 다비데의 무덤을 차례로 찾아 매듭짓는다. 살아 있는 친구 파올로에게는 끝내 전화를 걸지 못한다.</t>
-        </is>
-      </c>
-      <c r="F157" s="4" t="inlineStr"/>
+      <c r="B157" s="9" t="inlineStr">
+        <is>
+          <t>마테오티의 날</t>
+        </is>
+      </c>
+      <c r="C157" s="9" t="inlineStr">
+        <is>
+          <t>Il giorno di Matteotti</t>
+        </is>
+      </c>
+      <c r="D157" s="9" t="inlineStr">
+        <is>
+          <t>8부 11화 반전</t>
+        </is>
+      </c>
+      <c r="E157" s="9" t="inlineStr">
+        <is>
+          <t>(친구 시점) 6월 10일, 이레네가 광장에서 마테오티의 마지막 하원 연설을 낭독하고 파올로는 차 안에서 듣는다. 같은 날 살레미가 '건강상 이유'로 병원 가택연금에 옮겨지고, 파올로가 그의 말을 총리에게 전한다. '이제야 서로 이해하는군.'</t>
+        </is>
+      </c>
+      <c r="F157" s="9" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>9부 7화</t>
+          <t>9부 1화</t>
         </is>
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>그림자의 윤곽</t>
+          <t>전쟁이라는 말</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>Il profilo dell'ombra</t>
+          <t>La parola guerra</t>
         </is>
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>9부 7화</t>
+          <t>9부 1화 변형</t>
         </is>
       </c>
       <c r="E158" s="4" t="inlineStr">
         <is>
-          <t>크리벨리가 조용히 숨지고, 알레시오만 장례식에 간다. 그가 남긴 봉투가 브란카티 돈의 윤곽을 드러낸다.</t>
+          <t>[2029 법정] '2024년 11월 그 밤, 리날디는 헌재 결정에 불복하려 했나.' '했습니다. 그리고 하지 않았습니다.' 2023년, 루치아 사망 한 달 뒤 알레시오는 '외국 자금의 하이브리드 전쟁'을 말하기 시작한다.</t>
         </is>
       </c>
       <c r="F158" s="4" t="inlineStr"/>
@@ -8268,27 +8292,27 @@
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>9부 8화</t>
+          <t>9부 2화</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>퇴임을 준비하며</t>
+          <t>제청과 제소</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>Prepararsi all'addio</t>
+          <t>Il rinvio e il ricorso</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>9부 8화 변형</t>
+          <t>8부 7화 변형</t>
         </is>
       </c>
       <c r="E159" s="4" t="inlineStr">
         <is>
-          <t>(친구 시점) 저격 계약 이야기를 들은 파올로가 10년 만에 알레시오를 찾아와 모호하게 경고한다. 알레시오는 먼저 커피를 내지만 경호 강화는 거절한다.</t>
+          <t>팔레르모의 다른 판사가 이레네의 위헌 심판 제청을 받아들여 헌재로 보낸다. 레조네 요니카 주지사가 된 마리나는 비상 총리령 적용을 거부하고 개헌 조항의 핵심을 헌재에 제소한다. 요니카 교부금이 동결된다.</t>
         </is>
       </c>
       <c r="F159" s="4" t="inlineStr"/>
@@ -8296,27 +8320,27 @@
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
         <is>
-          <t>9부 9화</t>
+          <t>9부 3화</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>마리나</t>
+          <t>베카리아</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>Marina</t>
+          <t>Il Beccaria</t>
         </is>
       </c>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>9부 9화</t>
+          <t>8부 12화 반전</t>
         </is>
       </c>
       <c r="E160" s="4" t="inlineStr">
         <is>
-          <t>총선에서 이긴 이레네가 마리나 페를리토를 총리실 차관으로 부른다. 남부 지방에서 올라온 두 사람의 대화.</t>
+          <t>(친구 시점) 라디체와 알레시오가 제78조 전쟁상태 의결과 제60조 입법기 연장안을 짜고 파올로가 받아 친다. 그는 총리 책상 위 벨란디의 베카리아를 주머니에 넣고, 그날의 사본을 아이 방 벽 속에 숨긴다.</t>
         </is>
       </c>
       <c r="F160" s="4" t="inlineStr"/>
@@ -8324,27 +8348,27 @@
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>9부 10화</t>
+          <t>9부 4화</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>마지막 이양 준비</t>
+          <t>연장</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>Gli ultimi preparativi</t>
+          <t>La proroga</t>
         </is>
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>9부 10화</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="E161" s="4" t="inlineStr">
         <is>
-          <t>퇴임 전날 저녁, 테베레 강변을 걷던 알레시오가 저격당한다. 마지막 말은 '먼저 커피를'이다.</t>
+          <t>입법기 연장안이 하원에 오르자 콜라산티가 처음으로 등을 돌린다. '두 번은 안 된다던 사람이 누구였나.' 5부의 개헌 영상이 다시 돌고, 연정의 셈이 흔들린다.</t>
         </is>
       </c>
       <c r="F161" s="4" t="inlineStr"/>
@@ -8352,27 +8376,27 @@
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>9부 11화</t>
+          <t>9부 5화</t>
         </is>
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>홀로 선 자리</t>
+          <t>헌재 청문</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>Il posto dove si sta da soli</t>
+          <t>L'audizione alla Consulta</t>
         </is>
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>9부 11화</t>
+          <t>8부 8화 변형</t>
         </is>
       </c>
       <c r="E162" s="4" t="inlineStr">
         <is>
-          <t>선서를 미루자는 권유를 물리치고 이레네는 예정대로 퀴리날레에서 선서한다. 밤에 벨란디의 편지를 읽는다.</t>
+          <t>헌법재판소가 전문가 청문을 연다. 카를로가 비상 지출과 스파이웨어 계약 자료를 내고 12년 전 자신의 과오까지 털어놓는다. 계단을 내려오다 쓰러져 숨진다.</t>
         </is>
       </c>
       <c r="F162" s="4" t="inlineStr"/>
@@ -8380,27 +8404,27 @@
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>9부 12화</t>
+          <t>9부 6화</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>수사의 끝</t>
+          <t>장례 행렬</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>La fine dell'indagine</t>
+          <t>Il corteo</t>
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>9부 12화 변형</t>
+          <t>8부 9화 반전</t>
         </is>
       </c>
       <c r="E163" s="4" t="inlineStr">
         <is>
-          <t>(친구 시점) 선서식 이튿날, 파올로가 장부 사본을 들고 로마 검찰청에 자수해 협력자가 된다. 첫 진술로 실행범·조직자가 기소되고, 아내는 아이들을 데리고 떠난다.</t>
+          <t>카를로의 장례 행렬이 토레네라 항구로 향하고 군 병력이 길을 막는다. 최루탄 명령을 거부한 카라비니에리 대위를 징계하라는 요구를 몬탈토 사령관이 묵살한다. 알레시오는 그를 '배신자'라 부른다.</t>
         </is>
       </c>
       <c r="F163" s="4" t="inlineStr"/>
@@ -8408,41 +8432,544 @@
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
         <is>
-          <t>9부 에필로그</t>
+          <t>9부 7화</t>
         </is>
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
+          <t>퀴리날레의 거부</t>
+        </is>
+      </c>
+      <c r="C164" s="4" t="inlineStr">
+        <is>
+          <t>Il no del Quirinale</t>
+        </is>
+      </c>
+      <c r="D164" s="4" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="E164" s="4" t="inlineStr">
+        <is>
+          <t>베르티 대통령이 전쟁상태 선포를 거부하고 입법기 연장법을 양원에 되돌려 보낸다. '1948년 우리는 일부러 이 문을 만들지 않았습니다.' 알레시오는 방송에서 대통령을 공격한다.</t>
+        </is>
+      </c>
+      <c r="F164" s="4" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="4" t="inlineStr">
+        <is>
+          <t>9부 8화</t>
+        </is>
+      </c>
+      <c r="B165" s="4" t="inlineStr">
+        <is>
+          <t>두 번째 장부</t>
+        </is>
+      </c>
+      <c r="C165" s="4" t="inlineStr">
+        <is>
+          <t>Il secondo libro mastro</t>
+        </is>
+      </c>
+      <c r="D165" s="4" t="inlineStr">
+        <is>
+          <t>9부 12화 변형(앞당김)</t>
+        </is>
+      </c>
+      <c r="E165" s="4" t="inlineStr">
+        <is>
+          <t>(친구 시점) 루치아의 무덤 앞에서 로사와 마주친 파올로가 두 번째 장부와 베카리아를 들고 엘레나 사르토리를 찾아가 협력자가 된다. 아내는 아이들을 데리고 떠나고, 그는 새 이름을 받는다.</t>
+        </is>
+      </c>
+      <c r="F165" s="4" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="4" t="inlineStr">
+        <is>
+          <t>9부 9화</t>
+        </is>
+      </c>
+      <c r="B166" s="4" t="inlineStr">
+        <is>
+          <t>타는 땅</t>
+        </is>
+      </c>
+      <c r="C166" s="4" t="inlineStr">
+        <is>
+          <t>La terra che brucia</t>
+        </is>
+      </c>
+      <c r="D166" s="4" t="inlineStr">
+        <is>
+          <t>9부 2화·7화 변형</t>
+        </is>
+      </c>
+      <c r="E166" s="4" t="inlineStr">
+        <is>
+          <t>급수 제한 속 시칠리아에 산불이 번지고 군이 투입된다. 귀향한 알레시오에게 어촌 사람들이 등을 돌린다. 같은 주 크리벨리가 숨지고, 불법 감청 지시 목록이 든 봉투가 엘레나에게 간다.</t>
+        </is>
+      </c>
+      <c r="F166" s="4" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="4" t="inlineStr">
+        <is>
+          <t>9부 10화</t>
+        </is>
+      </c>
+      <c r="B167" s="4" t="inlineStr">
+        <is>
+          <t>최고 원리</t>
+        </is>
+      </c>
+      <c r="C167" s="4" t="inlineStr">
+        <is>
+          <t>I principi supremi</t>
+        </is>
+      </c>
+      <c r="D167" s="4" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="E167" s="4" t="inlineStr">
+        <is>
+          <t>헌법재판소가 '제78조의2'의 핵심 — 선거 연기, 영장 없는 구금과 통신 제한 — 을 헌법 개정으로도 바꿀 수 없는 최고 원리 위반으로 무효화한다. 노라와 베니아미노의 자료가 결정문 각주에 있다.</t>
+        </is>
+      </c>
+      <c r="F167" s="4" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="4" t="inlineStr">
+        <is>
+          <t>9부 11화</t>
+        </is>
+      </c>
+      <c r="B168" s="4" t="inlineStr">
+        <is>
+          <t>벼랑</t>
+        </is>
+      </c>
+      <c r="C168" s="4" t="inlineStr">
+        <is>
+          <t>Sull'orlo</t>
+        </is>
+      </c>
+      <c r="D168" s="4" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="E168" s="4" t="inlineStr">
+        <is>
+          <t>그 밤, 라디체가 헌재 결정의 효력을 '정지'하는 긴급 법령과 구금 유지 명령서를 가져온다. 몬탈토 사령관은 서면으로 거부하고, 대통령은 서명하지 않겠다며 최고국방회의를 소집한다. 그리말디가 불신임 동의안을 들고 오고, 키지궁 앞엔 로사 페란테가 서 있다.</t>
+        </is>
+      </c>
+      <c r="F168" s="4" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="4" t="inlineStr">
+        <is>
+          <t>9부 12화</t>
+        </is>
+      </c>
+      <c r="B169" s="4" t="inlineStr">
+        <is>
+          <t>새벽의 펜</t>
+        </is>
+      </c>
+      <c r="C169" s="4" t="inlineStr">
+        <is>
+          <t>La penna all'alba</t>
+        </is>
+      </c>
+      <c r="D169" s="4" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="E169" s="4" t="inlineStr">
+        <is>
+          <t>새벽 네 시, 텅 빈 키지궁. 리나가 모든 구두 지시 기록을 의회 정보위원회에 내겠다고 먼저 알리고, 커피 한 잔을 놓고 나간다. 서명란은 비어 있고, 펜은 아직 그의 손에 있다.</t>
+        </is>
+      </c>
+      <c r="F169" s="4" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="9" t="inlineStr">
+        <is>
+          <t>10부 1화</t>
+        </is>
+      </c>
+      <c r="B170" s="9" t="inlineStr">
+        <is>
+          <t>부엌</t>
+        </is>
+      </c>
+      <c r="C170" s="9" t="inlineStr">
+        <is>
+          <t>La cucina</t>
+        </is>
+      </c>
+      <c r="D170" s="9" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="E170" s="9" t="inlineStr">
+        <is>
+          <t>[2029 법정] 검사가 파올로에게 봉인된 봉투를 건넨다 — 리날디가 죽기 전 맡긴 자백서. '증인이 읽어 주겠습니까.' 2024년 11월 새벽, 알레시오는 경호를 물리고 로사 페란테의 부엌에 들어가 처음으로 먼저 커피를 끓이겠다고 청한다. 그녀는 딸의 마지막 수첩을 내민다.</t>
+        </is>
+      </c>
+      <c r="F170" s="9" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="9" t="inlineStr">
+        <is>
+          <t>10부 2화</t>
+        </is>
+      </c>
+      <c r="B171" s="9" t="inlineStr">
+        <is>
+          <t>찢긴 장</t>
+        </is>
+      </c>
+      <c r="C171" s="9" t="inlineStr">
+        <is>
+          <t>La pagina strappata</t>
+        </is>
+      </c>
+      <c r="D171" s="9" t="inlineStr">
+        <is>
+          <t>7부 9화 반향(신규)</t>
+        </is>
+      </c>
+      <c r="E171" s="9" t="inlineStr">
+        <is>
+          <t>어머니 안나가 지타에게서 받은 벨란디의 마지막 장 사본을 식탁에 놓는다. '예외는 늘 가장 좋은 이유로 온다.' 알레시오는 7년 전 찢은 원본이 아직 자기 지갑에 있음을 꺼내 보인다.</t>
+        </is>
+      </c>
+      <c r="F171" s="9" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="9" t="inlineStr">
+        <is>
+          <t>10부 3화</t>
+        </is>
+      </c>
+      <c r="B172" s="9" t="inlineStr">
+        <is>
+          <t>첫 신문</t>
+        </is>
+      </c>
+      <c r="C172" s="9" t="inlineStr">
+        <is>
+          <t>Il primo interrogatorio</t>
+        </is>
+      </c>
+      <c r="D172" s="9" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="E172" s="9" t="inlineStr">
+        <is>
+          <t>(친구 시점) 보호 거처의 첫 신문. 엘레나가 '그가 불복할 거라 보나'고 묻자, 파올로는 아홉 살 때 항구에서 알레시오가 남의 자전거를 돌려주러 갔던 이야기를 한다. 라디오에서 긴급 속보가 흘러나온다.</t>
+        </is>
+      </c>
+      <c r="F172" s="9" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="9" t="inlineStr">
+        <is>
+          <t>10부 4화</t>
+        </is>
+      </c>
+      <c r="B173" s="9" t="inlineStr">
+        <is>
+          <t>이행</t>
+        </is>
+      </c>
+      <c r="C173" s="9" t="inlineStr">
+        <is>
+          <t>L'esecuzione</t>
+        </is>
+      </c>
+      <c r="D173" s="9" t="inlineStr">
+        <is>
+          <t>9부 11화 변형</t>
+        </is>
+      </c>
+      <c r="E173" s="9" t="inlineStr">
+        <is>
+          <t>그는 불복 법령을 찢는다. 헌재 결정을 이행해 구금자를 풀고, 비상사태를 거두고, 살레미를 41-bis로 되돌리고, 스파이웨어 계약을 끊는다. 라디체는 문을 닫고 나간다.</t>
+        </is>
+      </c>
+      <c r="F173" s="9" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="9" t="inlineStr">
+        <is>
+          <t>10부 5화</t>
+        </is>
+      </c>
+      <c r="B174" s="9" t="inlineStr">
+        <is>
+          <t>내려놓다</t>
+        </is>
+      </c>
+      <c r="C174" s="9" t="inlineStr">
+        <is>
+          <t>Deporre</t>
+        </is>
+      </c>
+      <c r="D174" s="9" t="inlineStr">
+        <is>
+          <t>9부 11화 변형</t>
+        </is>
+      </c>
+      <c r="E174" s="9" t="inlineStr">
+        <is>
+          <t>하원에서 그는 루치아의 이름을 먼저 부르고 책임을 인정한다. '저는 킨키나투스가 아닙니다. 그는 용서받을 일이 없었으니까.' 마키아벨리를 스스로 반박하고 베카리아를 읽은 뒤 퀴리날레에 사표를 낸다. 대통령이 양원을 해산한다.</t>
+        </is>
+      </c>
+      <c r="F174" s="9" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="9" t="inlineStr">
+        <is>
+          <t>10부 6화</t>
+        </is>
+      </c>
+      <c r="B175" s="9" t="inlineStr">
+        <is>
+          <t>면책을 내려놓다</t>
+        </is>
+      </c>
+      <c r="C175" s="9" t="inlineStr">
+        <is>
+          <t>Senza scudo</t>
+        </is>
+      </c>
+      <c r="D175" s="9" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="E175" s="9" t="inlineStr">
+        <is>
+          <t>라디체가 먼저 수사를 받자 모든 책임을 전 총리에게 돌린다. 알레시오는 하원에 제96조 소추 허가를 막지 말라고 요청한다. 지지자들은 떠나고, 어머니는 처음으로 그의 전화를 받는다.</t>
+        </is>
+      </c>
+      <c r="F175" s="9" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="9" t="inlineStr">
+        <is>
+          <t>10부 7화</t>
+        </is>
+      </c>
+      <c r="B176" s="9" t="inlineStr">
+        <is>
+          <t>재건된 총선</t>
+        </is>
+      </c>
+      <c r="C176" s="9" t="inlineStr">
+        <is>
+          <t>Le elezioni restituite</t>
+        </is>
+      </c>
+      <c r="D176" s="9" t="inlineStr">
+        <is>
+          <t>9부 9화·11화 변형</t>
+        </is>
+      </c>
+      <c r="E176" s="9" t="inlineStr">
+        <is>
+          <t>2025년 봄, 제 날짜에 치러진 총선에서 이레네가 이기고 퀴리날레에서 선서한다. 마리나가 법무장관이 되어 예방 감청 승인 절차를 복원한다. 알레시오는 투표소 줄에 서 있다.</t>
+        </is>
+      </c>
+      <c r="F176" s="9" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="9" t="inlineStr">
+        <is>
+          <t>10부 8화</t>
+        </is>
+      </c>
+      <c r="B177" s="9" t="inlineStr">
+        <is>
+          <t>자백서</t>
+        </is>
+      </c>
+      <c r="C177" s="9" t="inlineStr">
+        <is>
+          <t>Il memoriale</t>
+        </is>
+      </c>
+      <c r="D177" s="9" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="E177" s="9" t="inlineStr">
+        <is>
+          <t>직권남용죄는 이미 폐지됐지만 그는 불법 감청, 불법 구금, 루치아의 죽음, 살레미 잔당·로지와의 거래를 모두 적은 자백서를 엘레나에게 맡기고 증인으로 서겠다고 한다. 니노 살레미와 브란카티가 소식을 듣는다.</t>
+        </is>
+      </c>
+      <c r="F177" s="9" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="9" t="inlineStr">
+        <is>
+          <t>10부 9화</t>
+        </is>
+      </c>
+      <c r="B178" s="9" t="inlineStr">
+        <is>
+          <t>먼저 커피를</t>
+        </is>
+      </c>
+      <c r="C178" s="9" t="inlineStr">
+        <is>
+          <t>Prima un caffè</t>
+        </is>
+      </c>
+      <c r="D178" s="9" t="inlineStr">
+        <is>
+          <t>9부 2화·6화 변형</t>
+        </is>
+      </c>
+      <c r="E178" s="9" t="inlineStr">
+        <is>
+          <t>토레네라의 짧은 계절. 그는 어부들, 쫓겨난 시장, 회개자의 아내를 찾아가 사과하고 다시 먼저 커피를 낸다. 몇은 문을 닫고, 몇은 잔을 받는다.</t>
+        </is>
+      </c>
+      <c r="F178" s="9" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="9" t="inlineStr">
+        <is>
+          <t>10부 10화</t>
+        </is>
+      </c>
+      <c r="B179" s="9" t="inlineStr">
+        <is>
+          <t>한 문장</t>
+        </is>
+      </c>
+      <c r="C179" s="9" t="inlineStr">
+        <is>
+          <t>Una frase</t>
+        </is>
+      </c>
+      <c r="D179" s="9" t="inlineStr">
+        <is>
+          <t>9부 8화 변형</t>
+        </is>
+      </c>
+      <c r="E179" s="9" t="inlineStr">
+        <is>
+          <t>(친구 시점) 보호 거처의 파올로가 수감 정보원에게서 살해 계획을 듣고 엘레나에게 전한다. 경호가 강화되고, 파올로는 허락받은 한 통의 전화에서 한 문장만 한다. 이번에 알레시오는 경호를 받아들이며 보르셀리노를 떠올린다.</t>
+        </is>
+      </c>
+      <c r="F179" s="9" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="9" t="inlineStr">
+        <is>
+          <t>10부 11화</t>
+        </is>
+      </c>
+      <c r="B180" s="9" t="inlineStr">
+        <is>
+          <t>항구의 바</t>
+        </is>
+      </c>
+      <c r="C180" s="9" t="inlineStr">
+        <is>
+          <t>Il bar del porto</t>
+        </is>
+      </c>
+      <c r="D180" s="9" t="inlineStr">
+        <is>
+          <t>9부 10화 변형</t>
+        </is>
+      </c>
+      <c r="E180" s="9" t="inlineStr">
+        <is>
+          <t>2026년 3월, 증언대에 서기 전날 아침 항구의 바. 그가 젊은 호위 경관에게 먼저 커피를 따르는 순간 오토바이에서 총성이 울린다. 탁자에는 김이 오르는 잔 두 개와 모카포트가 남는다.</t>
+        </is>
+      </c>
+      <c r="F180" s="9" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="9" t="inlineStr">
+        <is>
+          <t>10부 12화</t>
+        </is>
+      </c>
+      <c r="B181" s="9" t="inlineStr">
+        <is>
+          <t>자백서는 남는다</t>
+        </is>
+      </c>
+      <c r="C181" s="9" t="inlineStr">
+        <is>
+          <t>Il memoriale resta</t>
+        </is>
+      </c>
+      <c r="D181" s="9" t="inlineStr">
+        <is>
+          <t>9부 12화 변형</t>
+        </is>
+      </c>
+      <c r="E181" s="9" t="inlineStr">
+        <is>
+          <t>이레네는 국장 대신 유언대로 가족장을 치르되 조문 행렬을 막지 않는다. 그리말디와 어부들이 운구를 멘다. 형사소송법 제512조로 자백서가 증거가 되고, 니노 살레미와 실행범이 체포되며 브란카티는 해외로 달아난다.</t>
+        </is>
+      </c>
+      <c r="F181" s="9" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="9" t="inlineStr">
+        <is>
+          <t>10부 에필로그</t>
+        </is>
+      </c>
+      <c r="B182" s="9" t="inlineStr">
+        <is>
           <t>연결 고리</t>
         </is>
       </c>
-      <c r="C164" s="4" t="inlineStr">
+      <c r="C182" s="9" t="inlineStr">
         <is>
           <t>L'anello</t>
         </is>
       </c>
-      <c r="D164" s="4" t="inlineStr">
+      <c r="D182" s="9" t="inlineStr">
         <is>
           <t>9부 에필로그 변형</t>
         </is>
       </c>
-      <c r="E164" s="4" t="inlineStr">
-        <is>
-          <t>[2029 법정] 파올로의 증언과 장부로 인도된 브란카티와 두 자금책이 종신형을 받는다. 같은 주 마리나 페를리토가 총리로 선서하고, 새 이름의 파올로는 호위 경관에게 먼저 커피를 낸다.</t>
-        </is>
-      </c>
-      <c r="F164" s="4" t="inlineStr"/>
+      <c r="E182" s="9" t="inlineStr">
+        <is>
+          <t>[2029 법정] 인도된 브란카티와 니노 살레미, 실행범·조직자에게 종신형. 엘레나의 논고: '키케로는 재판 없이 처형하고 뉘우치지 않은 채 살생부에 올라 죽었습니다. 리날디는 뉘우치고 진실을 말하려다 죽었습니다.' 파올로가 자백서의 마지막 줄을 읽고, 보호 거처에서 호위 경관에게 먼저 커피를 낸다.</t>
+        </is>
+      </c>
+      <c r="F182" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="21">
     <mergeCell ref="B4:F4"/>
-    <mergeCell ref="A54:F54"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="B18:F18"/>
     <mergeCell ref="B12:F12"/>
-    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A47:F47"/>
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="A22:F22"/>
     <mergeCell ref="B14:F14"/>
@@ -8453,6 +8980,7 @@
     <mergeCell ref="B19:F19"/>
     <mergeCell ref="B9:F9"/>
     <mergeCell ref="B6:F6"/>
+    <mergeCell ref="A60:F60"/>
     <mergeCell ref="B20:F20"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="B5:F5"/>

--- a/기획안/혼합안_이탈리아_스페인_독일.xlsx
+++ b/기획안/혼합안_이탈리아_스페인_독일.xlsx
@@ -530,7 +530,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>원작: 러시아어 대본 9부×12화+에필로그. 원칙: 현안은 실제, 인물·기관·사건 이름은 가상. 국가 순서는 원작과의 유사도 추정 순. 최신화: 2026-10-03(제작된 부는 실제 대본 기준, 연두색 칸 = 제작 완료 화).</t>
+          <t>원작: 러시아어 대본 9부×12화+에필로그. 원칙: 현안은 실제, 인물·기관·사건 이름은 가상. 국가 순서는 원작과의 유사도 추정 순. 최신화: 2026-10-04(제작된 부는 실제 대본 기준, 연두색 칸 = 제작 완료 화).</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="N5" s="5" t="inlineStr">
         <is>
-          <t>1부 10화(부당 10화 구성의 1부 전체) 대본·학습노트 완료 (2026-10)</t>
+          <t>1~2부 20화(1부·2부 전체) 대본·학습노트 완료 (2026-10)</t>
         </is>
       </c>
       <c r="O5" s="6" t="inlineStr">
@@ -879,7 +879,7 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>0. 제작 현황 (2026-10-03 최신화)</t>
+          <t>0. 제작 현황 (2026-10-04 최신화)</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>1부 10화(부당 10화 구성의 1부 전체) 대본·학습노트 완료 (2026-10)</t>
+          <t>1~2부 20화(부당 10화 구성의 1부·2부 전체) 대본·학습노트 완료 (2026-10)</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>1부</t>
+          <t>1부, 2부</t>
         </is>
       </c>
     </row>
@@ -915,11 +915,11 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>학습 노트 10편(1부 1~10화, md·docx), 0_동사_시제_가이드(md·docx)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="360" customHeight="1">
+          <t>학습 노트 20편(1부 1~10화, 2부 1~10화, docx), 0_동사_시제_가이드(md·docx)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="409" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>기획 대비 변경</t>
@@ -937,7 +937,20 @@
 · 9화: 구금 중 폭행은 없고 약을 주지 않은 박탈만이 정본. 석방 11:40, 출소 18:20, 사망 20:52. 에바리스토는 끝내 커피를 마시지 못하고, 마누는 끝까지 usted를 쓴다
 · 10화: 장례 철야 커피와 무종교 영결식. 마누가 묘 앞에서 처음이자 마지막으로 tú를 쓰고, 토마스가 1974년 파업 구금을 고백한다. 국선 변호인 누리아가 사무소를 승계하고, 12월 3일 마드리드행. 로시오의 '등대' 착상이 레드 파로로 이어진다
 · 인물 추가: 누리아 바스티다·난도·레메/엔카르나·세르히오/바네사·안셀모. 쿠에스타(54)·소피아(70)의 나이와 1부 행적을 반영
-· [미해결 — 민감성] 에바리스토의 1974년 노동법률사무소 총격이 실제 1977년 아토차 변호사 살해 사건을 떠올리게 할 수 있음. 대본은 고치지 않고 표시만 해 두며 sensitivity에 점검 과제로 기록. 2부 이후 회상에서 차이를 유지하고 자문 검토 필요</t>
+· [미해결 — 민감성] 에바리스토의 1974년 노동법률사무소 총격이 실제 1977년 아토차 변호사 살해 사건을 떠올리게 할 수 있음. 대본은 고치지 않고 표시만 해 두며 sensitivity에 점검 과제로 기록. 2부 이후 회상에서 차이를 유지하고 자문 검토 필요
+[2부 제작 후 변경·확정]
+· 1화: 정체불명 재단 = «Fundación Atalaya»(연 15만 유로 3년 제안, 출자는 Inversiones Lara 2004, 이사 비다우레 = 솔리스의 처남). 레드 파로 개업 2010-02-01 calle del Sombrerete 9(옛 ultramarinos), 첫 손님 = 필리, 첫 의뢰인 = 아들 대출의 보증인 펠리사. 벽의 규칙 넷(먼저 커피 / 재단·기업 돈 사절 / 모두 적는다 / 마시면 설거지). 내무부 창구 «Vuelva usted mañana»
+· 2화: 2011-05 광장(실제 운동은 이름 없이 모티프만), 페르민 첫 등장(1982년 갱도 붕괴 때 에바리스토와 함께 일한 노조 대의원, 보온병 '마지막 잔'), 펠리사 퇴거 집행이 2011-06-02 현장에서 중단. 쿠에스타가 광장 가장자리에 나타나고 토마스가 비야페로사 소광장에서 처음 공개 발언
+· 3화: 알바로 합류 2011-11 → 2012-02 마드리드 로펌 외부 자문 수락(유령 컨설팅 «Consultoría Meridiana», 월 3천 유로). 첫 질문 = 발데로보스 가처분 단계. 2012-03-22 가처분 인용(증인 셀레스티노는 불출석)
+· 4화: 로시오 체포 2012-10-15(결정문을 든 채, '접근로 정비'로 가처분 우회한 중장비), 공사장 500m 접근금지 부과. 치안대 하사가 결정문을 조끼에 챙긴 것을 블라스가 목격
+· 5화: 쿠에스타의 제안(레티로 «Café del Estanque», 2012-11-06) 거절 → 협동조합 정비소 신용한도 중단, 토마스 퇴직. 쿠에스타가 알바로 이름을 흘린다(«el de la Caja»)
+· 6화: 2013-04 이스마엘 코르데로(27) 시추 참호 붕괴 사망 사건 고소 준비 중 초안 3판의 '2.80m'가 상대 편지에 인용 → 필리가 프린터 로그로 알바로 발각. 증인 네스토르 철회
+· 7화: 로시오 재판 2013-06-17, 징역 4년(공권력 공격 3년 + 공공질서 1년, 하한형), 법정 구속. 마누가 변호인. 전국 19개 도시에 «Libertad para Rocío»(얼굴 없이 글자만)
+· 8화: 2014-09~10 창당 3조건(레드 파로 분리 / 사건 위에 쓰는 강령 / 초상 금지)과 페르민의 8년 임기 제한, 당명은 펠리사의 말 «Horizonte Común». 창당 대회 2014-10-11 라바피에스 옛 인쇄소. 알바로가 상자(자백·증거)를 두고 감
+· 9화: 토마스의 유세 영상 «El del frontal»(1분 29초, 120만 회) → 2015-12-02 06:20 페로강 둑길에서 불 꺼진 검은 차에 사망. 인근 CCTV는 Servinor 관리 하에 '정비 중'. 목격자 세페리노, 벨트란 경위 재등장
+· 10화: 압수수색 전날 알바로가 공책 4권·USB 20개를 가지고 일부러 검문 길로 가 체포. 총선 54석(제3당), 토마스가 산 복권은 reintegro. 알바로 공책에 'T. R. — jueves — Atocha, 6.40'이라는 이니셜 한 줄(후속 복선)
+· 인물 추가: 소레닷 마린(테루엘 교사·창당 발기인), 콘수엘로 니에토(법원 서기), 이반(영상 촬영 청년), 아만시오 키로스(감정인), 로사리오 코르데로(이스마엘의 어머니), 베고냐 아리스티(판사)
+· [3부 이후 연결 과제] 로시오 옥중 사망(3부 4화) / T. R. 이니셜의 출처와 토마스 사건 배후(쿠에스타 '이번엔 누가 했는지 모른다') / 코르데로 고소 계류 / 알바로의 형사 절차와 4부 5화 피살 / 시점 인물 엘레나의 3부 서술로의 전환</t>
         </is>
       </c>
     </row>
@@ -2510,284 +2523,324 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="10" t="inlineStr">
+      <c r="A77" s="5" t="inlineStr">
         <is>
           <t>2부 1화</t>
         </is>
       </c>
-      <c r="B77" s="10" t="inlineStr">
+      <c r="B77" s="5" t="inlineStr">
         <is>
           <t>수도 상경</t>
         </is>
       </c>
-      <c r="C77" s="10" t="inlineStr">
+      <c r="C77" s="5" t="inlineStr">
         <is>
           <t>Rumbo a Madrid</t>
         </is>
       </c>
-      <c r="D77" s="10" t="inlineStr">
+      <c r="D77" s="5" t="inlineStr">
         <is>
           <t>2부 1화·2화 통합</t>
         </is>
       </c>
-      <c r="E77" s="10" t="inlineStr">
+      <c r="E77" s="5" t="inlineStr">
         <is>
           <t>마드리드에서 로시오와 ‘레드 파로’를 연 마누에게 정체불명의 재단이 거액을 내밀고, 필리가 그 돈이 솔리스의 것임을 밝힌다.</t>
         </is>
       </c>
-      <c r="F77" s="10" t="inlineStr"/>
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="78">
-      <c r="A78" s="10" t="inlineStr">
+      <c r="A78" s="5" t="inlineStr">
         <is>
           <t>2부 2화</t>
         </is>
       </c>
-      <c r="B78" s="10" t="inlineStr">
+      <c r="B78" s="5" t="inlineStr">
         <is>
           <t>광장의 목소리</t>
         </is>
       </c>
-      <c r="C78" s="10" t="inlineStr">
+      <c r="C78" s="5" t="inlineStr">
         <is>
           <t>La Voz de la Plaza</t>
         </is>
       </c>
-      <c r="D78" s="10" t="inlineStr">
+      <c r="D78" s="5" t="inlineStr">
         <is>
           <t>2부 4화</t>
         </is>
       </c>
-      <c r="E78" s="10" t="inlineStr">
+      <c r="E78" s="5" t="inlineStr">
         <is>
           <t>광장 점거 운동의 물결 속에 레드 파로가 퇴거 피해자·노동자들과 첫 대규모 집회를 연다.</t>
         </is>
       </c>
-      <c r="F78" s="10" t="inlineStr"/>
+      <c r="F78" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="79">
-      <c r="A79" s="10" t="inlineStr">
+      <c r="A79" s="5" t="inlineStr">
         <is>
           <t>2부 3화</t>
         </is>
       </c>
-      <c r="B79" s="10" t="inlineStr">
+      <c r="B79" s="5" t="inlineStr">
         <is>
           <t>알바로의 균열</t>
         </is>
       </c>
-      <c r="C79" s="10" t="inlineStr">
+      <c r="C79" s="5" t="inlineStr">
         <is>
           <t>La Grieta de Álvaro</t>
         </is>
       </c>
-      <c r="D79" s="10" t="inlineStr">
+      <c r="D79" s="5" t="inlineStr">
         <is>
           <t>2부 5화</t>
         </is>
       </c>
-      <c r="E79" s="10" t="inlineStr">
+      <c r="E79" s="5" t="inlineStr">
         <is>
           <t>고객을 잃고 빚에 몰린 알바로가 솔리스 측 로펌의 ‘자문’ 제안을 몰래 받아들인다.</t>
         </is>
       </c>
-      <c r="F79" s="10" t="inlineStr"/>
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="80">
-      <c r="A80" s="10" t="inlineStr">
+      <c r="A80" s="5" t="inlineStr">
         <is>
           <t>2부 4화</t>
         </is>
       </c>
-      <c r="B80" s="10" t="inlineStr">
+      <c r="B80" s="5" t="inlineStr">
         <is>
           <t>로시오의 구금</t>
         </is>
       </c>
-      <c r="C80" s="10" t="inlineStr">
+      <c r="C80" s="5" t="inlineStr">
         <is>
           <t>La Detención de Rocío</t>
         </is>
       </c>
-      <c r="D80" s="10" t="inlineStr">
+      <c r="D80" s="5" t="inlineStr">
         <is>
           <t>2부 6화</t>
         </is>
       </c>
-      <c r="E80" s="10" t="inlineStr">
+      <c r="E80" s="5" t="inlineStr">
         <is>
           <t>법원의 공사 중지 결정을 무시한 광산 중장비를 막아선 로시오가 ‘공권력 저항’ 혐의로 구속된다.</t>
         </is>
       </c>
-      <c r="F80" s="10" t="inlineStr"/>
+      <c r="F80" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="81">
-      <c r="A81" s="10" t="inlineStr">
+      <c r="A81" s="5" t="inlineStr">
         <is>
           <t>2부 5화</t>
         </is>
       </c>
-      <c r="B81" s="10" t="inlineStr">
+      <c r="B81" s="5" t="inlineStr">
         <is>
           <t>쿠에스타의 제안</t>
         </is>
       </c>
-      <c r="C81" s="10" t="inlineStr">
+      <c r="C81" s="5" t="inlineStr">
         <is>
           <t>La Oferta de Cuesta</t>
         </is>
       </c>
-      <c r="D81" s="10" t="inlineStr">
+      <c r="D81" s="5" t="inlineStr">
         <is>
           <t>2부 7화 변형</t>
         </is>
       </c>
-      <c r="E81" s="10" t="inlineStr">
+      <c r="E81" s="5" t="inlineStr">
         <is>
           <t>쿠에스타가 ‘조용히 하면 로시오는 풀린다’는 거래를 내밀고, 거절한 날 아버지가 정비소에서 해고된다.</t>
         </is>
       </c>
-      <c r="F81" s="10" t="inlineStr"/>
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="82">
-      <c r="A82" s="10" t="inlineStr">
+      <c r="A82" s="5" t="inlineStr">
         <is>
           <t>2부 6화</t>
         </is>
       </c>
-      <c r="B82" s="10" t="inlineStr">
+      <c r="B82" s="5" t="inlineStr">
         <is>
           <t>알바로의 배신 발각</t>
         </is>
       </c>
-      <c r="C82" s="10" t="inlineStr">
+      <c r="C82" s="5" t="inlineStr">
         <is>
           <t>La Traición al Descubierto</t>
         </is>
       </c>
-      <c r="D82" s="10" t="inlineStr">
+      <c r="D82" s="5" t="inlineStr">
         <is>
           <t>2부 10화</t>
         </is>
       </c>
-      <c r="E82" s="10" t="inlineStr">
+      <c r="E82" s="5" t="inlineStr">
         <is>
           <t>광산 산재 소송 서류가 제출 전날 유출되고, 필리의 추적 끝에 알바로가 드러난다.</t>
         </is>
       </c>
-      <c r="F82" s="10" t="inlineStr"/>
+      <c r="F82" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="83">
-      <c r="A83" s="10" t="inlineStr">
+      <c r="A83" s="5" t="inlineStr">
         <is>
           <t>2부 7화</t>
         </is>
       </c>
-      <c r="B83" s="10" t="inlineStr">
+      <c r="B83" s="5" t="inlineStr">
         <is>
           <t>로시오의 재판</t>
         </is>
       </c>
-      <c r="C83" s="10" t="inlineStr">
+      <c r="C83" s="5" t="inlineStr">
         <is>
           <t>El Juicio de Rocío</t>
         </is>
       </c>
-      <c r="D83" s="10" t="inlineStr">
+      <c r="D83" s="5" t="inlineStr">
         <is>
           <t>2부 11화 변형</t>
         </is>
       </c>
-      <c r="E83" s="10" t="inlineStr">
+      <c r="E83" s="5" t="inlineStr">
         <is>
           <t>공공질서 조항이 적용된 재판에서 로시오에게 징역 4년이 선고되고, ‘로시오를 석방하라’ 운동이 번진다.</t>
         </is>
       </c>
-      <c r="F83" s="10" t="inlineStr"/>
+      <c r="F83" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="84">
-      <c r="A84" s="10" t="inlineStr">
+      <c r="A84" s="5" t="inlineStr">
         <is>
           <t>2부 8화</t>
         </is>
       </c>
-      <c r="B84" s="10" t="inlineStr">
+      <c r="B84" s="5" t="inlineStr">
         <is>
           <t>정당 창당</t>
         </is>
       </c>
-      <c r="C84" s="10" t="inlineStr">
+      <c r="C84" s="5" t="inlineStr">
         <is>
           <t>La Fundación del Partido</t>
         </is>
       </c>
-      <c r="D84" s="10" t="inlineStr">
+      <c r="D84" s="5" t="inlineStr">
         <is>
           <t>3부 1화 변형</t>
         </is>
       </c>
-      <c r="E84" s="10" t="inlineStr">
+      <c r="E84" s="5" t="inlineStr">
         <is>
           <t>광산노조 원로 페르민과 광장 세대가 신당 ‘오리손테 코문’을 세우고, 흔들리던 알바로가 자료를 들고 돌아온다.</t>
         </is>
       </c>
-      <c r="F84" s="10" t="inlineStr"/>
+      <c r="F84" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="85">
-      <c r="A85" s="10" t="inlineStr">
+      <c r="A85" s="5" t="inlineStr">
         <is>
           <t>2부 9화</t>
         </is>
       </c>
-      <c r="B85" s="10" t="inlineStr">
+      <c r="B85" s="5" t="inlineStr">
         <is>
           <t>아버지의 죽음</t>
         </is>
       </c>
-      <c r="C85" s="10" t="inlineStr">
+      <c r="C85" s="5" t="inlineStr">
         <is>
           <t>La Muerte del Padre</t>
         </is>
       </c>
-      <c r="D85" s="10" t="inlineStr">
+      <c r="D85" s="5" t="inlineStr">
         <is>
           <t>3부 4화</t>
         </is>
       </c>
-      <c r="E85" s="10" t="inlineStr">
+      <c r="E85" s="5" t="inlineStr">
         <is>
           <t>첫 총선 유세 영상으로 화제가 된 아버지 토마스가 새벽길 뺑소니로 숨진다.</t>
         </is>
       </c>
-      <c r="F85" s="10" t="inlineStr"/>
+      <c r="F85" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="86">
-      <c r="A86" s="10" t="inlineStr">
+      <c r="A86" s="5" t="inlineStr">
         <is>
           <t>2부 10화</t>
         </is>
       </c>
-      <c r="B86" s="10" t="inlineStr">
+      <c r="B86" s="5" t="inlineStr">
         <is>
           <t>알바로의 희생</t>
         </is>
       </c>
-      <c r="C86" s="10" t="inlineStr">
+      <c r="C86" s="5" t="inlineStr">
         <is>
           <t>El Sacrificio de Álvaro</t>
         </is>
       </c>
-      <c r="D86" s="10" t="inlineStr">
+      <c r="D86" s="5" t="inlineStr">
         <is>
           <t>3부 9화 변형</t>
         </is>
       </c>
-      <c r="E86" s="10" t="inlineStr">
+      <c r="E86" s="5" t="inlineStr">
         <is>
           <t>압수수색 직전 엘레나의 취재원 자료를 빼돌린 알바로가 대신 체포되고, 오리손테 코문이 하원 제3당이 된다.</t>
         </is>
       </c>
-      <c r="F86" s="10" t="inlineStr"/>
+      <c r="F86" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">

--- a/기획안/혼합안_이탈리아_스페인_독일.xlsx
+++ b/기획안/혼합안_이탈리아_스페인_독일.xlsx
@@ -679,7 +679,7 @@
       </c>
       <c r="N5" s="5" t="inlineStr">
         <is>
-          <t>1~2부 20화(1부·2부 전체) 대본·학습노트 완료 (2026-10)</t>
+          <t>1~3부 30화(1~3부 전체) 대본·학습노트 완료 (2026-10)</t>
         </is>
       </c>
       <c r="O5" s="6" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>1~2부 20화(부당 10화 구성의 1부·2부 전체) 대본·학습노트 완료 (2026-10)</t>
+          <t>1~3부 30화(부당 10화 구성의 1~3부 전체) 대본·학습노트 완료 (2026-10)</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>1부, 2부</t>
+          <t>1부, 2부, 3부</t>
         </is>
       </c>
     </row>
@@ -915,7 +915,7 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>학습 노트 20편(1부 1~10화, 2부 1~10화, docx), 0_동사_시제_가이드(md·docx)</t>
+          <t>학습 노트 30편(1부 1~10화, 2부 1~10화, 3부 1~10화, docx), 0_동사_시제_가이드(md·docx)</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,23 @@
 · 9화: 토마스의 유세 영상 «El del frontal»(1분 29초, 120만 회) → 2015-12-02 06:20 페로강 둑길에서 불 꺼진 검은 차에 사망. 인근 CCTV는 Servinor 관리 하에 '정비 중'. 목격자 세페리노, 벨트란 경위 재등장
 · 10화: 압수수색 전날 알바로가 공책 4권·USB 20개를 가지고 일부러 검문 길로 가 체포. 총선 54석(제3당), 토마스가 산 복권은 reintegro. 알바로 공책에 'T. R. — jueves — Atocha, 6.40'이라는 이니셜 한 줄(후속 복선)
 · 인물 추가: 소레닷 마린(테루엘 교사·창당 발기인), 콘수엘로 니에토(법원 서기), 이반(영상 촬영 청년), 아만시오 키로스(감정인), 로사리오 코르데로(이스마엘의 어머니), 베고냐 아리스티(판사)
-· [3부 이후 연결 과제] 로시오 옥중 사망(3부 4화) / T. R. 이니셜의 출처와 토마스 사건 배후(쿠에스타 '이번엔 누가 했는지 모른다') / 코르데로 고소 계류 / 알바로의 형사 절차와 4부 5화 피살 / 시점 인물 엘레나의 3부 서술로의 전환</t>
+· [3부 이후 연결 과제] 로시오 옥중 사망(3부 4화) / T. R. 이니셜의 출처와 토마스 사건 배후(쿠에스타 '이번엔 누가 했는지 모른다') / 코르데로 고소 계류 / 알바로의 형사 절차와 4부 5화 피살 / 시점 인물 엘레나의 3부 서술로의 전환
+[3부 제작 후 변경·확정]
+· 형식: 엘레나의 음성 메모(«Nota de voz. + 날짜. + 시각.» … «Apuntado.»)로 서술. 도청을 피해 인터넷에 연결되지 않는 은색 녹음기(«MÍA» 스티커)를 쓴다. 10화에서 녹음기가 이솔리나를 거쳐 마누에게 전달되어 3부 전체가 '마누가 듣는 녹음'이라는 액자가 된다(첫 메모와 마지막 메모의 «Para quien me escuche, si alguien me escucha»)
+· 연도: 1화 2017-06 / 2~6화 2017-09~11 / 7화 2018-06 / 8화 2018-10~11 / 9화 2019-03~04 / 10화 2019-04-16~18(성주간)
+· 로시오 형기: 원 형기는 2017-06 만료였으나 2016-03 수감자 아구스티나 모르시요가 의사를 5시간 기다리다 숨진 뒤 12명 마당 연좌로 '공공질서 교란' 1년 9개월 추가, '범행 불인정(no asume el delito)'으로 3급 거부 → 출소 예정 2019-03
+· 1화: 집권당 = 이그나시오 발카르셀 총리의 콘코르디아당(Partido de la Concordia). 공개 예비경선 마누 68% vs 소레닷 마린 32%, 연설의 '끝나면 떠나겠다'(아무도 박수 치지 않음). 브루훌라 감사가 4,999유로 쪼개기 기부 11건 적발(IP 하나 = 세라노 112번지 아탈라야) → 55,000유로 반환. 엘레나는 아탈라야 고소 사건의 피의자 신문(취재원 비밀)
+· 2화: 2017-09-25 Minera Peñalba 새 허가로 남쪽 비탈 공사 재개(대법원 상고 계류 중), 10-02 단식 시작. 이레네 첫 등장(콤플루텐세 법대 4학년, 쿠엥카 출신, 할머니 아우렐리아가 키움, 헌재 판결 120/1990으로 응대 문서 정정, '국가 변호사 아니면 장관'). 하원 복도에 쿠에스타
+· 3화: 솔리스가 호르헤 후안 거리 «El Labrador» 별실에서 언론 보도·보증인법 해제·엘레나 고소 취하('덤')를 제안(웨이터 루벤 = 디오니시오의 아들이 제보) → 마누 공개 조건(광산 포기·발데로보스와 로사리오 코르데로 배상) → 솔리스 '90일 기술적 중지' + '쇄신의 선택지' 공개 지지 → 아탈라야 고소 취하. 페르민·로시오가 각각 '값(precio)을 매겼다'
+· 4화: 2017-10-15(일) 단식 14일째. 10:40 이송 지시 → 치안대 호송 '인력 없음' → 14:20 '마드리드'에서 '기다려라' → 16:31 출발 → 16:58 구급차 안 사망(병원 11km 전). 교도관 차로 빌체스가 기록부 사본 제공(«Se informa a UAR, según instrucción permanente n.º 7»). 블라스의 '벌들에게 알리기'(키냐레스의 벌통 22개)
+· 5화: 「5시간 51분」 기사(UAR 줄은 출처 하나라 제외), 물병 광장 47개 도시, 10-24 새벽 솔 광장에서 기동대원 마르코스 레데스마가 헬멧을 벗음(돌격 4분 뒤 중지), 10-26 24시간 총파업
+· 6화: 쿠에스타-엘레나 첫 대면(시르쿨로 데 베야스 아르테스, 커피값을 먼저 냄), UAR의 '두 개의 집'. 11-13 내무부 위기회의에서 총리 비서실장 살다냐가 헌법 116조 비상사태 제안 → 쿠에스타가 반대하고 독립 조사위·교도소 의료 협의체·레데스마 징계 철회를 제안(엘레나가 두 증언으로 재구성). 쿠에스타가 'UAR 상시 지침 7호' 사본을 우편함에 넣어 두 번째 출처 제공(«No se tome el café en la terraza»), 11-16 UAR 기사
+· 7화: 2017-12 엘레나 집에 조화, 2018-03 대법원 페냐알바 허가 무효, '로시오 법' 국민발안 70만 서명. 2018-06-02 알메나라 델 캄포(옛 Caja 지점 2층)에서 저격, 경호원 나초 에레라 중상·생존, 저격범 레미히오 토르네로(Servinor 경비원) 사살. 엘레나가 휴대폰 화면 촬영('J. MERIDIANA' 착신, «Confirmado. 12 h. Plaza.»), 총격 18일 전 아탈라야→메리디아나 4만 유로. 내무부는 '단독범' 발표
+· 8화: 재무부 '금융안정 지원 특별 프로그램'(보가라) → 아탈라야 연 240만 유로 → 메리디아나 → Servinor → 토르네로 9천 유로. 총리실 내부 메모 'R. S.'(살다냐, 필적 감정). 제보자 = 좌천된 국가 회계감사관 마리사 올메도. 2018-11-12 기사 → 보가라 사임 → 11-14 발카르셀 해산 예고(2019-01-21 해산, 03-17 총선)·불출마, 살다냐 경질. 원안의 '총리 사임'을 '해산·불출마'로 변경. 쿠에스타가 기밀비 '초록 장부'를 예고
+· 9화: 2019-03-17 오리손테 코문 131석 제1당. 인준 1차 04-09(171:179 부결), 2차 04-11(171:158, 기권 21), 04-13 취임(약속 선서). 마누의 무덤 순례(로시오에게 물, 에바리스토에게 커피와 다시 usted — 1부 10화의 tú는 한 번뿐, 토마스 묘비 «Se equivocó treinta años. Y lo dijo»). 소피아는 기록을 아직 넘기지 않음. 기밀비 전 출납관 아빌리오 토레시야의 '초록 장부' 사본 40쪽: «Jueves 26-11-2015 — 3.000 — Seguimiento — T. R. — Recoge: J. M. — Entrega: Atocha, 6.40», 콘코르디아 2015 선거 30만 유로. 'Atocha 6.40' = 목요일 현금 전달 규칙
+· 10화: 벨트란이 토마스를 친 SUV의 렌터카 계약 확보(메리디아나 법인카드, 하비에르 메나 오르투뇨 = J. M., 52세, 전 치안대원). 04-17 밤 정체불명의 남자(퇴직 경정 녹음 400시간)가 '목요일 아토차 6:40' 제안, 통화에 딸깍 두 번(4부 훌리안 복선). 04-18(성목요일) 엘레나가 녹음기와 사본을 이솔리나에게 맡기고 아토차 승강장에서 실종(벤치에 김 나는 종이컵 커피). 마지막 메모 «No hagas con esto lo que ellos hicieron... Llévalo a un juez» / «Las dos cosas, Manu». 마누는 내무부를 배제하고 벨트란·누리아·검찰에 지시, 빈 의자 앞에 커피('묻고 싶은 사람을 위해')
+· 인물 추가: 곤살로 이바라(«El Contraste» 편집장), 벤하민 소토(포렌식 회계사), 페데리코 몬레알(내무부 장관), 로드리고 살다냐(총리 비서실장), 베르나르도 아레니야스(안보 국무장관), 차로 빌체스(페냐플로르 교도관), 마르코스·소니아 레데스마, 루벤(디오니시오의 아들), 나초 에레라·엘사 몬테로, 에우세비오(알메나라 바 주인), 마리사 올메도(국가 회계감사관), 아빌리오 토레시야(기밀비 출납관), 하비에르 메나 오르투뇨(J. M.)
+· [4부 이후 연결 과제] 엘레나의 행방과 4월 17일 밤 통화를 들은 훌리안 / 메나 오르투뇨와 '퇴직 경정 녹음' 400시간 / 초록 장부 원본(아빌리오의 '보험') / 2부 칸딜 공책 41쪽의 T. R. 메모가 카하 쪽에 남은 경위 / 보가라·살다냐 수사와 콘코르디아 30만 유로 / 로시오 법 의회 심의 / 소피아가 아직 넘기지 않은 에바리스토 기록(6부 9화) / 엘레나의 마지막 부탁 '쓰지 말고 판사에게'(4부 녹음 파일의 유혹에 대한 답)</t>
         </is>
       </c>
     </row>
@@ -1994,7 +2010,7 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>[시점: 엘레나] 3부는 엘레나의 음성 메모로 전개된다. 집값·청년 실업·독립 여론으로 나라가 흔들리고, 로시오가 옥중 단식 끝에 숨지자 총파업이 번지며, 엘레나와 브루훌라가 좇은 비자금이 총리실에 닿아 총리가 사임한다. 조기 총선에서 이긴 마누가 인준받은 직후, 하수구 기사를 끝내지 못한 엘레나가 사라진다. 엘레나의 눈에 마누는 ‘유일하게 전화를 받는 정치인’이자 언젠가 기사로 써야 할 권력이다. 개인적 이해관계: 솔리스 계열 언론의 명예훼손 소송, 기사를 멈추라는 편집국, 도청당하는 전화, 마누에 대한 신뢰와 경계. 마지막 보이스오버(마지막 음성 메모): “이걸 누가 듣고 있다면, 나는 기사를 끝내지 못한 거예요. 마누, 이제 당신이 권력이에요. 당신도 쓸 거예요.”</t>
+          <t>[시점: 엘레나] 3부는 엘레나의 음성 메모로 전개된다. 집값·청년 실업·독립 여론으로 나라가 흔들리고, 로시오가 옥중 단식 끝에 숨지자 총파업이 번지며, 엘레나와 브루훌라가 좇은 비자금이 총리실에 닿아 총리가 의회 해산과 불출마를 발표한다. 조기 총선에서 이긴 마누가 인준받은 직후, 하수구 기사를 끝내지 못한 엘레나가 사라진다. 엘레나의 눈에 마누는 ‘유일하게 전화를 받는 정치인’이자 언젠가 기사로 써야 할 권력이다. 개인적 이해관계: 솔리스 계열 언론의 명예훼손 소송, 기사를 멈추라는 편집국, 도청당하는 전화, 마누에 대한 신뢰와 경계. 마지막 보이스오버(마지막 음성 메모, 마누가 듣는다): «No hagas con esto lo que ellos hicieron. No lo uses... Llévalo a un juez.» / «Para quien me escuche, si alguien me escucha: ahora ya sé quién eres.»(“그들이 한 짓을 이것으로 하지 마. 쓰지 마… 판사에게 가져가.” / “내 말을 듣는 사람에게, 누군가 듣는다면: 이제 당신이 누군지 알아.”)</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
@@ -2843,284 +2859,324 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="4" t="inlineStr">
+      <c r="A87" s="5" t="inlineStr">
         <is>
           <t>3부 1화</t>
         </is>
       </c>
-      <c r="B87" s="4" t="inlineStr">
+      <c r="B87" s="5" t="inlineStr">
         <is>
           <t>총리 후보로</t>
         </is>
       </c>
-      <c r="C87" s="4" t="inlineStr">
+      <c r="C87" s="5" t="inlineStr">
         <is>
           <t>Candidato</t>
         </is>
       </c>
-      <c r="D87" s="4" t="inlineStr">
+      <c r="D87" s="5" t="inlineStr">
         <is>
           <t>3부 12화 변형·4부 1화 통합</t>
         </is>
       </c>
-      <c r="E87" s="4" t="inlineStr">
-        <is>
-          <t>[엘레나] 1년 반 뒤 집값·청년 실업·독립 여론의 위기 속에 마누가 총리 후보가 되고, 엘레나는 캠프 감사인 이솔리나에게 커피를 받는다.</t>
-        </is>
-      </c>
-      <c r="F87" s="4" t="inlineStr"/>
+      <c r="E87" s="5" t="inlineStr">
+        <is>
+          <t>[엘레나] 1년 반 뒤인 2017년 6월, 마누가 당원 예비경선에서 68%로 총리 후보가 되고 '끝나면 떠나겠다'고 약속한다. 엘레나는 감사인 이솔리나에게 먼저 커피를 받고, 쪼개기 기부의 IP 하나가 아탈라야 재단의 주소임을 듣는다.</t>
+        </is>
+      </c>
+      <c r="F87" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="88">
-      <c r="A88" s="4" t="inlineStr">
+      <c r="A88" s="5" t="inlineStr">
         <is>
           <t>3부 2화</t>
         </is>
       </c>
-      <c r="B88" s="4" t="inlineStr">
+      <c r="B88" s="5" t="inlineStr">
         <is>
           <t>단식과 자원활동가</t>
         </is>
       </c>
-      <c r="C88" s="4" t="inlineStr">
+      <c r="C88" s="5" t="inlineStr">
         <is>
           <t>El Ayuno y la Voluntaria</t>
         </is>
       </c>
-      <c r="D88" s="4" t="inlineStr">
+      <c r="D88" s="5" t="inlineStr">
         <is>
           <t>4부 2화·3화 통합</t>
         </is>
       </c>
-      <c r="E88" s="4" t="inlineStr">
-        <is>
-          <t>[엘레나] 광산 공사 재개에 로시오가 옥중 단식을 시작하고, 엘레나는 캠프에 막 합류한 스물두 살 이레네를 인터뷰한다.</t>
-        </is>
-      </c>
-      <c r="F88" s="4" t="inlineStr"/>
+      <c r="E88" s="5" t="inlineStr">
+        <is>
+          <t>[엘레나] 광산 공사가 재개되자 교도소 연좌 사건으로 형기가 늘어난 로시오가 10월 2일 옥중 단식을 시작하고, 엘레나는 첫날 헌재 판결로 응대 문서를 고친 스물두 살 이레네를 인터뷰한다.</t>
+        </is>
+      </c>
+      <c r="F88" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="89">
-      <c r="A89" s="4" t="inlineStr">
+      <c r="A89" s="5" t="inlineStr">
         <is>
           <t>3부 3화</t>
         </is>
       </c>
-      <c r="B89" s="4" t="inlineStr">
+      <c r="B89" s="5" t="inlineStr">
         <is>
           <t>솔리스의 배신적 지지</t>
         </is>
       </c>
-      <c r="C89" s="4" t="inlineStr">
+      <c r="C89" s="5" t="inlineStr">
         <is>
           <t>El Apoyo Traicionero de Solís</t>
         </is>
       </c>
-      <c r="D89" s="4" t="inlineStr">
+      <c r="D89" s="5" t="inlineStr">
         <is>
           <t>4부 4화</t>
         </is>
       </c>
-      <c r="E89" s="4" t="inlineStr">
-        <is>
-          <t>[엘레나] 솔리스의 은밀한 지지 제안을 먼저 알아낸 엘레나 앞에서, 마누는 광산 철수와 보상을 공개 조건으로 건다.</t>
-        </is>
-      </c>
-      <c r="F89" s="4" t="inlineStr"/>
+      <c r="E89" s="5" t="inlineStr">
+        <is>
+          <t>[엘레나] 솔리스가 언론 보도와 엘레나의 고소 취하를 '덤'으로 내민 비밀 오찬을 엘레나가 먼저 알아내고, 마누는 광산 포기와 배상을 공개 조건으로 건다. 솔리스는 90일 중지와 함께 '쇄신의 선택지'라는 독이 든 지지를 발표한다.</t>
+        </is>
+      </c>
+      <c r="F89" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="90">
-      <c r="A90" s="4" t="inlineStr">
+      <c r="A90" s="5" t="inlineStr">
         <is>
           <t>3부 4화</t>
         </is>
       </c>
-      <c r="B90" s="4" t="inlineStr">
+      <c r="B90" s="5" t="inlineStr">
         <is>
           <t>로시오의 옥중 사망</t>
         </is>
       </c>
-      <c r="C90" s="4" t="inlineStr">
+      <c r="C90" s="5" t="inlineStr">
         <is>
           <t>La Muerte de Rocío</t>
         </is>
       </c>
-      <c r="D90" s="4" t="inlineStr">
+      <c r="D90" s="5" t="inlineStr">
         <is>
           <t>4부 5화</t>
         </is>
       </c>
-      <c r="E90" s="4" t="inlineStr">
-        <is>
-          <t>[엘레나] 병원 이송이 ‘호송 절차’로 지연되는 사이 단식 14일째 로시오가 숨지고, 엘레나는 이송 기록을 손에 넣는다.</t>
-        </is>
-      </c>
-      <c r="F90" s="4" t="inlineStr"/>
+      <c r="E90" s="5" t="inlineStr">
+        <is>
+          <t>[엘레나] 단식 14일째, 병원 이송이 치안대 '호송 인력 부족'으로 5시간 51분 지연되는 사이 로시오가 구급차 안에서 숨진다. 엘레나는 교도관이 건넨 기록부 사본에서 'UAR에 보고' 한 줄을 찾는다.</t>
+        </is>
+      </c>
+      <c r="F90" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="91">
-      <c r="A91" s="4" t="inlineStr">
+      <c r="A91" s="5" t="inlineStr">
         <is>
           <t>3부 5화</t>
         </is>
       </c>
-      <c r="B91" s="4" t="inlineStr">
+      <c r="B91" s="5" t="inlineStr">
         <is>
           <t>거리의 혁명</t>
         </is>
       </c>
-      <c r="C91" s="4" t="inlineStr">
+      <c r="C91" s="5" t="inlineStr">
         <is>
           <t>La Revolución en las Calles</t>
         </is>
       </c>
-      <c r="D91" s="4" t="inlineStr">
+      <c r="D91" s="5" t="inlineStr">
         <is>
           <t>4부 6화</t>
         </is>
       </c>
-      <c r="E91" s="4" t="inlineStr">
-        <is>
-          <t>[엘레나] 총파업과 광장 농성이 47개 도시로 번지고, 엘레나는 해산 명령을 거부한 경찰관을 인터뷰한다.</t>
-        </is>
-      </c>
-      <c r="F91" s="4" t="inlineStr"/>
+      <c r="E91" s="5" t="inlineStr">
+        <is>
+          <t>[엘레나] '5시간 51분' 기사 뒤 물병을 든 광장 농성이 47개 도시로 번지고 총파업이 열린다. 엘레나는 해산 명령 앞에서 헬멧을 벗은 기동대원 마르코스를 인터뷰한다.</t>
+        </is>
+      </c>
+      <c r="F91" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="92">
-      <c r="A92" s="4" t="inlineStr">
+      <c r="A92" s="5" t="inlineStr">
         <is>
           <t>3부 6화</t>
         </is>
       </c>
-      <c r="B92" s="4" t="inlineStr">
+      <c r="B92" s="5" t="inlineStr">
         <is>
           <t>쿠에스타의 선택</t>
         </is>
       </c>
-      <c r="C92" s="4" t="inlineStr">
+      <c r="C92" s="5" t="inlineStr">
         <is>
           <t>La Elección de Cuesta</t>
         </is>
       </c>
-      <c r="D92" s="4" t="inlineStr">
+      <c r="D92" s="5" t="inlineStr">
         <is>
           <t>4부 7화</t>
         </is>
       </c>
-      <c r="E92" s="4" t="inlineStr">
-        <is>
-          <t>[엘레나] 쿠에스타가 엘레나에게 ‘기사를 내면 나도 못 지킨다’고 경고하고, 긴급회의에서 비상사태 대신 협상을 택한다.</t>
-        </is>
-      </c>
-      <c r="F92" s="4" t="inlineStr"/>
+      <c r="E92" s="5" t="inlineStr">
+        <is>
+          <t>[엘레나] 쿠에스타가 엘레나에게 커피를 사며 'UAR 한 줄을 내면 나도 못 지킨다'고 경고하지만, 위기회의에서 비상사태 대신 협상을 택하고 그녀의 우편함에 두 번째 출처를 넣는다.</t>
+        </is>
+      </c>
+      <c r="F92" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="93">
-      <c r="A93" s="4" t="inlineStr">
+      <c r="A93" s="5" t="inlineStr">
         <is>
           <t>3부 7화</t>
         </is>
       </c>
-      <c r="B93" s="4" t="inlineStr">
+      <c r="B93" s="5" t="inlineStr">
         <is>
           <t>암살 시도</t>
         </is>
       </c>
-      <c r="C93" s="4" t="inlineStr">
+      <c r="C93" s="5" t="inlineStr">
         <is>
           <t>El Atentado</t>
         </is>
       </c>
-      <c r="D93" s="4" t="inlineStr">
+      <c r="D93" s="5" t="inlineStr">
         <is>
           <t>4부 8화</t>
         </is>
       </c>
-      <c r="E93" s="4" t="inlineStr">
-        <is>
-          <t>[엘레나] 보수 텃밭 도시 유세 현장에서 마누를 겨눈 저격이 벌어지고, 엘레나는 사살된 저격범의 휴대폰을 촬영한다.</t>
-        </is>
-      </c>
-      <c r="F93" s="4" t="inlineStr"/>
+      <c r="E93" s="5" t="inlineStr">
+        <is>
+          <t>[엘레나] 2018년 6월 보수 텃밭 알메나라 델 캄포 유세에서 저격이 벌어져 경호원이 쓰러지고 저격범은 사살된다. 엘레나는 18초 동안 저격범 휴대폰의 'J. MERIDIANA' 착신 화면을 찍는다.</t>
+        </is>
+      </c>
+      <c r="F93" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="94">
-      <c r="A94" s="4" t="inlineStr">
+      <c r="A94" s="5" t="inlineStr">
         <is>
           <t>3부 8화</t>
         </is>
       </c>
-      <c r="B94" s="4" t="inlineStr">
+      <c r="B94" s="5" t="inlineStr">
         <is>
           <t>구체제의 붕괴</t>
         </is>
       </c>
-      <c r="C94" s="4" t="inlineStr">
+      <c r="C94" s="5" t="inlineStr">
         <is>
           <t>La Caída del Viejo Régimen</t>
         </is>
       </c>
-      <c r="D94" s="4" t="inlineStr">
+      <c r="D94" s="5" t="inlineStr">
         <is>
           <t>4부 9화</t>
         </is>
       </c>
-      <c r="E94" s="4" t="inlineStr">
-        <is>
-          <t>[엘레나] 엘레나와 브루훌라가 좇은 비자금이 총리실과 암살 배후에 닿고, 기사가 나간 날 총리가 사임한다.</t>
-        </is>
-      </c>
-      <c r="F94" s="4" t="inlineStr"/>
+      <c r="E94" s="5" t="inlineStr">
+        <is>
+          <t>[엘레나] 엘레나와 브루훌라가 좇은 돈이 재무부 특별 프로그램(보가라)과 총리 비서실장 살다냐의 메모에 닿고, 기사 이틀 뒤 발카르셀 총리가 의회 해산과 불출마를 발표한다.</t>
+        </is>
+      </c>
+      <c r="F94" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="95">
-      <c r="A95" s="4" t="inlineStr">
+      <c r="A95" s="5" t="inlineStr">
         <is>
           <t>3부 9화</t>
         </is>
       </c>
-      <c r="B95" s="4" t="inlineStr">
+      <c r="B95" s="5" t="inlineStr">
         <is>
           <t>선거와 인준</t>
         </is>
       </c>
-      <c r="C95" s="4" t="inlineStr">
+      <c r="C95" s="5" t="inlineStr">
         <is>
           <t>Elecciones e Investidura</t>
         </is>
       </c>
-      <c r="D95" s="4" t="inlineStr">
+      <c r="D95" s="5" t="inlineStr">
         <is>
           <t>4부 11화 변형·12화 통합</t>
         </is>
       </c>
-      <c r="E95" s="4" t="inlineStr">
-        <is>
-          <t>[엘레나] 마누가 인준 표결을 통과하고 무덤들을 찾는 사이, 엘레나는 하수구와 여당을 잇는 기밀비 장부를 건네받는다.</t>
-        </is>
-      </c>
-      <c r="F95" s="4" t="inlineStr"/>
+      <c r="E95" s="5" t="inlineStr">
+        <is>
+          <t>[엘레나] 오리손테 코문이 제1당이 되고 마누가 2차 표결로 인준받아 세 무덤을 찾는 사이, 엘레나는 기밀비 '초록 장부'에서 'T. R. 미행 — 아토차 6시 40분' 줄을 건네받는다.</t>
+        </is>
+      </c>
+      <c r="F95" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="96">
-      <c r="A96" s="4" t="inlineStr">
+      <c r="A96" s="5" t="inlineStr">
         <is>
           <t>3부 10화</t>
         </is>
       </c>
-      <c r="B96" s="4" t="inlineStr">
+      <c r="B96" s="5" t="inlineStr">
         <is>
           <t>마지막 음성 메모</t>
         </is>
       </c>
-      <c r="C96" s="4" t="inlineStr">
+      <c r="C96" s="5" t="inlineStr">
         <is>
           <t>La Última Nota de Voz</t>
         </is>
       </c>
-      <c r="D96" s="4" t="inlineStr">
+      <c r="D96" s="5" t="inlineStr">
         <is>
           <t>3부 7화 변형</t>
         </is>
       </c>
-      <c r="E96" s="4" t="inlineStr">
-        <is>
-          <t>[엘레나] 취임 일주일 뒤, 하수구 기사 초안을 음성으로 남긴 엘레나가 제보자를 만나러 나가 흔적 없이 사라진다.</t>
-        </is>
-      </c>
-      <c r="F96" s="4" t="inlineStr"/>
+      <c r="E96" s="5" t="inlineStr">
+        <is>
+          <t>[엘레나] 취임 사흘 뒤, 엘레나는 하수구 기사 초안을 녹음기에 읽다가 '목요일 아토차 6시 40분'의 전화를 받고, 녹음기를 이솔리나에게 맡긴 채 사라진다. 마누는 그녀의 마지막 음성 메모를 듣는다.</t>
+        </is>
+      </c>
+      <c r="F96" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="10" t="inlineStr">

--- a/기획안/혼합안_이탈리아_스페인_독일.xlsx
+++ b/기획안/혼합안_이탈리아_스페인_독일.xlsx
@@ -679,7 +679,7 @@
       </c>
       <c r="N5" s="5" t="inlineStr">
         <is>
-          <t>1~3부 30화(1~3부 전체) 대본·학습노트 완료 (2026-10)</t>
+          <t>1~4부 40화(1~4부 전체) 대본·학습노트 완료 (2026-10)</t>
         </is>
       </c>
       <c r="O5" s="6" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>1~3부 30화(부당 10화 구성의 1~3부 전체) 대본·학습노트 완료 (2026-10)</t>
+          <t>1~4부 40화(부당 10화 구성의 1~4부 전체) 대본·학습노트 완료 (2026-10)</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>1부, 2부, 3부</t>
+          <t>1부, 2부, 3부, 4부</t>
         </is>
       </c>
     </row>
@@ -915,7 +915,7 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>학습 노트 30편(1부 1~10화, 2부 1~10화, 3부 1~10화, docx), 0_동사_시제_가이드(md·docx)</t>
+          <t>학습 노트 40편(1~4부 각 1~10화, docx), 0_동사_시제_가이드(md·docx)</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,22 @@
 · 9화: 2019-03-17 오리손테 코문 131석 제1당. 인준 1차 04-09(171:179 부결), 2차 04-11(171:158, 기권 21), 04-13 취임(약속 선서). 마누의 무덤 순례(로시오에게 물, 에바리스토에게 커피와 다시 usted — 1부 10화의 tú는 한 번뿐, 토마스 묘비 «Se equivocó treinta años. Y lo dijo»). 소피아는 기록을 아직 넘기지 않음. 기밀비 전 출납관 아빌리오 토레시야의 '초록 장부' 사본 40쪽: «Jueves 26-11-2015 — 3.000 — Seguimiento — T. R. — Recoge: J. M. — Entrega: Atocha, 6.40», 콘코르디아 2015 선거 30만 유로. 'Atocha 6.40' = 목요일 현금 전달 규칙
 · 10화: 벨트란이 토마스를 친 SUV의 렌터카 계약 확보(메리디아나 법인카드, 하비에르 메나 오르투뇨 = J. M., 52세, 전 치안대원). 04-17 밤 정체불명의 남자(퇴직 경정 녹음 400시간)가 '목요일 아토차 6:40' 제안, 통화에 딸깍 두 번(4부 훌리안 복선). 04-18(성목요일) 엘레나가 녹음기와 사본을 이솔리나에게 맡기고 아토차 승강장에서 실종(벤치에 김 나는 종이컵 커피). 마지막 메모 «No hagas con esto lo que ellos hicieron... Llévalo a un juez» / «Las dos cosas, Manu». 마누는 내무부를 배제하고 벨트란·누리아·검찰에 지시, 빈 의자 앞에 커피('묻고 싶은 사람을 위해')
 · 인물 추가: 곤살로 이바라(«El Contraste» 편집장), 벤하민 소토(포렌식 회계사), 페데리코 몬레알(내무부 장관), 로드리고 살다냐(총리 비서실장), 베르나르도 아레니야스(안보 국무장관), 차로 빌체스(페냐플로르 교도관), 마르코스·소니아 레데스마, 루벤(디오니시오의 아들), 나초 에레라·엘사 몬테로, 에우세비오(알메나라 바 주인), 마리사 올메도(국가 회계감사관), 아빌리오 토레시야(기밀비 출납관), 하비에르 메나 오르투뇨(J. M.)
-· [4부 이후 연결 과제] 엘레나의 행방과 4월 17일 밤 통화를 들은 훌리안 / 메나 오르투뇨와 '퇴직 경정 녹음' 400시간 / 초록 장부 원본(아빌리오의 '보험') / 2부 칸딜 공책 41쪽의 T. R. 메모가 카하 쪽에 남은 경위 / 보가라·살다냐 수사와 콘코르디아 30만 유로 / 로시오 법 의회 심의 / 소피아가 아직 넘기지 않은 에바리스토 기록(6부 9화) / 엘레나의 마지막 부탁 '쓰지 말고 판사에게'(4부 녹음 파일의 유혹에 대한 답)</t>
+· [4부 이후 연결 과제] 엘레나의 행방과 4월 17일 밤 통화를 들은 훌리안 / 메나 오르투뇨와 '퇴직 경정 녹음' 400시간 / 초록 장부 원본(아빌리오의 '보험') / 2부 칸딜 공책 41쪽의 T. R. 메모가 카하 쪽에 남은 경위 / 보가라·살다냐 수사와 콘코르디아 30만 유로 / 로시오 법 의회 심의 / 소피아가 아직 넘기지 않은 에바리스토 기록(6부 9화) / 엘레나의 마지막 부탁 '쓰지 말고 판사에게'(4부 녹음 파일의 유혹에 대한 답)
+[4부 제작 후 변경·확정]
+· 시점: 내부고발 경찰 훌리안 페란 오테로 경위(1975년생, UAR 기술반)의 보이스오버(«Julián (V.O.):»)와 감시 로그 화면. 딸 루시아(15세, 배구 리시버), 죽은 아내 아나, 1984년 작전에 배치됐다 떠난 경찰 아버지 시프리아노가 개인적 이해관계
+· 연도: 2019년 4월(엘레나 실종 직후)~2020년 2월 말(하수구법 공포). 팬데믹 이전에 닫음
+· 1화: 훌리안이 4월 17일 엘레나의 마지막 통화를 실시간 감청(딸깍 두 번=그의 녹음+라스트라의 터미널 01). 라스트라가 이튿날 로그 삭제. 새 임무 = 총리 휴대폰 코드명 FARO 관리. 스파이웨어 이름 «Lince». 재무부 '2013년 이전 기록 폐기'=첫 벽. 보가라가 총리 전화로 '1년 뒤엔 당신 없다'. 훌리안이 엘레나 통화 사본을 아버지 경찰모에 숨기고, 공중전화로 아빌리오에게 '장부를 공증인에게' 경고
+· 2화: 페르민 가르세스의 '룩셈부르크 계좌' 가짜 문건(서식 NI-3, 'Ministero' 오타). 훌리안이 2009년 비야페로사에서 그 서식을 포맷한 사람임을 자각. IBAN 검증 숫자 오류로 가짜 입증(브루훌라), 'e' 오타 사본을 익명으로 누리아에게. 라스트라가 2009 원본을 '2014 서버 이전 분실'로 조작. 집 콘센트(아버지 사진 뒤)에서 도청기 발견
+· 3화: 루뱅 대학+브루훌라가 휴대폰 10대에서 Lince 발견(이레네 것은 4월 24일=엘레나 실종 엿새 뒤). 총리가 도청자에게 직접 '내일 10시 법원에'. 라스트라의 '흔적 삭제' 명령 → 훌리안은 시스템에선 지우되 10개 감염 날짜를 손으로 종이에. 집은 라디오로 덮고 쪽지로 대화
+· 4화: 퇴직 경정 바렐라의 30년 녹음(UAR 서버의 '유산'). 쿠에스타가 '범죄/사생활' 구분 기준으로 일부만 훌리안에게. 2013년 이스마엘 코르데로(광부) 사망의 감정서 조작('2.80m→3m') 녹음. 훌리안이 곤살로에게 '목소리는 지도, 증거는 보물'로 넘김. 오리손테 코문은 '우리 편으로 쓰자'를 거부(필리·페르민·누리아·마누, 엘레나의 말)
+· 5화: 레드 파로 알바로 힐 몬테스가 판사 부패망 조사 중 11월 카라반첼 주차장에서 청부 총격 피살. 훌리안이 그 미행(OBJ. 338, 터미널 01)을 로그에서 봄='조명을 켠 책임'. 루시아의 '손 드는 선수' 이야기. 훌리안이 이레네를 통해 총리 쪽에 첫 접촉, 대가는 '딸 루시아가 기록에 안 나오는 것'
+· 6화: 루시아 학교 앞 회색 차 → 쿠에스타의 조언으로 번호판을 스토킹 고발('태워' 못 쓰게). 솔리스 은닉구조(룩셈부르크 지주사-파나마 신탁-아탈라야, 서명자 처남 비다우레)가 브루훌라+검찰 공조로 붕괴, 바라하스 공항에서 솔리스 체포. 훌리안이 '손댄 자/밝힌 자' 중 밝힌 자가 되기로 결심
+· 7화: 봉인 파일에서 엘레나 휴대폰 마지막 신호(4월 18일 아토차→과달라하라 선로→시에라 폐광 '라 나바'). 바 주인 오비디오가 차고 달력 4월 18일에 '밤에 차·두 남자' 기록=결정적 증언. 1월 17일 폐광 수직갱에서 유해 발견. 훌리안은 자기를 '정보원' 아닌 '청취자(oyente)'로 불러 달라 함
+· 8화: 하원 조사위. 쿠에스타가 면책·거래 없이 35년사 증언, 1984 에스쿠데로 사건 서류에 아버지 시프리아노의 이름(=떠난 사람)을 공개 호명. 훌리안도 같은 자리에서 '하지 않은 일(부작위)'을 증언. 라스트라 직무 배제, '명령을 따랐을 뿐' 변론 택함
+· 9화: 「정보기관 사법통제법(하수구법)」 제9조=총리실 자신 포함 판사 승인 없는 감청 전면 금지. 통과일에 훌리안 배지 반납, 보호증인으로 새 이름(가운데 이름 '시프리아노')·새 도시. 루시아는 승급전을 포기하고 이사 선택, 이름만은 지킴. 제9조 3항 단서(법 이전 불법 녹음을 자진 제출하면 소지만으로는 불처벌)=마누 측이 넣은 익명의 구원. 쿠에스타 미결 구금
+· 10화: 2020-02-27 하수구법 공포일 밤, 북부의 새 도시. TV에서 알타 마르카 수반 다비드 오르타가 10-18 자결 주민투표 발표(연설문 작성자 칸델라 몬토로가 뒷모습으로 첫 등장). 마누는 '경찰 아닌 법정으로, 진압경찰 없이, 대화'. 훌리안이 시점을 칸델라에게 넘기며 '서류 태우지 말고 판사에게'를 이레네 통해 전함. 원안의 '엘레나 유해 발견·쿠에스타 증언'을 4부 안에서 모두 소화하고, 「솔리스 공항 체포」를 6화로 앞당김(원안 4부 6화 유지)
+· 인물 추가: 헤라르도 라스트라 경감(터미널 01, '다른 집'), 치노(기술반 동료), 에르메네힐도 바렐라(30년 녹음·3부 10화 전화의 목소리), 하비에르 메나 오르투뇨(J.M.), 콘셉시온 리바스 판사, 벨트란(재등장), 아빌리오 토레시야(재등장), 아나 로드리게스(보호증인 담당), 오비디오(라 나바 바 주인), 아나·시프리아노 페란(훌리안의 가족)
+· [5부 이후 연결 과제] 하수구 재판(이듬해, 훌리안 비공개 증언)·라스트라 '명령 수행' 변론 / 쿠에스타의 1984년 '거울'과 의회 증언 후속 / 메나·바렐라의 형사 절차 / 제9조의 실제 준수 여부 / 알타 마르카 주민투표(5부, 칸델라 시점)로의 이행 / 솔리스 재판(7부 9화)·보가라 도피와 인도(8부 10화)로의 복선</t>
         </is>
       </c>
     </row>
@@ -3179,284 +3194,324 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="10" t="inlineStr">
+      <c r="A97" s="5" t="inlineStr">
         <is>
           <t>4부 1화</t>
         </is>
       </c>
-      <c r="B97" s="10" t="inlineStr">
+      <c r="B97" s="5" t="inlineStr">
         <is>
           <t>첫 벽과 새 임무</t>
         </is>
       </c>
-      <c r="C97" s="10" t="inlineStr">
+      <c r="C97" s="5" t="inlineStr">
         <is>
           <t>El Primer Muro</t>
         </is>
       </c>
-      <c r="D97" s="10" t="inlineStr">
+      <c r="D97" s="5" t="inlineStr">
         <is>
           <t>5부 1화·2화 통합 변형</t>
         </is>
       </c>
-      <c r="E97" s="10" t="inlineStr">
-        <is>
-          <t>[훌리안] 재무부가 기밀비 자료를 감추고, 경위 훌리안은 새 총리의 전화를 ‘관리’하라는 임무를 받는다. 보가라는 ‘1년 뒤엔 당신 없다’고 말한다.</t>
-        </is>
-      </c>
-      <c r="F97" s="10" t="inlineStr"/>
+      <c r="E97" s="5" t="inlineStr">
+        <is>
+          <t>[훌리안] 엘레나 실종 나흘 뒤, 감시 지하실의 경위 훌리안은 그녀의 마지막 통화를 자기가 들었음을 안다. 재무부는 기밀비 기록을 감추고, 그는 새 총리의 휴대폰 'FARO'를 '관리'하라는 임무를 받는다. 보가라는 '1년 뒤엔 당신 없다'고 한다.</t>
+        </is>
+      </c>
+      <c r="F97" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="98">
-      <c r="A98" s="10" t="inlineStr">
+      <c r="A98" s="5" t="inlineStr">
         <is>
           <t>4부 2화</t>
         </is>
       </c>
-      <c r="B98" s="10" t="inlineStr">
+      <c r="B98" s="5" t="inlineStr">
         <is>
           <t>조작된 서류</t>
         </is>
       </c>
-      <c r="C98" s="10" t="inlineStr">
+      <c r="C98" s="5" t="inlineStr">
         <is>
           <t>El Informe Falso</t>
         </is>
       </c>
-      <c r="D98" s="10" t="inlineStr">
+      <c r="D98" s="5" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="E98" s="10" t="inlineStr">
-        <is>
-          <t>[훌리안] 당 간부의 가짜 해외 계좌 문건이 뿌려지고, 훌리안은 그 서식이 에바리스토를 옭아맨 보고서와 같음을 알아본다.</t>
-        </is>
-      </c>
-      <c r="F98" s="10" t="inlineStr"/>
+      <c r="E98" s="5" t="inlineStr">
+        <is>
+          <t>[훌리안] 페르민 가르세스의 가짜 해외 계좌 문건이 신문 세 곳에 동시에 뿌려지고, 훌리안은 그 서식이 2009년 에바리스토를 가둔 메모와 같고 자기가 포맷한 것임을 알아본다. 'e' 하나 빠진 오타로 조작이 드러난다.</t>
+        </is>
+      </c>
+      <c r="F98" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="99">
-      <c r="A99" s="10" t="inlineStr">
+      <c r="A99" s="5" t="inlineStr">
         <is>
           <t>4부 3화</t>
         </is>
       </c>
-      <c r="B99" s="10" t="inlineStr">
+      <c r="B99" s="5" t="inlineStr">
         <is>
           <t>내 전화 속의 눈</t>
         </is>
       </c>
-      <c r="C99" s="10" t="inlineStr">
+      <c r="C99" s="5" t="inlineStr">
         <is>
           <t>El Ojo en Mi Teléfono</t>
         </is>
       </c>
-      <c r="D99" s="10" t="inlineStr">
+      <c r="D99" s="5" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="E99" s="10" t="inlineStr">
-        <is>
-          <t>[훌리안] 총리와 이레네, 기자들의 전화에서 스파이웨어가 발견된다. 그것을 심은 훌리안에게 흔적을 지우라는 명령이 내려온다.</t>
-        </is>
-      </c>
-      <c r="F99" s="10" t="inlineStr"/>
+      <c r="E99" s="5" t="inlineStr">
+        <is>
+          <t>[훌리안] 루뱅 대학과 브루훌라가 총리·이레네·기자 등 열 대의 휴대폰에서 스파이웨어 'Lince'를 찾아낸다. 지우라는 명령에 훌리안은 시스템에서만 지우고 감염 날짜 열 개를 손으로 적어 둔다.</t>
+        </is>
+      </c>
+      <c r="F99" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="100">
-      <c r="A100" s="10" t="inlineStr">
+      <c r="A100" s="5" t="inlineStr">
         <is>
           <t>4부 4화</t>
         </is>
       </c>
-      <c r="B100" s="10" t="inlineStr">
+      <c r="B100" s="5" t="inlineStr">
         <is>
           <t>경정의 녹음</t>
         </is>
       </c>
-      <c r="C100" s="10" t="inlineStr">
+      <c r="C100" s="5" t="inlineStr">
         <is>
           <t>Las Grabaciones del Comisario</t>
         </is>
       </c>
-      <c r="D100" s="10" t="inlineStr">
+      <c r="D100" s="5" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="E100" s="10" t="inlineStr">
-        <is>
-          <t>[훌리안] 훌리안이 퇴직 경정의 녹음 파일을 언론에 넘기고, 마누는 그것을 ‘우리 편’으로 쓰자는 유혹을 거부한다.</t>
-        </is>
-      </c>
-      <c r="F100" s="10" t="inlineStr"/>
+      <c r="E100" s="5" t="inlineStr">
+        <is>
+          <t>[훌리안] 30년을 녹음해 온 퇴직 경정의 파일에서 2013년 광부 사망 감정서 조작이 드러난다. 훌리안은 '목소리는 지도일 뿐'이라며 편집장에게 넘기고, 오리손테 코문은 그것을 '우리 편으로 쓰자'는 유혹을 거부한다.</t>
+        </is>
+      </c>
+      <c r="F100" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="101">
-      <c r="A101" s="10" t="inlineStr">
+      <c r="A101" s="5" t="inlineStr">
         <is>
           <t>4부 5화</t>
         </is>
       </c>
-      <c r="B101" s="10" t="inlineStr">
+      <c r="B101" s="5" t="inlineStr">
         <is>
           <t>개혁의 대가</t>
         </is>
       </c>
-      <c r="C101" s="10" t="inlineStr">
+      <c r="C101" s="5" t="inlineStr">
         <is>
           <t>El Precio de la Reforma</t>
         </is>
       </c>
-      <c r="D101" s="10" t="inlineStr">
+      <c r="D101" s="5" t="inlineStr">
         <is>
           <t>5부 5화</t>
         </is>
       </c>
-      <c r="E101" s="10" t="inlineStr">
-        <is>
-          <t>[훌리안] 법관 부패망을 조사하던 알바로가 피살되고, 감시 로그에서 그 동선을 본 훌리안이 마누에게 처음 연락한다.</t>
-        </is>
-      </c>
-      <c r="F101" s="10" t="inlineStr"/>
+      <c r="E101" s="5" t="inlineStr">
+        <is>
+          <t>[훌리안] 판사 부패망을 쫓던 레드 파로의 알바로가 청부 총격으로 피살되고, 훌리안은 그 미행이 감시 로그에 있었음을 안다. 딸의 말에 떠밀려 그는 처음으로 총리 쪽에 연락한다.</t>
+        </is>
+      </c>
+      <c r="F101" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="102">
-      <c r="A102" s="10" t="inlineStr">
+      <c r="A102" s="5" t="inlineStr">
         <is>
           <t>4부 6화</t>
         </is>
       </c>
-      <c r="B102" s="10" t="inlineStr">
+      <c r="B102" s="5" t="inlineStr">
         <is>
           <t>솔리스의 몰락</t>
         </is>
       </c>
-      <c r="C102" s="10" t="inlineStr">
+      <c r="C102" s="5" t="inlineStr">
         <is>
           <t>La Caída de Solís</t>
         </is>
       </c>
-      <c r="D102" s="10" t="inlineStr">
+      <c r="D102" s="5" t="inlineStr">
         <is>
           <t>5부 3화·8화 통합</t>
         </is>
       </c>
-      <c r="E102" s="10" t="inlineStr">
-        <is>
-          <t>[훌리안] 솔리스 언론이 유출자 색출에 나서 딸의 학교 앞에 차가 서고, 은닉 구조가 드러난 솔리스는 공항에서 체포된다.</t>
-        </is>
-      </c>
-      <c r="F102" s="10" t="inlineStr"/>
+      <c r="E102" s="5" t="inlineStr">
+        <is>
+          <t>[훌리안] 솔리스 측이 유출자를 찾아 딸의 학교 앞에 차를 세우자, 훌리안은 번호판을 고발해 감시를 '태워' 버린다. 룩셈부르크·파나마로 이어진 은닉 구조가 무너지고 솔리스는 바라하스 공항에서 체포된다.</t>
+        </is>
+      </c>
+      <c r="F102" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="103">
-      <c r="A103" s="10" t="inlineStr">
+      <c r="A103" s="5" t="inlineStr">
         <is>
           <t>4부 7화</t>
         </is>
       </c>
-      <c r="B103" s="10" t="inlineStr">
+      <c r="B103" s="5" t="inlineStr">
         <is>
           <t>엘레나를 찾아서</t>
         </is>
       </c>
-      <c r="C103" s="10" t="inlineStr">
+      <c r="C103" s="5" t="inlineStr">
         <is>
           <t>Buscando a Elena</t>
         </is>
       </c>
-      <c r="D103" s="10" t="inlineStr">
+      <c r="D103" s="5" t="inlineStr">
         <is>
           <t>5부 9화 확장</t>
         </is>
       </c>
-      <c r="E103" s="10" t="inlineStr">
-        <is>
-          <t>[훌리안] 봉인된 감시 파일에서 엘레나의 마지막 위치를 찾은 훌리안의 제보로 산속 폐광에서 그녀의 유해가 발견된다.</t>
-        </is>
-      </c>
-      <c r="F103" s="10" t="inlineStr"/>
+      <c r="E103" s="5" t="inlineStr">
+        <is>
+          <t>[훌리안] 봉인됐던 감시 파일에서 엘레나의 마지막 위치가 과달라하라 시에라의 폐광으로 좁혀지고, 여든 살 바 주인의 달력 한 칸이 결정적 증언이 된다. 아흐레 만에 폐광 수직갱에서 그녀의 유해가 발견된다.</t>
+        </is>
+      </c>
+      <c r="F103" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="104">
-      <c r="A104" s="10" t="inlineStr">
+      <c r="A104" s="5" t="inlineStr">
         <is>
           <t>4부 8화</t>
         </is>
       </c>
-      <c r="B104" s="10" t="inlineStr">
+      <c r="B104" s="5" t="inlineStr">
         <is>
           <t>두 경찰의 증언</t>
         </is>
       </c>
-      <c r="C104" s="10" t="inlineStr">
+      <c r="C104" s="5" t="inlineStr">
         <is>
           <t>El Testimonio de Dos Policías</t>
         </is>
       </c>
-      <c r="D104" s="10" t="inlineStr">
+      <c r="D104" s="5" t="inlineStr">
         <is>
           <t>5부 9화 확장</t>
         </is>
       </c>
-      <c r="E104" s="10" t="inlineStr">
-        <is>
-          <t>[훌리안] 쿠에스타가 면책 없이 하수구 35년사를 증언하고 물러나며, 훌리안도 같은 자리에서 자신의 가담을 인정한다.</t>
-        </is>
-      </c>
-      <c r="F104" s="10" t="inlineStr"/>
+      <c r="E104" s="5" t="inlineStr">
+        <is>
+          <t>[훌리안] 하원 조사위에서 쿠에스타 경정이 면책 없이 35년의 하수구사를 증언하고, 훌리안의 아버지 이름을 '떠난 사람'으로 호명한다. 훌리안도 같은 자리에서 자신이 '하지 않은 일'을 인정한다.</t>
+        </is>
+      </c>
+      <c r="F104" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="105">
-      <c r="A105" s="10" t="inlineStr">
+      <c r="A105" s="5" t="inlineStr">
         <is>
           <t>4부 9화</t>
         </is>
       </c>
-      <c r="B105" s="10" t="inlineStr">
+      <c r="B105" s="5" t="inlineStr">
         <is>
           <t>하수구를 닫는 법</t>
         </is>
       </c>
-      <c r="C105" s="10" t="inlineStr">
+      <c r="C105" s="5" t="inlineStr">
         <is>
           <t>La Ley de las Cloacas</t>
         </is>
       </c>
-      <c r="D105" s="10" t="inlineStr">
+      <c r="D105" s="5" t="inlineStr">
         <is>
           <t>5부 10화 변형</t>
         </is>
       </c>
-      <c r="E105" s="10" t="inlineStr">
-        <is>
-          <t>[훌리안] 정보기관 사법통제법에 총리실 자신의 감청 금지 조항이 들어가고, 훌리안은 배지를 반납해 새 이름을 받는다.</t>
-        </is>
-      </c>
-      <c r="F105" s="10" t="inlineStr"/>
+      <c r="E105" s="5" t="inlineStr">
+        <is>
+          <t>[훌리안] 정보기관을 사법 통제 아래 두는 '하수구법'에 총리실 자신의 감청까지 금지하는 제9조가 들어간다. 그 법이 통과된 날, 훌리안은 배지를 반납하고 딸과 함께 새 이름·새 도시를 받는다.</t>
+        </is>
+      </c>
+      <c r="F105" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="106">
-      <c r="A106" s="10" t="inlineStr">
+      <c r="A106" s="5" t="inlineStr">
         <is>
           <t>4부 10화</t>
         </is>
       </c>
-      <c r="B106" s="10" t="inlineStr">
+      <c r="B106" s="5" t="inlineStr">
         <is>
           <t>첫 번째 균열</t>
         </is>
       </c>
-      <c r="C106" s="10" t="inlineStr">
+      <c r="C106" s="5" t="inlineStr">
         <is>
           <t>La Primera Grieta</t>
         </is>
       </c>
-      <c r="D106" s="10" t="inlineStr">
+      <c r="D106" s="5" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="E106" s="10" t="inlineStr">
-        <is>
-          <t>[훌리안] 법이 통과된 날 밤, 새 이름의 집에서 딸과 TV를 보던 훌리안 앞에 알타 마르카 수반이 주민투표 날짜를 발표한다.</t>
-        </is>
-      </c>
-      <c r="F106" s="10" t="inlineStr"/>
+      <c r="E106" s="5" t="inlineStr">
+        <is>
+          <t>[훌리안] 하수구법이 공포된 날 밤, 새 도시의 새 집에서 부녀가 텔레비전을 켜는 순간, 알타 마르카 수반 오르타가 자결 주민투표 날짜를 발표한다. 한 균열을 닫자마자 다른 균열이 열리고, 훌리안은 이야기를 칸델라에게 넘긴다.</t>
+        </is>
+      </c>
+      <c r="F106" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">

--- a/기획안/혼합안_이탈리아_스페인_독일.xlsx
+++ b/기획안/혼합안_이탈리아_스페인_독일.xlsx
@@ -679,7 +679,7 @@
       </c>
       <c r="N5" s="5" t="inlineStr">
         <is>
-          <t>1~4부 40화(1~4부 전체) 대본·학습노트 완료 (2026-10)</t>
+          <t>1~5부 50화(1~5부 전체) 대본·학습노트 완료 (2026-10)</t>
         </is>
       </c>
       <c r="O5" s="6" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>1~4부 40화(부당 10화 구성의 1~4부 전체) 대본·학습노트 완료 (2026-10)</t>
+          <t>1~5부 50화(부당 10화 구성의 1~5부 전체) 대본·학습노트 완료 (2026-10)</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>1부, 2부, 3부, 4부</t>
+          <t>1부, 2부, 3부, 4부, 5부</t>
         </is>
       </c>
     </row>
@@ -915,7 +915,7 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>학습 노트 40편(1~4부 각 1~10화, docx), 0_동사_시제_가이드(md·docx)</t>
+          <t>학습 노트 50편(1~5부 각 1~10화, docx), 0_동사_시제_가이드(md·docx)</t>
         </is>
       </c>
     </row>
@@ -981,7 +981,24 @@
 · 9화: 「정보기관 사법통제법(하수구법)」 제9조=총리실 자신 포함 판사 승인 없는 감청 전면 금지. 통과일에 훌리안 배지 반납, 보호증인으로 새 이름(가운데 이름 '시프리아노')·새 도시. 루시아는 승급전을 포기하고 이사 선택, 이름만은 지킴. 제9조 3항 단서(법 이전 불법 녹음을 자진 제출하면 소지만으로는 불처벌)=마누 측이 넣은 익명의 구원. 쿠에스타 미결 구금
 · 10화: 2020-02-27 하수구법 공포일 밤, 북부의 새 도시. TV에서 알타 마르카 수반 다비드 오르타가 10-18 자결 주민투표 발표(연설문 작성자 칸델라 몬토로가 뒷모습으로 첫 등장). 마누는 '경찰 아닌 법정으로, 진압경찰 없이, 대화'. 훌리안이 시점을 칸델라에게 넘기며 '서류 태우지 말고 판사에게'를 이레네 통해 전함. 원안의 '엘레나 유해 발견·쿠에스타 증언'을 4부 안에서 모두 소화하고, 「솔리스 공항 체포」를 6화로 앞당김(원안 4부 6화 유지)
 · 인물 추가: 헤라르도 라스트라 경감(터미널 01, '다른 집'), 치노(기술반 동료), 에르메네힐도 바렐라(30년 녹음·3부 10화 전화의 목소리), 하비에르 메나 오르투뇨(J.M.), 콘셉시온 리바스 판사, 벨트란(재등장), 아빌리오 토레시야(재등장), 아나 로드리게스(보호증인 담당), 오비디오(라 나바 바 주인), 아나·시프리아노 페란(훌리안의 가족)
-· [5부 이후 연결 과제] 하수구 재판(이듬해, 훌리안 비공개 증언)·라스트라 '명령 수행' 변론 / 쿠에스타의 1984년 '거울'과 의회 증언 후속 / 메나·바렐라의 형사 절차 / 제9조의 실제 준수 여부 / 알타 마르카 주민투표(5부, 칸델라 시점)로의 이행 / 솔리스 재판(7부 9화)·보가라 도피와 인도(8부 10화)로의 복선</t>
+· [5부 이후 연결 과제] 하수구 재판(이듬해, 훌리안 비공개 증언)·라스트라 '명령 수행' 변론 / 쿠에스타의 1984년 '거울'과 의회 증언 후속 / 메나·바렐라의 형사 절차 / 제9조의 실제 준수 여부 / 알타 마르카 주민투표(5부, 칸델라 시점)로의 이행 / 솔리스 재판(7부 9화)·보가라 도피와 인도(8부 10화)로의 복선
+[5부 제작 후 변경·확정]
+· 시점: 알타 마르카 수반 다비드 오르타(55세)의 연설문 작성자 칸델라 몬토로 비달(1985년생, 35~36세)의 보이스오버(«Candela (V.O.):»). 장치: 화마다 «BORRADOR n»(연설문 초안의 한 줄이 화면에 나옴; 1화 7번~10화 사진전까지 이어짐). 가족: 동생 다니(24세, 사진가·시청각 전공), 다니의 연인 노아 페라스(23세, 통합론자 철물점 주인 마티아스 페라스의 딸), 부모 라몬(은퇴 조선소 목수, 독립 지지)·암파로(약사, 중립), 외삼촌 토마스 비달(통합론자, 재향군인회 간부, 은퇴 군인)
+· 가상 지명(실제 지역과 1:1 대응 없음): 자치공동체 알타 마르카, 수도 아르헨타, 의회 «Parlamento de la Marca», 자치경찰 «Guardia Marquesa», 정부 청사 «Palacio de la Marca», 지역어 «el marqués»(대본은 스페인어로 표기, 지문에 '(en marqués)'), 광장 «Plaza de las Salinas», 정당 «Marca Libre»(독립)·«Convivencia»(통합)·«Marca Común»(5부 말 메르세데스의 신당). 관련 인물: 부수반 메르세데스 알칸타라, 비서실장 페드로 알라미야, 야당 대표 루시아 베나벤트, 교장 마리솔
+· 연도: 2020년 9월 24일(헌재 정지)~2022년 2월 11일(협약 서명식). 모든 날짜는 요일 검증
+· 1화(2020-09-24~10-17): 헌재의 정지 결정 이후 오르타의 «Hay dos legalidades» 연설, 교장 마리솔의 «Mis llaves no son de nadie», 가족 저녁(외삼촌·노아 가족), 철물점 가게 낙서와 «esa gente también es la tierra» 한 줄, 해변에서 다니의 '집에 돌아온다' 약속 세 번
+· 2화(2020-10-18 일): 투표일 오전 7:30 줄 → 8:05 국가경찰의 법원 명령과 자치경찰의 15분 휴전 → 8:25 화면 밖 충돌(폭력은 직접 보이지 않음) → 다니의 왼쪽 눈 실명(고무탄, 비묘사). 마누의 '정부는 책임' 발표(칸델라는 맞는 말이라 불신), 오르타의 «con un ojo menos, mañana tenemos al mundo de nuestro lado»에 칸델라가 성명서 거부(«Mi hermano no es un argumento»), 다니의 «Que no me conviertan en un cartel»
+· 3화(2020-11): 메르세데스가 '3%' 장부를 칸델라에게 보여 주고(보관은 요구 안 함) 11-10 마드리드 검찰에 접수. 오르타는 '중앙의 조작이라 써라' → 칸델라가 '검찰이 때늦다는 말은 쓰되 장부가 가짜란 말은 못 쓴다'. 이레네를 통한 훌리안의 쪽지(«No queme los papeles. Llévelos a un juez. Aunque tarde.»)와 아버지 라몬의 조선소 이야기가 겹침
+· 4화(2020-12-15~18): 일방적 독립 선언문 낭독(2020-12-17). 오르타가 칸델라의 한 줄 «Los que piensan de otro modo también son la Marca»를 건너뜀. 야당 46명 퇴장, 마누의 TV 연설('mis conciudadanos', '단절이 아니라 공존을 위한 문'), 12-18 기업 본사 이전(트럭), 철물점 주인 마티아스 «Ha hecho lo que ha podido». 옥상의 오르타 «Si la leía, tenía que creérmela»
+· 5화(2021-01): 암파로 약국의 카드 오류·외상('Me están cobrando los dos'), 국채 금리 3→6.5%·등급 2단계 하락 예고, 메르세데스의 협상 제안, 유럽 위원의 '인정 불가이나 대화의 자리' 거절, 1-18 국방장관 레도 사임(군 개입 거부, 빈 의자). 칸델라는 '약속 대신 비용을 말하는' BORRADOR 14 작성
+· 6화(2021-02): 칸델라가 오르타의 비공개 특사로 몽클로아 방문. 마누가 먼저 커피(«Primero un café»), 아랑고 부총리의 '무기한 자치 정지·일괄 체포' 요구를 상원의장 소토와 내무장관 발디비아가 기한·상원 승인 조건으로 제동, 마누는 '전투에는 이기고 집을 잃는다' 논리로 6개월 기한·일부 권한·조기 선거·판사에 의한 개별 책임으로 결정(2-11 의회). 이레네가 전한 쪽지: «No hagas con esto lo que ellos hicieron»
+· 7화(2021-03-01~06): 퇴역 장성들의 '새벽 계획'(대본에는 세부·작전 없음, 명단 한 장뿐). 외삼촌 토마스가 만찬에서 서명·약속을 거부하고 일어남, 칸델라의 이름이 명단에 있음을 알려 줌, 벨몬테 대령이 몽클로아 새벽 5시 부엌에서 마누에게 '판사에게'로 인도되어 진술. 3-6 사법 영장으로 7명 구속. 오르타에게 칸델라: «Le digo que lo habría usado.»
+· 8화(2021-04-12~19): 오르타가 재판을 피해 망명(출석일 4-19), 칸델라가 4-15 새벽 4시 국경(산타 아우로라 고개)까지 운전하고 차를 돌림. 메르세데스는 4-19 법정에서 «Que conste en acta» 증언. 가상 지명: «Paso de Santa Aurelia»(국경은 북쪽, 상대 국가는 명시하지 않음)
+· 9화(2021-05-10~06-29): 마누 «Hoy no hablo. Mañana, tampoco.»(판결 전후 침묵), 6-9 판결(6명 자격정지 18개월~3년·벌금, 횡령 무죄, 오르타 궐석), 6-20 조기 선거(Marca Común 44, Marca Libre 38, Convivencia 32, 기타 21), 메르세데스의 요청으로 칸델라·마티아스·베나벤트가 언어 조항(«Nadie será obligado a elegir», «El español es de todos. El marqués es de todos los que lo quieran.») 작성. 12월에 지워진 문장을 서문으로
+· 10화(2022-01-17~02-11): 마누 지지율 45%(알타 마르카 31%), 다니의 사진전 «Una cola no tiene ideas»(마티아스가 사진 속 자기 뒷목을 알아봄, 병원 복도 사진은 «Autor desconocido»), 2-11 Pacto de Argenta 서명식 TV 중계(주민투표 2022-01-16 투표율 71%, 찬성 57%), 마누 «Esta noche no hay vencedores. Hay vecinos.», 방파제에서 칸델라의 마지막 V.O.(독립은 여전히 원하나 '빼앗지 않고 얻는 방법'을 찾으며, 마누는 그 길을 막지 않은 첫 총리)
+· 원안 대비 변경: 원안 5부 4화(선언)·6화(고립)·7화(음모)·10화(협약)·12화(재선) 등 12화 구성 계획을 10화로 압축하며 '법정과 협약'을 통합. 오르타의 이름과 일부 동선, 정당명은 모두 가상. 5부 7화에서 하수구 잔당 항목은 대본에 넣지 않음(대령의 제보와 외삼촌의 거부에 집중)
+· 인물 추가: 마리솔(교장), 마티아스 페라스(철물점), 노아 페라스, 토마스 비달, 루시아 베나벤트(Convivencia 대표), 필라 부인(약국 단골), 클레멘테 보라스(경제 고문), 로케 아랑고(부총리), 가브리엘라 소토(상원의장), 클라우디오 벨몬테(대령), 에밀리아노 사우라(퇴역 장성), 에밀리오 코스타 경감과 루이사 가르시아 경사(국가경찰 현장)
+· [5부 이후 연결 과제] 칸델라의 '쓰지 않은 글'과 새로 쓰는 글 / 마누의 재선 정국(6부 이레네 시점) / 오르타의 망명지 재판·사면 논쟁(7부 2화에서 사면법에 대한 대법원 판단) / 협약 언어 조항의 시행(교육·행정) / 다니의 시력과 사진 작업 / 메르세데스의 이후 정국</t>
         </is>
       </c>
     </row>
@@ -3514,284 +3531,324 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="4" t="inlineStr">
+      <c r="A107" s="5" t="inlineStr">
         <is>
           <t>5부 1화</t>
         </is>
       </c>
-      <c r="B107" s="4" t="inlineStr">
+      <c r="B107" s="5" t="inlineStr">
         <is>
           <t>두 개의 법</t>
         </is>
       </c>
-      <c r="C107" s="4" t="inlineStr">
+      <c r="C107" s="5" t="inlineStr">
         <is>
           <t>Dos Legalidades</t>
         </is>
       </c>
-      <c r="D107" s="4" t="inlineStr">
+      <c r="D107" s="5" t="inlineStr">
         <is>
           <t>5부 4화 확장</t>
         </is>
       </c>
-      <c r="E107" s="4" t="inlineStr">
-        <is>
-          <t>[칸델라] 헌재 정지 결정에도 칸델라가 쓴 연설과 함께 주민투표가 강행되고, 공무원·교사·지방 경찰이 어느 명령을 따를지 갈라진다.</t>
-        </is>
-      </c>
-      <c r="F107" s="4" t="inlineStr"/>
+      <c r="E107" s="5" t="inlineStr">
+        <is>
+          <t>[칸델라] 헌재 정지 결정에도 칸델라가 쓴 «두 개의 법» 연설과 함께 주민투표가 강행되고, 교장·공무원·자치경찰이 어느 명령을 따를지 갈라진다.</t>
+        </is>
+      </c>
+      <c r="F107" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="108">
-      <c r="A108" s="4" t="inlineStr">
+      <c r="A108" s="5" t="inlineStr">
         <is>
           <t>5부 2화</t>
         </is>
       </c>
-      <c r="B108" s="4" t="inlineStr">
+      <c r="B108" s="5" t="inlineStr">
         <is>
           <t>투표일의 곤봉</t>
         </is>
       </c>
-      <c r="C108" s="4" t="inlineStr">
+      <c r="C108" s="5" t="inlineStr">
         <is>
           <t>La Jornada de las Porras</t>
         </is>
       </c>
-      <c r="D108" s="4" t="inlineStr">
+      <c r="D108" s="5" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="E108" s="4" t="inlineStr">
-        <is>
-          <t>[칸델라] 진압대의 고무탄에 동생 다니가 한쪽 눈을 잃고, 병원 복도의 칸델라는 마누의 현장 지휘 중단 발표를 듣는다.</t>
-        </is>
-      </c>
-      <c r="F108" s="4" t="inlineStr"/>
+      <c r="E108" s="5" t="inlineStr">
+        <is>
+          <t>[칸델라] 투표일 아침 줄 선 사람들 곁에서 두 경찰이 15분 버티다 충돌하고, 동생 다니가 왼쪽 눈을 잃는다. 칸델라는 오르타의 «눈 하나 덕에» 성명서를 거부한다.</t>
+        </is>
+      </c>
+      <c r="F108" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="109">
-      <c r="A109" s="4" t="inlineStr">
+      <c r="A109" s="5" t="inlineStr">
         <is>
           <t>5부 3화</t>
         </is>
       </c>
-      <c r="B109" s="4" t="inlineStr">
+      <c r="B109" s="5" t="inlineStr">
         <is>
           <t>3%의 장부</t>
         </is>
       </c>
-      <c r="C109" s="4" t="inlineStr">
+      <c r="C109" s="5" t="inlineStr">
         <is>
           <t>El Libro del Tres por Ciento</t>
         </is>
       </c>
-      <c r="D109" s="4" t="inlineStr">
+      <c r="D109" s="5" t="inlineStr">
         <is>
           <t>5부 4화 확장</t>
         </is>
       </c>
-      <c r="E109" s="4" t="inlineStr">
-        <is>
-          <t>[칸델라] 부수반 메르세데스가 ‘3% 수수료’ 장부를 들고 마드리드로 가고, 수반은 칸델라에게 ‘중앙의 조작’이라 쓰라고 한다.</t>
-        </is>
-      </c>
-      <c r="F109" s="4" t="inlineStr"/>
+      <c r="E109" s="5" t="inlineStr">
+        <is>
+          <t>[칸델라] 부수반 메르세데스가 ‘3% 수수료’ 장부를 칸델라에게 보여 주고 마드리드 검찰에 접수하며, 칸델라는 장부가 가짜라는 문장을 쓰지 않는다.</t>
+        </is>
+      </c>
+      <c r="F109" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="110">
-      <c r="A110" s="4" t="inlineStr">
+      <c r="A110" s="5" t="inlineStr">
         <is>
           <t>5부 4화</t>
         </is>
       </c>
-      <c r="B110" s="4" t="inlineStr">
+      <c r="B110" s="5" t="inlineStr">
         <is>
           <t>일방적 선언</t>
         </is>
       </c>
-      <c r="C110" s="4" t="inlineStr">
+      <c r="C110" s="5" t="inlineStr">
         <is>
           <t>La Declaración Unilateral</t>
         </is>
       </c>
-      <c r="D110" s="4" t="inlineStr">
+      <c r="D110" s="5" t="inlineStr">
         <is>
           <t>5부 4화 확장</t>
         </is>
       </c>
-      <c r="E110" s="4" t="inlineStr">
-        <is>
-          <t>[칸델라] 칸델라가 쓴 독립 선언문이 의회에서 낭독되고, 다음 날부터 기업 본사 수백 곳이 지역을 떠난다.</t>
-        </is>
-      </c>
-      <c r="F110" s="4" t="inlineStr"/>
+      <c r="E110" s="5" t="inlineStr">
+        <is>
+          <t>[칸델라] 칸델라가 쓴 독립 선언문이 의회에서 낭독되지만 오르타가 그녀의 한 줄(“다르게 생각하는 이들도 마르카다”)만 건너뛰고, 다음 날부터 기업 본사가 떠난다.</t>
+        </is>
+      </c>
+      <c r="F110" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="111">
-      <c r="A111" s="4" t="inlineStr">
+      <c r="A111" s="5" t="inlineStr">
         <is>
           <t>5부 5화</t>
         </is>
       </c>
-      <c r="B111" s="4" t="inlineStr">
+      <c r="B111" s="5" t="inlineStr">
         <is>
           <t>고립과 압박</t>
         </is>
       </c>
-      <c r="C111" s="4" t="inlineStr">
+      <c r="C111" s="5" t="inlineStr">
         <is>
           <t>Aislamiento y Presión</t>
         </is>
       </c>
-      <c r="D111" s="4" t="inlineStr">
+      <c r="D111" s="5" t="inlineStr">
         <is>
           <t>5부 6화 변형</t>
         </is>
       </c>
-      <c r="E111" s="4" t="inlineStr">
-        <is>
-          <t>[칸델라] 국채 금리 급등과 신용등급 강등, 유럽의 압박이 양쪽을 조이고 국방장관이 사임한다.</t>
-        </is>
-      </c>
-      <c r="F111" s="4" t="inlineStr"/>
+      <c r="E111" s="5" t="inlineStr">
+        <is>
+          <t>[칸델라] 카드 오류와 외상으로 약국이 흔들리고, 국채 금리·신용등급·유럽의 거절이 이어지며 국방장관이 군 개입 거부로 사임한다.</t>
+        </is>
+      </c>
+      <c r="F111" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="112">
-      <c r="A112" s="4" t="inlineStr">
+      <c r="A112" s="5" t="inlineStr">
         <is>
           <t>5부 6화</t>
         </is>
       </c>
-      <c r="B112" s="4" t="inlineStr">
+      <c r="B112" s="5" t="inlineStr">
         <is>
           <t>직접 통치의 유혹</t>
         </is>
       </c>
-      <c r="C112" s="4" t="inlineStr">
+      <c r="C112" s="5" t="inlineStr">
         <is>
           <t>La Tentación del Mando Directo</t>
         </is>
       </c>
-      <c r="D112" s="4" t="inlineStr">
+      <c r="D112" s="5" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="E112" s="4" t="inlineStr">
-        <is>
-          <t>[칸델라] 비공개 협상으로 몽클로아에 간 칸델라에게 마누가 먼저 커피를 내고, 일괄 체포 대신 6개월 기한 개입을 택한다.</t>
-        </is>
-      </c>
-      <c r="F112" s="4" t="inlineStr"/>
+      <c r="E112" s="5" t="inlineStr">
+        <is>
+          <t>[칸델라] 비공개 특사로 몽클로아에 간 칸델라가 마누의 «먼저 커피»를 받고, 무기한 정지·일괄 체포 대신 6개월 기한·상원 승인·조기 선거를 택하는 과정을 지켜본다.</t>
+        </is>
+      </c>
+      <c r="F112" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="113">
-      <c r="A113" s="4" t="inlineStr">
+      <c r="A113" s="5" t="inlineStr">
         <is>
           <t>5부 7화</t>
         </is>
       </c>
-      <c r="B113" s="4" t="inlineStr">
+      <c r="B113" s="5" t="inlineStr">
         <is>
           <t>새벽의 음모</t>
         </is>
       </c>
-      <c r="C113" s="4" t="inlineStr">
+      <c r="C113" s="5" t="inlineStr">
         <is>
           <t>El Complot del Amanecer</t>
         </is>
       </c>
-      <c r="D113" s="4" t="inlineStr">
+      <c r="D113" s="5" t="inlineStr">
         <is>
           <t>5부 7화 변형</t>
         </is>
       </c>
-      <c r="E113" s="4" t="inlineStr">
-        <is>
-          <t>[칸델라] 퇴역 장성과 하수구 잔당의 새벽 음모 명단에 칸델라의 이름도 있지만, 한 대령의 제보로 무산된다.</t>
-        </is>
-      </c>
-      <c r="F113" s="4" t="inlineStr"/>
+      <c r="E113" s="5" t="inlineStr">
+        <is>
+          <t>[칸델라] 퇴역 장성의 새벽 음모 명단에 칸델라의 이름이 있다는 것을 외삼촌 토마스가 알리고, 벨몬테 대령이 마누에게 ‘판사에게’ 진술해 무산된다(작전 세부 없음).</t>
+        </is>
+      </c>
+      <c r="F113" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="114">
-      <c r="A114" s="4" t="inlineStr">
+      <c r="A114" s="5" t="inlineStr">
         <is>
           <t>5부 8화</t>
         </is>
       </c>
-      <c r="B114" s="4" t="inlineStr">
+      <c r="B114" s="5" t="inlineStr">
         <is>
           <t>국경 앞에서</t>
         </is>
       </c>
-      <c r="C114" s="4" t="inlineStr">
+      <c r="C114" s="5" t="inlineStr">
         <is>
           <t>Ante la Frontera</t>
         </is>
       </c>
-      <c r="D114" s="4" t="inlineStr">
+      <c r="D114" s="5" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="E114" s="4" t="inlineStr">
-        <is>
-          <t>[칸델라] 수반 오르타는 국경을 넘어 망명하고, 칸델라는 국경 앞에서 차를 돌려 메르세데스처럼 남기로 한다.</t>
-        </is>
-      </c>
-      <c r="F114" s="4" t="inlineStr"/>
+      <c r="E114" s="5" t="inlineStr">
+        <is>
+          <t>[칸델라] 오르타가 재판을 피해 국경을 넘고 칸델라는 국경 앞에서 차를 돌리며, 메르세데스는 남아 법정에서 «Que conste en acta»를 증언한다.</t>
+        </is>
+      </c>
+      <c r="F114" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="115">
-      <c r="A115" s="4" t="inlineStr">
+      <c r="A115" s="5" t="inlineStr">
         <is>
           <t>5부 9화</t>
         </is>
       </c>
-      <c r="B115" s="4" t="inlineStr">
+      <c r="B115" s="5" t="inlineStr">
         <is>
           <t>법정과 협약</t>
         </is>
       </c>
-      <c r="C115" s="4" t="inlineStr">
+      <c r="C115" s="5" t="inlineStr">
         <is>
           <t>El Tribunal y el Pacto</t>
         </is>
       </c>
-      <c r="D115" s="4" t="inlineStr">
+      <c r="D115" s="5" t="inlineStr">
         <is>
           <t>신규·5부 10화 변형 통합</t>
         </is>
       </c>
-      <c r="E115" s="4" t="inlineStr">
-        <is>
-          <t>[칸델라] 마누가 지도자 재판에 대한 발언을 거부하고, 조기 지방선거 뒤 칸델라가 새 자치 협약의 언어 조항을 쓴다.</t>
-        </is>
-      </c>
-      <c r="F115" s="4" t="inlineStr"/>
+      <c r="E115" s="5" t="inlineStr">
+        <is>
+          <t>[칸델라] 마누가 지도자 재판에 침묵하고 조기 선거로 메르세데스의 신당이 1당이 되며, 칸델라가 마티아스·베나벤트와 언어 조항을 쓴다.</t>
+        </is>
+      </c>
+      <c r="F115" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="116">
-      <c r="A116" s="4" t="inlineStr">
+      <c r="A116" s="5" t="inlineStr">
         <is>
           <t>5부 10화</t>
         </is>
       </c>
-      <c r="B116" s="4" t="inlineStr">
+      <c r="B116" s="5" t="inlineStr">
         <is>
           <t>재선의 기로</t>
         </is>
       </c>
-      <c r="C116" s="4" t="inlineStr">
+      <c r="C116" s="5" t="inlineStr">
         <is>
           <t>En la Encrucijada</t>
         </is>
       </c>
-      <c r="D116" s="4" t="inlineStr">
+      <c r="D116" s="5" t="inlineStr">
         <is>
           <t>5부 12화 변형</t>
         </is>
       </c>
-      <c r="E116" s="4" t="inlineStr">
-        <is>
-          <t>[칸델라] 양쪽 모두에게 배신자가 된 마누의 지지율이 45%로 떨어지고, 칸델라는 다니와 함께 협약 서명식을 본다.</t>
-        </is>
-      </c>
-      <c r="F116" s="4" t="inlineStr"/>
+      <c r="E116" s="5" t="inlineStr">
+        <is>
+          <t>[칸델라] 지지율 45%의 마누를 두고 다니의 사진전과 협약 서명식이 이어지고, 방파제에서 칸델라가 마지막 V.O.로 5부를 닫는다.</t>
+        </is>
+      </c>
+      <c r="F116" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="10" t="inlineStr">

--- a/기획안/혼합안_이탈리아_스페인_독일.xlsx
+++ b/기획안/혼합안_이탈리아_스페인_독일.xlsx
@@ -679,7 +679,7 @@
       </c>
       <c r="N5" s="5" t="inlineStr">
         <is>
-          <t>1~5부 50화(1~5부 전체) 대본·학습노트 완료 (2026-10)</t>
+          <t>1~6부 60화(1~6부 전체) 대본·학습노트 완료 (2026-10)</t>
         </is>
       </c>
       <c r="O5" s="6" t="inlineStr">
@@ -858,7 +858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F147"/>
+  <dimension ref="A1:G147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -879,7 +879,7 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>0. 제작 현황 (2026-10-04 최신화)</t>
+          <t>0. 제작 현황 (2026-10-05 최신화)</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>1~5부 50화(부당 10화 구성의 1~5부 전체) 대본·학습노트 완료 (2026-10)</t>
+          <t>1~6부 60화(부당 10화 구성의 1~6부 전체) 대본·학습노트 완료 (2026-10)</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>1부, 2부, 3부, 4부, 5부</t>
+          <t>1부, 2부, 3부, 4부, 5부, 6부</t>
         </is>
       </c>
     </row>
@@ -915,7 +915,7 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>학습 노트 50편(1~5부 각 1~10화, docx), 0_동사_시제_가이드(md·docx)</t>
+          <t>학습 노트 60편(1~6부 각 1~10화, docx), 0_동사_시제_가이드(md·docx)</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,23 @@
 · 10화(2022-01-17~02-11): 마누 지지율 45%(알타 마르카 31%), 다니의 사진전 «Una cola no tiene ideas»(마티아스가 사진 속 자기 뒷목을 알아봄, 병원 복도 사진은 «Autor desconocido»), 2-11 Pacto de Argenta 서명식 TV 중계(주민투표 2022-01-16 투표율 71%, 찬성 57%), 마누 «Esta noche no hay vencedores. Hay vecinos.», 방파제에서 칸델라의 마지막 V.O.(독립은 여전히 원하나 '빼앗지 않고 얻는 방법'을 찾으며, 마누는 그 길을 막지 않은 첫 총리)
 · 원안 대비 변경: 원안 5부 4화(선언)·6화(고립)·7화(음모)·10화(협약)·12화(재선) 등 12화 구성 계획을 10화로 압축하며 '법정과 협약'을 통합. 오르타의 이름과 일부 동선, 정당명은 모두 가상. 5부 7화에서 하수구 잔당 항목은 대본에 넣지 않음(대령의 제보와 외삼촌의 거부에 집중)
 · 인물 추가: 마리솔(교장), 마티아스 페라스(철물점), 노아 페라스, 토마스 비달, 루시아 베나벤트(Convivencia 대표), 필라 부인(약국 단골), 클레멘테 보라스(경제 고문), 로케 아랑고(부총리), 가브리엘라 소토(상원의장), 클라우디오 벨몬테(대령), 에밀리아노 사우라(퇴역 장성), 에밀리오 코스타 경감과 루이사 가르시아 경사(국가경찰 현장)
-· [5부 이후 연결 과제] 칸델라의 '쓰지 않은 글'과 새로 쓰는 글 / 마누의 재선 정국(6부 이레네 시점) / 오르타의 망명지 재판·사면 논쟁(7부 2화에서 사면법에 대한 대법원 판단) / 협약 언어 조항의 시행(교육·행정) / 다니의 시력과 사진 작업 / 메르세데스의 이후 정국</t>
+· [5부 이후 연결 과제] 칸델라의 '쓰지 않은 글'과 새로 쓰는 글 / 마누의 재선 정국(6부 이레네 시점) / 오르타의 망명지 재판·사면 논쟁(7부 2화에서 사면법에 대한 대법원 판단) / 협약 언어 조항의 시행(교육·행정) / 다니의 시력과 사진 작업 / 메르세데스의 이후 정국
+[6부 제작 후 변경·확정]
+· 시점: 후계자 이레네 마르토스(1995년생, 28세; 쿠엥카 출신, 할머니 아우렐리아가 키움)의 보이스오버(«Irene (V.O.):»). 장치: 화마다 끝에 «LECCIÓN n»(마누·주변 인물에게 배운 것; 1~10화에서 LECCIÓN 1~17). 지명·기구(가상): 푸에르토 알레그레(해안 도시 유세 장소), 라 레스팅가(엘 이에로 부두), 발데로보스(1부 광산 마을; 불길이 닥침), 감사원 «브루훌라(Brújula)», 위기결정위원회(Comisión de Decisión de Crisis). 야당 «보스 이 보토(Voz y Voto)»(코바루비아스), 강경 분파 «프렌테 델 알바(Frente del Alba)»(소규모, 모든 정당이 부인)
+· 연도: 2023-04-24(딥페이크)~2024-06-27(위기결정위원회법 통과). 총선 2023-05-14(일): 오리손테 코문 131, 보스 이 보토 118, 콘코르디아 63, 마르카 코문·지역정당 24, 기타 14(과반 176 미달). 모든 날짜 요일 검증
+· 1화(2023-04-24~05-02): 마누의 목소리를 흉내 낸 가짜 영상(임대료 20% 인상)과 가짜 증인(쿠엥카 수예점 페피). 이레네의 '반박 대신 대체' 전략(작은 진실: 이름·거리·액수), 4-29 쿠엥카 마요르 광장 단독 유세(47개 임차 사례의 주소를 읽고 '나를 믿지 말고 확인하라'), 청년 가브리. 이솔리나는 «Primero un café»·«El miedo es información»
+· 2화(2023-05-07 일): 푸에르토 알레그레 마지막 주말 유세. 폭발은 소리·정적·사물로만 연출(사망 3·부상 17). 이솔리나(64) 사망, 이레네 오른팔 골절(두 곳), 시로 이마 부상. 마누는 '이름과 판사가 있을 때까지' 아무도 지목하지 않기로 하고, 라디갈레스의 '아무것도 배제하지 않는다'에 필리가 불안해함. 메르세데스는 가장 먼저 '우리 쪽이 아니다'라고 전화
+· 3화(2023-05-11~15): 이솔리나 장례(사라고사; 시로의 추도사·«Irene: bien» 마지막 메모), 5-13 성찰의 날 마누가 라디갈레스의 성명 제안을 거절, 5-14 투표소에서 가브리의 '확인했다', 선거 밤 마누의 4항 연설과 빈 의자·커피, 새벽 시로가 공책을 이레네에게 넘김(«Lunes 8: llamar a Irene para…»)
+· 4화(2023-08-07~13): 복합위기 — 변전소 공격(인명 피해 없음, 기술 세부 없음, «Frente del Alba» 성명), 엘 이에로 이주민 1,800명(아미나타 남매), 시에라 델 로보 산불 → 발데로보스. 마누는 예외 상태·알타 마르카 '위험 지역' 지정을 거절하고 ALBA·MAR·FUEGO 세 열로 대응
+· 5화(2023-09): 시로가 «Centinela» 계약(4,100만 유로 수의 계약, 기밀비)을 이레네에게 알림 — 이솔리나의 미완 메모의 뜻. 라디갈레스의 5개 조치(사전 영장 없는 72시간 감청, 선거 연기, 플랫폼 삭제, 불투명 재정 등록, 10일 구금)를 마누가 대부분 거절하고 24시간 당직 판사 대안 제시
+· 6화(2023-11): 마누가 시로에게 12월 6일 이후로 보고서를 미뤄 달라고 부탁했다가 거절당하고 사과(«Que conste… Perdóname por haber llamado»). 라디갈레스의 '안부 인사'가 위협으로 읽힘
+· 7화(2023-12-05~2024-01-29): 마누의 구두 허락 1건(가브리엘 메나 루한, 오인으로 판명)을 이레네가 기록(«Que conste que me equivoco»), 12-06 판사 이바녜스에게 자진 출두, 2024-01-15 검찰총장 나바레테의 유출, 마누의 회견과 개인 자격 고소, 01-29 대법원이 검찰총장에게 비밀 누설죄(자격 정지 2년·벌금) 선고하며 12-05의 감청도 위법이라고 명시
+· 8화(2024-02-19~03-02): 라디갈레스의 '상설 감시법', 필리와 이레네의 오리손테 코문 정치위원회 공개 반대(«No hay nada más permanente que lo temporal»), 마누가 철회하고 24시간 당직 판사 법안으로 대체
+· 9화(2024-04-15~05-12): 소피아가 에바리스토의 공책 6권(203명, 1974~1992)을 마누와 이레네에게 인계하는 조건(마누의 공개적 실수와 판사 출두), 증언자 동의 원칙, 기억 검찰에 '동의된 것만 인계', 가족 만남에서 이레네가 이름을 읽음
+· 10화(2024-06-07~27): 알타 마르카 자치경찰 순경 이반 칼레로 페레르(29) 순직, 정보국장의 '추적 불가' 작전 제안을 마누가 거절(«Es la misma frase, con otra fecha»), 위기결정위원회법 구상, 아르헨타 장례식(메르세데스 추도사, 칸델라·다니 등장, 카르멘 페레르 «Lo haré»), 6-27 하원 표결 297 찬성
+· 원안 대비 변경: 원안 6부 12화 구성(재신임·테러·산불·유혹·검찰총장 재판 등)을 10화로 압축. 원안의 7부 일부(스파이웨어 감사, 구두 허락, 정면 대결, 에바리스토의 기록, 위기결정위원회)를 6부로 앞당겨 통합. 카나리아·산불·다나·검찰총장 사건은 실제 사건의 뼈대만 취하고 지명·인명·날짜는 가상화(푸에르토 알레그레, 라 레스팅가, 시에라 델 로보 등)
+· 인물 추가: 이솔리나 테하다·시로 안드라데(브루훌라 감사원), 클라라 테하다(이솔리나의 동생), 아미나타 디알로·이브라, 마르타(구조대장·자치경찰 동료), 콘수엘로(발데로보스 촌장), 가브리·페피·아우렐리아, 알폰소 코르테스(정보국장), 마르셀라 이바녜스 판사, 이폴리토 나바레테(검찰총장), 클라우디아 로메로(기억 검찰), 파스쿠알라 오르투뇨, 카르멘 페레르·이반 칼레로 페레르
+· [6부 이후 연결 과제] 7부 「권력의 한계」(연임 두 번 제한법과 마누의 자기 적용), 이솔리나의 카드 «커피를 잊지 말 것» 발견, 쿠엥카 사건 후속, 라디갈레스의 후속 행적, 센티넬 계약의 법적 정리, 기억 검찰 인계의 후속, 칸델라와 이레네의 재회</t>
         </is>
       </c>
     </row>
@@ -3851,284 +3867,324 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="10" t="inlineStr">
+      <c r="A117" s="5" t="inlineStr">
         <is>
           <t>6부 1화</t>
         </is>
       </c>
-      <c r="B117" s="10" t="inlineStr">
+      <c r="B117" s="5" t="inlineStr">
         <is>
           <t>거짓의 공장</t>
         </is>
       </c>
-      <c r="C117" s="10" t="inlineStr">
+      <c r="C117" s="5" t="inlineStr">
         <is>
           <t>La Fábrica de Bulos</t>
         </is>
       </c>
-      <c r="D117" s="10" t="inlineStr">
+      <c r="D117" s="5" t="inlineStr">
         <is>
           <t>6부 3화 변형</t>
         </is>
       </c>
-      <c r="E117" s="10" t="inlineStr">
-        <is>
-          <t>[이레네] 집세와 이민 공포를 앞세운 코바루비아스의 딥페이크와 가짜 증인 속에, 이레네가 처음 단독 유세에 나선다.</t>
-        </is>
-      </c>
-      <c r="F117" s="10" t="inlineStr"/>
+      <c r="E117" s="5" t="inlineStr">
+        <is>
+          <t>[이레네] 마누의 목소리를 흉내 낸 딥페이크와 가짜 증인이 퍼지는 가운데, 이레네가 ‘반박 대신 대체’ 전략으로 쿠엥카 광장에서 처음 단독 유세에 나선다.</t>
+        </is>
+      </c>
+      <c r="F117" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="118">
-      <c r="A118" s="10" t="inlineStr">
+      <c r="A118" s="5" t="inlineStr">
         <is>
           <t>6부 2화</t>
         </is>
       </c>
-      <c r="B118" s="10" t="inlineStr">
+      <c r="B118" s="5" t="inlineStr">
         <is>
           <t>유세장 테러</t>
         </is>
       </c>
-      <c r="C118" s="10" t="inlineStr">
+      <c r="C118" s="5" t="inlineStr">
         <is>
           <t>El Atentado del Mitin</t>
         </is>
       </c>
-      <c r="D118" s="10" t="inlineStr">
+      <c r="D118" s="5" t="inlineStr">
         <is>
           <t>6부 6화</t>
         </is>
       </c>
-      <c r="E118" s="10" t="inlineStr">
-        <is>
-          <t>[이레네] 발렌시아 유세장 폭탄에 바로 곁의 이솔리나가 숨지고, 이레네는 오른팔을 크게 다친다.</t>
-        </is>
-      </c>
-      <c r="F118" s="10" t="inlineStr"/>
+      <c r="E118" s="5" t="inlineStr">
+        <is>
+          <t>[이레네] 항구 도시 유세장 폭발로 바로 곁의 이솔리나가 숨지고, 이레네는 오른팔을 다친다. 마누는 이름과 판사가 있을 때까지 아무도 지목하지 않는다.</t>
+        </is>
+      </c>
+      <c r="F118" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="119">
-      <c r="A119" s="10" t="inlineStr">
+      <c r="A119" s="5" t="inlineStr">
         <is>
           <t>6부 3화</t>
         </is>
       </c>
-      <c r="B119" s="10" t="inlineStr">
+      <c r="B119" s="5" t="inlineStr">
         <is>
           <t>재선의 밤</t>
         </is>
       </c>
-      <c r="C119" s="10" t="inlineStr">
+      <c r="C119" s="5" t="inlineStr">
         <is>
           <t>La Noche de la Reelección</t>
         </is>
       </c>
-      <c r="D119" s="10" t="inlineStr">
+      <c r="D119" s="5" t="inlineStr">
         <is>
           <t>6부 9화 변형·12화 변형 통합</t>
         </is>
       </c>
-      <c r="E119" s="10" t="inlineStr">
-        <is>
-          <t>[이레네] 마누는 테러를 표로 바꾸지 않은 채 다시 제1당이 되고, 붕대를 감은 이레네가 이솔리나의 빈 의자를 본다.</t>
-        </is>
-      </c>
-      <c r="F119" s="10" t="inlineStr"/>
+      <c r="E119" s="5" t="inlineStr">
+        <is>
+          <t>[이레네] 이솔리나의 장례 뒤 선거에서 마누는 테러를 표로 바꾸지 않은 채 제1당이 되고, 이레네는 빈 의자와 이솔리나의 미완의 메모를 마주한다.</t>
+        </is>
+      </c>
+      <c r="F119" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="120">
-      <c r="A120" s="10" t="inlineStr">
+      <c r="A120" s="5" t="inlineStr">
         <is>
           <t>6부 4화</t>
         </is>
       </c>
-      <c r="B120" s="10" t="inlineStr">
+      <c r="B120" s="5" t="inlineStr">
         <is>
           <t>복합위기</t>
         </is>
       </c>
-      <c r="C120" s="10" t="inlineStr">
+      <c r="C120" s="5" t="inlineStr">
         <is>
           <t>La Crisis Múltiple</t>
         </is>
       </c>
-      <c r="D120" s="10" t="inlineStr">
+      <c r="D120" s="5" t="inlineStr">
         <is>
           <t>7부 2화 변형</t>
         </is>
       </c>
-      <c r="E120" s="10" t="inlineStr">
-        <is>
-          <t>[이레네] 강경 분파의 기반시설 폭탄, 카나리아 이주민 급증과 일괄 합법화 논쟁, 최악의 산불이 한꺼번에 터진다.</t>
-        </is>
-      </c>
-      <c r="F120" s="10" t="inlineStr"/>
+      <c r="E120" s="5" t="inlineStr">
+        <is>
+          <t>[이레네] 변전소 공격, 카나리아 이주민 급증, 산불이 한꺼번에 터지는 가운데 마누가 예외 상태를 거절하고 대피·인도적 대응·사법 절차의 세 줄로 대응한다.</t>
+        </is>
+      </c>
+      <c r="F120" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="121">
-      <c r="A121" s="10" t="inlineStr">
+      <c r="A121" s="5" t="inlineStr">
         <is>
           <t>6부 5화</t>
         </is>
       </c>
-      <c r="B121" s="10" t="inlineStr">
+      <c r="B121" s="5" t="inlineStr">
         <is>
           <t>하수구의 유혹</t>
         </is>
       </c>
-      <c r="C121" s="10" t="inlineStr">
+      <c r="C121" s="5" t="inlineStr">
         <is>
           <t>La Tentación de las Cloacas</t>
         </is>
       </c>
-      <c r="D121" s="10" t="inlineStr">
+      <c r="D121" s="5" t="inlineStr">
         <is>
           <t>7부 3화·4화 통합 변형</t>
         </is>
       </c>
-      <c r="E121" s="10" t="inlineStr">
-        <is>
-          <t>[이레네] 라디갈레스 내무장관이 감청 권한과 선거 연기, 언론·플랫폼 통제안을 한꺼번에 총리 책상에 올린다.</t>
-        </is>
-      </c>
-      <c r="F121" s="10" t="inlineStr"/>
+      <c r="E121" s="5" t="inlineStr">
+        <is>
+          <t>[이레네] 시로가 ‘센티넬’ 수의 계약을 알리고, 라디갈레스가 사전 영장 없는 감청·선거 연기·플랫폼 통제를 올리자 이레네가 사례를 요구해 마누의 방향을 바꾼다.</t>
+        </is>
+      </c>
+      <c r="F121" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="122">
-      <c r="A122" s="10" t="inlineStr">
+      <c r="A122" s="5" t="inlineStr">
         <is>
           <t>6부 6화</t>
         </is>
       </c>
-      <c r="B122" s="10" t="inlineStr">
+      <c r="B122" s="5" t="inlineStr">
         <is>
           <t>브루훌라에 부탁</t>
         </is>
       </c>
-      <c r="C122" s="10" t="inlineStr">
+      <c r="C122" s="5" t="inlineStr">
         <is>
           <t>Un Favor a Brújula</t>
         </is>
       </c>
-      <c r="D122" s="10" t="inlineStr">
+      <c r="D122" s="5" t="inlineStr">
         <is>
           <t>7부 6화</t>
         </is>
       </c>
-      <c r="E122" s="10" t="inlineStr">
-        <is>
-          <t>[이레네] 스파이웨어 계약 감사를 미뤄 달라는 마누의 전화를 시로가 거절하는 것을 이레네가 옆에서 듣는다.</t>
-        </is>
-      </c>
-      <c r="F122" s="10" t="inlineStr"/>
+      <c r="E122" s="5" t="inlineStr">
+        <is>
+          <t>[이레네] 마누가 감사 보고서를 미뤄 달라고 직접 전화하자 시로가 거절하고, 이레네가 옆에서 그 전화를 듣는다.</t>
+        </is>
+      </c>
+      <c r="F122" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="123">
-      <c r="A123" s="10" t="inlineStr">
+      <c r="A123" s="5" t="inlineStr">
         <is>
           <t>6부 7화</t>
         </is>
       </c>
-      <c r="B123" s="10" t="inlineStr">
+      <c r="B123" s="5" t="inlineStr">
         <is>
           <t>작은 월권</t>
         </is>
       </c>
-      <c r="C123" s="10" t="inlineStr">
+      <c r="C123" s="5" t="inlineStr">
         <is>
           <t>Un Pequeño Exceso</t>
         </is>
       </c>
-      <c r="D123" s="10" t="inlineStr">
+      <c r="D123" s="5" t="inlineStr">
         <is>
           <t>7부 7화</t>
         </is>
       </c>
-      <c r="E123" s="10" t="inlineStr">
-        <is>
-          <t>[이레네] 판사 승인 없는 감청 한 건의 구두 허락을 이레네가 목격하고, 그 기록을 흘린 검찰총장이 대법원에서 유죄를 받는다.</t>
-        </is>
-      </c>
-      <c r="F123" s="10" t="inlineStr"/>
+      <c r="E123" s="5" t="inlineStr">
+        <is>
+          <t>[이레네] 이레네가 마누의 판사 승인 없는 감청 구두 허락 1건을 기록하고 마누는 판사에게 자진 출두하며, 그 기록을 흘린 검찰총장이 대법원에서 유죄를 받는다.</t>
+        </is>
+      </c>
+      <c r="F123" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="124">
-      <c r="A124" s="10" t="inlineStr">
+      <c r="A124" s="5" t="inlineStr">
         <is>
           <t>6부 8화</t>
         </is>
       </c>
-      <c r="B124" s="10" t="inlineStr">
+      <c r="B124" s="5" t="inlineStr">
         <is>
           <t>이레네의 정면 대결</t>
         </is>
       </c>
-      <c r="C124" s="10" t="inlineStr">
+      <c r="C124" s="5" t="inlineStr">
         <is>
           <t>El Enfrentamiento de Irene</t>
         </is>
       </c>
-      <c r="D124" s="10" t="inlineStr">
+      <c r="D124" s="5" t="inlineStr">
         <is>
           <t>7부 8화</t>
         </is>
       </c>
-      <c r="E124" s="10" t="inlineStr">
-        <is>
-          <t>[이레네] 비상 감시 체계 상설화에 맞서 이레네와 필리가 처음으로 총리에게 공개적으로 반대한다.</t>
-        </is>
-      </c>
-      <c r="F124" s="10" t="inlineStr"/>
+      <c r="E124" s="5" t="inlineStr">
+        <is>
+          <t>[이레네] 라디갈레스의 상설 감시법에 맞서 이레네와 필리가 정당 공개 회의에서 처음으로 총리에게 반대하고 마누가 법안을 철회한다.</t>
+        </is>
+      </c>
+      <c r="F124" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="125">
-      <c r="A125" s="10" t="inlineStr">
+      <c r="A125" s="5" t="inlineStr">
         <is>
           <t>6부 9화</t>
         </is>
       </c>
-      <c r="B125" s="10" t="inlineStr">
+      <c r="B125" s="5" t="inlineStr">
         <is>
           <t>에바리스토의 기록</t>
         </is>
       </c>
-      <c r="C125" s="10" t="inlineStr">
+      <c r="C125" s="5" t="inlineStr">
         <is>
           <t>Los Cuadernos de Evaristo</t>
         </is>
       </c>
-      <c r="D125" s="10" t="inlineStr">
+      <c r="D125" s="5" t="inlineStr">
         <is>
           <t>7부 9화</t>
         </is>
       </c>
-      <c r="E125" s="10" t="inlineStr">
-        <is>
-          <t>[이레네] 이레네는 마누와 함께 소피아를 찾아가 에바리스토가 기록한 더러운 전쟁 피해자들의 증언을 읽는다.</t>
-        </is>
-      </c>
-      <c r="F125" s="10" t="inlineStr"/>
+      <c r="E125" s="5" t="inlineStr">
+        <is>
+          <t>[이레네] 마누와 이레네가 소피아를 찾아가 에바리스토의 증언 공책을 받고, 증언자 가족의 동의를 먼저 구해 기억 검찰에 인계한다.</t>
+        </is>
+      </c>
+      <c r="F125" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="126">
-      <c r="A126" s="10" t="inlineStr">
+      <c r="A126" s="5" t="inlineStr">
         <is>
           <t>6부 10화</t>
         </is>
       </c>
-      <c r="B126" s="10" t="inlineStr">
+      <c r="B126" s="5" t="inlineStr">
         <is>
           <t>벼랑 끝의 포기</t>
         </is>
       </c>
-      <c r="C126" s="10" t="inlineStr">
+      <c r="C126" s="5" t="inlineStr">
         <is>
           <t>La Renuncia al Borde del Abismo</t>
         </is>
       </c>
-      <c r="D126" s="10" t="inlineStr">
+      <c r="D126" s="5" t="inlineStr">
         <is>
           <t>7부 10화 변형</t>
         </is>
       </c>
-      <c r="E126" s="10" t="inlineStr">
-        <is>
-          <t>[이레네] 지방 경찰관이 순직해도 마누는 비밀작전을 거부하고, 위기결정위원회 법으로 비상권한을 묶는다.</t>
-        </is>
-      </c>
-      <c r="F126" s="10" t="inlineStr"/>
+      <c r="E126" s="5" t="inlineStr">
+        <is>
+          <t>[이레네] 자치경찰 순경이 순직한 밤 마누는 추적 불가 비밀작전을 거부하고, 위기결정위원회법으로 비상권한을 묶는다.</t>
+        </is>
+      </c>
+      <c r="F126" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="4" t="inlineStr">

--- a/기획안/혼합안_이탈리아_스페인_독일.xlsx
+++ b/기획안/혼합안_이탈리아_스페인_독일.xlsx
@@ -679,7 +679,7 @@
       </c>
       <c r="N5" s="5" t="inlineStr">
         <is>
-          <t>1~6부 60화(1~6부 전체) 대본·학습노트 완료 (2026-10)</t>
+          <t>1~7부 70화(1~7부 전체) 대본·학습노트 완료 (2026-10)</t>
         </is>
       </c>
       <c r="O5" s="6" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>1~6부 60화(부당 10화 구성의 1~6부 전체) 대본·학습노트 완료 (2026-10)</t>
+          <t>1~7부 70화(부당 10화 구성의 1~7부 전체) 대본·학습노트 완료 (2026-10)</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>1부, 2부, 3부, 4부, 5부, 6부</t>
+          <t>1부, 2부, 3부, 4부, 5부, 6부, 7부</t>
         </is>
       </c>
     </row>
@@ -915,7 +915,7 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>학습 노트 60편(1~6부 각 1~10화, docx), 0_동사_시제_가이드(md·docx)</t>
+          <t>학습 노트 70편(1~7부 각 1~10화, docx), 0_동사_시제_가이드(md·docx)</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,22 @@
 · 10화(2024-06-07~27): 알타 마르카 자치경찰 순경 이반 칼레로 페레르(29) 순직, 정보국장의 '추적 불가' 작전 제안을 마누가 거절(«Es la misma frase, con otra fecha»), 위기결정위원회법 구상, 아르헨타 장례식(메르세데스 추도사, 칸델라·다니 등장, 카르멘 페레르 «Lo haré»), 6-27 하원 표결 297 찬성
 · 원안 대비 변경: 원안 6부 12화 구성(재신임·테러·산불·유혹·검찰총장 재판 등)을 10화로 압축. 원안의 7부 일부(스파이웨어 감사, 구두 허락, 정면 대결, 에바리스토의 기록, 위기결정위원회)를 6부로 앞당겨 통합. 카나리아·산불·다나·검찰총장 사건은 실제 사건의 뼈대만 취하고 지명·인명·날짜는 가상화(푸에르토 알레그레, 라 레스팅가, 시에라 델 로보 등)
 · 인물 추가: 이솔리나 테하다·시로 안드라데(브루훌라 감사원), 클라라 테하다(이솔리나의 동생), 아미나타 디알로·이브라, 마르타(구조대장·자치경찰 동료), 콘수엘로(발데로보스 촌장), 가브리·페피·아우렐리아, 알폰소 코르테스(정보국장), 마르셀라 이바녜스 판사, 이폴리토 나바레테(검찰총장), 클라우디아 로메로(기억 검찰), 파스쿠알라 오르투뇨, 카르멘 페레르·이반 칼레로 페레르
-· [6부 이후 연결 과제] 7부 「권력의 한계」(연임 두 번 제한법과 마누의 자기 적용), 이솔리나의 카드 «커피를 잊지 말 것» 발견, 쿠엥카 사건 후속, 라디갈레스의 후속 행적, 센티넬 계약의 법적 정리, 기억 검찰 인계의 후속, 칸델라와 이레네의 재회</t>
+· [6부 이후 연결 과제] 7부 「권력의 한계」(연임 두 번 제한법과 마누의 자기 적용), 이솔리나의 카드 «커피를 잊지 말 것» 발견, 쿠엥카 사건 후속, 라디갈레스의 후속 행적, 센티넬 계약의 법적 정리, 기억 검찰 인계의 후속, 칸델라와 이레네의 재회
+[7부 제작 후 변경·확정]
+· 시점: 이레네 마르토스(29~30세)의 보이스오버(«Irene (V.O.):»), 화 끝 «LECCIÓN 18~27»(6부 1~17에서 이어짐). 연도: 2024-09-16~2026-02-03. 가상 기구: 투명성청(Agencia de Transparencia), 이솔리나 테하다 홀(브루훌라 신관). 모든 날짜 요일 검증
+· 1화(2024-09-16·10-03): 마누가 「권력의 한계」 3개 조항(총리 두 입법기 제한, 예외 조치 서면·기한, 투명성청의 10년 후 공개)을 발표하며 '소급 불가로 내게는 해당 안 된다'고 먼저 말함. 이레네가 투명성청 설립을 맡고, 시로가 이솔리나의 옛 서랍에서 카드 «No olvidar el café»(뒷면 «13-IV-2019 Para Manu»)를 건넴
+· 2화(2024-11-14·15·21): 헌재가 사면법 합헌(13:2), 대법원은 오르타의 공금·정당자금 혐의 제외. 11-15 아르헨타 항구의 귀환(칸델라·다니와 이레네 재회), 11-21 오르타가 산타 아우로라 고개에서 걸어 귀국·자진 구속(«Que conste que he venido yo»)
+· 3화(2025-01-22): 교도소 병원의 쿠에스타 마지막 대화 — '하수구는 장소가 아니라 습관', 엘레나는 명령하지 않았지만 알고도 침묵한 자기 몫, «No fue razón de Estado. Fue miedo.», 이레네에게 '선한 사람은 멈출 때를 모른다. 너는 안다'
+· 4화(2025-05-12): 반도 전역 대정전(가상, 원인 단정 없음). 마누가 위성 전화로 이레네를 현장 대리인으로 지명(아무도 탓하지 않기·환자 먼저·기록), 이레네가 사이버 공격 성명 거절, 복구 순서 결정(몽클로아는 마지막), 라디오 메시지
+· 5화(2025-06): 메르세데스가 오르타 시절의 숨은 부채 21억 유로 공개, 이레네·칸델라의 재정 협상(후견 대신 합동 감사·전면 공개, «No hay tutela. Hay ventanas.» — 다니의 아이디어), 오르타 시절 3% 구조의 공사 초과비용 일부가 정당 자금이었음을 명시
+· 6화(2025-10-06~10): 구세력의 4개 전선(헌재·의회·방송·검찰) 총공세, 시로의 2014년 보고서 40쪽→10쪽 서명(이솔리나 전근 협박)을 방송이 폭로하기 전에 청문회에서 스스로 고백한 뒤 심정지 4분(소생), 클라라의 보온병 커피
+· 7화(2025-11-14): 「권력의 한계」 법 서명·국왕 재가(제도로만 언급), 코바루비아스의 인간적 고백('스스로를 제한하는 적과 싸우기 어렵다'), 테라스에서 마누가 '두 번이면 충분하다'를 설명하고 결정 전날 이레네에게 먼저 말하겠다고 약속, 쿠에스타의 경고 전달
+· 8화(2025-12-04): 이솔리나 테하다 홀 개관(«Aquí se firma lo que se ha leído»), 소피아가 에바리스토의 1986년 마지막 수업 카드(«No olvidar el café», 6명에게만)를 공개 — 에바리스토→이솔리나→마누의 계보, '커피는 시간이 있다고 알리는 가장 값싼 방법'
+· 9화(2026-01-21): 솔리스 징역 16년·벌금 4천만 유로, 파나마·키프로스·지브롤터를 거친 자금이 알카라 데 에나레스 창고(프렌테 델 알바)로 흐르고 최종 수익자로 추정된 보가라가 전날 밤 전용기로 출국. 정부는 수사를 지휘하지 않고 협력만 하기로 함, «Que no se note la rabia. Que se note la paciencia.»
+· 10화(2026-02-02·03): 전날 밤 부엌에서 이레네에게 먼저 말한 뒤, 2-3 하원에서 의회 해산(조기 총선 3-29), 출마 거부, 후계 지명 없음. 메르세데스·필리·아우렐리아의 반응
+· 원안 대비 변경: 원안 7부(권력의 한계 구체화·사면·쿠에스타·정전·부채·결전·서명·추모·판결·해산)를 10화로 유지하되 6부에서 앞당긴 일부 사건(스파이웨어 감사·위기결정위원회)은 6부에서 완결. 소급 불가·해산 시점은 실제 정국의 시간표를 따르지 않고 가상 일정으로 처리. 정전·사면 판결·검찰총장·주거·산불 등은 실제 사건의 뼈대만 취함
+· 인물 추가: 베아트리스 올모(송전망 사장), 마르가리타 오소리오(재판장), 베아트리스 라사(반부패 검사), 알폰소 코르테스(정보국장, 6부 10화), 가브리(감사원 수습, 6부 1화 인물의 성장), 클라라 테하다·시로의 회복
+· [7부 이후 연결 과제] 8부 「내려오는 길」(해산 이후: 당의 충격과 코바루비아스의 '속임수' 공세, 다나 폭우, 배관공 사건, 다니의 눈을 멀게 한 경찰관 재판, 공개 예비경선, 쿠에스타의 죽음과 봉투, 카르멘, 총선의 밤, 인수인계, 보가라 재판의 증인)과 에필로그(마누)</t>
         </is>
       </c>
     </row>
@@ -4187,284 +4202,324 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="4" t="inlineStr">
+      <c r="A127" s="5" t="inlineStr">
         <is>
           <t>7부 1화</t>
         </is>
       </c>
-      <c r="B127" s="4" t="inlineStr">
+      <c r="B127" s="5" t="inlineStr">
         <is>
           <t>권력의 한계</t>
         </is>
       </c>
-      <c r="C127" s="4" t="inlineStr">
+      <c r="C127" s="5" t="inlineStr">
         <is>
           <t>Los Límites del Poder</t>
         </is>
       </c>
-      <c r="D127" s="4" t="inlineStr">
+      <c r="D127" s="5" t="inlineStr">
         <is>
           <t>8부 1화·2화 통합</t>
         </is>
       </c>
-      <c r="E127" s="4" t="inlineStr">
-        <is>
-          <t>[이레네] 마누가 「권력의 한계」 법안을 발표하고, 투명성청을 재편하던 이레네가 이솔리나의 카드 ‘커피를 잊지 말 것’을 발견한다.</t>
-        </is>
-      </c>
-      <c r="F127" s="4" t="inlineStr"/>
+      <c r="E127" s="5" t="inlineStr">
+        <is>
+          <t>[이레네] 마누가 「권력의 한계」 법안을 발표하고, 투명성청을 짜던 이레네가 이솔리나의 옛 서랍에서 카드 «커피를 잊지 말 것»을 발견한다.</t>
+        </is>
+      </c>
+      <c r="F127" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="128">
-      <c r="A128" s="4" t="inlineStr">
+      <c r="A128" s="5" t="inlineStr">
         <is>
           <t>7부 2화</t>
         </is>
       </c>
-      <c r="B128" s="4" t="inlineStr">
+      <c r="B128" s="5" t="inlineStr">
         <is>
           <t>돌아온 사람들</t>
         </is>
       </c>
-      <c r="C128" s="4" t="inlineStr">
+      <c r="C128" s="5" t="inlineStr">
         <is>
           <t>Los Que Vuelven</t>
         </is>
       </c>
-      <c r="D128" s="4" t="inlineStr">
+      <c r="D128" s="5" t="inlineStr">
         <is>
           <t>8부 3화 변형</t>
         </is>
       </c>
-      <c r="E128" s="4" t="inlineStr">
-        <is>
-          <t>[이레네] 헌법재판소는 사면법을 합헌으로 보지만, 대법원은 공금 유용 혐의의 망명 수반 오르타에게는 적용을 거부한다.</t>
-        </is>
-      </c>
-      <c r="F128" s="4" t="inlineStr"/>
+      <c r="E128" s="5" t="inlineStr">
+        <is>
+          <t>[이레네] 헌재는 사면법을 합헌으로 보지만 대법원은 오르타의 공금 혐의를 제외하고, 오르타는 국경을 걸어 돌아와 스스로 구속된다.</t>
+        </is>
+      </c>
+      <c r="F128" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="129">
-      <c r="A129" s="4" t="inlineStr">
+      <c r="A129" s="5" t="inlineStr">
         <is>
           <t>7부 3화</t>
         </is>
       </c>
-      <c r="B129" s="4" t="inlineStr">
+      <c r="B129" s="5" t="inlineStr">
         <is>
           <t>쿠에스타의 마지막 대화</t>
         </is>
       </c>
-      <c r="C129" s="4" t="inlineStr">
+      <c r="C129" s="5" t="inlineStr">
         <is>
           <t>La Última Conversación con Cuesta</t>
         </is>
       </c>
-      <c r="D129" s="4" t="inlineStr">
+      <c r="D129" s="5" t="inlineStr">
         <is>
           <t>8부 5화</t>
         </is>
       </c>
-      <c r="E129" s="4" t="inlineStr">
-        <is>
-          <t>[이레네] 병실 문밖에서 기다리는 이레네, 마누는 병든 쿠에스타에게 하수구의 남은 뿌리와 엘레나 사건을 마지막으로 묻는다.</t>
-        </is>
-      </c>
-      <c r="F129" s="4" t="inlineStr"/>
+      <c r="E129" s="5" t="inlineStr">
+        <is>
+          <t>[이레네] 병실 문밖에서 듣는 이레네, 마누는 쿠에스타에게 하수구의 남은 뿌리와 엘레나 사건을 마지막으로 묻는다.</t>
+        </is>
+      </c>
+      <c r="F129" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="130">
-      <c r="A130" s="4" t="inlineStr">
+      <c r="A130" s="5" t="inlineStr">
         <is>
           <t>7부 4화</t>
         </is>
       </c>
-      <c r="B130" s="4" t="inlineStr">
+      <c r="B130" s="5" t="inlineStr">
         <is>
           <t>이레네에게 실권 위임</t>
         </is>
       </c>
-      <c r="C130" s="4" t="inlineStr">
+      <c r="C130" s="5" t="inlineStr">
         <is>
           <t>El Poder a Irene</t>
         </is>
       </c>
-      <c r="D130" s="4" t="inlineStr">
+      <c r="D130" s="5" t="inlineStr">
         <is>
           <t>8부 6화</t>
         </is>
       </c>
-      <c r="E130" s="4" t="inlineStr">
-        <is>
-          <t>[이레네] 이베리아 대정전과 재생에너지 탓 공방 속에 마누가 이레네에게 실권을 넘기고, 그녀는 처음 혼자 결정한다.</t>
-        </is>
-      </c>
-      <c r="F130" s="4" t="inlineStr"/>
+      <c r="E130" s="5" t="inlineStr">
+        <is>
+          <t>[이레네] 반도 대정전 속에서 해외의 마누가 이레네를 현장 대리인으로 지명하고, 그녀는 아무도 탓하지 않고 환자를 먼저 복구한다.</t>
+        </is>
+      </c>
+      <c r="F130" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="131">
-      <c r="A131" s="4" t="inlineStr">
+      <c r="A131" s="5" t="inlineStr">
         <is>
           <t>7부 5화</t>
         </is>
       </c>
-      <c r="B131" s="4" t="inlineStr">
+      <c r="B131" s="5" t="inlineStr">
         <is>
           <t>알타 마르카의 빚</t>
         </is>
       </c>
-      <c r="C131" s="4" t="inlineStr">
+      <c r="C131" s="5" t="inlineStr">
         <is>
           <t>Las Deudas de Alta Marca</t>
         </is>
       </c>
-      <c r="D131" s="4" t="inlineStr">
+      <c r="D131" s="5" t="inlineStr">
         <is>
           <t>8부 7화</t>
         </is>
       </c>
-      <c r="E131" s="4" t="inlineStr">
-        <is>
-          <t>[이레네] 메르세데스가 수반이 되어 숨은 부채를 공개하고, 이레네는 비서실장 칸델라와 첫 재정 협상을 한다.</t>
-        </is>
-      </c>
-      <c r="F131" s="4" t="inlineStr"/>
+      <c r="E131" s="5" t="inlineStr">
+        <is>
+          <t>[이레네] 메르세데스가 오르타 시절의 숨은 부채를 공개하고, 이레네는 비서실장 칸델라와 후견 없는 첫 재정 협상을 한다.</t>
+        </is>
+      </c>
+      <c r="F131" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="132">
-      <c r="A132" s="4" t="inlineStr">
+      <c r="A132" s="5" t="inlineStr">
         <is>
           <t>7부 6화</t>
         </is>
       </c>
-      <c r="B132" s="4" t="inlineStr">
+      <c r="B132" s="5" t="inlineStr">
         <is>
           <t>마지막 정치적 결전</t>
         </is>
       </c>
-      <c r="C132" s="4" t="inlineStr">
+      <c r="C132" s="5" t="inlineStr">
         <is>
           <t>El Último Combate</t>
         </is>
       </c>
-      <c r="D132" s="4" t="inlineStr">
+      <c r="D132" s="5" t="inlineStr">
         <is>
           <t>8부 8화</t>
         </is>
       </c>
-      <c r="E132" s="4" t="inlineStr">
-        <is>
-          <t>[이레네] 구세력이 헌재·의회·방송·검찰에서 총공세를 펴고, 시로가 옛 과오를 고백한 뒤 쓰러진다.</t>
-        </is>
-      </c>
-      <c r="F132" s="4" t="inlineStr"/>
+      <c r="E132" s="5" t="inlineStr">
+        <is>
+          <t>[이레네] 구세력이 헌재·의회·방송·검찰에서 총공세를 펴고, 시로가 옛 서명을 스스로 고백한 뒤 쓰러진다.</t>
+        </is>
+      </c>
+      <c r="F132" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="133">
-      <c r="A133" s="4" t="inlineStr">
+      <c r="A133" s="5" t="inlineStr">
         <is>
           <t>7부 7화</t>
         </is>
       </c>
-      <c r="B133" s="4" t="inlineStr">
+      <c r="B133" s="5" t="inlineStr">
         <is>
           <t>두 번이면 충분하다</t>
         </is>
       </c>
-      <c r="C133" s="4" t="inlineStr">
+      <c r="C133" s="5" t="inlineStr">
         <is>
           <t>Dos Veces Bastan</t>
         </is>
       </c>
-      <c r="D133" s="4" t="inlineStr">
+      <c r="D133" s="5" t="inlineStr">
         <is>
           <t>8부 9화 변형</t>
         </is>
       </c>
-      <c r="E133" s="4" t="inlineStr">
-        <is>
-          <t>[이레네] 총리 연임 두 번 제한이 서명되지만, 소급 불가 원칙상 마누 자신은 다시 나설 수 있다.</t>
-        </is>
-      </c>
-      <c r="F133" s="4" t="inlineStr"/>
+      <c r="E133" s="5" t="inlineStr">
+        <is>
+          <t>[이레네] 총리 연임 두 번 제한법이 서명되지만 소급 불가라 마누 자신은 다시 나설 수 있고, 결정은 전날 이레네에게 먼저 말하기로 한다.</t>
+        </is>
+      </c>
+      <c r="F133" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="134">
-      <c r="A134" s="4" t="inlineStr">
+      <c r="A134" s="5" t="inlineStr">
         <is>
           <t>7부 8화</t>
         </is>
       </c>
-      <c r="B134" s="4" t="inlineStr">
+      <c r="B134" s="5" t="inlineStr">
         <is>
           <t>이솔리나를 기리며</t>
         </is>
       </c>
-      <c r="C134" s="4" t="inlineStr">
+      <c r="C134" s="5" t="inlineStr">
         <is>
           <t>En Memoria de Isolina</t>
         </is>
       </c>
-      <c r="D134" s="4" t="inlineStr">
+      <c r="D134" s="5" t="inlineStr">
         <is>
           <t>8부 10화</t>
         </is>
       </c>
-      <c r="E134" s="4" t="inlineStr">
-        <is>
-          <t>[이레네] 추모의 밤, 이레네와 마누는 ‘커피를 잊지 말 것’이 에바리스토의 원칙과 같았음을 깨닫는다.</t>
-        </is>
-      </c>
-      <c r="F134" s="4" t="inlineStr"/>
+      <c r="E134" s="5" t="inlineStr">
+        <is>
+          <t>[이레네] 이솔리나 홀 개관의 밤, 소피아가 에바리스토의 카드를 보여 주며 ‘커피를 잊지 말 것’의 뜻이 한 계보였음이 드러난다.</t>
+        </is>
+      </c>
+      <c r="F134" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="135">
-      <c r="A135" s="4" t="inlineStr">
+      <c r="A135" s="5" t="inlineStr">
         <is>
           <t>7부 9화</t>
         </is>
       </c>
-      <c r="B135" s="4" t="inlineStr">
+      <c r="B135" s="5" t="inlineStr">
         <is>
           <t>판결과 달아난 돈</t>
         </is>
       </c>
-      <c r="C135" s="4" t="inlineStr">
+      <c r="C135" s="5" t="inlineStr">
         <is>
           <t>La Sentencia y el Dinero Huido</t>
         </is>
       </c>
-      <c r="D135" s="4" t="inlineStr">
+      <c r="D135" s="5" t="inlineStr">
         <is>
           <t>8부 11화·12화 통합</t>
         </is>
       </c>
-      <c r="E135" s="4" t="inlineStr">
-        <is>
-          <t>[이레네] 솔리스가 유죄를 받은 주에, 이솔리나를 죽인 테러 자금이 가리킨 보가라는 해외로 빠져나간다.</t>
-        </is>
-      </c>
-      <c r="F135" s="4" t="inlineStr"/>
+      <c r="E135" s="5" t="inlineStr">
+        <is>
+          <t>[이레네] 솔리스가 징역 16년을 받는 날, 테러 자금이 가리킨 보가라가 전날 밤 해외로 빠져나가고 정부는 수사를 지휘하지 않는다.</t>
+        </is>
+      </c>
+      <c r="F135" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="136">
-      <c r="A136" s="4" t="inlineStr">
+      <c r="A136" s="5" t="inlineStr">
         <is>
           <t>7부 10화</t>
         </is>
       </c>
-      <c r="B136" s="4" t="inlineStr">
+      <c r="B136" s="5" t="inlineStr">
         <is>
           <t>해산</t>
         </is>
       </c>
-      <c r="C136" s="4" t="inlineStr">
+      <c r="C136" s="5" t="inlineStr">
         <is>
           <t>La Disolución</t>
         </is>
       </c>
-      <c r="D136" s="4" t="inlineStr">
+      <c r="D136" s="5" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="E136" s="4" t="inlineStr">
-        <is>
-          <t>[이레네] 전날 밤 이레네에게만 말한 대로, 마누는 의회 해산과 조기 총선을 발표하고 출마하지 않겠다고 한다.</t>
-        </is>
-      </c>
-      <c r="F136" s="4" t="inlineStr"/>
+      <c r="E136" s="5" t="inlineStr">
+        <is>
+          <t>[이레네] 전날 밤 부엌에서 이레네에게만 말한 대로, 마누는 의회 해산과 조기 총선을 발표하고 출마하지 않겠다고 한다.</t>
+        </is>
+      </c>
+      <c r="F136" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="10" t="inlineStr">

--- a/기획안/혼합안_이탈리아_스페인_독일.xlsx
+++ b/기획안/혼합안_이탈리아_스페인_독일.xlsx
@@ -679,7 +679,7 @@
       </c>
       <c r="N5" s="5" t="inlineStr">
         <is>
-          <t>1~7부 70화(1~7부 전체) 대본·학습노트 완료 (2026-10)</t>
+          <t>1~8부 80화 + 에필로그 대본·학습노트 완료 (2026-10)</t>
         </is>
       </c>
       <c r="O5" s="6" t="inlineStr">
@@ -858,7 +858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G147"/>
+  <dimension ref="A1:F147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -891,7 +891,7 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>1~7부 70화(부당 10화 구성의 1~7부 전체) 대본·학습노트 완료 (2026-10)</t>
+          <t>1~8부 80화 + 에필로그 대본·학습노트 완료 — 시리즈 전체 완결 (2026-10)</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>1부, 2부, 3부, 4부, 5부, 6부, 7부</t>
+          <t>1부, 2부, 3부, 4부, 5부, 6부, 7부, 8부, 에필로그</t>
         </is>
       </c>
     </row>
@@ -915,7 +915,7 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>학습 노트 70편(1~7부 각 1~10화, docx), 0_동사_시제_가이드(md·docx)</t>
+          <t>학습 노트 81편(1~8부 각 1~10화 + 에필로그, docx), 0_동사_시제_가이드(md·docx)</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>· 1화: 폭발 일시(2009.10.2 03:42)·사망 3명(안드레스·오스카르·조니)·10월 22일 예심법원 2호의 '작업자 과실' 잠정 종결 확정. 스승의 과거는 1974년 11월 calle del Carmen 노동법률사무소 총격(가상)으로 구체화
+          <t xml:space="preserve">· 1화: 폭발 일시(2009.10.2 03:42)·사망 3명(안드레스·오스카르·조니)·10월 22일 예심법원 2호의 '작업자 과실' 잠정 종결 확정. 스승의 과거는 1974년 11월 calle del Carmen 노동법률사무소 총격(가상)으로 구체화
 · 2화: 세 배 연봉 스카우트의 주체를 1화 회사 측 로펌 «Bermúdez Sáenz Abogados»(솔리스·la Caja 자문)로 묶음. 합의금에서 빠진 한 명 = 파견직 욜란다 레이
 · 3화: 협박 전화는 11월 1일(모든 성인의 날) 새벽 부모 집으로. 고소를 받는 경관 벨트란 추가(제도 안의 양심)
 · 4화: 엘레나의 '정보 교환' → 원칙 약속(«Hoy por ti, mañana por mí»)으로. 양돈장 모회사 Inversiones Lara 2004로 솔리스와 연결
@@ -1029,7 +1029,11 @@
 · 10화(2026-02-02·03): 전날 밤 부엌에서 이레네에게 먼저 말한 뒤, 2-3 하원에서 의회 해산(조기 총선 3-29), 출마 거부, 후계 지명 없음. 메르세데스·필리·아우렐리아의 반응
 · 원안 대비 변경: 원안 7부(권력의 한계 구체화·사면·쿠에스타·정전·부채·결전·서명·추모·판결·해산)를 10화로 유지하되 6부에서 앞당긴 일부 사건(스파이웨어 감사·위기결정위원회)은 6부에서 완결. 소급 불가·해산 시점은 실제 정국의 시간표를 따르지 않고 가상 일정으로 처리. 정전·사면 판결·검찰총장·주거·산불 등은 실제 사건의 뼈대만 취함
 · 인물 추가: 베아트리스 올모(송전망 사장), 마르가리타 오소리오(재판장), 베아트리스 라사(반부패 검사), 알폰소 코르테스(정보국장, 6부 10화), 가브리(감사원 수습, 6부 1화 인물의 성장), 클라라 테하다·시로의 회복
-· [7부 이후 연결 과제] 8부 「내려오는 길」(해산 이후: 당의 충격과 코바루비아스의 '속임수' 공세, 다나 폭우, 배관공 사건, 다니의 눈을 멀게 한 경찰관 재판, 공개 예비경선, 쿠에스타의 죽음과 봉투, 카르멘, 총선의 밤, 인수인계, 보가라 재판의 증인)과 에필로그(마누)</t>
+· [7부 이후 연결 과제] 8부 「내려오는 길」(해산 이후: 당의 충격과 코바루비아스의 '속임수' 공세, 다나 폭우, 배관공 사건, 다니의 눈을 멀게 한 경찰관 재판, 공개 예비경선, 쿠에스타의 죽음과 봉투, 카르멘, 총선의 밤, 인수인계, 보가라 재판의 증인)과 에필로그(마누)
+· [8부 제작 후 변경·확정] 8부 「내려오는 길」 10화(2026-02-04~09-22)와 에필로그(2030-04-17) 완료. 시점은 이레네(보이스오버 LECCIÓN 28~37), 에필로그는 마누. 1화 마누의 불출마 후 당내 충격 / 2화 비야페로사 폭우(2-10) / 3화 조직국장 사건(2-17, 가상 시히 파레데스) / 4화 경찰관 재판(2-19, 가상 라울 파르도) / 5화 공개 예비경선(2-28) / 6화 쿠에스타의 죽음·장례·봉투(3-04~06) / 7화 카르멘의 죽음(3-16) / 8화 총선(3-29, 138 대 133) / 9화 인준·인수인계(4-23) / 10화 보가라 재판의 증인(9-22) / 에필로그 메르세데스 취임(2030-4-17)
+· 모티프 마무리: 카드 «No olvidar el café»의 계보 E.(1986)→I.→M.(2019-4-13)→I.(2026-4-23)→M. A.(2030-4-17), «Primero un café, luego lo demás», «Apuntado», «Las dos cosas», 쿠에스타의 마지막 문장 «Haced con esto lo que yo no hice: contarlo entero.»
+· 원안 대비 변경: 원안 9부 구성을 8부 10화와 에필로그로 압축·통합했다. 마누의 부친(토마스 로블레스) 사건의 세 가지 질문은 판사가 사건 종결 뒤 알리기로 하고, 에필로그에서 서한으로 받는다(내용은 비공개로 둠). 홍수·정전·정치 공작은 실제 사건의 뼈대만 취한 가상 일정과 가상 이름으로 처리했으며, 폭력·감시·정치 공작은 윤리 수준의 서술로 제한했다
+</t>
         </is>
       </c>
     </row>
@@ -4544,10 +4548,14 @@
       </c>
       <c r="E137" s="10" t="inlineStr">
         <is>
-          <t>[이레네] 당은 충격에 빠지고 코바루비아스는 ‘속임수’라 공격하며, 필리는 처음으로 마누에게 소리를 지른다.</t>
-        </is>
-      </c>
-      <c r="F137" s="10" t="inlineStr"/>
+          <t>[이레네] 마누의 불출마 선언 뒤 당이 충격에 빠지고 필리는 처음으로 마누에게 소리를 지르며, 코바루비아스는 ‘속임수’라 공격하고 이레네는 «Es las dos cosas»로 응수한다. 마누는 칼레 델 솜브레레테 상담소로 돌아가겠다고 말한다.</t>
+        </is>
+      </c>
+      <c r="F137" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="10" t="inlineStr">
@@ -4572,10 +4580,14 @@
       </c>
       <c r="E138" s="10" t="inlineStr">
         <is>
-          <t>[이레네] 산불 뒤 다나 폭우가 비야페로사를 덮치고, 선거 관리 내각은 몇 시간 늦은 지방정부 경보의 책임을 따진다.</t>
-        </is>
-      </c>
-      <c r="F138" s="10" t="inlineStr"/>
+          <t>[이레네] 2026-02-10 불탄 시에라 델 로보 아래 비야페로사에 폭우가 덮치는데 경보가 5시간 반 늦었고 사망자는 없었다. 콘수엘로의 40만 유로 요청과 이레네의 경보 기록 열람 요구(30일 법).</t>
+        </is>
+      </c>
+      <c r="F138" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="10" t="inlineStr">
@@ -4600,10 +4612,14 @@
       </c>
       <c r="E139" s="10" t="inlineStr">
         <is>
-          <t>[이레네] 당 ‘배관공’이 반부패 수사관들의 약점을 사 모은 사실이 드러나고, 이레네와 마누는 당사 압수수색을 막지 않는다.</t>
-        </is>
-      </c>
-      <c r="F139" s="10" t="inlineStr"/>
+          <t>[이레네] 2026-02-17 시히 파레데스 조직국장이 수사관들의 사적 정보를 사들인 사건으로 당사가 압수수색을 받고, 이네스 바라도 경찰서장·이바녜스 판사와의 대면에서 당이 책임을 어디까지 지는지가 시험된다(기술적 수법은 다루지 않음).</t>
+        </is>
+      </c>
+      <c r="F139" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="10" t="inlineStr">
@@ -4628,10 +4644,14 @@
       </c>
       <c r="E140" s="10" t="inlineStr">
         <is>
-          <t>[이레네] 다니의 눈을 멀게 한 경찰관의 재판에서, 이레네는 칸델라 남매 곁에서 방청하는 마누를 지켜본다.</t>
-        </is>
-      </c>
-      <c r="F140" s="10" t="inlineStr"/>
+          <t>[이레네] 2026-02-19 아르헨타 법원, 다니의 눈을 멀게 한 경찰관 라울 파르도(38)의 재판. «El ojo no es de nadie. Es mío.» 집행유예 3년·12만 유로·4년 자격정지, 지휘관 명령은 별건 회부. 계단에서 마누가 사과하고 라몬은 «que sea el primer día»라고 한다.</t>
+        </is>
+      </c>
+      <c r="F140" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="10" t="inlineStr">
@@ -4656,10 +4676,14 @@
       </c>
       <c r="E141" s="10" t="inlineStr">
         <is>
-          <t>[이레네] 마누가 누구도 지지하지 않은 공개 예비경선에서 이레네가 이기고, 두 사람은 비로소 동등하게 커피를 마신다.</t>
-        </is>
-      </c>
-      <c r="F141" s="10" t="inlineStr"/>
+          <t>[이레네] 페피의 금빛 단추와 단춧구멍, 쿠엥카의 서명 6,140명, 텔레비전 토론. 공개 예비경선 결과 라디갈레스 31·키로가 15·이레네 54. 이레네가 몽클로아에서 커피를 내린다.</t>
+        </is>
+      </c>
+      <c r="F141" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="10" t="inlineStr">
@@ -4684,10 +4708,14 @@
       </c>
       <c r="E142" s="10" t="inlineStr">
         <is>
-          <t>[이레네] 쿠에스타가 홀로 숨지고, 아무도 오지 않은 장례식에 간 마누는 남겨진 봉투를 검찰에 넘긴다.</t>
-        </is>
-      </c>
-      <c r="F142" s="10" t="inlineStr"/>
+          <t>[이레네] 2026-03-04 새벽 4시 20분 쿠에스타가 홀로 숨지고, 3-06 신부·장례식장 직원·훌리안·마누·이레네가 장례를 치른다. «Si viene, que no lo abra solo.» 봉투를 열지 않고 라사 검사에게 넘긴다. LECCIÓN 33.</t>
+        </is>
+      </c>
+      <c r="F142" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="10" t="inlineStr">
@@ -4712,10 +4740,14 @@
       </c>
       <c r="E143" s="10" t="inlineStr">
         <is>
-          <t>[이레네] 몇 년째 비밀 통화를 해 온 카르멘이 숨지고, 마누는 유세 대신 조문객에게 커피를 낸 뒤 무덤들을 차례로 찾는다.</t>
-        </is>
-      </c>
-      <c r="F143" s="10" t="inlineStr"/>
+          <t>[이레네] 2026-03-16 카르멘 시드(75)가 숨지고, 마누는 유세 대신 조문객에게 커피를 낸다. 서랍 속 수첩에서 2015년부터 매달 «Llamó»만 적힌 비밀 통화가 드러나며, 마누는 에바리스토·로시오·엘레나·알바로의 무덤을 차례로 찾는다.</t>
+        </is>
+      </c>
+      <c r="F143" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="10" t="inlineStr">
@@ -4740,10 +4772,14 @@
       </c>
       <c r="E144" s="10" t="inlineStr">
         <is>
-          <t>[이레네] 이레네의 당이 제1당이 되고 코바루비아스가 패배를 인정한다. 그녀는 메르세데스를 제1부총리로 택한다.</t>
-        </is>
-      </c>
-      <c r="F144" s="10" t="inlineStr"/>
+          <t>[이레네] 2026-03-29 투표소의 마누, 출구조사와 138 대 133의 개표, 코바루비아스의 패배 인정(«Me equivoqué»). 새벽 1시 반 이레네가 메르세데스에게 첫 부총리를 제안하고, «첫날 지킬 수 있는 법 하나»를 조건으로 수락받는다.</t>
+        </is>
+      </c>
+      <c r="F144" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="10" t="inlineStr">
@@ -4758,7 +4794,7 @@
       </c>
       <c r="C145" s="10" t="inlineStr">
         <is>
-          <t>El Relevo</t>
+          <t>El Traspaso</t>
         </is>
       </c>
       <c r="D145" s="10" t="inlineStr">
@@ -4768,10 +4804,14 @@
       </c>
       <c r="E145" s="10" t="inlineStr">
         <is>
-          <t>[이레네] 하원 인준을 받은 날, 이레네는 책상 위 ‘커피를 잊지 말 것’ 카드를 발견하고 걸어 나가는 마누를 창밖으로 본다.</t>
-        </is>
-      </c>
-      <c r="F145" s="10" t="inlineStr"/>
+          <t>[이레네] 2026-04-23 이레네가 찬성 183·반대 133·기권 34로 인준되고, 마누는 필리에게 «Que no la dejes sola»를 당부하며 상자 하나를 들고 몽클로아를 떠난다. 책상 위 카드 «No olvidar el café» 뒷면에 마누가 «I. — 23-IV-2026»을 써 두었다.</t>
+        </is>
+      </c>
+      <c r="F145" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="10" t="inlineStr">
@@ -4786,7 +4826,7 @@
       </c>
       <c r="C146" s="10" t="inlineStr">
         <is>
-          <t>El Testigo</t>
+          <t>Los Testigos</t>
         </is>
       </c>
       <c r="D146" s="10" t="inlineStr">
@@ -4796,10 +4836,14 @@
       </c>
       <c r="E146" s="10" t="inlineStr">
         <is>
-          <t>[이레네] 인도된 보가라의 재판에서 마누와 훌리안이 평범한 증인으로 선서하고, 이레네는 한마디도 하지 않는다.</t>
-        </is>
-      </c>
-      <c r="F146" s="10" t="inlineStr"/>
+          <t>[이레네] 2026-09-22 국가법원, 인도된 보가라의 재판. 마누와 훌리안 페란이 평범한 증인으로 선서하고(«Prometo»), 이레네는 방청석에서 한마디도 하지 않는다. 라사 검사가 쿠에스타의 마지막 문장 «Haced con esto lo que yo no hice: contarlo entero.»만 마누에게 읽어 준다.</t>
+        </is>
+      </c>
+      <c r="F146" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="10" t="inlineStr">
@@ -4824,10 +4868,14 @@
       </c>
       <c r="E147" s="10" t="inlineStr">
         <is>
-          <t>[마누] 4년 뒤 메르세데스가 총리 선서를 하는 아침, 비야페로사 무료 법률상담소의 마누는 의뢰인에게 먼저 커피를 낸다.</t>
-        </is>
-      </c>
-      <c r="F147" s="10" t="inlineStr"/>
+          <t>[마누] 2030-04-17 메르세데스가 총리로 취임하는 아침, 비야페로사 상담소의 마누는 의뢰인에게 «Primero un café»부터 낸다. 법원이 보낸 서한을 읽고 «las dos cosas»를 받아들이며, 카드의 뒷면에 «M. A. — 17-IV-2030»이 추가되어 고리가 이어진다.</t>
+        </is>
+      </c>
+      <c r="F147" s="5" t="inlineStr">
+        <is>
+          <t>✔ 대본·노트</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="26">
